--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CBBDFE-FFD5-BA4D-A943-2ECB3AC12F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F30DA0D-88A3-7D4D-A78D-371D276C3905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="17800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFP" sheetId="1" r:id="rId1"/>
@@ -7541,7 +7541,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I28" s="36">
         <v>1</v>
@@ -7890,7 +7890,7 @@
         <v>39</v>
       </c>
       <c r="H38" s="50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I38" s="50">
         <v>1</v>
@@ -8556,7 +8556,7 @@
         <v>2</v>
       </c>
       <c r="H56" s="39">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I56" s="36">
         <v>1</v>
@@ -8856,7 +8856,7 @@
         <v>2</v>
       </c>
       <c r="H64" s="43">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I64" s="28"/>
       <c r="J64" s="34"/>
@@ -9004,7 +9004,7 @@
         <v>31</v>
       </c>
       <c r="H68" s="28">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I68" s="28">
         <v>1</v>
@@ -9432,7 +9432,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I80" s="61"/>
       <c r="J80" s="63"/>
@@ -10010,7 +10010,7 @@
         <v>46</v>
       </c>
       <c r="H96" s="28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I96" s="28">
         <v>1</v>
@@ -12945,29 +12945,29 @@
       <c r="C180" s="61"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.70069444444444395" right="0.70069444444444395" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F30DA0D-88A3-7D4D-A78D-371D276C3905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF0399A-E6B3-3B4F-A3C9-D4C5DB5D7694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFP" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="668">
   <si>
     <t>Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -2015,15 +2015,6 @@
     <t>Lernmaterial</t>
   </si>
   <si>
-    <t>2, 18, 19, 20, 21, 22</t>
-  </si>
-  <si>
-    <t>202,29,34</t>
-  </si>
-  <si>
-    <t>201, 39</t>
-  </si>
-  <si>
     <t>43, 46, 51, 203</t>
   </si>
   <si>
@@ -2033,9 +2024,6 @@
     <t>Dokumentation</t>
   </si>
   <si>
-    <t>5, 202</t>
-  </si>
-  <si>
     <t xml:space="preserve">Objektorientierung </t>
   </si>
   <si>
@@ -2073,6 +2061,9 @@
   </si>
   <si>
     <t>if/elsel</t>
+  </si>
+  <si>
+    <t>23,29,34</t>
   </si>
 </sst>
 </file>
@@ -2282,7 +2273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -2509,6 +2500,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -6935,7 +6932,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" s="28">
         <v>1</v>
@@ -6976,7 +6973,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="28">
         <v>1</v>
@@ -7048,7 +7045,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" s="28">
         <v>1</v>
@@ -7091,7 +7088,7 @@
         <v>10</v>
       </c>
       <c r="H16" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="28">
         <v>1</v>
@@ -7132,7 +7129,7 @@
         <v>8</v>
       </c>
       <c r="H17" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="28">
         <v>1</v>
@@ -7173,7 +7170,7 @@
         <v>8</v>
       </c>
       <c r="H18" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="28">
         <v>1</v>
@@ -7216,7 +7213,7 @@
         <v>8</v>
       </c>
       <c r="H19" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="28">
         <v>1</v>
@@ -7240,15 +7237,15 @@
     </row>
     <row r="20" spans="1:1024" s="73" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="66">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="B20" s="67">
         <v>8</v>
       </c>
       <c r="C20" s="66"/>
       <c r="D20" s="67"/>
-      <c r="E20" s="67" t="s">
-        <v>651</v>
+      <c r="E20" s="3">
+        <v>2.1800000000000002</v>
       </c>
       <c r="F20" s="68" t="s">
         <v>146</v>
@@ -7256,7 +7253,9 @@
       <c r="G20" s="69">
         <v>2</v>
       </c>
-      <c r="H20" s="66"/>
+      <c r="H20" s="66">
+        <v>3</v>
+      </c>
       <c r="I20" s="66"/>
       <c r="J20" s="70"/>
       <c r="K20" s="70"/>
@@ -7271,9 +7270,11 @@
     </row>
     <row r="21" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="36">
-        <v>18</v>
-      </c>
-      <c r="B21" s="47"/>
+        <v>201</v>
+      </c>
+      <c r="B21" s="47">
+        <v>8</v>
+      </c>
       <c r="C21" s="36">
         <v>17</v>
       </c>
@@ -7285,10 +7286,10 @@
         <v>102</v>
       </c>
       <c r="G21" s="36">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="H21" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" s="36">
         <v>1</v>
@@ -7313,7 +7314,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="3">
-        <v>18</v>
+        <v>201</v>
       </c>
       <c r="C22" s="36">
         <v>18</v>
@@ -7326,7 +7327,7 @@
         <v>103</v>
       </c>
       <c r="G22" s="36">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="H22" s="36">
         <v>3</v>
@@ -7375,7 +7376,7 @@
       <c r="M23" s="40"/>
       <c r="N23" s="40"/>
       <c r="O23" s="89" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>261</v>
@@ -7406,7 +7407,7 @@
       <c r="M24" s="40"/>
       <c r="N24" s="40"/>
       <c r="O24" s="89" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>261</v>
@@ -7431,7 +7432,7 @@
         <v>105</v>
       </c>
       <c r="G25" s="36">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="H25" s="36">
         <v>3</v>
@@ -7644,7 +7645,9 @@
       <c r="F31" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="50"/>
+      <c r="G31" s="50">
+        <v>2</v>
+      </c>
       <c r="H31" s="50">
         <v>2</v>
       </c>
@@ -7664,7 +7667,9 @@
       <c r="AMJ31" s="93"/>
     </row>
     <row r="32" spans="1:1024" s="92" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="50"/>
+      <c r="A32" s="50">
+        <v>210</v>
+      </c>
       <c r="B32" s="51"/>
       <c r="C32" s="50">
         <v>27</v>
@@ -7676,8 +7681,12 @@
       <c r="F32" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
+      <c r="G32" s="50">
+        <v>39</v>
+      </c>
+      <c r="H32" s="50">
+        <v>2</v>
+      </c>
       <c r="I32" s="50">
         <v>2</v>
       </c>
@@ -7913,10 +7922,10 @@
     </row>
     <row r="39" spans="1:1024" s="81" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="74">
-        <v>202</v>
-      </c>
-      <c r="B39" s="75" t="s">
-        <v>653</v>
+        <v>23</v>
+      </c>
+      <c r="B39" s="98">
+        <v>18.39</v>
       </c>
       <c r="C39" s="74"/>
       <c r="D39" s="75"/>
@@ -7941,7 +7950,7 @@
     </row>
     <row r="40" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="28">
-        <v>23</v>
+        <v>202</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="28">
@@ -7955,7 +7964,7 @@
         <v>108</v>
       </c>
       <c r="G40" s="28">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="H40" s="28">
         <v>3</v>
@@ -7993,7 +8002,7 @@
         <v>108</v>
       </c>
       <c r="G41" s="28">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="H41" s="28">
         <v>3</v>
@@ -8097,7 +8106,7 @@
         <v>109</v>
       </c>
       <c r="G44" s="28">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="H44" s="28"/>
       <c r="I44" s="28">
@@ -8136,10 +8145,10 @@
         <v>301</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G45" s="28">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="H45" s="28">
         <v>3</v>
@@ -8183,7 +8192,7 @@
         <v>111</v>
       </c>
       <c r="G46" s="28">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="H46" s="28">
         <v>3</v>
@@ -8291,7 +8300,7 @@
         <v>112</v>
       </c>
       <c r="G49" s="43">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="H49" s="43">
         <v>3</v>
@@ -8363,7 +8372,7 @@
         <v>113</v>
       </c>
       <c r="G51" s="28">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="H51" s="28"/>
       <c r="I51" s="28">
@@ -8387,8 +8396,8 @@
       <c r="A52" s="28">
         <v>27</v>
       </c>
-      <c r="B52" s="21" t="s">
-        <v>657</v>
+      <c r="B52" s="98">
+        <v>5.23</v>
       </c>
       <c r="C52" s="28">
         <v>46</v>
@@ -8401,7 +8410,7 @@
         <v>114</v>
       </c>
       <c r="G52" s="28">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H52" s="28">
         <v>3</v>
@@ -8445,7 +8454,7 @@
         <v>73</v>
       </c>
       <c r="G53" s="28">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="H53" s="28">
         <v>3</v>
@@ -8540,7 +8549,7 @@
         <v>29</v>
       </c>
       <c r="B56" s="3">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="C56" s="36">
         <v>50</v>
@@ -8658,7 +8667,7 @@
         <v>34</v>
       </c>
       <c r="B59" s="51">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="C59" s="50">
         <v>53</v>
@@ -8841,8 +8850,8 @@
       <c r="A64" s="28">
         <v>31</v>
       </c>
-      <c r="B64" s="21" t="s">
-        <v>652</v>
+      <c r="B64" s="99" t="s">
+        <v>667</v>
       </c>
       <c r="C64" s="28"/>
       <c r="D64" s="21"/>
@@ -9536,7 +9545,9 @@
       <c r="G83" s="28">
         <v>43</v>
       </c>
-      <c r="H83" s="28"/>
+      <c r="H83" s="28">
+        <v>3</v>
+      </c>
       <c r="I83" s="28">
         <v>1</v>
       </c>
@@ -9561,7 +9572,7 @@
       </c>
       <c r="D84" s="21"/>
       <c r="E84" s="21" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F84" s="21" t="s">
         <v>92</v>
@@ -9570,9 +9581,11 @@
         <v>46</v>
       </c>
       <c r="H84" s="28">
-        <v>3</v>
-      </c>
-      <c r="I84" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="I84" s="28">
+        <v>1</v>
+      </c>
       <c r="J84" s="34" t="s">
         <v>393</v>
       </c>
@@ -9777,7 +9790,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="28">
-        <v>203</v>
+        <v>52</v>
       </c>
       <c r="B90" s="21"/>
       <c r="C90" s="28">
@@ -9785,7 +9798,7 @@
       </c>
       <c r="D90" s="21"/>
       <c r="E90" s="21" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F90" s="33" t="s">
         <v>93</v>
@@ -9814,10 +9827,10 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="28">
+        <v>203</v>
+      </c>
+      <c r="B91" s="21">
         <v>52</v>
-      </c>
-      <c r="B91" s="21">
-        <v>203</v>
       </c>
       <c r="C91" s="28">
         <v>81</v>
@@ -9994,7 +10007,7 @@
         <v>55</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C96" s="28">
         <v>86</v>
@@ -10962,7 +10975,7 @@
         <v>72</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C123" s="36"/>
       <c r="D123" s="3"/>
@@ -10970,7 +10983,7 @@
         <v>490</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G123" s="36">
         <v>43</v>
@@ -11002,7 +11015,7 @@
         <v>492</v>
       </c>
       <c r="F124" s="41" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="G124" s="36">
         <v>72</v>
@@ -11036,7 +11049,7 @@
         <v>492</v>
       </c>
       <c r="F125" s="41" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="G125" s="36"/>
       <c r="H125" s="36"/>
@@ -11068,7 +11081,7 @@
         <v>495</v>
       </c>
       <c r="F126" s="41" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="G126" s="36">
         <v>72</v>
@@ -11102,7 +11115,7 @@
         <v>495</v>
       </c>
       <c r="F127" s="41" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="G127" s="36"/>
       <c r="H127" s="36"/>
@@ -11130,7 +11143,7 @@
         <v>495</v>
       </c>
       <c r="F128" s="41" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="G128" s="36"/>
       <c r="H128" s="36"/>
@@ -11164,7 +11177,7 @@
         <v>498</v>
       </c>
       <c r="F129" s="41" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="G129" s="36">
         <v>72</v>
@@ -11199,7 +11212,7 @@
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="3" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F130" s="49" t="s">
         <v>501</v>
@@ -11234,7 +11247,7 @@
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F131" s="49" t="s">
         <v>501</v>
@@ -11263,7 +11276,7 @@
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F132" s="49" t="s">
         <v>501</v>
@@ -11289,14 +11302,14 @@
         <v>79</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C133" s="36">
         <v>119</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="3" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="F133" s="49" t="s">
         <v>504</v>
@@ -12097,7 +12110,7 @@
       <c r="D155" s="84"/>
       <c r="E155" s="84"/>
       <c r="F155" s="85" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="G155" s="83">
         <v>43</v>
@@ -12117,7 +12130,7 @@
         <v>93</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C156" s="28">
         <v>139</v>
@@ -12656,7 +12669,7 @@
         <v>43</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="G171" s="36">
         <v>208</v>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F30DA0D-88A3-7D4D-A78D-371D276C3905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFB1290-7C41-8440-91A9-6B95DF401538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFB1290-7C41-8440-91A9-6B95DF401538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FF76D7-6411-0B46-9B67-3258444951C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17660" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFP" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="661">
   <si>
     <t>Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -689,9 +689,6 @@
     <t>Python-Variablen sind Namen, die auf Speicherorte verweisen und Daten eines bestimmten Typs enthalten, wobei der Wert einer Variablen im Laufe eines Programms verändert werden kann. Python ist eine dynamisch typisierte Sprache, was bedeutet, dass der Datentyp einer Variablen nicht explizit deklariert werden muss und sich während der Laufzeit ändern kann, wobei Variablennamen sinnvoll gewählt und Groß- und Kleinschreibung beachtet werden sollten.</t>
   </si>
   <si>
-    <t>2,6,7</t>
-  </si>
-  <si>
     <t>6de52e3c-8bf7-4f10-b4bc-11f633d3fd50</t>
   </si>
   <si>
@@ -701,15 +698,9 @@
     <t>In Python sind Anweisungen (Statements) Instruktionen, die vom Interpreter ausgeführt werden, wie zum Beispiel Funktionsaufrufe oder Wertzuweisungen an Variablen. Ausdrücke (Expressions) hingegen sind spezielle Anweisungen, die einen Wert zurückliefern, wie arithmetische Berechnungen, wobei das Gleichheitszeichen in der Programmierung als Zuweisungsoperator dient und sich von der mathematischen Bedeutung unterscheidet.</t>
   </si>
   <si>
-    <t>2,8</t>
-  </si>
-  <si>
     <t>In Python wird die funktionale Programmierung durch den Einsatz von Funktionen und Unveränderlichkeit von Daten unterstützt, um Seiteneffekte zu vermeiden und die Code-Wartbarkeit zu verbessern. Python bietet verschiedene Datentypen wie Listen, Tupel und Dictionary, welche es ermöglichen, auf eine deklarative Weise mit Funktionen höherer Ordnung zu arbeiten. Dazu gehören Lambda-Ausdrücke und eingebaute Funktionen wie map, filter und reduce, die dabei helfen, Daten effizient und einfach zu verarbeiten.</t>
   </si>
   <si>
-    <t>2,8,9</t>
-  </si>
-  <si>
     <t>ad1eb799-2e9e-4279-b396-2788a52a2c28</t>
   </si>
   <si>
@@ -722,15 +713,9 @@
     <t>In Python sind Strings eine Sequenz von Zeichen, die in einfachen, doppelten oder dreifachen Anführungszeichen definiert werden können, wobei letztere auch Zeilenumbrüche und Anführungszeichen im Text erlauben. Strings sind in Python unveränderlich (immutable), unterstützen aber eine Vielzahl von Operationen wie Konkatenation, Wiederholung, Indizierung und eingebaute Methoden wie split, replace und format, um nur einige zu nennen.</t>
   </si>
   <si>
-    <t>2,8,10</t>
-  </si>
-  <si>
     <t>Integer sind ganze Zahlen ohne Dezimalstellen, die in der funktionalen Programmierung als grundlegender Datentyp für Zählvorgänge, Indexierung und mathematische Berechnungen verwendet werden. Sie ermöglichen es, deterministische Funktionen zu schreiben, die mit diskreten Werten arbeiten und somit eine wichtige Rolle in der Struktur und Logik von Algorithmen spielen.</t>
   </si>
   <si>
-    <t>2,8,10,11</t>
-  </si>
-  <si>
     <t>e6e07da5-6eb5-4e34-a7b0-944cbdb4d484</t>
   </si>
   <si>
@@ -740,9 +725,6 @@
     <t>In Python gibt es drei Haupttypen von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen verwendet werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) für spezielle mathematische Anwendungen gedacht.</t>
   </si>
   <si>
-    <t>2,8,10,12</t>
-  </si>
-  <si>
     <t>0da90d38-8a08-4714-bfdd-a99c86f1e982</t>
   </si>
   <si>
@@ -752,9 +734,6 @@
     <t>In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) für spezielle mathematische Anwendungen vorgesehen.</t>
   </si>
   <si>
-    <t>2,8,10,13</t>
-  </si>
-  <si>
     <t>Complex</t>
   </si>
   <si>
@@ -773,9 +752,6 @@
     <t>11,12,13</t>
   </si>
   <si>
-    <t>2,8,10,14</t>
-  </si>
-  <si>
     <t>03efcfad-eda1-4b7c-9ccf-d75f50fa3e5e</t>
   </si>
   <si>
@@ -785,9 +761,6 @@
     <t>Python bietet verschiedene Operatoren für mathematische Operationen, wie die Standardaddition, -subtraktion, -multiplikation und -division, sowie spezielle Operatoren für ganzzahlige Division (//), Modulus (%) und Exponentiation (**). Bei der Division von Ganzzahlen wird automatisch ein Fließkommawert zurückgegeben, während die ganzzahlige Division immer abrundet; zudem können alle Operatoren in Verbindung mit dem Zuweisungsoperator (z.B. +=, *=) für verkürzte Operationen verwendet werden.</t>
   </si>
   <si>
-    <t>2,8,16</t>
-  </si>
-  <si>
     <t>34e378fc-083d-4cf2-be91-49fd8832b619</t>
   </si>
   <si>
@@ -797,9 +770,6 @@
     <t>In Python repräsentieren Booleans die Wahrheitswerte True und False, während None ein spezieller Datentyp ist, der zur Initialisierung von Variablen verwendet wird und nur den Wert None annehmen kann. Diese Datentypen sind essentiell für Vergleichsoperationen und Kontrollstrukturen, wobei None oft genutzt wird, um den Zustand "kein Wert" oder "nicht initialisiert" darzustellen.</t>
   </si>
   <si>
-    <t>2,8,17</t>
-  </si>
-  <si>
     <t>489bad95-fd32-46e7-952b-268c283cfe4a</t>
   </si>
   <si>
@@ -812,9 +782,6 @@
     <t>9, 10,16,17</t>
   </si>
   <si>
-    <t>2,8,10,11,12,13,15</t>
-  </si>
-  <si>
     <t>fb6ac78c-acf4-42f1-8b65-ab55d1522566</t>
   </si>
   <si>
@@ -833,9 +800,6 @@
     <t>Python Kontrollstrukturen umfassen If-Statements, die mit Vergleichsoperatoren wie gleich (==), nicht gleich (!=), größer (&gt;), kleiner (&lt;), größer gleich (&gt;=) und kleiner gleich (&lt;=) arbeiten, sowie logische Operatoren wie and, or und not, um boolesche Ausdrücke zu verknüpfen. Wichtig ist dabei die korrekte Einrückung, da sie die Programmlogik bestimmt, und Schleifen wie die while-Schleife, die zur Wiederholung von Code-Blöcken verwendet wird.</t>
   </si>
   <si>
-    <t>2,18,19</t>
-  </si>
-  <si>
     <t>7746f92a-3fc5-4566-8a04-6bab9bf3c34e</t>
   </si>
   <si>
@@ -848,15 +812,9 @@
     <t>In Python ermöglichen if-else-Kontrollstrukturen die Ausführung von Codeblöcken basierend auf Bedingungen, die zu wahren (True) oder falschen (False) Werten evaluiert werden. Ein if-Statement führt den nachfolgenden Codeblock aus, wenn die Bedingung wahr ist, während ein else-Statement den Codeblock ausführt, wenn alle vorherigen Bedingungen falsch sind; elif-Statements bieten zusätzliche Bedingungsüberprüfungen.</t>
   </si>
   <si>
-    <t>2,18,20</t>
-  </si>
-  <si>
     <t>Schleifen sind Strukturen in der Programmierung, die es ermöglichen, einen Codeblock wiederholt auszuführen, solange eine bestimmte Bedingung erfüllt ist oder über eine Sammlung von Elementen zu iterieren. In Python werden häufig `for`- und `while`-Schleifen verwendet, um iterative Aufgaben effizient zu bewältigen, wie das Durchlaufen von Listen oder das wiederholte Ausführen von Berechnungen bis eine Bedingung nicht mehr zutrifft.</t>
   </si>
   <si>
-    <t>2,18,20,21</t>
-  </si>
-  <si>
     <t>while</t>
   </si>
   <si>
@@ -872,9 +830,6 @@
     <t>In dem Code-Beispiel zur Python-Kontrollstruktur `while` wird eine Schleife verwendet, um ein Kartenspiel zu simulieren, bei dem Karten gezogen werden, bis keine mehr übrig sind. Die `while`-Schleife prüft dabei kontinuierlich, ob die Liste der Preiskarten noch Elemente enthält, und entfernt mit der `pop`-Methode jeweils das letzte Element, bis die Liste leer ist und die Schleife beendet wird.</t>
   </si>
   <si>
-    <t>2,18,20,22</t>
-  </si>
-  <si>
     <t>for</t>
   </si>
   <si>
@@ -893,15 +848,9 @@
     <t>In Python ermöglichen for-Schleifen das Durchlaufen von iterierbaren Objekten wie Listen, indem man eine Variable über die Elemente iterieren lässt, beispielsweise mit `for element in my_list`. Die `range`-Funktion wird oft in for-Schleifen verwendet, um über eine Sequenz von Zahlen zu iterieren, wobei man Start-, Stopp- und Schrittweite angeben kann, um beispielsweise mit `for i in range(1, 10, 3)` die Zahlen 1, 4 und 7 zu durchlaufen.</t>
   </si>
   <si>
-    <t>2,39</t>
-  </si>
-  <si>
     <t>Datenstrukturen sind grundlegende Konzepte in der Informatik, die es ermöglichen, Daten effizient zu speichern, zu organisieren und darauf zuzugreifen. In der funktionalen Programmierung werden sie genutzt, um Daten unveränderlich zu halten und Operationen darauf durch Funktionen auszudrücken, die keine Seiteneffekte haben und oft rekursiv sind.</t>
   </si>
   <si>
-    <t>2,39,40</t>
-  </si>
-  <si>
     <t>c81c925d-9104-4807-9e11-2e5e5d1f6cc4</t>
   </si>
   <si>
@@ -914,27 +863,18 @@
     <t>Listen in der funktionalen Programmierung mit Python sind grundlegende Datenstrukturen, die es ermöglichen, eine Sammlung von Elementen zu speichern und zu manipulieren. Sie unterstützen Operationen wie das Filtern, Abbilden und Falten von Daten, wodurch sie für die Anwendung funktionaler Konzepte wie Unveränderlichkeit und Funktionen höherer Ordnung zentral sind.</t>
   </si>
   <si>
-    <t>2,39,41</t>
-  </si>
-  <si>
     <t>dc3a876f-2fba-4494-bf16-aa80914fdec2</t>
   </si>
   <si>
     <t>Tupel in Python sind unveränderliche (immutable) Datenstrukturen, die es ermöglichen, eine geordnete Sammlung von Elementen unterschiedlicher Datentypen zu speichern. Sie werden häufig in funktionalen Programmieransätzen verwendet, um Daten zu gruppieren und Funktionen zu ermöglichen, mehrere Werte sicher und ohne Seiteneffekte zu verarbeiten.</t>
   </si>
   <si>
-    <t>2,39,42</t>
-  </si>
-  <si>
     <t>24bec9c7-6e78-4b46-ba4d-a1faa644620d</t>
   </si>
   <si>
     <t>Ein Dictionary in Python ist eine Sammlung von Schlüssel-Wert-Paaren, die es ermöglicht, Werte effizient über Schlüssel zu speichern und abzurufen. Es unterstützt Operationen wie das Einfügen, Ändern und Löschen von Elementen und ist besonders nützlich, um Assoziationen zwischen eindeutigen Schlüsseln und zugehörigen Daten zu verwalten.</t>
   </si>
   <si>
-    <t>2,23</t>
-  </si>
-  <si>
     <t>19aca104-2bd1-472b-9a5e-74f2dc5a6b1a</t>
   </si>
   <si>
@@ -965,9 +905,6 @@
     <t>In dem Codebeispiel werden Teile eines Kartenspiels in Python-Funktionen ausgelagert, um den Code übersichtlicher und modularer zu gestalten. Die Funktionen `StrategieSpieler1` und `StrategieSpieler2` werden definiert, um die Strategie der Spieler zu kapseln, wobei die Funktionen Eingabeparameter wie den Wert der Preiskarte und die verbleibenden Karten des Spielers erhalten und die ausgewählte Karte zurückgeben.</t>
   </si>
   <si>
-    <t>2,23,24</t>
-  </si>
-  <si>
     <t>916876d2-d005-485d-afd9-14a36d45a5b2</t>
   </si>
   <si>
@@ -980,9 +917,6 @@
     <t>Python-Funktionen können mit Docstrings dokumentiert werden, die mit drei Anführungszeichen beginnen und eine systematische Beschreibung der Funktion, ihrer Parameter und Rückgabewerte enthalten. Docstrings sind besonders hilfreich in größeren Projekten, da sie es ermöglichen, die Funktionsweise von Code auch Monate später noch zu verstehen, und können mit der `help()`-Funktion abgerufen werden, um Nutzern und Entwicklern die Verwendung der Funktionen zu erleichtern.</t>
   </si>
   <si>
-    <t>2,23,25</t>
-  </si>
-  <si>
     <t>0586d1bc-a676-4adb-8cdb-59a27c06b232</t>
   </si>
   <si>
@@ -995,9 +929,6 @@
     <t>Python-Funktionen können sowohl Positional Arguments als auch Keyword Arguments akzeptieren, wobei die Reihenfolge bei Positional Arguments wichtig ist und bei Keyword Arguments durch die explizite Benennung irrelevant wird. Zusätzlich können Funktionen in Python mit `*args` und `**kwargs` eine variable Anzahl von Positional bzw. Keyword Arguments empfangen, was die Flexibilität bei der Übergabe von Argumenten erhöht.</t>
   </si>
   <si>
-    <t>2,23,26</t>
-  </si>
-  <si>
     <t>ef0c4946-e519-41fd-b9ea-9169c1ee0f67</t>
   </si>
   <si>
@@ -1016,9 +947,6 @@
     <t>Funktionen als Variablen am Beispiel Goofspiel</t>
   </si>
   <si>
-    <t>2,23,27</t>
-  </si>
-  <si>
     <t>5a8cf9ca-0145-4c82-901a-fcdbb26ac401</t>
   </si>
   <si>
@@ -1028,9 +956,6 @@
     <t>Python-Funktionen können in ausgelagerten Dateien organisiert und mit dem `import`-Befehl in andere Skripte eingebunden werden, wobei der Namespace des importierten Moduls verwendet wird. Um Funktionen direkt im Namensraum verfügbar zu machen, kann `from Modul import Funktionsname` verwendet werden, während `import Modul as Alias` es ermöglicht, Funktionen mit einem benutzerdefinierten Namespace anzusprechen.</t>
   </si>
   <si>
-    <t>2,23,28</t>
-  </si>
-  <si>
     <t>3817eef2-f212-41b2-9b22-70f0a934e291</t>
   </si>
   <si>
@@ -1040,9 +965,6 @@
     <t>Python-Funktionen höherer Ordnung sind Funktionen, die andere Funktionen als Argumente entgegennehmen und auf Elemente einer Liste anwenden. Sie ermöglichen es, Operationen wie das Quadrieren von Zahlen oder das Hinzufügen von Absätzen zu Strings in Listen effizient durchzuführen, indem man eine allgemeine Funktion wie "auf jedes Element" definiert und diese dann mit spezifischen Funktionen für unterschiedliche Aufgaben verwendet.</t>
   </si>
   <si>
-    <t>2,29</t>
-  </si>
-  <si>
     <t>7185bc4d-a06f-4326-9d37-932f2920ae4f</t>
   </si>
   <si>
@@ -1052,9 +974,6 @@
     <t>In Python können Variablen entweder global oder lokal sein, wobei globale Variablen überall im Code verwendet werden können und lokale Variablen nur innerhalb der Funktion, in der sie definiert wurden. Änderungen an globalen, veränderbaren (mutable) Variablen innerhalb einer Funktion sind auch außerhalb sichtbar, während Änderungen an lokalen Variablen nach dem Funktionsaufruf nicht bestehen bleiben.</t>
   </si>
   <si>
-    <t>2,29,30</t>
-  </si>
-  <si>
     <t>38bcbb98-a103-488d-b627-e5808a8e6780</t>
   </si>
   <si>
@@ -1148,9 +1067,6 @@
     <t>Currying ist eine Technik in der funktionalen Programmierung, bei der eine Funktion, die mehrere Argumente erwartet, in eine Sequenz von Funktionen umgewandelt wird, die jeweils genau ein Argument nehmen. Auf diese Weise kann eine Funktion mit mehreren Parametern schrittweise angewendet werden, indem sie für jedes Argument eine neue Funktion zurückgibt, bis alle Argumente verarbeitet sind.</t>
   </si>
   <si>
-    <t>2,35</t>
-  </si>
-  <si>
     <t>Python bietet eine Vielzahl von Tools, die die funktionale Programmierung unterstützen, wie zum Beispiel Lambda-Funktionen, die map(), filter() und reduce() Funktionen sowie umfassende Module wie functools und itertools, die fortgeschrittene funktionale Konzepte ermöglichen. Diese Tools erleichtern es, in Python sauberen, modularen und effizienten Code zu schreiben, der die Prinzipien der funktionalen Programmierung wie Unveränderlichkeit und Funktionen höherer Ordnung nutzt.</t>
   </si>
   <si>
@@ -1238,54 +1154,36 @@
     <t>Syntaktische Grundelemente sind die Bausteine einer Programmiersprache, die festlegen, wie Befehle und Anweisungen strukturiert sein müssen, um vom Compiler verstanden und ausgeführt zu werden. In der objektorientierten Programmierung mit Java beinhalten diese Elemente unter anderem Klassen, Methoden, Variablen, Datentypen und Kontrollstrukturen, die zusammen das Gerüst für die Erstellung von Objekten und die Definition ihres Verhaltens bilden.</t>
   </si>
   <si>
-    <t>43,46</t>
-  </si>
-  <si>
     <t>ceee4725-8691-42ae-be01-c63164ede826</t>
   </si>
   <si>
     <t>Datentypen in der Programmierung definieren die Art der Werte, die eine Variable speichern kann, und legen fest, welche Operationen mit diesen Werten durchgeführt werden können. In Java gibt es primitive Datentypen wie int, char und float für grundlegende Werte sowie Referenzdatentypen für Objekte und Arrays, die auf komplexe Datenstrukturen verweisen.</t>
   </si>
   <si>
-    <t>43,46,47</t>
-  </si>
-  <si>
     <t>b44cb78c-a8ff-4a2d-b8fa-5c0d88629667</t>
   </si>
   <si>
     <t>Integer in der Programmierung repräsentieren ganze Zahlen und sind ein fundamentaler Datentyp, der in vielen Programmiersprachen, einschließlich Java, verwendet wird. In Java ist `Integer` auch eine Klasse, die Methoden zur Manipulation von ganzen Zahlen bereitstellt und es ermöglicht, ganze Zahlen als Objekte zu behandeln, was für die objektorientierte Programmierung wichtig ist.</t>
   </si>
   <si>
-    <t>43,46,48</t>
-  </si>
-  <si>
     <t>5f03b842-f8c2-4f63-8bb9-83142d6f98b3</t>
   </si>
   <si>
     <t>Ein Float in der Programmierung bezeichnet einen Datentyp, der eine Gleitkommazahl repräsentiert und wird verwendet, um numerische Werte mit Dezimalstellen zu speichern und zu verarbeiten. In Java ist `float` ein primitiver Datentyp, der 32 Bit Speicherplatz belegt und eine geringere Präzision als der 64 Bit `double` Datentyp bietet, was bei der Entwicklung von Anwendungen, die hohe numerische Genauigkeit erfordern, berücksichtigt werden muss.</t>
   </si>
   <si>
-    <t>43,46,49</t>
-  </si>
-  <si>
     <t>5b9ff9c4-8f45-4ce2-ae79-43fee72e6ecb</t>
   </si>
   <si>
     <t>Der Datentyp `char` in Java wird verwendet, um einzelne Zeichen zu speichern, die durch 16-Bit Unicode-Zeichen repräsentiert werden, was es ermöglicht, nahezu jedes Zeichen aus jedem Sprachalphabet darzustellen. Ein `char`-Wert kann innerhalb eines Programms für die Verarbeitung von Textdaten, wie das Lesen von Eingaben oder das Darstellen von Zeichenketten, genutzt werden.</t>
   </si>
   <si>
-    <t>43,46,50</t>
-  </si>
-  <si>
     <t>ac5c805f-3619-4e90-99b5-3377c6d7458c</t>
   </si>
   <si>
     <t>Boolesche Werte, repräsentiert durch den Datentyp `boolean` in Java, sind grundlegende Elemente der Programmierung, die nur zwei mögliche Zustände annehmen können: `true` oder `false`. Sie spielen eine zentrale Rolle in der Steuerung des Programmflusses durch bedingte Anweisungen wie `if`-`else` und Schleifen wie `while` und `for`, indem sie als Bedingungen verwendet werden, die bestimmen, ob bestimmte Blöcke von Code ausgeführt werden sollen.</t>
   </si>
   <si>
-    <t>43,46,51</t>
-  </si>
-  <si>
     <t>7f4461ab-864c-4531-8656-4616b739f5fa</t>
   </si>
   <si>
@@ -1295,9 +1193,6 @@
     <t>Ein String in der Programmierung ist eine Sequenz von Zeichen, die als Datentyp in vielen Programmiersprachen, einschließlich Java, verwendet wird, um Text zu repräsentieren. In Java ist String eine Klasse, die Methoden zur Manipulation von Text, wie das Suchen von Zeichen, das Vergleichen von Strings oder das Ändern von Textinhalten, bereitstellt und aufgrund ihrer Unveränderlichkeit besondere Überlegungen im Hinblick auf Speichereffizienz und Performance erfordert.</t>
   </si>
   <si>
-    <t>43,46,51,52</t>
-  </si>
-  <si>
     <t>Operationen auf Strings</t>
   </si>
   <si>
@@ -1307,18 +1202,12 @@
     <t>Operationen auf Strings in der Programmierung ermöglichen es, Textdaten zu manipulieren, indem Funktionen wie das Verketten, Teilen, Suchen und Ersetzen von Teilstrings sowie das Umwandeln von Groß- und Kleinschreibung angewendet werden. In Java werden diese Operationen durch Methoden der Klasse `String` bereitgestellt, die unveränderliche Objekte repräsentiert, wobei jede Änderung an einem String ein neues Objekt erzeugt.</t>
   </si>
   <si>
-    <t>43,46,51,53</t>
-  </si>
-  <si>
     <t>2960e92b-b82d-443a-8b32-ed87447c76e1</t>
   </si>
   <si>
     <t>Es werden grundlegende Konzepte der objektorientierten Programmierung wie Klassen, Objekte, Vererbung, Polymorphismus und Kapselung vermittelt. Methoden in Java sind dabei essenzielle Bausteine, die Verhalten und Funktionalitäten von Objekten definieren und es ermöglichen, wiederverwendbaren und modularen Code zu schreiben.</t>
   </si>
   <si>
-    <t>43,46,54</t>
-  </si>
-  <si>
     <t>f16f3f43-404e-44cb-b813-9de902878f39</t>
   </si>
   <si>
@@ -1328,9 +1217,6 @@
     <t>In Java müssen Variablen einen spezifischen Typ haben, der ihre Verwendung und die Art der Werte, die sie speichern können, bestimmt. Fehler bei der Zuweisung von Typen oder der Verwendung von Konstanten können zu Fehlermeldungen oder unerwünschtem Verhalten der Anwendung führen.</t>
   </si>
   <si>
-    <t>43,46,55</t>
-  </si>
-  <si>
     <t>acb1bed9-2c68-4456-b748-2c635f506b32</t>
   </si>
   <si>
@@ -1352,9 +1238,6 @@
     <t>In Java werden Variablen mit einem spezifischen Namen und Typ deklariert, wobei das Schlüsselwort `final` eine Variable als unveränderliche Konstante kennzeichnet. Variablen haben einen definierten Gültigkeitsbereich, der durch Codeblöcke mit geschweiften Klammern festgelegt wird, und innerhalb desselben Gültigkeitsbereichs darf ein Variablenname nicht mehrfach verwendet werden.</t>
   </si>
   <si>
-    <t>43,57</t>
-  </si>
-  <si>
     <t>Anweisungen in der objekorientierten Programmierung sind die Bausteine, die es ermöglichen, Aktionen auszuführen, Zustände zu verändern und die Kontrollflusssteuerung innerhalb von Methoden zu definieren. In Java werden diese Anweisungen durch Sprachelemente wie Schleifen (for, while), Verzweigungen (if, switch), Zuweisungen und Methodenaufrufe repräsentiert, um komplexe Logik innerhalb von Objekten zu implementieren.</t>
   </si>
   <si>
@@ -1412,9 +1295,6 @@
     <t>Programmier-Konventionen sind Richtlinien zur Gestaltung des Quellcodes, die dazu beitragen, die Lesbarkeit, Wartbarkeit und Konsistenz in Softwareprojekten zu verbessern. Sie umfassen Namenskonventionen, Formatierungsregeln und Best Practices für die Strukturierung von Code, wie die Verwendung von Einrückungen und Kommentaren, und sind besonders wichtig in der objekorientierten Programmierung, um die Komplexität von Klassen, Methoden und Objekten zu managen.</t>
   </si>
   <si>
-    <t>43,62</t>
-  </si>
-  <si>
     <t>Kontrollstrukturen sind entscheidend in der Programmierung, da sie den Fluss der Ausführung steuern, indem sie bedingte Anweisungen (if-else), Schleifen (for, while, do-while) und Sprunganweisungen (break, continue) bereitstellen. Diese Strukturen ermöglichen es Entwicklern, komplexe Logik zu implementieren, indem sie bestimmen, wann und wie oft bestimmte Codeblöcke ausgeführt werden.</t>
   </si>
   <si>
@@ -1493,9 +1373,6 @@
     <t>In dem Beispiel BigX wird gezeigt, wie man mit Java Kontrollstrukturen wie for-Schleifen und if-Anweisungen ein großes "X" in der Konsole darstellen kann. Die Größe des "X" wird durch eine Variable bestimmt, und durch geschachtelte for-Schleifen und Bedingungen wird für jede Zeile und Spalte entschieden, ob ein "X" oder ein Leerzeichen ausgegeben wird, um die Form des "X" zu erzeugen.</t>
   </si>
   <si>
-    <t>43,68</t>
-  </si>
-  <si>
     <t>Datenstrukturen sind Sammlungen von Datenwerten, die Beziehungen untereinander aufweisen und ermöglichen es, Daten effizient zu organisieren, zu verarbeiten und zu speichern. Zu den grundlegenden Datenstrukturen gehören Arrays, Listen, Stacks, Queues, Bäume und Graphen, die jeweils unterschiedliche Operationen wie Einfügen, Löschen und Suchen von Daten optimieren.</t>
   </si>
   <si>
@@ -1511,9 +1388,6 @@
     <t>43,68,69,70</t>
   </si>
   <si>
-    <t>mehrdimansionales Array</t>
-  </si>
-  <si>
     <t>bb1b43c5-9f89-42e1-a9d1-4e522837aba4</t>
   </si>
   <si>
@@ -1532,9 +1406,6 @@
     <t>Java bietet eine Vielzahl von Klassen und Paketen zur Dateiverarbeitung, die man durch Import-Anweisungen in den eigenen Code einbinden kann. Um Dateien zu lesen, zu schreiben und zu bearbeiten, muss man die entsprechenden Klassen und Methoden kennen und nutzen, wie zum Beispiel die File-Klasse für Dateioperationen und verschiedene Methoden für das Öffnen, Schließen, Lesen und Schreiben von Dateien, wobei oft ein Puffer verwendet wird, um die Effizienz zu steigern.</t>
   </si>
   <si>
-    <t>43,72</t>
-  </si>
-  <si>
     <t>Objekte in der objektorientierten Programmierung sind Instanzen von Klassen, die sowohl Daten in Form von Attributen als auch Verhalten durch Methoden kapseln. Sie ermöglichen die Modellierung realer oder abstrakter Konzepte durch Wiederverwendung und Erweiterung von Code, was zu einer strukturierten und wartbaren Softwarearchitektur führt.</t>
   </si>
   <si>
@@ -1646,9 +1517,6 @@
     <t>Die Unified Modeling Language (UML) ist eine standardisierte Modellierungssprache, die eine visuelle Darstellung von Software-Systemen ermöglicht, um Strukturen und Verhaltensweisen objektorientierter Programme zu veranschaulichen. Sie umfasst verschiedene Diagrammtypen wie Klassendiagramme, Sequenzdiagramme und Zustandsdiagramme, die Entwicklern helfen, Entwurfsmuster zu definieren und die Kommunikation innerhalb des Entwicklungsteams zu verbessern.</t>
   </si>
   <si>
-    <t>43,85</t>
-  </si>
-  <si>
     <t>67eea819-ab11-42ab-8c06-3bb5ad6aab13</t>
   </si>
   <si>
@@ -1664,9 +1532,6 @@
     <t>Die Unified Modeling Language (UML) ist eine standardisierte Modellierungssprache, die verwendet wird, um die Struktur und das Design von Software-Systemen visuell darzustellen. In einem UML-Beispiel könnten Diagramme wie Klassendiagramme, Sequenzdiagramme und Zustandsdiagramme genutzt werden, um die Beziehungen zwischen Objekten, deren Verhalten und Lebenszyklen in einem objektorientierten Programm zu veranschaulichen.</t>
   </si>
   <si>
-    <t>43,85,86</t>
-  </si>
-  <si>
     <t>8f589647-2d48-4438-b5cf-9d4988ba00f0</t>
   </si>
   <si>
@@ -1676,9 +1541,6 @@
     <t>Java UML Klassen dienen als Blaupausen für Objekte und definieren deren Struktur durch Attribute und Methoden. Während Attribute die Eigenschaften einer Klasse festlegen und Initialwerte haben können, ermöglichen Methoden die Manipulation dieser Eigenschaften und das Ausführen von Operationen; Klassen können in UML-Diagrammen unterschiedlich dargestellt werden, je nachdem ob sie Attribute, Methoden oder beides enthalten.</t>
   </si>
   <si>
-    <t>43,85,87</t>
-  </si>
-  <si>
     <t>7af88cb2-bab7-474c-a721-90b29cc868fa</t>
   </si>
   <si>
@@ -1688,9 +1550,6 @@
     <t>In UML (Unified Modeling Language) können Objekte als Instanzen von Klassen dargestellt werden, wobei Objekte klein und Klassen groß geschrieben werden, getrennt durch einen Doppelpunkt. Objekte werden mit ihren Attributen und Werten gezeigt, und Beziehungen zwischen Objekten werden durch Linien repräsentiert, wobei die Identität und Gleichheit von Objekten im Speicher durch ihre Darstellung unterschieden werden kann.</t>
   </si>
   <si>
-    <t>43,85,88</t>
-  </si>
-  <si>
     <t>6156a4db-89f9-4f8f-b510-37e12793acec</t>
   </si>
   <si>
@@ -1700,9 +1559,6 @@
     <t>Java UML Attribute repräsentieren die Eigenschaften einer Klasse und können mit einer Multiplizität versehen werden, die angibt, wie viele Instanzen eines Attributs existieren dürfen. Diese Multiplizität wird in eckigen Klammern dargestellt, wobei die Untergrenze und Obergrenze durch zwei Punkte getrennt sind, und ein Stern (*) steht für eine unbestimmte Anzahl von Instanzen.</t>
   </si>
   <si>
-    <t>43,85,89</t>
-  </si>
-  <si>
     <t>9ce7ca44-357a-4395-9c38-157fb9b2afb2</t>
   </si>
   <si>
@@ -1712,9 +1568,6 @@
     <t>In UML werden Operationen (Methoden) einer Klasse durch runde Klammern dargestellt, um sie von Attributen zu unterscheiden, die keine Klammern haben. Die Rückgabetypen und Parameter der Operationen werden in UML spezifiziert, wobei Parameter mit "In" für Eingabeparameter gekennzeichnet werden können und der Typ mit einem Doppelpunkt vom Namen getrennt wird, wobei UML im Gegensatz zu Java nicht sofort Typfehler aufzeigt.</t>
   </si>
   <si>
-    <t>43,85,90</t>
-  </si>
-  <si>
     <t>0e0fd849-4f1a-4485-9cdf-f79c487d50a9</t>
   </si>
   <si>
@@ -1724,9 +1577,6 @@
     <t>Java UML Assoziationen beschreiben die Beziehungen zwischen verschiedenen Klassen in einem Klassendiagramm, wobei Assoziationen die Verbindungen zwischen Objekten darstellen und durch Linien repräsentiert werden. Diese Assoziationen können verschiedene Multiplizitäten aufweisen, die angeben, wie viele Instanzen einer Klasse mit Instanzen einer anderen Klasse in Beziehung stehen können, und können auch Rollennamen enthalten, die die Art der Beziehung näher spezifizieren.</t>
   </si>
   <si>
-    <t>43,85,90,91</t>
-  </si>
-  <si>
     <t>Navigierbarkeit</t>
   </si>
   <si>
@@ -1739,9 +1589,6 @@
     <t>In UML-Diagrammen kann die Navigierbarkeit von Assoziationen zwischen Klassen durch Pfeile dargestellt werden, wobei die Richtung des Pfeils die Richtung der Navigierbarkeit angibt. In Java wird diese Navigierbarkeit durch Referenzvariablen als Attribute in den Klassen implementiert, wodurch Objekte einer Klasse auf assoziierte Objekte einer anderen Klasse zugreifen können.</t>
   </si>
   <si>
-    <t>43,85,92</t>
-  </si>
-  <si>
     <t>98667aa3-81c3-472e-8eda-849c71e4e278</t>
   </si>
   <si>
@@ -1808,9 +1655,6 @@
     <t>In Java UML Vererbung übernimmt eine Unterklasse alle Attribute, Methoden und Anfangswerte der Oberklasse, wobei Unterklassen nie etwas von der geerbten Funktionalität löschen können. Zusätzlich können Unterklassen das Verhalten von Methoden neu definieren, indem sie diese überschreiben, wobei die überschriebenen Methoden die gleiche Signatur wie die der Oberklasse haben müssen.</t>
   </si>
   <si>
-    <t>43,98</t>
-  </si>
-  <si>
     <t>518e1e49-1530-450d-9935-11e1b558532a</t>
   </si>
   <si>
@@ -1820,9 +1664,6 @@
     <t>In Java ermöglicht Polymorphie, dass Methoden und Operatoren mehrere Formen annehmen können, indem sie mehrmals definiert und implementiert werden. Die Vererbungshierarchie und die Möglichkeit, Methoden zu überladen und zu überschreiben, erlauben es, dass Objekte einer Oberklasse als Objekte einer Unterklasse interpretiert werden können, wodurch zur Laufzeit die passende Methode dynamisch gebunden und ausgeführt wird, was als Polymorphismus bezeichnet wird.</t>
   </si>
   <si>
-    <t>43,98,99</t>
-  </si>
-  <si>
     <t>eaaf62a0-6720-469c-91c0-52b9e68bbbe6</t>
   </si>
   <si>
@@ -1847,9 +1688,6 @@
     <t>In Java bezeichnet der Begriff "Exceptions" Ausnahmesituationen, die während der Ausführung eines Programms auftreten können, wenn etwas Unerwartetes geschieht, wie beispielsweise eine Division durch Null. Um solche Ausnahmen zu behandeln, bietet Java die Try-Catch-Blöcke an, in denen der Code, der eine Ausnahme auslösen könnte, in einem Try-Block platziert wird und die Behandlung der Ausnahme im zugehörigen Catch-Block erfolgt, wodurch der Code übersichtlicher und robuster gegenüber Fehlern wird.</t>
   </si>
   <si>
-    <t>43,100,101,102</t>
-  </si>
-  <si>
     <t>f22f543e-2cbc-48aa-a268-549bbcdf8e34</t>
   </si>
   <si>
@@ -1922,18 +1760,12 @@
     <t>Threads in Java sind eigenständige Ausführungspfade, die es ermöglichen, mehrere Operationen gleichzeitig innerhalb eines Programms durchzuführen. Sie werden genutzt, um die Effizienz zu steigern und eine reaktive Benutzeroberfläche zu gewährleisten, indem langwierige Prozesse im Hintergrund ablaufen, ohne die Hauptanwendung zu blockieren.</t>
   </si>
   <si>
-    <t>43,108</t>
-  </si>
-  <si>
     <t>cd49aafd-4a0a-4670-b4d7-83ba456fcfd3</t>
   </si>
   <si>
     <t>Sockets sind Endpunkte für die Kommunikation zwischen zwei Maschinen über ein Netzwerk, wobei in Java die Klassen `Socket` für Client-Anwendungen und `ServerSocket` für Server-Anwendungen verwendet werden, um eine Verbindung herzustellen und Daten auszutauschen. Sie ermöglichen es Programmen, über TCP/IP-Protokolle zu kommunizieren, indem sie Datenströme für das Senden und Empfangen von Informationen bereitstellen.</t>
   </si>
   <si>
-    <t>43,108,109</t>
-  </si>
-  <si>
     <t>fe681e57-e984-4ef6-9bbc-0c6ddc6fc85e</t>
   </si>
   <si>
@@ -2015,27 +1847,9 @@
     <t>Lernmaterial</t>
   </si>
   <si>
-    <t>2, 18, 19, 20, 21, 22</t>
-  </si>
-  <si>
-    <t>202,29,34</t>
-  </si>
-  <si>
-    <t>201, 39</t>
-  </si>
-  <si>
-    <t>43, 46, 51, 203</t>
-  </si>
-  <si>
-    <t>43, 46, 204</t>
-  </si>
-  <si>
     <t>Dokumentation</t>
   </si>
   <si>
-    <t>5, 202</t>
-  </si>
-  <si>
     <t xml:space="preserve">Objektorientierung </t>
   </si>
   <si>
@@ -2066,13 +1880,169 @@
     <t>62, 68</t>
   </si>
   <si>
-    <t>85, 72</t>
-  </si>
-  <si>
-    <t>Fortgeschrittene Java-Features</t>
-  </si>
-  <si>
     <t>if/elsel</t>
+  </si>
+  <si>
+    <t>2,8,210</t>
+  </si>
+  <si>
+    <t>2,9.210</t>
+  </si>
+  <si>
+    <t>2,10,210</t>
+  </si>
+  <si>
+    <t>2,10,11,210</t>
+  </si>
+  <si>
+    <t>2,10,12,210</t>
+  </si>
+  <si>
+    <t>2,10,13,210</t>
+  </si>
+  <si>
+    <t>2,10,14,210</t>
+  </si>
+  <si>
+    <t>2,16,210</t>
+  </si>
+  <si>
+    <t>2,17,210</t>
+  </si>
+  <si>
+    <t>2,10,11,12,13,15,210</t>
+  </si>
+  <si>
+    <t>2,18,201</t>
+  </si>
+  <si>
+    <t>2,19,201</t>
+  </si>
+  <si>
+    <t>2,20,201</t>
+  </si>
+  <si>
+    <t>2,20,21,201</t>
+  </si>
+  <si>
+    <t>2,20,22,201</t>
+  </si>
+  <si>
+    <t>2,39,211</t>
+  </si>
+  <si>
+    <t>2,40,211</t>
+  </si>
+  <si>
+    <t>2,41,211</t>
+  </si>
+  <si>
+    <t>2,42,211</t>
+  </si>
+  <si>
+    <t>2,23,202</t>
+  </si>
+  <si>
+    <t>2,24,202</t>
+  </si>
+  <si>
+    <t>2,25,202</t>
+  </si>
+  <si>
+    <t>2,26,202</t>
+  </si>
+  <si>
+    <t>2,27,202</t>
+  </si>
+  <si>
+    <t>2,28,202</t>
+  </si>
+  <si>
+    <t>2,29,212</t>
+  </si>
+  <si>
+    <t>2,30,212</t>
+  </si>
+  <si>
+    <t>202,212,34</t>
+  </si>
+  <si>
+    <t>43,46,204</t>
+  </si>
+  <si>
+    <t>43,47,204</t>
+  </si>
+  <si>
+    <t>43,48,204</t>
+  </si>
+  <si>
+    <t>43,49,204</t>
+  </si>
+  <si>
+    <t>43,50,204</t>
+  </si>
+  <si>
+    <t>43,51,68,203,204</t>
+  </si>
+  <si>
+    <t>43,57,205</t>
+  </si>
+  <si>
+    <t>43,85,206</t>
+  </si>
+  <si>
+    <t>43,86,206</t>
+  </si>
+  <si>
+    <t>43,87,206</t>
+  </si>
+  <si>
+    <t>43,88,206</t>
+  </si>
+  <si>
+    <t>43,89,206</t>
+  </si>
+  <si>
+    <t>43,90,206</t>
+  </si>
+  <si>
+    <t>43,90,91,206</t>
+  </si>
+  <si>
+    <t>43,92,206</t>
+  </si>
+  <si>
+    <t>43,108,209</t>
+  </si>
+  <si>
+    <t>43,108,109,209</t>
+  </si>
+  <si>
+    <t>43,54,204</t>
+  </si>
+  <si>
+    <t>43,55,204</t>
+  </si>
+  <si>
+    <t>43,52,68,203,204</t>
+  </si>
+  <si>
+    <t>43,53,68,203,204</t>
+  </si>
+  <si>
+    <t>43,100,102</t>
+  </si>
+  <si>
+    <t>Polymorphie</t>
+  </si>
+  <si>
+    <t>43,98,207</t>
+  </si>
+  <si>
+    <t>43,99,207</t>
+  </si>
+  <si>
+    <t>mehrdimensionales Array</t>
   </si>
 </sst>
 </file>
@@ -2177,7 +2147,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2246,18 +2216,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor rgb="FFD0CECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB2B2B2"/>
         <bgColor rgb="FFD0CECE"/>
       </patternFill>
@@ -2282,7 +2240,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -2450,9 +2408,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2482,27 +2437,13 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2510,6 +2451,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3018,10 +2977,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="96"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
@@ -3040,10 +2999,10 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="97"/>
+      <c r="B5" s="90"/>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
@@ -3060,10 +3019,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="94"/>
+      <c r="B6" s="87"/>
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3080,10 +3039,10 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="95" t="s">
+      <c r="A7" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="95"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
@@ -3100,10 +3059,10 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="94"/>
+      <c r="B8" s="87"/>
       <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
@@ -3252,10 +3211,10 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="94"/>
+      <c r="B15" s="87"/>
       <c r="C15" s="2" t="s">
         <v>56</v>
       </c>
@@ -3272,10 +3231,10 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="95"/>
+      <c r="B16" s="88"/>
       <c r="C16" s="1" t="s">
         <v>61</v>
       </c>
@@ -6483,7 +6442,7 @@
     <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="5" width="16.5" style="22" customWidth="1"/>
+    <col min="5" max="5" width="18.5" style="22" customWidth="1"/>
     <col min="6" max="6" width="43.6640625" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
@@ -6620,7 +6579,9 @@
       <c r="A4" s="28">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
+      <c r="B4" s="21">
+        <v>4</v>
+      </c>
       <c r="C4" s="28">
         <v>2</v>
       </c>
@@ -6662,7 +6623,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="36">
         <v>3</v>
@@ -6700,19 +6661,19 @@
       </c>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="36">
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="36">
         <v>4</v>
       </c>
       <c r="D6" s="37"/>
-      <c r="E6" s="37" t="s">
-        <v>209</v>
+      <c r="E6" s="37">
+        <v>2.7</v>
       </c>
       <c r="F6" s="41" t="s">
         <v>91</v>
@@ -6727,10 +6688,10 @@
         <v>1</v>
       </c>
       <c r="J6" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="K6" s="40" t="s">
         <v>210</v>
-      </c>
-      <c r="K6" s="40" t="s">
-        <v>211</v>
       </c>
       <c r="L6" s="40"/>
       <c r="M6" s="40"/>
@@ -6739,24 +6700,20 @@
         <v>91</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q6" s="42"/>
     </row>
     <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="B7" s="21">
-        <v>7</v>
-      </c>
-      <c r="C7" s="28">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C7" s="28"/>
       <c r="D7" s="19"/>
-      <c r="E7" s="19" t="s">
-        <v>213</v>
-      </c>
+      <c r="E7" s="19"/>
       <c r="F7" s="21" t="s">
         <v>92</v>
       </c>
@@ -6776,79 +6733,87 @@
       <c r="N7" s="34"/>
       <c r="O7" s="2"/>
       <c r="P7" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Q7" s="35"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="28">
-        <v>6</v>
-      </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>93</v>
+        <v>5</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="91" t="s">
+        <v>607</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>92</v>
       </c>
       <c r="G8" s="28">
-        <v>8</v>
-      </c>
-      <c r="H8" s="45">
-        <v>3</v>
-      </c>
-      <c r="I8" s="28">
+        <v>210</v>
+      </c>
+      <c r="H8" s="28">
+        <v>1</v>
+      </c>
+      <c r="I8" s="43">
         <v>1</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>217</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="K8" s="34"/>
       <c r="L8" s="34"/>
       <c r="M8" s="34"/>
       <c r="N8" s="34"/>
-      <c r="O8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q8" s="42"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q8" s="35"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="21"/>
+      <c r="A9" s="28">
+        <v>9</v>
+      </c>
+      <c r="B9" s="21">
+        <v>8</v>
+      </c>
       <c r="C9" s="28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="21"/>
-      <c r="E9" s="21" t="s">
-        <v>215</v>
+      <c r="E9" s="92" t="s">
+        <v>608</v>
       </c>
       <c r="F9" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="45"/>
+      <c r="G9" s="28">
+        <v>210</v>
+      </c>
+      <c r="H9" s="45">
+        <v>3</v>
+      </c>
       <c r="I9" s="28">
-        <v>2</v>
-      </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>214</v>
+      </c>
       <c r="L9" s="34"/>
       <c r="M9" s="34"/>
       <c r="N9" s="34"/>
       <c r="O9" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q9" s="42"/>
     </row>
@@ -6856,11 +6821,11 @@
       <c r="A10" s="28"/>
       <c r="B10" s="21"/>
       <c r="C10" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="21"/>
-      <c r="E10" s="21" t="s">
-        <v>215</v>
+      <c r="E10" s="92" t="s">
+        <v>608</v>
       </c>
       <c r="F10" s="44" t="s">
         <v>93</v>
@@ -6868,7 +6833,7 @@
       <c r="G10" s="28"/>
       <c r="H10" s="45"/>
       <c r="I10" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" s="34"/>
       <c r="K10" s="34"/>
@@ -6876,101 +6841,93 @@
       <c r="M10" s="34"/>
       <c r="N10" s="34"/>
       <c r="O10" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q10" s="42"/>
     </row>
-    <row r="11" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="28">
-        <v>10</v>
-      </c>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="28"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="28"/>
+      <c r="C11" s="28">
+        <v>8</v>
+      </c>
       <c r="D11" s="21"/>
-      <c r="E11" s="21" t="s">
-        <v>220</v>
+      <c r="E11" s="92" t="s">
+        <v>608</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="28">
-        <v>8</v>
-      </c>
-      <c r="H11" s="45">
-        <v>2</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G11" s="28"/>
+      <c r="H11" s="45"/>
       <c r="I11" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" s="34"/>
       <c r="K11" s="34"/>
       <c r="L11" s="34"/>
       <c r="M11" s="34"/>
       <c r="N11" s="34"/>
-      <c r="O11" s="2"/>
+      <c r="O11" s="2" t="s">
+        <v>215</v>
+      </c>
       <c r="P11" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q11" s="35"/>
+        <v>216</v>
+      </c>
+      <c r="Q11" s="42"/>
     </row>
     <row r="12" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
-        <v>11</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="28">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B12" s="21">
+        <v>8</v>
+      </c>
+      <c r="C12" s="28"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="F12" s="46" t="s">
-        <v>133</v>
+      <c r="E12" s="92" t="s">
+        <v>609</v>
+      </c>
+      <c r="F12" s="44" t="s">
+        <v>94</v>
       </c>
       <c r="G12" s="28">
-        <v>10</v>
-      </c>
-      <c r="H12" s="28">
-        <v>3</v>
+        <v>210</v>
+      </c>
+      <c r="H12" s="45">
+        <v>2</v>
       </c>
       <c r="I12" s="28">
         <v>1</v>
       </c>
-      <c r="J12" s="34" t="s">
-        <v>223</v>
-      </c>
-      <c r="K12" s="34" t="s">
-        <v>224</v>
-      </c>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
       <c r="L12" s="34"/>
       <c r="M12" s="34"/>
       <c r="N12" s="34"/>
-      <c r="O12" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" s="2" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="Q12" s="35"/>
     </row>
     <row r="13" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="21"/>
-      <c r="E13" s="21" t="s">
-        <v>226</v>
+      <c r="E13" s="92" t="s">
+        <v>610</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G13" s="28">
         <v>10</v>
@@ -6982,42 +6939,54 @@
         <v>1</v>
       </c>
       <c r="J13" s="34" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="34"/>
       <c r="N13" s="34"/>
       <c r="O13" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="Q13" s="35"/>
     </row>
     <row r="14" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="21"/>
+      <c r="A14" s="28">
+        <v>12</v>
+      </c>
+      <c r="B14" s="21">
+        <v>11</v>
+      </c>
       <c r="C14" s="28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" s="21"/>
-      <c r="E14" s="21" t="s">
-        <v>226</v>
+      <c r="E14" s="92" t="s">
+        <v>611</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
+      <c r="G14" s="28">
+        <v>10</v>
+      </c>
+      <c r="H14" s="28">
+        <v>3</v>
+      </c>
       <c r="I14" s="28">
-        <v>2</v>
-      </c>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="K14" s="34" t="s">
+        <v>222</v>
+      </c>
       <c r="L14" s="34"/>
       <c r="M14" s="34"/>
       <c r="N14" s="34"/>
@@ -7025,360 +6994,364 @@
         <v>134</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="Q14" s="35"/>
     </row>
     <row r="15" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="28">
-        <v>13</v>
-      </c>
+      <c r="A15" s="28"/>
       <c r="B15" s="21"/>
       <c r="C15" s="28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="21"/>
-      <c r="E15" s="21" t="s">
-        <v>230</v>
+      <c r="E15" s="92" t="s">
+        <v>611</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="G15" s="28">
-        <v>10</v>
-      </c>
-      <c r="H15" s="28">
-        <v>3</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
       <c r="I15" s="28">
-        <v>1</v>
-      </c>
-      <c r="J15" s="34" t="s">
-        <v>232</v>
-      </c>
-      <c r="K15" s="34" t="s">
-        <v>233</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
       <c r="L15" s="34"/>
       <c r="M15" s="34"/>
       <c r="N15" s="34"/>
       <c r="O15" s="2" t="s">
-        <v>234</v>
+        <v>134</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="Q15" s="35"/>
     </row>
     <row r="16" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
-        <v>14</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>236</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B16" s="21"/>
       <c r="C16" s="28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="21"/>
-      <c r="E16" s="21" t="s">
-        <v>237</v>
+      <c r="E16" s="92" t="s">
+        <v>612</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>101</v>
+        <v>224</v>
       </c>
       <c r="G16" s="28">
         <v>10</v>
       </c>
       <c r="H16" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="28">
         <v>1</v>
       </c>
       <c r="J16" s="34" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="K16" s="34" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="34"/>
       <c r="N16" s="34"/>
       <c r="O16" s="2" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="Q16" s="35"/>
     </row>
     <row r="17" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
-        <v>16</v>
-      </c>
-      <c r="B17" s="21"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>229</v>
+      </c>
       <c r="C17" s="28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="21"/>
-      <c r="E17" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>97</v>
+      <c r="E17" s="92" t="s">
+        <v>613</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="G17" s="28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H17" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="28">
         <v>1</v>
       </c>
       <c r="J17" s="34" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="K17" s="34" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="L17" s="34"/>
       <c r="M17" s="34"/>
       <c r="N17" s="34"/>
       <c r="O17" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="Q17" s="35"/>
     </row>
     <row r="18" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
-        <v>17</v>
-      </c>
-      <c r="B18" s="21"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="21">
+        <v>8</v>
+      </c>
       <c r="C18" s="28">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" s="21"/>
-      <c r="E18" s="21" t="s">
-        <v>245</v>
+      <c r="E18" s="92" t="s">
+        <v>614</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G18" s="28">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="H18" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="28">
         <v>1</v>
       </c>
       <c r="J18" s="34" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="K18" s="34" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="34"/>
       <c r="N18" s="34"/>
       <c r="O18" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="Q18" s="35"/>
     </row>
     <row r="19" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
+        <v>17</v>
+      </c>
+      <c r="B19" s="21">
+        <v>8</v>
+      </c>
+      <c r="C19" s="28">
         <v>15</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="C19" s="28">
-        <v>16</v>
-      </c>
       <c r="D19" s="21"/>
-      <c r="E19" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="F19" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="43">
-        <v>8</v>
+      <c r="E19" s="92" t="s">
+        <v>615</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="28">
+        <v>210</v>
       </c>
       <c r="H19" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="28">
         <v>1</v>
       </c>
       <c r="J19" s="34" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="K19" s="34" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="34"/>
       <c r="N19" s="34"/>
       <c r="O19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q19" s="35"/>
+    </row>
+    <row r="20" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="28">
+        <v>15</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="28">
+        <v>16</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="92" t="s">
+        <v>616</v>
+      </c>
+      <c r="F20" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q19" s="35"/>
-    </row>
-    <row r="20" spans="1:1024" s="73" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="66">
+      <c r="G20" s="43">
+        <v>210</v>
+      </c>
+      <c r="H20" s="28">
+        <v>1</v>
+      </c>
+      <c r="I20" s="28">
+        <v>1</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="K20" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q20" s="35"/>
+    </row>
+    <row r="21" spans="1:1024" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="66">
         <v>201</v>
       </c>
-      <c r="B20" s="67">
-        <v>8</v>
-      </c>
-      <c r="C20" s="66"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67" t="s">
-        <v>651</v>
-      </c>
-      <c r="F20" s="68" t="s">
+      <c r="B21" s="67">
+        <v>210</v>
+      </c>
+      <c r="C21" s="66"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="G20" s="69">
+      <c r="G21" s="68">
         <v>2</v>
       </c>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
-      <c r="L20" s="70"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q20" s="72"/>
-    </row>
-    <row r="21" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="36">
+      <c r="H21" s="66">
+        <v>3</v>
+      </c>
+      <c r="I21" s="66"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="69"/>
+      <c r="M21" s="69"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q21" s="71"/>
+    </row>
+    <row r="22" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="36">
         <v>18</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="36">
+      <c r="B22" s="47"/>
+      <c r="C22" s="36">
         <v>17</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="D22" s="3"/>
+      <c r="E22" s="93" t="s">
+        <v>617</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="G21" s="36">
-        <v>201</v>
-      </c>
-      <c r="H21" s="36">
-        <v>3</v>
-      </c>
-      <c r="I21" s="36">
-        <v>1</v>
-      </c>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40" t="s">
-        <v>254</v>
-      </c>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q21" s="35"/>
-    </row>
-    <row r="22" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A22" s="36">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3">
-        <v>18</v>
-      </c>
-      <c r="C22" s="36">
-        <v>18</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>103</v>
       </c>
       <c r="G22" s="36">
         <v>201</v>
       </c>
       <c r="H22" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" s="36">
         <v>1</v>
       </c>
-      <c r="J22" s="40" t="s">
-        <v>258</v>
-      </c>
+      <c r="J22" s="40"/>
       <c r="K22" s="40" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="L22" s="40"/>
       <c r="M22" s="40"/>
       <c r="N22" s="40"/>
       <c r="O22" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q22" s="42"/>
+        <v>245</v>
+      </c>
+      <c r="Q22" s="35"/>
     </row>
     <row r="23" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A23" s="36"/>
-      <c r="B23" s="3"/>
+      <c r="A23" s="36">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3">
+        <v>18</v>
+      </c>
       <c r="C23" s="36">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="3" t="s">
-        <v>257</v>
+      <c r="E23" s="93" t="s">
+        <v>618</v>
       </c>
       <c r="F23" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
+      <c r="G23" s="36">
+        <v>201</v>
+      </c>
+      <c r="H23" s="36">
+        <v>3</v>
+      </c>
       <c r="I23" s="36">
-        <v>2</v>
-      </c>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J23" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>247</v>
+      </c>
       <c r="L23" s="40"/>
       <c r="M23" s="40"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="89" t="s">
-        <v>670</v>
+      <c r="O23" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="Q23" s="42"/>
     </row>
@@ -7386,11 +7359,11 @@
       <c r="A24" s="36"/>
       <c r="B24" s="3"/>
       <c r="C24" s="36">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="3" t="s">
-        <v>257</v>
+      <c r="E24" s="93" t="s">
+        <v>618</v>
       </c>
       <c r="F24" s="41" t="s">
         <v>103</v>
@@ -7398,201 +7371,199 @@
       <c r="G24" s="36"/>
       <c r="H24" s="36"/>
       <c r="I24" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24" s="40"/>
       <c r="K24" s="40"/>
       <c r="L24" s="40"/>
       <c r="M24" s="40"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="89" t="s">
-        <v>670</v>
+      <c r="O24" s="82" t="s">
+        <v>606</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="Q24" s="42"/>
     </row>
-    <row r="25" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="36">
+    <row r="25" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A25" s="36"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="36">
         <v>20</v>
       </c>
-      <c r="B25" s="3">
-        <v>19</v>
-      </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="3">
-        <v>19</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>262</v>
+      <c r="D25" s="3"/>
+      <c r="E25" s="93" t="s">
+        <v>618</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G25" s="36">
-        <v>201</v>
-      </c>
-      <c r="H25" s="36">
+        <v>103</v>
+      </c>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36">
         <v>3</v>
-      </c>
-      <c r="I25" s="36">
-        <v>1</v>
       </c>
       <c r="J25" s="40"/>
       <c r="K25" s="40"/>
       <c r="L25" s="40"/>
       <c r="M25" s="40"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="48" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q25" s="35"/>
+      <c r="O25" s="82" t="s">
+        <v>606</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q25" s="42"/>
     </row>
     <row r="26" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="36">
+        <v>20</v>
+      </c>
+      <c r="B26" s="3">
+        <v>19</v>
+      </c>
+      <c r="C26" s="36"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="93" t="s">
+        <v>619</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="36">
+        <v>201</v>
+      </c>
+      <c r="H26" s="36">
+        <v>3</v>
+      </c>
+      <c r="I26" s="36">
+        <v>1</v>
+      </c>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="48" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q26" s="35"/>
+    </row>
+    <row r="27" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="36">
         <v>21</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="36">
-        <v>21</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="F26" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="G26" s="36">
-        <v>20</v>
-      </c>
-      <c r="H26" s="36">
-        <v>2</v>
-      </c>
-      <c r="I26" s="36">
-        <v>1</v>
-      </c>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40" t="s">
-        <v>267</v>
-      </c>
-      <c r="N26" s="40"/>
-      <c r="O26" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q26" s="35"/>
-    </row>
-    <row r="27" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="36"/>
       <c r="B27" s="3"/>
       <c r="C27" s="36">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="3" t="s">
-        <v>264</v>
+      <c r="E27" s="93" t="s">
+        <v>620</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
+        <v>251</v>
+      </c>
+      <c r="G27" s="36">
+        <v>20</v>
+      </c>
+      <c r="H27" s="36">
+        <v>2</v>
+      </c>
       <c r="I27" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
+      <c r="K27" s="40" t="s">
+        <v>252</v>
+      </c>
       <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
+      <c r="M27" s="40" t="s">
+        <v>253</v>
+      </c>
       <c r="N27" s="40"/>
       <c r="O27" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="Q27" s="35"/>
     </row>
-    <row r="28" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A28" s="36">
-        <v>22</v>
-      </c>
+    <row r="28" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="36"/>
       <c r="B28" s="3"/>
       <c r="C28" s="36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="3" t="s">
-        <v>270</v>
+      <c r="E28" s="93" t="s">
+        <v>620</v>
       </c>
       <c r="F28" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="G28" s="36">
-        <v>20</v>
-      </c>
-      <c r="H28" s="36">
-        <v>3</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
       <c r="I28" s="36">
-        <v>1</v>
-      </c>
-      <c r="J28" s="40" t="s">
-        <v>272</v>
-      </c>
-      <c r="K28" s="40" t="s">
-        <v>273</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
       <c r="L28" s="40"/>
-      <c r="M28" s="40" t="s">
-        <v>274</v>
-      </c>
+      <c r="M28" s="40"/>
       <c r="N28" s="40"/>
       <c r="O28" s="1" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q28" s="42"/>
+        <v>255</v>
+      </c>
+      <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A29" s="36"/>
+      <c r="A29" s="36">
+        <v>22</v>
+      </c>
       <c r="B29" s="3"/>
       <c r="C29" s="36">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="3" t="s">
-        <v>270</v>
+      <c r="E29" s="93" t="s">
+        <v>621</v>
       </c>
       <c r="F29" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
+        <v>256</v>
+      </c>
+      <c r="G29" s="36">
+        <v>20</v>
+      </c>
+      <c r="H29" s="36">
+        <v>3</v>
+      </c>
       <c r="I29" s="36">
-        <v>2</v>
-      </c>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J29" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="K29" s="40" t="s">
+        <v>258</v>
+      </c>
       <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
+      <c r="M29" s="40" t="s">
+        <v>259</v>
+      </c>
       <c r="N29" s="40"/>
       <c r="O29" s="1" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="Q29" s="42"/>
     </row>
@@ -7600,19 +7571,19 @@
       <c r="A30" s="36"/>
       <c r="B30" s="3"/>
       <c r="C30" s="36">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="3" t="s">
-        <v>270</v>
+      <c r="E30" s="93" t="s">
+        <v>621</v>
       </c>
       <c r="F30" s="49" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
       <c r="I30" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="40"/>
       <c r="K30" s="40"/>
@@ -7620,149 +7591,154 @@
       <c r="M30" s="40"/>
       <c r="N30" s="40"/>
       <c r="O30" s="1" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="Q30" s="42"/>
     </row>
-    <row r="31" spans="1:1024" s="92" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="50">
-        <v>39</v>
-      </c>
-      <c r="B31" s="51">
-        <v>8</v>
-      </c>
-      <c r="C31" s="50">
+    <row r="31" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A31" s="36"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="36">
+        <v>25</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="93" t="s">
+        <v>621</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36">
+        <v>3</v>
+      </c>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q31" s="42"/>
+    </row>
+    <row r="32" spans="1:1024" s="85" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="50">
+        <v>211</v>
+      </c>
+      <c r="B32" s="51">
+        <v>201</v>
+      </c>
+      <c r="C32" s="50">
         <v>26</v>
       </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51" t="s">
-        <v>277</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50">
-        <v>2</v>
-      </c>
-      <c r="I31" s="50">
-        <v>1</v>
-      </c>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="53"/>
-      <c r="P31" s="90" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q31" s="91"/>
-      <c r="AMJ31" s="93"/>
-    </row>
-    <row r="32" spans="1:1024" s="92" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="50"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="50">
-        <v>27</v>
-      </c>
       <c r="D32" s="51"/>
-      <c r="E32" s="51" t="s">
-        <v>277</v>
-      </c>
+      <c r="E32" s="51"/>
       <c r="F32" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50">
+      <c r="G32" s="50">
         <v>2</v>
       </c>
+      <c r="H32" s="50">
+        <v>3</v>
+      </c>
+      <c r="I32" s="50"/>
       <c r="J32" s="52"/>
       <c r="K32" s="52"/>
       <c r="L32" s="52"/>
       <c r="M32" s="52"/>
       <c r="N32" s="52"/>
       <c r="O32" s="53"/>
-      <c r="P32" s="90" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q32" s="91"/>
-      <c r="AMJ32" s="93"/>
-    </row>
-    <row r="33" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P32" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q32" s="84"/>
+      <c r="AMJ32" s="86"/>
+    </row>
+    <row r="33" spans="1:1024" s="85" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="50">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="51"/>
       <c r="C33" s="50">
+        <v>27</v>
+      </c>
+      <c r="D33" s="51"/>
+      <c r="E33" s="94" t="s">
+        <v>622</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" s="50">
+        <v>211</v>
+      </c>
+      <c r="H33" s="50">
+        <v>1</v>
+      </c>
+      <c r="I33" s="50">
+        <v>1</v>
+      </c>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="52"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q33" s="84"/>
+      <c r="AMJ33" s="86"/>
+    </row>
+    <row r="34" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="50">
+        <v>40</v>
+      </c>
+      <c r="B34" s="51">
+        <v>39</v>
+      </c>
+      <c r="C34" s="50">
         <v>28</v>
       </c>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="F33" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="G33" s="50">
-        <v>39</v>
-      </c>
-      <c r="H33" s="50">
-        <v>3</v>
-      </c>
-      <c r="I33" s="50">
-        <v>1</v>
-      </c>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="L33" s="52"/>
-      <c r="M33" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="N33" s="52"/>
-      <c r="O33" s="53" t="s">
-        <v>282</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q33" s="57"/>
-      <c r="AMJ33"/>
-    </row>
-    <row r="34" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="50"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="50">
-        <v>29</v>
-      </c>
       <c r="D34" s="51"/>
-      <c r="E34" s="51" t="s">
-        <v>279</v>
+      <c r="E34" s="94" t="s">
+        <v>623</v>
       </c>
       <c r="F34" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
+      <c r="G34" s="50">
+        <v>211</v>
+      </c>
+      <c r="H34" s="50">
+        <v>3</v>
+      </c>
       <c r="I34" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
+      <c r="K34" s="52" t="s">
+        <v>263</v>
+      </c>
       <c r="L34" s="52"/>
-      <c r="M34" s="52"/>
+      <c r="M34" s="52" t="s">
+        <v>264</v>
+      </c>
       <c r="N34" s="52"/>
       <c r="O34" s="53" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="Q34" s="57"/>
       <c r="AMJ34"/>
@@ -7771,11 +7747,11 @@
       <c r="A35" s="50"/>
       <c r="B35" s="51"/>
       <c r="C35" s="50">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" s="51"/>
-      <c r="E35" s="51" t="s">
-        <v>279</v>
+      <c r="E35" s="94" t="s">
+        <v>623</v>
       </c>
       <c r="F35" s="56" t="s">
         <v>127</v>
@@ -7783,7 +7759,7 @@
       <c r="G35" s="50"/>
       <c r="H35" s="50"/>
       <c r="I35" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35" s="52"/>
       <c r="K35" s="52"/>
@@ -7791,203 +7767,203 @@
       <c r="M35" s="52"/>
       <c r="N35" s="52"/>
       <c r="O35" s="53" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="Q35" s="57"/>
       <c r="AMJ35"/>
     </row>
     <row r="36" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="50">
-        <v>41</v>
-      </c>
+      <c r="A36" s="50"/>
       <c r="B36" s="51"/>
       <c r="C36" s="50">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36" s="51"/>
-      <c r="E36" s="51" t="s">
-        <v>284</v>
+      <c r="E36" s="94" t="s">
+        <v>623</v>
       </c>
       <c r="F36" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="G36" s="50">
-        <v>39</v>
-      </c>
-      <c r="H36" s="50">
-        <v>6</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
       <c r="I36" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36" s="52"/>
       <c r="K36" s="52"/>
       <c r="L36" s="52"/>
-      <c r="M36" s="52" t="s">
-        <v>285</v>
-      </c>
+      <c r="M36" s="52"/>
       <c r="N36" s="52"/>
       <c r="O36" s="53" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="Q36" s="57"/>
       <c r="AMJ36"/>
     </row>
     <row r="37" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="50"/>
-      <c r="B37" s="51"/>
+      <c r="A37" s="50">
+        <v>41</v>
+      </c>
+      <c r="B37" s="51">
+        <v>39</v>
+      </c>
       <c r="C37" s="50">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" s="51"/>
-      <c r="E37" s="51" t="s">
-        <v>284</v>
+      <c r="E37" s="94" t="s">
+        <v>624</v>
       </c>
       <c r="F37" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
+      <c r="G37" s="50">
+        <v>211</v>
+      </c>
+      <c r="H37" s="50">
+        <v>2</v>
+      </c>
       <c r="I37" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" s="52"/>
       <c r="K37" s="52"/>
       <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
+      <c r="M37" s="52" t="s">
+        <v>267</v>
+      </c>
       <c r="N37" s="52"/>
       <c r="O37" s="53" t="s">
         <v>128</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="Q37" s="57"/>
       <c r="AMJ37"/>
     </row>
     <row r="38" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="50">
-        <v>42</v>
-      </c>
+      <c r="A38" s="50"/>
       <c r="B38" s="51"/>
       <c r="C38" s="50">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" s="51"/>
-      <c r="E38" s="51" t="s">
-        <v>287</v>
+      <c r="E38" s="94" t="s">
+        <v>624</v>
       </c>
       <c r="F38" s="56" t="s">
-        <v>129</v>
-      </c>
-      <c r="G38" s="50">
-        <v>39</v>
-      </c>
-      <c r="H38" s="50">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
       <c r="I38" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="52"/>
       <c r="K38" s="52"/>
       <c r="L38" s="52"/>
-      <c r="M38" s="52" t="s">
-        <v>288</v>
-      </c>
+      <c r="M38" s="52"/>
       <c r="N38" s="52"/>
       <c r="O38" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="Q38" s="57"/>
       <c r="AMJ38"/>
     </row>
-    <row r="39" spans="1:1024" s="81" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="74">
+    <row r="39" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="50">
+        <v>42</v>
+      </c>
+      <c r="B39" s="51">
+        <v>39</v>
+      </c>
+      <c r="C39" s="50">
+        <v>33</v>
+      </c>
+      <c r="D39" s="51"/>
+      <c r="E39" s="94" t="s">
+        <v>625</v>
+      </c>
+      <c r="F39" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="G39" s="50">
+        <v>211</v>
+      </c>
+      <c r="H39" s="50">
+        <v>1</v>
+      </c>
+      <c r="I39" s="50">
+        <v>1</v>
+      </c>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="N39" s="52"/>
+      <c r="O39" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q39" s="57"/>
+      <c r="AMJ39"/>
+    </row>
+    <row r="40" spans="1:1024" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="73">
         <v>202</v>
       </c>
-      <c r="B39" s="75" t="s">
-        <v>653</v>
-      </c>
-      <c r="C39" s="74"/>
-      <c r="D39" s="75"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="76" t="s">
+      <c r="B40" s="74">
+        <v>201.21100000000001</v>
+      </c>
+      <c r="C40" s="73"/>
+      <c r="D40" s="74"/>
+      <c r="E40" s="74"/>
+      <c r="F40" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="G39" s="74">
+      <c r="G40" s="73">
         <v>2</v>
       </c>
-      <c r="H39" s="74"/>
-      <c r="I39" s="74"/>
-      <c r="J39" s="77"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="77"/>
-      <c r="M39" s="77"/>
-      <c r="N39" s="77"/>
-      <c r="O39" s="78"/>
-      <c r="P39" s="79"/>
-      <c r="Q39" s="80"/>
-      <c r="AMJ39" s="82"/>
-    </row>
-    <row r="40" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="28">
+      <c r="H40" s="73">
+        <v>3</v>
+      </c>
+      <c r="I40" s="73"/>
+      <c r="J40" s="76"/>
+      <c r="K40" s="76"/>
+      <c r="L40" s="76"/>
+      <c r="M40" s="76"/>
+      <c r="N40" s="76"/>
+      <c r="O40" s="77"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="79"/>
+      <c r="AMJ40" s="81"/>
+    </row>
+    <row r="41" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="28">
         <v>23</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="28">
-        <v>34</v>
-      </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="G40" s="28">
-        <v>202</v>
-      </c>
-      <c r="H40" s="28">
-        <v>3</v>
-      </c>
-      <c r="I40" s="28">
-        <v>1</v>
-      </c>
-      <c r="J40" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q40" s="54"/>
-      <c r="AMJ40"/>
-    </row>
-    <row r="41" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
       <c r="B41" s="21"/>
       <c r="C41" s="28">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D41" s="21"/>
-      <c r="E41" s="21" t="s">
-        <v>290</v>
+      <c r="E41" s="92" t="s">
+        <v>626</v>
       </c>
       <c r="F41" s="21" t="s">
         <v>108</v>
@@ -8001,7 +7977,9 @@
       <c r="I41" s="28">
         <v>1</v>
       </c>
-      <c r="J41" s="34"/>
+      <c r="J41" s="34" t="s">
+        <v>271</v>
+      </c>
       <c r="K41" s="34"/>
       <c r="L41" s="34"/>
       <c r="M41" s="34"/>
@@ -8010,7 +7988,7 @@
         <v>108</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="Q41" s="54"/>
       <c r="AMJ41"/>
@@ -8022,8 +8000,8 @@
         <v>36</v>
       </c>
       <c r="D42" s="21"/>
-      <c r="E42" s="21" t="s">
-        <v>290</v>
+      <c r="E42" s="92" t="s">
+        <v>626</v>
       </c>
       <c r="F42" s="21" t="s">
         <v>108</v>
@@ -8042,7 +8020,7 @@
         <v>108</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="Q42" s="54"/>
       <c r="AMJ42"/>
@@ -8054,8 +8032,8 @@
         <v>37</v>
       </c>
       <c r="D43" s="21"/>
-      <c r="E43" s="21" t="s">
-        <v>290</v>
+      <c r="E43" s="92" t="s">
+        <v>626</v>
       </c>
       <c r="F43" s="21" t="s">
         <v>108</v>
@@ -8067,18 +8045,18 @@
       </c>
       <c r="J43" s="34"/>
       <c r="K43" s="34" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="L43" s="34"/>
       <c r="M43" s="34" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="N43" s="34"/>
       <c r="O43" s="2" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="Q43" s="54"/>
       <c r="AMJ43"/>
@@ -8090,8 +8068,8 @@
         <v>38</v>
       </c>
       <c r="D44" s="21"/>
-      <c r="E44" s="21" t="s">
-        <v>290</v>
+      <c r="E44" s="21">
+        <v>2.202</v>
       </c>
       <c r="F44" s="33" t="s">
         <v>109</v>
@@ -8104,19 +8082,19 @@
         <v>1</v>
       </c>
       <c r="J44" s="34" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="K44" s="34" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="L44" s="34"/>
       <c r="M44" s="34"/>
       <c r="N44" s="34"/>
       <c r="O44" s="2" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="Q44" s="54"/>
       <c r="AMJ44"/>
@@ -8132,35 +8110,35 @@
         <v>39</v>
       </c>
       <c r="D45" s="21"/>
-      <c r="E45" s="21" t="s">
-        <v>301</v>
+      <c r="E45" s="92" t="s">
+        <v>627</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>656</v>
+        <v>595</v>
       </c>
       <c r="G45" s="28">
         <v>202</v>
       </c>
       <c r="H45" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45" s="28">
         <v>1</v>
       </c>
       <c r="J45" s="34" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="K45" s="34" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="L45" s="34"/>
       <c r="M45" s="34"/>
       <c r="N45" s="34"/>
       <c r="O45" s="2" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="Q45" s="54"/>
       <c r="AMJ45"/>
@@ -8176,8 +8154,8 @@
         <v>40</v>
       </c>
       <c r="D46" s="21"/>
-      <c r="E46" s="21" t="s">
-        <v>306</v>
+      <c r="E46" s="92" t="s">
+        <v>628</v>
       </c>
       <c r="F46" s="33" t="s">
         <v>111</v>
@@ -8192,19 +8170,19 @@
         <v>1</v>
       </c>
       <c r="J46" s="34" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="K46" s="34" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="L46" s="34"/>
       <c r="M46" s="34"/>
       <c r="N46" s="34"/>
       <c r="O46" s="2" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="Q46" s="54"/>
       <c r="AMJ46"/>
@@ -8216,8 +8194,8 @@
         <v>41</v>
       </c>
       <c r="D47" s="21"/>
-      <c r="E47" s="21" t="s">
-        <v>306</v>
+      <c r="E47" s="92" t="s">
+        <v>628</v>
       </c>
       <c r="F47" s="33" t="s">
         <v>111</v>
@@ -8233,10 +8211,10 @@
       <c r="M47" s="34"/>
       <c r="N47" s="34"/>
       <c r="O47" s="2" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="Q47" s="54"/>
       <c r="AMJ47"/>
@@ -8248,8 +8226,8 @@
         <v>42</v>
       </c>
       <c r="D48" s="21"/>
-      <c r="E48" s="21" t="s">
-        <v>306</v>
+      <c r="E48" s="92" t="s">
+        <v>628</v>
       </c>
       <c r="F48" s="33" t="s">
         <v>111</v>
@@ -8265,10 +8243,10 @@
       <c r="M48" s="34"/>
       <c r="N48" s="34"/>
       <c r="O48" s="2" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="Q48" s="54"/>
       <c r="AMJ48"/>
@@ -8284,8 +8262,8 @@
         <v>43</v>
       </c>
       <c r="D49" s="21"/>
-      <c r="E49" s="21" t="s">
-        <v>311</v>
+      <c r="E49" s="92" t="s">
+        <v>629</v>
       </c>
       <c r="F49" s="58" t="s">
         <v>112</v>
@@ -8294,19 +8272,19 @@
         <v>202</v>
       </c>
       <c r="H49" s="43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" s="28">
         <v>1</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="K49" s="34" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="L49" s="34" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="M49" s="34"/>
       <c r="N49" s="34"/>
@@ -8314,7 +8292,7 @@
         <v>112</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="AMJ49"/>
     </row>
@@ -8325,8 +8303,8 @@
         <v>44</v>
       </c>
       <c r="D50" s="21"/>
-      <c r="E50" s="21" t="s">
-        <v>311</v>
+      <c r="E50" s="92" t="s">
+        <v>629</v>
       </c>
       <c r="F50" s="58" t="s">
         <v>112</v>
@@ -8345,7 +8323,7 @@
         <v>112</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="AMJ50"/>
     </row>
@@ -8356,8 +8334,8 @@
         <v>45</v>
       </c>
       <c r="D51" s="21"/>
-      <c r="E51" s="21" t="s">
-        <v>311</v>
+      <c r="E51" s="92" t="s">
+        <v>629</v>
       </c>
       <c r="F51" s="33" t="s">
         <v>113</v>
@@ -8370,14 +8348,14 @@
         <v>1</v>
       </c>
       <c r="J51" s="34" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="K51" s="34"/>
       <c r="L51" s="34"/>
       <c r="M51" s="34"/>
       <c r="N51" s="34"/>
       <c r="O51" s="2" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" s="54"/>
@@ -8387,33 +8365,33 @@
       <c r="A52" s="28">
         <v>27</v>
       </c>
-      <c r="B52" s="21" t="s">
-        <v>657</v>
+      <c r="B52" s="21">
+        <v>23</v>
       </c>
       <c r="C52" s="28">
         <v>46</v>
       </c>
       <c r="D52" s="21"/>
-      <c r="E52" s="21" t="s">
-        <v>318</v>
+      <c r="E52" s="92" t="s">
+        <v>630</v>
       </c>
       <c r="F52" s="33" t="s">
         <v>114</v>
       </c>
       <c r="G52" s="28">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="H52" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52" s="28">
         <v>1</v>
       </c>
       <c r="J52" s="34" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="K52" s="34" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="L52" s="34"/>
       <c r="M52" s="34"/>
@@ -8422,7 +8400,7 @@
         <v>114</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="Q52" s="54"/>
       <c r="AMJ52"/>
@@ -8438,8 +8416,8 @@
         <v>47</v>
       </c>
       <c r="D53" s="21"/>
-      <c r="E53" s="21" t="s">
-        <v>322</v>
+      <c r="E53" s="92" t="s">
+        <v>631</v>
       </c>
       <c r="F53" s="33" t="s">
         <v>73</v>
@@ -8454,10 +8432,10 @@
         <v>1</v>
       </c>
       <c r="J53" s="34" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="K53" s="34" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="L53" s="34"/>
       <c r="M53" s="34"/>
@@ -8466,7 +8444,7 @@
         <v>73</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="Q53" s="54"/>
       <c r="AMJ53"/>
@@ -8478,8 +8456,8 @@
         <v>48</v>
       </c>
       <c r="D54" s="21"/>
-      <c r="E54" s="21" t="s">
-        <v>322</v>
+      <c r="E54" s="92" t="s">
+        <v>631</v>
       </c>
       <c r="F54" s="33" t="s">
         <v>73</v>
@@ -8498,7 +8476,7 @@
         <v>73</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="Q54" s="54"/>
       <c r="AMJ54"/>
@@ -8510,8 +8488,8 @@
         <v>49</v>
       </c>
       <c r="D55" s="21"/>
-      <c r="E55" s="21" t="s">
-        <v>322</v>
+      <c r="E55" s="92" t="s">
+        <v>631</v>
       </c>
       <c r="F55" s="33" t="s">
         <v>73</v>
@@ -8530,25 +8508,21 @@
         <v>73</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="Q55" s="54"/>
       <c r="AMJ55"/>
     </row>
     <row r="56" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="36">
-        <v>29</v>
+        <v>212</v>
       </c>
       <c r="B56" s="3">
         <v>202</v>
       </c>
-      <c r="C56" s="36">
-        <v>50</v>
-      </c>
+      <c r="C56" s="36"/>
       <c r="D56" s="3"/>
-      <c r="E56" s="3" t="s">
-        <v>326</v>
-      </c>
+      <c r="E56" s="3"/>
       <c r="F56" s="37" t="s">
         <v>115</v>
       </c>
@@ -8556,17 +8530,11 @@
         <v>2</v>
       </c>
       <c r="H56" s="39">
-        <v>2</v>
-      </c>
-      <c r="I56" s="36">
-        <v>1</v>
-      </c>
-      <c r="J56" s="40" t="s">
-        <v>327</v>
-      </c>
-      <c r="K56" s="40" t="s">
-        <v>328</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I56" s="36"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
       <c r="L56" s="40"/>
       <c r="M56" s="40"/>
       <c r="N56" s="40"/>
@@ -8574,161 +8542,171 @@
         <v>115</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="Q56" s="54"/>
       <c r="AMJ56"/>
     </row>
     <row r="57" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="36">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="36">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D57" s="3"/>
-      <c r="E57" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F57" s="59" t="s">
-        <v>117</v>
+      <c r="E57" s="93" t="s">
+        <v>632</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>115</v>
       </c>
       <c r="G57" s="39">
-        <v>29</v>
+        <v>212</v>
       </c>
       <c r="H57" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="36">
         <v>1</v>
       </c>
       <c r="J57" s="40" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="K57" s="40" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="L57" s="40"/>
       <c r="M57" s="40"/>
       <c r="N57" s="40"/>
       <c r="O57" s="1" t="s">
-        <v>333</v>
+        <v>115</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q57" s="57"/>
+        <v>303</v>
+      </c>
+      <c r="Q57" s="54"/>
       <c r="AMJ57"/>
     </row>
     <row r="58" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="36"/>
+      <c r="A58" s="36">
+        <v>30</v>
+      </c>
       <c r="B58" s="3"/>
       <c r="C58" s="36">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="3" t="s">
-        <v>330</v>
+      <c r="E58" s="93" t="s">
+        <v>633</v>
       </c>
       <c r="F58" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="G58" s="39"/>
-      <c r="H58" s="39"/>
+      <c r="G58" s="39">
+        <v>212</v>
+      </c>
+      <c r="H58" s="39">
+        <v>2</v>
+      </c>
       <c r="I58" s="36">
-        <v>2</v>
-      </c>
-      <c r="J58" s="40"/>
-      <c r="K58" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J58" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="K58" s="40" t="s">
+        <v>305</v>
+      </c>
       <c r="L58" s="40"/>
       <c r="M58" s="40"/>
       <c r="N58" s="40"/>
       <c r="O58" s="1" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="Q58" s="57"/>
       <c r="AMJ58"/>
     </row>
     <row r="59" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="50">
+      <c r="A59" s="36"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="36">
+        <v>52</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="93" t="s">
+        <v>633</v>
+      </c>
+      <c r="F59" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="36">
+        <v>2</v>
+      </c>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="40"/>
+      <c r="M59" s="40"/>
+      <c r="N59" s="40"/>
+      <c r="O59" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q59" s="57"/>
+      <c r="AMJ59"/>
+    </row>
+    <row r="60" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="50">
         <v>34</v>
       </c>
-      <c r="B59" s="51">
+      <c r="B60" s="51">
         <v>202</v>
       </c>
-      <c r="C59" s="50">
+      <c r="C60" s="50">
         <v>53</v>
-      </c>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="F59" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="G59" s="50">
-        <v>2</v>
-      </c>
-      <c r="H59" s="50">
-        <v>3</v>
-      </c>
-      <c r="I59" s="50">
-        <v>1</v>
-      </c>
-      <c r="J59" s="52" t="s">
-        <v>336</v>
-      </c>
-      <c r="K59" s="52" t="s">
-        <v>337</v>
-      </c>
-      <c r="L59" s="52"/>
-      <c r="M59" s="52" t="s">
-        <v>338</v>
-      </c>
-      <c r="N59" s="52" t="s">
-        <v>339</v>
-      </c>
-      <c r="O59" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="P59" s="53" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q59" s="54"/>
-      <c r="AMJ59"/>
-    </row>
-    <row r="60" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="50"/>
-      <c r="B60" s="51"/>
-      <c r="C60" s="50">
-        <v>54</v>
       </c>
       <c r="D60" s="51"/>
       <c r="E60" s="51" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="F60" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="G60" s="50"/>
-      <c r="H60" s="50"/>
+      <c r="G60" s="50">
+        <v>2</v>
+      </c>
+      <c r="H60" s="50">
+        <v>3</v>
+      </c>
       <c r="I60" s="50">
-        <v>2</v>
-      </c>
-      <c r="J60" s="52"/>
-      <c r="K60" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="J60" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="K60" s="52" t="s">
+        <v>310</v>
+      </c>
       <c r="L60" s="52"/>
-      <c r="M60" s="52"/>
-      <c r="N60" s="52"/>
+      <c r="M60" s="52" t="s">
+        <v>311</v>
+      </c>
+      <c r="N60" s="52" t="s">
+        <v>312</v>
+      </c>
       <c r="O60" s="53" t="s">
         <v>121</v>
       </c>
       <c r="P60" s="53" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
       <c r="Q60" s="54"/>
       <c r="AMJ60"/>
@@ -8737,11 +8715,11 @@
       <c r="A61" s="50"/>
       <c r="B61" s="51"/>
       <c r="C61" s="50">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D61" s="51"/>
       <c r="E61" s="51" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="F61" s="51" t="s">
         <v>121</v>
@@ -8749,7 +8727,7 @@
       <c r="G61" s="50"/>
       <c r="H61" s="50"/>
       <c r="I61" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J61" s="52"/>
       <c r="K61" s="52"/>
@@ -8760,7 +8738,7 @@
         <v>121</v>
       </c>
       <c r="P61" s="53" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
       <c r="Q61" s="54"/>
       <c r="AMJ61"/>
@@ -8769,170 +8747,168 @@
       <c r="A62" s="50"/>
       <c r="B62" s="51"/>
       <c r="C62" s="50">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D62" s="51"/>
       <c r="E62" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="F62" s="51"/>
+        <v>308</v>
+      </c>
+      <c r="F62" s="51" t="s">
+        <v>121</v>
+      </c>
       <c r="G62" s="50"/>
       <c r="H62" s="50"/>
       <c r="I62" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" s="52"/>
-      <c r="K62" s="52" t="s">
-        <v>341</v>
-      </c>
+      <c r="K62" s="52"/>
       <c r="L62" s="52"/>
-      <c r="M62" s="52" t="s">
-        <v>342</v>
-      </c>
+      <c r="M62" s="52"/>
       <c r="N62" s="52"/>
       <c r="O62" s="53" t="s">
-        <v>343</v>
+        <v>121</v>
       </c>
       <c r="P62" s="53" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="Q62" s="54"/>
       <c r="AMJ62"/>
     </row>
-    <row r="63" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="50"/>
       <c r="B63" s="51"/>
       <c r="C63" s="50">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D63" s="51"/>
       <c r="E63" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="F63" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="G63" s="50">
-        <v>34</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="F63" s="51"/>
+      <c r="G63" s="50"/>
       <c r="H63" s="50"/>
       <c r="I63" s="50">
         <v>1</v>
       </c>
-      <c r="J63" s="52" t="s">
-        <v>345</v>
-      </c>
+      <c r="J63" s="52"/>
       <c r="K63" s="52" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="L63" s="52"/>
-      <c r="M63" s="52"/>
+      <c r="M63" s="52" t="s">
+        <v>315</v>
+      </c>
       <c r="N63" s="52"/>
       <c r="O63" s="53" t="s">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="P63" s="53" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q63" s="57"/>
+        <v>317</v>
+      </c>
+      <c r="Q63" s="54"/>
       <c r="AMJ63"/>
     </row>
-    <row r="64" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="28">
-        <v>31</v>
-      </c>
-      <c r="B64" s="21" t="s">
-        <v>652</v>
-      </c>
-      <c r="C64" s="28"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="60" t="s">
-        <v>349</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G64" s="43">
-        <v>2</v>
-      </c>
-      <c r="H64" s="43">
-        <v>2</v>
-      </c>
-      <c r="I64" s="28"/>
-      <c r="J64" s="34"/>
-      <c r="K64" s="34"/>
-      <c r="L64" s="34"/>
-      <c r="M64" s="34"/>
-      <c r="N64" s="34"/>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q64" s="54"/>
+    <row r="64" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="50"/>
+      <c r="B64" s="51"/>
+      <c r="C64" s="50">
+        <v>57</v>
+      </c>
+      <c r="D64" s="51"/>
+      <c r="E64" s="51" t="s">
+        <v>308</v>
+      </c>
+      <c r="F64" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="G64" s="50">
+        <v>34</v>
+      </c>
+      <c r="H64" s="50"/>
+      <c r="I64" s="50">
+        <v>1</v>
+      </c>
+      <c r="J64" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="K64" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="L64" s="52"/>
+      <c r="M64" s="52"/>
+      <c r="N64" s="52"/>
+      <c r="O64" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="P64" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q64" s="57"/>
       <c r="AMJ64"/>
     </row>
     <row r="65" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="28">
-        <v>32</v>
-      </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="28">
-        <v>58</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B65" s="92" t="s">
+        <v>634</v>
+      </c>
+      <c r="C65" s="28"/>
       <c r="D65" s="21"/>
-      <c r="E65" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="F65" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="G65" s="28">
-        <v>31</v>
-      </c>
-      <c r="H65" s="28">
+      <c r="E65" s="60"/>
+      <c r="F65" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G65" s="43">
         <v>2</v>
       </c>
-      <c r="I65" s="28">
-        <v>1</v>
-      </c>
-      <c r="J65" s="34" t="s">
-        <v>352</v>
-      </c>
-      <c r="K65" s="34" t="s">
-        <v>353</v>
-      </c>
+      <c r="H65" s="43">
+        <v>2</v>
+      </c>
+      <c r="I65" s="28"/>
+      <c r="J65" s="34"/>
+      <c r="K65" s="34"/>
       <c r="L65" s="34"/>
       <c r="M65" s="34"/>
       <c r="N65" s="34"/>
-      <c r="O65" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" s="2" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="Q65" s="54"/>
       <c r="AMJ65"/>
     </row>
     <row r="66" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="28"/>
+      <c r="A66" s="28">
+        <v>32</v>
+      </c>
       <c r="B66" s="21"/>
       <c r="C66" s="28">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D66" s="21"/>
       <c r="E66" s="21" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="F66" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
+      <c r="G66" s="28">
+        <v>31</v>
+      </c>
+      <c r="H66" s="28">
+        <v>2</v>
+      </c>
       <c r="I66" s="28">
-        <v>2</v>
-      </c>
-      <c r="J66" s="34"/>
-      <c r="K66" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J66" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="K66" s="34" t="s">
+        <v>326</v>
+      </c>
       <c r="L66" s="34"/>
       <c r="M66" s="34"/>
       <c r="N66" s="34"/>
@@ -8940,199 +8916,197 @@
         <v>118</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="Q66" s="54"/>
       <c r="AMJ66"/>
     </row>
-    <row r="67" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="28"/>
       <c r="B67" s="21"/>
       <c r="C67" s="28">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D67" s="21"/>
-      <c r="E67" s="60" t="s">
-        <v>349</v>
+      <c r="E67" s="21" t="s">
+        <v>324</v>
       </c>
       <c r="F67" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="G67" s="28">
-        <v>31</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="G67" s="28"/>
       <c r="H67" s="28"/>
       <c r="I67" s="28">
-        <v>1</v>
-      </c>
-      <c r="J67" s="34" t="s">
-        <v>355</v>
-      </c>
-      <c r="K67" s="34" t="s">
-        <v>356</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J67" s="34"/>
+      <c r="K67" s="34"/>
       <c r="L67" s="34"/>
       <c r="M67" s="34"/>
       <c r="N67" s="34"/>
       <c r="O67" s="2" t="s">
-        <v>357</v>
+        <v>118</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="Q67" s="57"/>
+        <v>327</v>
+      </c>
+      <c r="Q67" s="54"/>
       <c r="AMJ67"/>
     </row>
-    <row r="68" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="28">
-        <v>33</v>
-      </c>
-      <c r="B68" s="21">
-        <v>32</v>
-      </c>
+    <row r="68" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="28"/>
+      <c r="B68" s="21"/>
       <c r="C68" s="28">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D68" s="21"/>
-      <c r="E68" s="21" t="s">
-        <v>359</v>
+      <c r="E68" s="60" t="s">
+        <v>322</v>
       </c>
       <c r="F68" s="33" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G68" s="28">
         <v>31</v>
       </c>
-      <c r="H68" s="28">
-        <v>1</v>
-      </c>
+      <c r="H68" s="28"/>
       <c r="I68" s="28">
         <v>1</v>
       </c>
       <c r="J68" s="34" t="s">
-        <v>360</v>
-      </c>
-      <c r="K68" s="34"/>
+        <v>328</v>
+      </c>
+      <c r="K68" s="34" t="s">
+        <v>329</v>
+      </c>
       <c r="L68" s="34"/>
       <c r="M68" s="34"/>
       <c r="N68" s="34"/>
       <c r="O68" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q68" s="57"/>
+      <c r="AMJ68"/>
+    </row>
+    <row r="69" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" s="28">
+        <v>33</v>
+      </c>
+      <c r="B69" s="21">
+        <v>32</v>
+      </c>
+      <c r="C69" s="28">
+        <v>61</v>
+      </c>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F69" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="P68" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q68" s="54"/>
-      <c r="AMJ68"/>
-    </row>
-    <row r="69" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" s="36">
-        <v>35</v>
-      </c>
-      <c r="B69" s="3">
+      <c r="G69" s="28">
         <v>31</v>
       </c>
-      <c r="C69" s="36">
-        <v>62</v>
-      </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G69" s="36">
-        <v>2</v>
-      </c>
-      <c r="H69" s="36">
-        <v>3</v>
-      </c>
-      <c r="I69" s="36"/>
-      <c r="J69" s="40"/>
-      <c r="K69" s="40"/>
-      <c r="L69" s="40"/>
-      <c r="M69" s="40"/>
-      <c r="N69" s="40"/>
-      <c r="O69" s="1"/>
+      <c r="H69" s="28">
+        <v>1</v>
+      </c>
+      <c r="I69" s="28">
+        <v>1</v>
+      </c>
+      <c r="J69" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="K69" s="34"/>
+      <c r="L69" s="34"/>
+      <c r="M69" s="34"/>
+      <c r="N69" s="34"/>
+      <c r="O69" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="P69" s="2" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="Q69" s="54"/>
       <c r="AMJ69"/>
     </row>
-    <row r="70" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="36">
-        <v>36</v>
-      </c>
-      <c r="B70" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="B70" s="3">
+        <v>31</v>
+      </c>
       <c r="C70" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D70" s="3"/>
-      <c r="E70" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="F70" s="41" t="s">
-        <v>123</v>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="G70" s="36">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H70" s="36">
         <v>3</v>
       </c>
-      <c r="I70" s="36">
-        <v>1</v>
-      </c>
-      <c r="J70" s="40" t="s">
-        <v>365</v>
-      </c>
-      <c r="K70" s="40" t="s">
-        <v>366</v>
-      </c>
+      <c r="I70" s="36"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="40"/>
       <c r="L70" s="40"/>
-      <c r="M70" s="40" t="s">
-        <v>367</v>
-      </c>
+      <c r="M70" s="40"/>
       <c r="N70" s="40"/>
-      <c r="O70" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q70" s="57"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q70" s="54"/>
       <c r="AMJ70"/>
     </row>
     <row r="71" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="36"/>
+      <c r="A71" s="36">
+        <v>36</v>
+      </c>
       <c r="B71" s="3"/>
       <c r="C71" s="36">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="3" t="s">
-        <v>364</v>
+      <c r="E71" s="93" t="s">
+        <v>336</v>
       </c>
       <c r="F71" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
+      <c r="G71" s="36">
+        <v>35</v>
+      </c>
+      <c r="H71" s="36">
+        <v>3</v>
+      </c>
       <c r="I71" s="36">
-        <v>2</v>
-      </c>
-      <c r="J71" s="40"/>
-      <c r="K71" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J71" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="K71" s="40" t="s">
+        <v>338</v>
+      </c>
       <c r="L71" s="40"/>
-      <c r="M71" s="40"/>
+      <c r="M71" s="40" t="s">
+        <v>339</v>
+      </c>
       <c r="N71" s="40"/>
       <c r="O71" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="Q71" s="57"/>
       <c r="AMJ71"/>
@@ -9141,11 +9115,11 @@
       <c r="A72" s="36"/>
       <c r="B72" s="3"/>
       <c r="C72" s="36">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="F72" s="41" t="s">
         <v>123</v>
@@ -9153,7 +9127,7 @@
       <c r="G72" s="36"/>
       <c r="H72" s="36"/>
       <c r="I72" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J72" s="40"/>
       <c r="K72" s="40"/>
@@ -9164,70 +9138,70 @@
         <v>123</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="Q72" s="57"/>
       <c r="AMJ72"/>
     </row>
     <row r="73" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="36">
-        <v>37</v>
-      </c>
+      <c r="A73" s="36"/>
       <c r="B73" s="3"/>
       <c r="C73" s="36">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="3" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="F73" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="G73" s="36">
-        <v>35</v>
-      </c>
-      <c r="H73" s="36">
-        <v>2</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
       <c r="I73" s="36">
-        <v>1</v>
-      </c>
-      <c r="J73" s="40" t="s">
-        <v>369</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J73" s="40"/>
       <c r="K73" s="40"/>
       <c r="L73" s="40"/>
       <c r="M73" s="40"/>
       <c r="N73" s="40"/>
       <c r="O73" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="P73" s="2" t="s">
-        <v>370</v>
+        <v>123</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="Q73" s="57"/>
       <c r="AMJ73"/>
     </row>
     <row r="74" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="36"/>
+      <c r="A74" s="36">
+        <v>37</v>
+      </c>
       <c r="B74" s="3"/>
       <c r="C74" s="36">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D74" s="3"/>
-      <c r="E74" s="3" t="s">
-        <v>364</v>
+      <c r="E74" s="93" t="s">
+        <v>343</v>
       </c>
       <c r="F74" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="G74" s="36"/>
-      <c r="H74" s="36"/>
+      <c r="G74" s="36">
+        <v>35</v>
+      </c>
+      <c r="H74" s="36">
+        <v>1</v>
+      </c>
       <c r="I74" s="36">
-        <v>2</v>
-      </c>
-      <c r="J74" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J74" s="40" t="s">
+        <v>341</v>
+      </c>
       <c r="K74" s="40"/>
       <c r="L74" s="40"/>
       <c r="M74" s="40"/>
@@ -9236,7 +9210,7 @@
         <v>124</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="Q74" s="57"/>
       <c r="AMJ74"/>
@@ -9249,7 +9223,7 @@
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="F75" s="41"/>
       <c r="G75" s="36"/>
@@ -9258,17 +9232,17 @@
         <v>1</v>
       </c>
       <c r="J75" s="40" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="K75" s="40"/>
       <c r="L75" s="40"/>
       <c r="M75" s="40"/>
       <c r="N75" s="40"/>
       <c r="O75" s="1" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="Q75" s="57"/>
       <c r="AMJ75"/>
@@ -9281,7 +9255,7 @@
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="F76" s="41"/>
       <c r="G76" s="36"/>
@@ -9290,17 +9264,17 @@
         <v>1</v>
       </c>
       <c r="J76" s="40" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="K76" s="40"/>
       <c r="L76" s="40"/>
       <c r="M76" s="40"/>
       <c r="N76" s="40"/>
       <c r="O76" s="1" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="Q76" s="57"/>
       <c r="AMJ76"/>
@@ -9313,7 +9287,7 @@
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="F77" s="41"/>
       <c r="G77" s="36"/>
@@ -9322,17 +9296,17 @@
         <v>1</v>
       </c>
       <c r="J77" s="40" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="K77" s="40"/>
       <c r="L77" s="40"/>
       <c r="M77" s="40"/>
       <c r="N77" s="40"/>
       <c r="O77" s="1" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="Q77" s="54"/>
       <c r="AMJ77"/>
@@ -9347,7 +9321,7 @@
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
       <c r="F78" s="41" t="s">
         <v>125</v>
@@ -9362,21 +9336,21 @@
         <v>1</v>
       </c>
       <c r="J78" s="40" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="K78" s="40" t="s">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="L78" s="40"/>
       <c r="M78" s="40" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="N78" s="40"/>
       <c r="O78" s="1" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="Q78" s="57"/>
       <c r="AMJ78"/>
@@ -9389,7 +9363,7 @@
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
       <c r="F79" s="41" t="s">
         <v>125</v>
@@ -9405,10 +9379,10 @@
       <c r="M79" s="40"/>
       <c r="N79" s="40"/>
       <c r="O79" s="1" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="Q79" s="57"/>
       <c r="AMJ79"/>
@@ -9422,11 +9396,9 @@
       </c>
       <c r="C80" s="61"/>
       <c r="D80" s="62"/>
-      <c r="E80" s="62">
-        <v>43</v>
-      </c>
+      <c r="E80" s="62"/>
       <c r="F80" s="4" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="G80" s="25">
         <v>1</v>
@@ -9454,7 +9426,7 @@
       </c>
       <c r="D81" s="21"/>
       <c r="E81" s="21" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="F81" s="19" t="s">
         <v>130</v>
@@ -9463,13 +9435,13 @@
         <v>43</v>
       </c>
       <c r="H81" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81" s="28">
         <v>1</v>
       </c>
       <c r="J81" s="34" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="K81" s="34"/>
       <c r="L81" s="34"/>
@@ -9477,7 +9449,7 @@
       <c r="N81" s="34"/>
       <c r="O81" s="2"/>
       <c r="P81" s="2" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="Q81" s="42"/>
     </row>
@@ -9491,7 +9463,7 @@
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3" t="s">
-        <v>389</v>
+        <v>361</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>132</v>
@@ -9500,13 +9472,13 @@
         <v>43</v>
       </c>
       <c r="H82" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I82" s="36">
         <v>1</v>
       </c>
       <c r="J82" s="40" t="s">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="40"/>
@@ -9514,32 +9486,30 @@
       <c r="N82" s="40"/>
       <c r="O82" s="1"/>
       <c r="P82" s="1" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="Q82" s="42"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="28">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="B83" s="21">
         <v>56</v>
       </c>
       <c r="C83" s="28"/>
       <c r="D83" s="21"/>
-      <c r="E83" s="21" t="s">
-        <v>392</v>
-      </c>
+      <c r="E83" s="21"/>
       <c r="F83" s="21" t="s">
         <v>92</v>
       </c>
       <c r="G83" s="28">
         <v>43</v>
       </c>
-      <c r="H83" s="28"/>
-      <c r="I83" s="28">
-        <v>1</v>
-      </c>
+      <c r="H83" s="28">
+        <v>3</v>
+      </c>
+      <c r="I83" s="28"/>
       <c r="J83" s="34"/>
       <c r="K83" s="34"/>
       <c r="L83" s="34"/>
@@ -9547,34 +9517,36 @@
       <c r="N83" s="34"/>
       <c r="O83" s="2"/>
       <c r="P83" s="2" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="Q83" s="42"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="28">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="B84" s="21"/>
       <c r="C84" s="28">
         <v>75</v>
       </c>
       <c r="D84" s="21"/>
-      <c r="E84" s="21" t="s">
-        <v>655</v>
+      <c r="E84" s="92" t="s">
+        <v>635</v>
       </c>
       <c r="F84" s="21" t="s">
         <v>92</v>
       </c>
       <c r="G84" s="28">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="H84" s="28">
-        <v>3</v>
-      </c>
-      <c r="I84" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="I84" s="28">
+        <v>1</v>
+      </c>
       <c r="J84" s="34" t="s">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="K84" s="34"/>
       <c r="L84" s="34"/>
@@ -9582,7 +9554,7 @@
       <c r="N84" s="34"/>
       <c r="O84" s="2"/>
       <c r="P84" s="2" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="Q84" s="42"/>
     </row>
@@ -9591,29 +9563,29 @@
         <v>47</v>
       </c>
       <c r="B85" s="21">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="C85" s="28">
         <v>76</v>
       </c>
       <c r="D85" s="21"/>
-      <c r="E85" s="21" t="s">
-        <v>395</v>
+      <c r="E85" s="92" t="s">
+        <v>636</v>
       </c>
       <c r="F85" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G85" s="28">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="H85" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" s="28">
         <v>1</v>
       </c>
       <c r="J85" s="34" t="s">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="K85" s="34"/>
       <c r="L85" s="34"/>
@@ -9621,7 +9593,7 @@
       <c r="N85" s="34"/>
       <c r="O85" s="2"/>
       <c r="P85" s="2" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="Q85" s="42"/>
     </row>
@@ -9636,23 +9608,23 @@
         <v>77</v>
       </c>
       <c r="D86" s="21"/>
-      <c r="E86" s="21" t="s">
-        <v>398</v>
+      <c r="E86" s="92" t="s">
+        <v>637</v>
       </c>
       <c r="F86" s="33" t="s">
         <v>134</v>
       </c>
       <c r="G86" s="28">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="H86" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="28">
         <v>1</v>
       </c>
       <c r="J86" s="34" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="K86" s="34"/>
       <c r="L86" s="34"/>
@@ -9660,7 +9632,7 @@
       <c r="N86" s="34"/>
       <c r="O86" s="2"/>
       <c r="P86" s="2" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="Q86" s="42"/>
     </row>
@@ -9669,29 +9641,29 @@
         <v>49</v>
       </c>
       <c r="B87" s="21">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="C87" s="28">
         <v>78</v>
       </c>
       <c r="D87" s="21"/>
-      <c r="E87" s="21" t="s">
-        <v>401</v>
+      <c r="E87" s="92" t="s">
+        <v>638</v>
       </c>
       <c r="F87" s="33" t="s">
         <v>135</v>
       </c>
       <c r="G87" s="28">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="H87" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I87" s="28">
         <v>1</v>
       </c>
       <c r="J87" s="34" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="K87" s="34"/>
       <c r="L87" s="34"/>
@@ -9699,7 +9671,7 @@
       <c r="N87" s="34"/>
       <c r="O87" s="2"/>
       <c r="P87" s="2" t="s">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="Q87" s="42"/>
     </row>
@@ -9708,29 +9680,29 @@
         <v>50</v>
       </c>
       <c r="B88" s="21">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="C88" s="28">
         <v>79</v>
       </c>
       <c r="D88" s="21"/>
-      <c r="E88" s="21" t="s">
-        <v>404</v>
+      <c r="E88" s="92" t="s">
+        <v>639</v>
       </c>
       <c r="F88" s="33" t="s">
         <v>97</v>
       </c>
       <c r="G88" s="28">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="H88" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88" s="28">
         <v>1</v>
       </c>
       <c r="J88" s="34" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="K88" s="34"/>
       <c r="L88" s="34"/>
@@ -9738,137 +9710,153 @@
       <c r="N88" s="34"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2" t="s">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="Q88" s="42"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="28">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B89" s="21">
-        <v>69</v>
-      </c>
-      <c r="C89" s="28"/>
+        <v>46</v>
+      </c>
+      <c r="C89" s="28">
+        <v>85</v>
+      </c>
       <c r="D89" s="21"/>
-      <c r="E89" s="21" t="s">
-        <v>407</v>
+      <c r="E89" s="92" t="s">
+        <v>652</v>
       </c>
       <c r="F89" s="33" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="G89" s="28">
-        <v>68</v>
-      </c>
-      <c r="H89" s="28"/>
+        <v>204</v>
+      </c>
+      <c r="H89" s="28">
+        <v>1</v>
+      </c>
       <c r="I89" s="28">
         <v>1</v>
       </c>
-      <c r="J89" s="82"/>
-      <c r="K89" s="82"/>
-      <c r="L89" s="82"/>
-      <c r="M89" s="82"/>
+      <c r="J89" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="K89" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="L89" s="34"/>
+      <c r="M89" s="34"/>
       <c r="N89" s="34"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q89" s="42"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+        <v>384</v>
+      </c>
+      <c r="Q89" s="35"/>
+    </row>
+    <row r="90" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="28">
-        <v>203</v>
-      </c>
-      <c r="B90" s="21"/>
+        <v>55</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>597</v>
+      </c>
       <c r="C90" s="28">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D90" s="21"/>
-      <c r="E90" s="21" t="s">
-        <v>654</v>
+      <c r="E90" s="92" t="s">
+        <v>653</v>
       </c>
       <c r="F90" s="33" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="G90" s="28">
-        <v>51</v>
+        <v>204</v>
       </c>
       <c r="H90" s="28">
-        <v>3</v>
-      </c>
-      <c r="I90" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="I90" s="28">
+        <v>1</v>
+      </c>
       <c r="J90" s="34" t="s">
-        <v>408</v>
-      </c>
-      <c r="K90" s="34"/>
+        <v>385</v>
+      </c>
+      <c r="K90" s="34" t="s">
+        <v>386</v>
+      </c>
       <c r="L90" s="34"/>
-      <c r="M90" s="34" t="s">
-        <v>409</v>
-      </c>
+      <c r="M90" s="34"/>
       <c r="N90" s="34"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q90" s="42"/>
+        <v>387</v>
+      </c>
+      <c r="Q90" s="35"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A91" s="28">
-        <v>52</v>
-      </c>
-      <c r="B91" s="21">
-        <v>203</v>
-      </c>
-      <c r="C91" s="28">
-        <v>81</v>
-      </c>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="F91" s="46" t="s">
-        <v>412</v>
-      </c>
-      <c r="G91" s="28">
-        <v>51</v>
-      </c>
-      <c r="H91" s="28">
-        <v>3</v>
-      </c>
-      <c r="I91" s="28">
-        <v>1</v>
-      </c>
-      <c r="J91" s="34" t="s">
-        <v>413</v>
-      </c>
-      <c r="K91" s="34"/>
-      <c r="L91" s="34"/>
-      <c r="M91" s="34"/>
-      <c r="N91" s="34"/>
-      <c r="O91" s="2"/>
-      <c r="P91" s="2" t="s">
-        <v>414</v>
+      <c r="A91" s="36">
+        <v>56</v>
+      </c>
+      <c r="B91" s="3">
+        <v>45</v>
+      </c>
+      <c r="C91" s="36">
+        <v>87</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G91" s="36">
+        <v>43</v>
+      </c>
+      <c r="H91" s="64">
+        <v>1</v>
+      </c>
+      <c r="I91" s="36">
+        <v>1</v>
+      </c>
+      <c r="J91" s="40" t="s">
+        <v>389</v>
+      </c>
+      <c r="K91" s="40" t="s">
+        <v>390</v>
+      </c>
+      <c r="L91" s="40"/>
+      <c r="M91" s="40"/>
+      <c r="N91" s="40"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="Q91" s="42"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A92" s="28"/>
-      <c r="B92" s="21"/>
-      <c r="C92" s="28">
-        <v>82</v>
-      </c>
+    <row r="92" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A92" s="28">
+        <v>57</v>
+      </c>
+      <c r="B92" s="21">
+        <v>204</v>
+      </c>
+      <c r="C92" s="28"/>
       <c r="D92" s="21"/>
-      <c r="E92" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="F92" s="46" t="s">
-        <v>412</v>
-      </c>
-      <c r="G92" s="28"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="28">
-        <v>2</v>
-      </c>
+      <c r="E92" s="21"/>
+      <c r="F92" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="G92" s="28">
+        <v>43</v>
+      </c>
+      <c r="H92" s="28">
+        <v>1</v>
+      </c>
+      <c r="I92" s="28"/>
       <c r="J92" s="34"/>
       <c r="K92" s="34"/>
       <c r="L92" s="34"/>
@@ -9876,138 +9864,150 @@
       <c r="N92" s="34"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q92" s="42"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A93" s="28"/>
+        <v>392</v>
+      </c>
+      <c r="Q92" s="35"/>
+    </row>
+    <row r="93" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A93" s="28">
+        <v>58</v>
+      </c>
       <c r="B93" s="21"/>
       <c r="C93" s="28">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D93" s="21"/>
       <c r="E93" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="F93" s="46" t="s">
-        <v>412</v>
-      </c>
-      <c r="G93" s="28"/>
-      <c r="H93" s="28"/>
+        <v>393</v>
+      </c>
+      <c r="F93" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="G93" s="28">
+        <v>57</v>
+      </c>
+      <c r="H93" s="28">
+        <v>1</v>
+      </c>
       <c r="I93" s="28">
-        <v>3</v>
-      </c>
-      <c r="J93" s="34"/>
-      <c r="K93" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J93" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="K93" s="34" t="s">
+        <v>395</v>
+      </c>
       <c r="L93" s="34"/>
       <c r="M93" s="34"/>
       <c r="N93" s="34"/>
       <c r="O93" s="2"/>
       <c r="P93" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q93" s="42"/>
+        <v>396</v>
+      </c>
+      <c r="Q93" s="35"/>
     </row>
     <row r="94" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="28">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B94" s="21">
-        <v>203</v>
+        <v>58</v>
       </c>
       <c r="C94" s="28">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D94" s="21"/>
       <c r="E94" s="21" t="s">
-        <v>415</v>
-      </c>
-      <c r="F94" s="46" t="s">
-        <v>160</v>
+        <v>397</v>
+      </c>
+      <c r="F94" s="33" t="s">
+        <v>5</v>
       </c>
       <c r="G94" s="28">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H94" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I94" s="28">
         <v>1</v>
       </c>
       <c r="J94" s="34" t="s">
-        <v>416</v>
-      </c>
-      <c r="K94" s="34"/>
+        <v>398</v>
+      </c>
+      <c r="K94" s="34" t="s">
+        <v>399</v>
+      </c>
       <c r="L94" s="34"/>
       <c r="M94" s="34"/>
       <c r="N94" s="34"/>
       <c r="O94" s="2"/>
       <c r="P94" s="2" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="Q94" s="35"/>
     </row>
     <row r="95" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="28">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B95" s="21">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="C95" s="28">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D95" s="21"/>
       <c r="E95" s="21" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="F95" s="33" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G95" s="28">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H95" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I95" s="28">
         <v>1</v>
       </c>
       <c r="J95" s="34" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="K95" s="34" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="L95" s="34"/>
       <c r="M95" s="34"/>
       <c r="N95" s="34"/>
       <c r="O95" s="2"/>
       <c r="P95" s="2" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="28">
-        <v>55</v>
-      </c>
-      <c r="B96" s="21" t="s">
-        <v>659</v>
+        <v>61</v>
+      </c>
+      <c r="B96" s="21">
+        <v>60</v>
       </c>
       <c r="C96" s="28">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D96" s="21"/>
       <c r="E96" s="21" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="F96" s="33" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G96" s="28">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H96" s="28">
         <v>1</v>
@@ -10016,730 +10016,688 @@
         <v>1</v>
       </c>
       <c r="J96" s="34" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="K96" s="34" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="L96" s="34"/>
       <c r="M96" s="34"/>
       <c r="N96" s="34"/>
       <c r="O96" s="2"/>
       <c r="P96" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q96" s="35"/>
+        <v>408</v>
+      </c>
+      <c r="Q96" s="42"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A97" s="36">
-        <v>56</v>
-      </c>
-      <c r="B97" s="3">
-        <v>45</v>
-      </c>
-      <c r="C97" s="36">
-        <v>87</v>
-      </c>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G97" s="36">
+      <c r="A97" s="28">
+        <v>205</v>
+      </c>
+      <c r="B97" s="21">
+        <v>61</v>
+      </c>
+      <c r="C97" s="28">
+        <v>92</v>
+      </c>
+      <c r="D97" s="21"/>
+      <c r="E97" s="92" t="s">
+        <v>641</v>
+      </c>
+      <c r="F97" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="G97" s="28">
+        <v>57</v>
+      </c>
+      <c r="H97" s="28">
+        <v>1</v>
+      </c>
+      <c r="I97" s="28">
+        <v>1</v>
+      </c>
+      <c r="J97" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="K97" s="34"/>
+      <c r="L97" s="34"/>
+      <c r="M97" s="34"/>
+      <c r="N97" s="34"/>
+      <c r="O97" s="2"/>
+      <c r="P97" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q97" s="42"/>
+    </row>
+    <row r="98" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A98" s="36">
+        <v>62</v>
+      </c>
+      <c r="B98" s="3">
+        <v>57</v>
+      </c>
+      <c r="C98" s="36"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G98" s="36">
         <v>43</v>
       </c>
-      <c r="H97" s="64">
+      <c r="H98" s="36">
+        <v>3</v>
+      </c>
+      <c r="I98" s="36"/>
+      <c r="J98" s="40"/>
+      <c r="K98" s="40"/>
+      <c r="L98" s="40"/>
+      <c r="M98" s="40"/>
+      <c r="N98" s="40"/>
+      <c r="O98" s="1"/>
+      <c r="P98" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q98" s="35"/>
+    </row>
+    <row r="99" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A99" s="36">
+        <v>63</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="36">
+        <v>93</v>
+      </c>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F99" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="G99" s="36">
+        <v>62</v>
+      </c>
+      <c r="H99" s="36">
+        <v>3</v>
+      </c>
+      <c r="I99" s="36">
+        <v>1</v>
+      </c>
+      <c r="J99" s="40" t="s">
+        <v>413</v>
+      </c>
+      <c r="K99" s="40" t="s">
+        <v>414</v>
+      </c>
+      <c r="L99" s="40"/>
+      <c r="M99" s="40"/>
+      <c r="N99" s="40"/>
+      <c r="O99" s="1"/>
+      <c r="P99" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q99" s="35"/>
+    </row>
+    <row r="100" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A100" s="36"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="36">
+        <v>94</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F100" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="G100" s="36"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36">
         <v>2</v>
       </c>
-      <c r="I97" s="36">
-        <v>1</v>
-      </c>
-      <c r="J97" s="40" t="s">
-        <v>427</v>
-      </c>
-      <c r="K97" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="L97" s="40"/>
-      <c r="M97" s="40"/>
-      <c r="N97" s="40"/>
-      <c r="O97" s="1"/>
-      <c r="P97" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q97" s="42"/>
-    </row>
-    <row r="98" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A98" s="28">
-        <v>57</v>
-      </c>
-      <c r="B98" s="21">
-        <v>46</v>
-      </c>
-      <c r="C98" s="28"/>
-      <c r="D98" s="21"/>
-      <c r="E98" s="21" t="s">
-        <v>430</v>
-      </c>
-      <c r="F98" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="G98" s="28">
-        <v>43</v>
-      </c>
-      <c r="H98" s="28">
+      <c r="J100" s="40"/>
+      <c r="K100" s="40"/>
+      <c r="L100" s="40"/>
+      <c r="M100" s="40"/>
+      <c r="N100" s="40"/>
+      <c r="O100" s="1"/>
+      <c r="P100" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q100" s="35"/>
+    </row>
+    <row r="101" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A101" s="36"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="36">
+        <v>95</v>
+      </c>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F101" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="G101" s="36"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36">
+        <v>3</v>
+      </c>
+      <c r="J101" s="40"/>
+      <c r="K101" s="40"/>
+      <c r="L101" s="40"/>
+      <c r="M101" s="40"/>
+      <c r="N101" s="40"/>
+      <c r="O101" s="1"/>
+      <c r="P101" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q101" s="35"/>
+    </row>
+    <row r="102" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A102" s="36">
+        <v>64</v>
+      </c>
+      <c r="B102" s="3">
+        <v>63</v>
+      </c>
+      <c r="C102" s="36">
+        <v>96</v>
+      </c>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="F102" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="G102" s="36">
+        <v>62</v>
+      </c>
+      <c r="H102" s="36">
         <v>2</v>
       </c>
-      <c r="I98" s="28"/>
-      <c r="J98" s="34"/>
-      <c r="K98" s="34"/>
-      <c r="L98" s="34"/>
-      <c r="M98" s="34"/>
-      <c r="N98" s="34"/>
-      <c r="O98" s="2"/>
-      <c r="P98" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q98" s="35"/>
-    </row>
-    <row r="99" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A99" s="28">
-        <v>58</v>
-      </c>
-      <c r="B99" s="21"/>
-      <c r="C99" s="28">
-        <v>88</v>
-      </c>
-      <c r="D99" s="21"/>
-      <c r="E99" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="F99" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="G99" s="28">
-        <v>57</v>
-      </c>
-      <c r="H99" s="28">
+      <c r="I102" s="36">
+        <v>1</v>
+      </c>
+      <c r="J102" s="40" t="s">
+        <v>417</v>
+      </c>
+      <c r="K102" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="L102" s="40"/>
+      <c r="M102" s="40"/>
+      <c r="N102" s="40"/>
+      <c r="O102" s="1"/>
+      <c r="P102" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q102" s="35"/>
+    </row>
+    <row r="103" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A103" s="36"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="36">
+        <v>97</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="F103" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="G103" s="36"/>
+      <c r="H103" s="36"/>
+      <c r="I103" s="36">
         <v>2</v>
       </c>
-      <c r="I99" s="28">
-        <v>1</v>
-      </c>
-      <c r="J99" s="34" t="s">
-        <v>433</v>
-      </c>
-      <c r="K99" s="34" t="s">
-        <v>434</v>
-      </c>
-      <c r="L99" s="34"/>
-      <c r="M99" s="34"/>
-      <c r="N99" s="34"/>
-      <c r="O99" s="2"/>
-      <c r="P99" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q99" s="35"/>
-    </row>
-    <row r="100" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A100" s="28">
-        <v>59</v>
-      </c>
-      <c r="B100" s="21">
-        <v>58</v>
-      </c>
-      <c r="C100" s="28">
-        <v>89</v>
-      </c>
-      <c r="D100" s="21"/>
-      <c r="E100" s="21" t="s">
-        <v>436</v>
-      </c>
-      <c r="F100" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="28">
-        <v>57</v>
-      </c>
-      <c r="H100" s="28">
-        <v>2</v>
-      </c>
-      <c r="I100" s="28">
-        <v>1</v>
-      </c>
-      <c r="J100" s="34" t="s">
-        <v>437</v>
-      </c>
-      <c r="K100" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="L100" s="34"/>
-      <c r="M100" s="34"/>
-      <c r="N100" s="34"/>
-      <c r="O100" s="2"/>
-      <c r="P100" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q100" s="35"/>
-    </row>
-    <row r="101" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A101" s="28">
-        <v>60</v>
-      </c>
-      <c r="B101" s="21">
-        <v>59</v>
-      </c>
-      <c r="C101" s="28">
-        <v>90</v>
-      </c>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="F101" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G101" s="28">
-        <v>57</v>
-      </c>
-      <c r="H101" s="28">
-        <v>2</v>
-      </c>
-      <c r="I101" s="28">
-        <v>1</v>
-      </c>
-      <c r="J101" s="34" t="s">
-        <v>441</v>
-      </c>
-      <c r="K101" s="34" t="s">
-        <v>442</v>
-      </c>
-      <c r="L101" s="34"/>
-      <c r="M101" s="34"/>
-      <c r="N101" s="34"/>
-      <c r="O101" s="2"/>
-      <c r="P101" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q101" s="35"/>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A102" s="28">
-        <v>61</v>
-      </c>
-      <c r="B102" s="21">
-        <v>60</v>
-      </c>
-      <c r="C102" s="28">
-        <v>91</v>
-      </c>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21" t="s">
-        <v>444</v>
-      </c>
-      <c r="F102" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="G102" s="28">
-        <v>57</v>
-      </c>
-      <c r="H102" s="28">
-        <v>2</v>
-      </c>
-      <c r="I102" s="28">
-        <v>1</v>
-      </c>
-      <c r="J102" s="34" t="s">
-        <v>445</v>
-      </c>
-      <c r="K102" s="34" t="s">
-        <v>446</v>
-      </c>
-      <c r="L102" s="34"/>
-      <c r="M102" s="34"/>
-      <c r="N102" s="34"/>
-      <c r="O102" s="2"/>
-      <c r="P102" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q102" s="42"/>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A103" s="28">
-        <v>205</v>
-      </c>
-      <c r="B103" s="21">
-        <v>61</v>
-      </c>
-      <c r="C103" s="28">
-        <v>92</v>
-      </c>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21" t="s">
-        <v>430</v>
-      </c>
-      <c r="F103" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="G103" s="28">
-        <v>57</v>
-      </c>
-      <c r="H103" s="28">
-        <v>1</v>
-      </c>
-      <c r="I103" s="28">
-        <v>1</v>
-      </c>
-      <c r="J103" s="34" t="s">
-        <v>448</v>
-      </c>
-      <c r="K103" s="34"/>
-      <c r="L103" s="34"/>
-      <c r="M103" s="34"/>
-      <c r="N103" s="34"/>
-      <c r="O103" s="2"/>
-      <c r="P103" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q103" s="42"/>
+      <c r="J103" s="40"/>
+      <c r="K103" s="40"/>
+      <c r="L103" s="40"/>
+      <c r="M103" s="40"/>
+      <c r="N103" s="40"/>
+      <c r="O103" s="1"/>
+      <c r="P103" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q103" s="35"/>
     </row>
     <row r="104" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="36">
+        <v>65</v>
+      </c>
+      <c r="B104" s="3">
+        <v>63</v>
+      </c>
+      <c r="C104" s="36">
+        <v>98</v>
+      </c>
+      <c r="D104" s="3">
+        <v>63</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F104" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="G104" s="36">
         <v>62</v>
       </c>
-      <c r="B104" s="3">
-        <v>57</v>
-      </c>
-      <c r="C104" s="36"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G104" s="36">
-        <v>43</v>
-      </c>
       <c r="H104" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I104" s="36">
         <v>1</v>
       </c>
-      <c r="J104" s="40"/>
-      <c r="K104" s="40"/>
+      <c r="J104" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="K104" s="40" t="s">
+        <v>422</v>
+      </c>
       <c r="L104" s="40"/>
       <c r="M104" s="40"/>
       <c r="N104" s="40"/>
       <c r="O104" s="1"/>
       <c r="P104" s="1" t="s">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="Q104" s="35"/>
     </row>
     <row r="105" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A105" s="36">
-        <v>63</v>
-      </c>
+      <c r="A105" s="36"/>
       <c r="B105" s="3"/>
       <c r="C105" s="36">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="3" t="s">
-        <v>452</v>
+        <v>420</v>
       </c>
       <c r="F105" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="G105" s="36">
-        <v>62</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G105" s="36"/>
       <c r="H105" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I105" s="36">
         <v>2</v>
       </c>
-      <c r="J105" s="40" t="s">
-        <v>453</v>
-      </c>
-      <c r="K105" s="40" t="s">
-        <v>454</v>
-      </c>
+      <c r="J105" s="40"/>
+      <c r="K105" s="40"/>
       <c r="L105" s="40"/>
       <c r="M105" s="40"/>
       <c r="N105" s="40"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="Q105" s="35"/>
     </row>
     <row r="106" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A106" s="36"/>
+      <c r="A106" s="36">
+        <v>66</v>
+      </c>
       <c r="B106" s="3"/>
       <c r="C106" s="36">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="F106" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="G106" s="36"/>
-      <c r="H106" s="36"/>
+        <v>424</v>
+      </c>
+      <c r="F106" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="G106" s="36">
+        <v>65</v>
+      </c>
+      <c r="H106" s="36">
+        <v>1</v>
+      </c>
       <c r="I106" s="36">
-        <v>2</v>
-      </c>
-      <c r="J106" s="40"/>
-      <c r="K106" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J106" s="40" t="s">
+        <v>425</v>
+      </c>
+      <c r="K106" s="40" t="s">
+        <v>426</v>
+      </c>
       <c r="L106" s="40"/>
       <c r="M106" s="40"/>
       <c r="N106" s="40"/>
       <c r="O106" s="1"/>
       <c r="P106" s="1" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="Q106" s="35"/>
     </row>
     <row r="107" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A107" s="36"/>
+      <c r="A107" s="36">
+        <v>67</v>
+      </c>
       <c r="B107" s="3"/>
       <c r="C107" s="36">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="F107" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="G107" s="36"/>
-      <c r="H107" s="36"/>
+        <v>428</v>
+      </c>
+      <c r="F107" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="G107" s="36">
+        <v>65</v>
+      </c>
+      <c r="H107" s="36">
+        <v>1</v>
+      </c>
       <c r="I107" s="36">
-        <v>3</v>
-      </c>
-      <c r="J107" s="40"/>
-      <c r="K107" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J107" s="40" t="s">
+        <v>429</v>
+      </c>
+      <c r="K107" s="40" t="s">
+        <v>430</v>
+      </c>
       <c r="L107" s="40"/>
       <c r="M107" s="40"/>
       <c r="N107" s="40"/>
       <c r="O107" s="1"/>
       <c r="P107" s="1" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A108" s="36">
-        <v>64</v>
-      </c>
-      <c r="B108" s="3">
-        <v>63</v>
-      </c>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A108" s="36"/>
+      <c r="B108" s="3"/>
       <c r="C108" s="36">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="F108" s="41" t="s">
-        <v>147</v>
+        <v>432</v>
+      </c>
+      <c r="F108" s="49" t="s">
+        <v>433</v>
       </c>
       <c r="G108" s="36">
-        <v>62</v>
-      </c>
-      <c r="H108" s="36">
-        <v>2</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H108" s="36"/>
       <c r="I108" s="36">
         <v>1</v>
       </c>
-      <c r="J108" s="40" t="s">
-        <v>457</v>
-      </c>
+      <c r="J108" s="40"/>
       <c r="K108" s="40" t="s">
-        <v>458</v>
-      </c>
-      <c r="L108" s="40"/>
+        <v>434</v>
+      </c>
+      <c r="L108" s="40" t="s">
+        <v>435</v>
+      </c>
       <c r="M108" s="40"/>
       <c r="N108" s="40"/>
       <c r="O108" s="1"/>
       <c r="P108" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q108" s="35"/>
-    </row>
-    <row r="109" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A109" s="36"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="36">
-        <v>97</v>
-      </c>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="F109" s="41" t="s">
-        <v>147</v>
-      </c>
-      <c r="G109" s="36"/>
-      <c r="H109" s="36"/>
-      <c r="I109" s="36">
+        <v>436</v>
+      </c>
+      <c r="Q108" s="42"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A109" s="28">
+        <v>68</v>
+      </c>
+      <c r="B109" s="21">
+        <v>204</v>
+      </c>
+      <c r="C109" s="28"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G109" s="45">
+        <v>43</v>
+      </c>
+      <c r="H109" s="28">
+        <v>3</v>
+      </c>
+      <c r="I109" s="28"/>
+      <c r="J109" s="34"/>
+      <c r="K109" s="34"/>
+      <c r="L109" s="34"/>
+      <c r="M109" s="34"/>
+      <c r="N109" s="34"/>
+      <c r="O109" s="2"/>
+      <c r="P109" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q109" s="42"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A110" s="28">
+        <v>203</v>
+      </c>
+      <c r="B110" s="21"/>
+      <c r="C110" s="28"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="21"/>
+      <c r="F110" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="G110" s="28">
+        <v>68</v>
+      </c>
+      <c r="H110" s="28">
+        <v>1</v>
+      </c>
+      <c r="I110" s="28"/>
+      <c r="J110" s="81"/>
+      <c r="K110" s="81"/>
+      <c r="L110" s="81"/>
+      <c r="M110" s="81"/>
+      <c r="N110" s="34"/>
+      <c r="O110" s="2"/>
+      <c r="P110" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q110" s="42"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A111" s="28">
+        <v>51</v>
+      </c>
+      <c r="B111" s="21"/>
+      <c r="C111" s="28">
+        <v>80</v>
+      </c>
+      <c r="D111" s="21"/>
+      <c r="E111" s="92" t="s">
+        <v>640</v>
+      </c>
+      <c r="F111" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="G111" s="28">
+        <v>203</v>
+      </c>
+      <c r="H111" s="28">
+        <v>1</v>
+      </c>
+      <c r="I111" s="28">
+        <v>1</v>
+      </c>
+      <c r="J111" s="34" t="s">
+        <v>374</v>
+      </c>
+      <c r="K111" s="34"/>
+      <c r="L111" s="34"/>
+      <c r="M111" s="34" t="s">
+        <v>375</v>
+      </c>
+      <c r="N111" s="34"/>
+      <c r="O111" s="2"/>
+      <c r="P111" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q111" s="42"/>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A112" s="28">
+        <v>52</v>
+      </c>
+      <c r="B112" s="21">
+        <v>51</v>
+      </c>
+      <c r="C112" s="28">
+        <v>81</v>
+      </c>
+      <c r="D112" s="21"/>
+      <c r="E112" s="92" t="s">
+        <v>654</v>
+      </c>
+      <c r="F112" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="G112" s="28">
+        <v>51</v>
+      </c>
+      <c r="H112" s="28">
+        <v>3</v>
+      </c>
+      <c r="I112" s="28">
+        <v>1</v>
+      </c>
+      <c r="J112" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="K112" s="34"/>
+      <c r="L112" s="34"/>
+      <c r="M112" s="34"/>
+      <c r="N112" s="34"/>
+      <c r="O112" s="2"/>
+      <c r="P112" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q112" s="42"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A113" s="28"/>
+      <c r="B113" s="21"/>
+      <c r="C113" s="28">
+        <v>82</v>
+      </c>
+      <c r="D113" s="21"/>
+      <c r="E113" s="92" t="s">
+        <v>654</v>
+      </c>
+      <c r="F113" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="G113" s="28"/>
+      <c r="H113" s="28"/>
+      <c r="I113" s="28">
         <v>2</v>
       </c>
-      <c r="J109" s="40"/>
-      <c r="K109" s="40"/>
-      <c r="L109" s="40"/>
-      <c r="M109" s="40"/>
-      <c r="N109" s="40"/>
-      <c r="O109" s="1"/>
-      <c r="P109" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q109" s="35"/>
-    </row>
-    <row r="110" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A110" s="36">
-        <v>65</v>
-      </c>
-      <c r="B110" s="3">
-        <v>63</v>
-      </c>
-      <c r="C110" s="36">
-        <v>98</v>
-      </c>
-      <c r="D110" s="3">
-        <v>63</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F110" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G110" s="36">
-        <v>62</v>
-      </c>
-      <c r="H110" s="36">
-        <v>2</v>
-      </c>
-      <c r="I110" s="36">
-        <v>1</v>
-      </c>
-      <c r="J110" s="40" t="s">
-        <v>461</v>
-      </c>
-      <c r="K110" s="40" t="s">
-        <v>462</v>
-      </c>
-      <c r="L110" s="40"/>
-      <c r="M110" s="40"/>
-      <c r="N110" s="40"/>
-      <c r="O110" s="1"/>
-      <c r="P110" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q110" s="35"/>
-    </row>
-    <row r="111" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A111" s="36"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="36">
-        <v>99</v>
-      </c>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F111" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G111" s="36"/>
-      <c r="H111" s="36">
-        <v>2</v>
-      </c>
-      <c r="I111" s="36">
-        <v>2</v>
-      </c>
-      <c r="J111" s="40"/>
-      <c r="K111" s="40"/>
-      <c r="L111" s="40"/>
-      <c r="M111" s="40"/>
-      <c r="N111" s="40"/>
-      <c r="O111" s="1"/>
-      <c r="P111" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q111" s="35"/>
-    </row>
-    <row r="112" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A112" s="36">
-        <v>66</v>
-      </c>
-      <c r="B112" s="3"/>
-      <c r="C112" s="36">
-        <v>100</v>
-      </c>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="F112" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="G112" s="36">
-        <v>65</v>
-      </c>
-      <c r="H112" s="36">
-        <v>2</v>
-      </c>
-      <c r="I112" s="36">
-        <v>1</v>
-      </c>
-      <c r="J112" s="40" t="s">
-        <v>465</v>
-      </c>
-      <c r="K112" s="40" t="s">
-        <v>466</v>
-      </c>
-      <c r="L112" s="40"/>
-      <c r="M112" s="40"/>
-      <c r="N112" s="40"/>
-      <c r="O112" s="1"/>
-      <c r="P112" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q112" s="35"/>
-    </row>
-    <row r="113" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A113" s="36">
-        <v>67</v>
-      </c>
-      <c r="B113" s="3"/>
-      <c r="C113" s="36">
-        <v>101</v>
-      </c>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="F113" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="G113" s="36">
-        <v>65</v>
-      </c>
-      <c r="H113" s="36">
-        <v>2</v>
-      </c>
-      <c r="I113" s="36">
-        <v>1</v>
-      </c>
-      <c r="J113" s="40" t="s">
-        <v>469</v>
-      </c>
-      <c r="K113" s="40" t="s">
-        <v>470</v>
-      </c>
-      <c r="L113" s="40"/>
-      <c r="M113" s="40"/>
-      <c r="N113" s="40"/>
-      <c r="O113" s="1"/>
-      <c r="P113" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q113" s="35"/>
+      <c r="J113" s="34"/>
+      <c r="K113" s="34"/>
+      <c r="L113" s="34"/>
+      <c r="M113" s="34"/>
+      <c r="N113" s="34"/>
+      <c r="O113" s="2"/>
+      <c r="P113" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q113" s="42"/>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A114" s="36"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="36">
-        <v>102</v>
-      </c>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="F114" s="49" t="s">
-        <v>473</v>
-      </c>
-      <c r="G114" s="36">
-        <v>65</v>
-      </c>
-      <c r="H114" s="36"/>
-      <c r="I114" s="36">
-        <v>1</v>
-      </c>
-      <c r="J114" s="40"/>
-      <c r="K114" s="40" t="s">
-        <v>474</v>
-      </c>
-      <c r="L114" s="40" t="s">
-        <v>475</v>
-      </c>
-      <c r="M114" s="40"/>
-      <c r="N114" s="40"/>
-      <c r="O114" s="1"/>
-      <c r="P114" s="1" t="s">
-        <v>476</v>
+      <c r="A114" s="28"/>
+      <c r="B114" s="21"/>
+      <c r="C114" s="28">
+        <v>83</v>
+      </c>
+      <c r="D114" s="21"/>
+      <c r="E114" s="92" t="s">
+        <v>654</v>
+      </c>
+      <c r="F114" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="G114" s="28"/>
+      <c r="H114" s="28"/>
+      <c r="I114" s="28">
+        <v>3</v>
+      </c>
+      <c r="J114" s="34"/>
+      <c r="K114" s="34"/>
+      <c r="L114" s="34"/>
+      <c r="M114" s="34"/>
+      <c r="N114" s="34"/>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="Q114" s="42"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="28">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B115" s="21">
-        <v>46</v>
-      </c>
-      <c r="C115" s="28"/>
+        <v>51</v>
+      </c>
+      <c r="C115" s="28">
+        <v>84</v>
+      </c>
       <c r="D115" s="21"/>
-      <c r="E115" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="F115" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="G115" s="45">
-        <v>43</v>
+      <c r="E115" s="92" t="s">
+        <v>655</v>
+      </c>
+      <c r="F115" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="G115" s="28">
+        <v>51</v>
       </c>
       <c r="H115" s="28">
         <v>3</v>
       </c>
-      <c r="I115" s="28"/>
-      <c r="J115" s="34"/>
+      <c r="I115" s="28">
+        <v>1</v>
+      </c>
+      <c r="J115" s="34" t="s">
+        <v>380</v>
+      </c>
       <c r="K115" s="34"/>
       <c r="L115" s="34"/>
       <c r="M115" s="34"/>
       <c r="N115" s="34"/>
       <c r="O115" s="2"/>
       <c r="P115" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q115" s="42"/>
+        <v>381</v>
+      </c>
+      <c r="Q115" s="35"/>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="28">
-        <v>69</v>
+        <v>213</v>
       </c>
       <c r="B116" s="21"/>
-      <c r="C116" s="28">
-        <v>103</v>
-      </c>
+      <c r="C116" s="28"/>
       <c r="D116" s="21"/>
-      <c r="E116" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="F116" s="33" t="s">
+      <c r="E116" s="92"/>
+      <c r="F116" s="96" t="s">
         <v>150</v>
       </c>
       <c r="G116" s="28">
@@ -10748,48 +10706,52 @@
       <c r="H116" s="28">
         <v>3</v>
       </c>
-      <c r="I116" s="28">
-        <v>1</v>
-      </c>
-      <c r="J116" s="34" t="s">
-        <v>480</v>
-      </c>
+      <c r="I116" s="28"/>
+      <c r="J116" s="34"/>
       <c r="K116" s="34"/>
       <c r="L116" s="34"/>
       <c r="M116" s="34"/>
       <c r="N116" s="34"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2" t="s">
-        <v>481</v>
+        <v>440</v>
       </c>
       <c r="Q116" s="42"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A117" s="28"/>
+      <c r="A117" s="28">
+        <v>69</v>
+      </c>
       <c r="B117" s="21"/>
       <c r="C117" s="28">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D117" s="21"/>
-      <c r="E117" s="21" t="s">
-        <v>479</v>
+      <c r="E117" s="92" t="s">
+        <v>438</v>
       </c>
       <c r="F117" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="G117" s="28"/>
-      <c r="H117" s="28"/>
+      <c r="G117" s="28">
+        <v>213</v>
+      </c>
+      <c r="H117" s="28">
+        <v>3</v>
+      </c>
       <c r="I117" s="28">
-        <v>2</v>
-      </c>
-      <c r="J117" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J117" s="34" t="s">
+        <v>439</v>
+      </c>
       <c r="K117" s="34"/>
       <c r="L117" s="34"/>
       <c r="M117" s="34"/>
       <c r="N117" s="34"/>
       <c r="O117" s="2"/>
       <c r="P117" s="2" t="s">
-        <v>481</v>
+        <v>440</v>
       </c>
       <c r="Q117" s="42"/>
     </row>
@@ -10797,11 +10759,11 @@
       <c r="A118" s="28"/>
       <c r="B118" s="21"/>
       <c r="C118" s="28">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="21" t="s">
-        <v>479</v>
+        <v>438</v>
       </c>
       <c r="F118" s="33" t="s">
         <v>150</v>
@@ -10809,7 +10771,7 @@
       <c r="G118" s="28"/>
       <c r="H118" s="28"/>
       <c r="I118" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J118" s="34"/>
       <c r="K118" s="34"/>
@@ -10818,75 +10780,75 @@
       <c r="N118" s="34"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2" t="s">
-        <v>481</v>
+        <v>440</v>
       </c>
       <c r="Q118" s="42"/>
     </row>
-    <row r="119" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A119" s="28">
-        <v>70</v>
-      </c>
-      <c r="B119" s="21">
-        <v>69</v>
-      </c>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A119" s="28"/>
+      <c r="B119" s="21"/>
       <c r="C119" s="28">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D119" s="21"/>
       <c r="E119" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="F119" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="G119" s="28">
-        <v>68</v>
-      </c>
-      <c r="H119" s="28">
+        <v>438</v>
+      </c>
+      <c r="F119" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G119" s="28"/>
+      <c r="H119" s="28"/>
+      <c r="I119" s="28">
         <v>3</v>
       </c>
-      <c r="I119" s="28">
-        <v>1</v>
-      </c>
-      <c r="J119" s="34" t="s">
-        <v>484</v>
-      </c>
+      <c r="J119" s="34"/>
       <c r="K119" s="34"/>
       <c r="L119" s="34"/>
       <c r="M119" s="34"/>
       <c r="N119" s="34"/>
       <c r="O119" s="2"/>
       <c r="P119" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="Q119" s="35"/>
+        <v>440</v>
+      </c>
+      <c r="Q119" s="42"/>
     </row>
     <row r="120" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A120" s="28"/>
-      <c r="B120" s="21"/>
+      <c r="A120" s="28">
+        <v>70</v>
+      </c>
+      <c r="B120" s="21">
+        <v>69</v>
+      </c>
       <c r="C120" s="28">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D120" s="21"/>
       <c r="E120" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="F120" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="G120" s="28"/>
-      <c r="H120" s="28"/>
+        <v>441</v>
+      </c>
+      <c r="F120" s="96" t="s">
+        <v>660</v>
+      </c>
+      <c r="G120" s="28">
+        <v>213</v>
+      </c>
+      <c r="H120" s="28">
+        <v>3</v>
+      </c>
       <c r="I120" s="28">
-        <v>2</v>
-      </c>
-      <c r="J120" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J120" s="34" t="s">
+        <v>442</v>
+      </c>
       <c r="K120" s="34"/>
       <c r="L120" s="34"/>
       <c r="M120" s="34"/>
       <c r="N120" s="34"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="Q120" s="35"/>
     </row>
@@ -10894,19 +10856,19 @@
       <c r="A121" s="28"/>
       <c r="B121" s="21"/>
       <c r="C121" s="28">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D121" s="21"/>
       <c r="E121" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="F121" s="46" t="s">
-        <v>483</v>
+        <v>441</v>
+      </c>
+      <c r="F121" s="96" t="s">
+        <v>660</v>
       </c>
       <c r="G121" s="28"/>
       <c r="H121" s="28"/>
       <c r="I121" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J121" s="34"/>
       <c r="K121" s="34"/>
@@ -10915,68 +10877,57 @@
       <c r="N121" s="34"/>
       <c r="O121" s="2"/>
       <c r="P121" s="2" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A122" s="28">
-        <v>71</v>
-      </c>
+    <row r="122" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A122" s="28"/>
       <c r="B122" s="21"/>
       <c r="C122" s="28">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D122" s="21"/>
       <c r="E122" s="21" t="s">
-        <v>486</v>
-      </c>
-      <c r="F122" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="G122" s="28">
-        <v>103</v>
-      </c>
-      <c r="H122" s="28">
-        <v>1</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="F122" s="96" t="s">
+        <v>660</v>
+      </c>
+      <c r="G122" s="28"/>
+      <c r="H122" s="28"/>
       <c r="I122" s="28">
-        <v>1</v>
-      </c>
-      <c r="J122" s="34" t="s">
-        <v>487</v>
-      </c>
-      <c r="K122" s="34" t="s">
-        <v>488</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J122" s="34"/>
+      <c r="K122" s="34"/>
       <c r="L122" s="34"/>
       <c r="M122" s="34"/>
       <c r="N122" s="34"/>
       <c r="O122" s="2"/>
       <c r="P122" s="2" t="s">
-        <v>489</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="Q122" s="35"/>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="36">
         <v>72</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>667</v>
+        <v>605</v>
       </c>
       <c r="C123" s="36"/>
       <c r="D123" s="3"/>
-      <c r="E123" s="3" t="s">
-        <v>490</v>
-      </c>
+      <c r="E123" s="3"/>
       <c r="F123" s="3" t="s">
-        <v>666</v>
+        <v>604</v>
       </c>
       <c r="G123" s="36">
         <v>43</v>
       </c>
       <c r="H123" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I123" s="36"/>
       <c r="J123" s="40"/>
@@ -10986,7 +10937,7 @@
       <c r="N123" s="40"/>
       <c r="O123" s="1"/>
       <c r="P123" s="1" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.2">
@@ -10999,10 +10950,10 @@
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="3" t="s">
-        <v>492</v>
+        <v>449</v>
       </c>
       <c r="F124" s="41" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="G124" s="36">
         <v>72</v>
@@ -11014,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="40" t="s">
-        <v>493</v>
+        <v>450</v>
       </c>
       <c r="K124" s="40"/>
       <c r="L124" s="40"/>
@@ -11022,7 +10973,7 @@
       <c r="N124" s="40"/>
       <c r="O124" s="1"/>
       <c r="P124" s="1" t="s">
-        <v>494</v>
+        <v>451</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.2">
@@ -11033,10 +10984,10 @@
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="3" t="s">
-        <v>492</v>
+        <v>449</v>
       </c>
       <c r="F125" s="41" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="G125" s="36"/>
       <c r="H125" s="36"/>
@@ -11050,7 +11001,7 @@
       <c r="N125" s="40"/>
       <c r="O125" s="1"/>
       <c r="P125" s="1" t="s">
-        <v>494</v>
+        <v>451</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
@@ -11065,22 +11016,22 @@
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="3" t="s">
-        <v>495</v>
+        <v>452</v>
       </c>
       <c r="F126" s="41" t="s">
-        <v>660</v>
+        <v>598</v>
       </c>
       <c r="G126" s="36">
         <v>72</v>
       </c>
       <c r="H126" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I126" s="36">
         <v>1</v>
       </c>
       <c r="J126" s="40" t="s">
-        <v>496</v>
+        <v>453</v>
       </c>
       <c r="K126" s="40"/>
       <c r="L126" s="40"/>
@@ -11088,7 +11039,7 @@
       <c r="N126" s="40"/>
       <c r="O126" s="1"/>
       <c r="P126" s="1" t="s">
-        <v>497</v>
+        <v>454</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.2">
@@ -11099,10 +11050,10 @@
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="3" t="s">
-        <v>495</v>
+        <v>452</v>
       </c>
       <c r="F127" s="41" t="s">
-        <v>660</v>
+        <v>598</v>
       </c>
       <c r="G127" s="36"/>
       <c r="H127" s="36"/>
@@ -11116,7 +11067,7 @@
       <c r="N127" s="40"/>
       <c r="O127" s="1"/>
       <c r="P127" s="1" t="s">
-        <v>497</v>
+        <v>454</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.2">
@@ -11127,10 +11078,10 @@
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="3" t="s">
-        <v>495</v>
+        <v>452</v>
       </c>
       <c r="F128" s="41" t="s">
-        <v>660</v>
+        <v>598</v>
       </c>
       <c r="G128" s="36"/>
       <c r="H128" s="36"/>
@@ -11144,7 +11095,7 @@
       <c r="N128" s="40"/>
       <c r="O128" s="1"/>
       <c r="P128" s="1" t="s">
-        <v>497</v>
+        <v>454</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.2">
@@ -11161,22 +11112,22 @@
         <v>75</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>498</v>
+        <v>455</v>
       </c>
       <c r="F129" s="41" t="s">
-        <v>661</v>
+        <v>599</v>
       </c>
       <c r="G129" s="36">
         <v>72</v>
       </c>
       <c r="H129" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I129" s="36">
         <v>1</v>
       </c>
       <c r="J129" s="40" t="s">
-        <v>499</v>
+        <v>456</v>
       </c>
       <c r="K129" s="40"/>
       <c r="L129" s="40"/>
@@ -11184,7 +11135,7 @@
       <c r="N129" s="40"/>
       <c r="O129" s="1"/>
       <c r="P129" s="1" t="s">
-        <v>500</v>
+        <v>457</v>
       </c>
     </row>
     <row r="130" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -11199,10 +11150,10 @@
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="3" t="s">
-        <v>662</v>
+        <v>600</v>
       </c>
       <c r="F130" s="49" t="s">
-        <v>501</v>
+        <v>458</v>
       </c>
       <c r="G130" s="36">
         <v>72</v>
@@ -11214,7 +11165,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="40" t="s">
-        <v>502</v>
+        <v>459</v>
       </c>
       <c r="K130" s="40"/>
       <c r="L130" s="40"/>
@@ -11222,7 +11173,7 @@
       <c r="N130" s="40"/>
       <c r="O130" s="1"/>
       <c r="P130" s="1" t="s">
-        <v>503</v>
+        <v>460</v>
       </c>
       <c r="Q130" s="35"/>
     </row>
@@ -11234,10 +11185,10 @@
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3" t="s">
-        <v>662</v>
+        <v>600</v>
       </c>
       <c r="F131" s="49" t="s">
-        <v>501</v>
+        <v>458</v>
       </c>
       <c r="G131" s="36"/>
       <c r="H131" s="36"/>
@@ -11251,7 +11202,7 @@
       <c r="N131" s="40"/>
       <c r="O131" s="1"/>
       <c r="P131" s="1" t="s">
-        <v>503</v>
+        <v>460</v>
       </c>
       <c r="Q131" s="35"/>
     </row>
@@ -11263,10 +11214,10 @@
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3" t="s">
-        <v>662</v>
+        <v>600</v>
       </c>
       <c r="F132" s="49" t="s">
-        <v>501</v>
+        <v>458</v>
       </c>
       <c r="G132" s="36"/>
       <c r="H132" s="36"/>
@@ -11280,7 +11231,7 @@
       <c r="N132" s="40"/>
       <c r="O132" s="1"/>
       <c r="P132" s="1" t="s">
-        <v>503</v>
+        <v>460</v>
       </c>
       <c r="Q132" s="35"/>
     </row>
@@ -11289,41 +11240,41 @@
         <v>79</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>665</v>
+        <v>603</v>
       </c>
       <c r="C133" s="36">
         <v>119</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="3" t="s">
-        <v>663</v>
+        <v>601</v>
       </c>
       <c r="F133" s="49" t="s">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="G133" s="36">
         <v>72</v>
       </c>
       <c r="H133" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I133" s="36">
         <v>1</v>
       </c>
       <c r="J133" s="40" t="s">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="K133" s="40" t="s">
-        <v>506</v>
+        <v>463</v>
       </c>
       <c r="L133" s="40"/>
       <c r="M133" s="40" t="s">
-        <v>507</v>
+        <v>464</v>
       </c>
       <c r="N133" s="40"/>
       <c r="O133" s="1"/>
       <c r="P133" s="1" t="s">
-        <v>508</v>
+        <v>465</v>
       </c>
       <c r="Q133" s="42"/>
     </row>
@@ -11337,7 +11288,7 @@
       <c r="C134" s="28"/>
       <c r="D134" s="21"/>
       <c r="E134" s="21" t="s">
-        <v>509</v>
+        <v>466</v>
       </c>
       <c r="F134" s="21" t="s">
         <v>160</v>
@@ -11346,7 +11297,7 @@
         <v>72</v>
       </c>
       <c r="H134" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I134" s="28"/>
       <c r="J134" s="34"/>
@@ -11356,7 +11307,7 @@
       <c r="N134" s="34"/>
       <c r="O134" s="2"/>
       <c r="P134" s="2" t="s">
-        <v>510</v>
+        <v>467</v>
       </c>
       <c r="Q134" s="35"/>
     </row>
@@ -11370,7 +11321,7 @@
       </c>
       <c r="D135" s="21"/>
       <c r="E135" s="21" t="s">
-        <v>511</v>
+        <v>468</v>
       </c>
       <c r="F135" s="33" t="s">
         <v>161</v>
@@ -11379,23 +11330,23 @@
         <v>80</v>
       </c>
       <c r="H135" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I135" s="28">
         <v>1</v>
       </c>
       <c r="J135" s="34" t="s">
-        <v>512</v>
+        <v>469</v>
       </c>
       <c r="K135" s="34" t="s">
-        <v>513</v>
+        <v>470</v>
       </c>
       <c r="L135" s="34"/>
       <c r="M135" s="34"/>
       <c r="N135" s="34"/>
       <c r="O135" s="2"/>
       <c r="P135" s="2" t="s">
-        <v>514</v>
+        <v>471</v>
       </c>
       <c r="Q135" s="35"/>
     </row>
@@ -11411,7 +11362,7 @@
       </c>
       <c r="D136" s="21"/>
       <c r="E136" s="21" t="s">
-        <v>515</v>
+        <v>472</v>
       </c>
       <c r="F136" s="33" t="s">
         <v>162</v>
@@ -11420,23 +11371,23 @@
         <v>80</v>
       </c>
       <c r="H136" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="28">
         <v>1</v>
       </c>
       <c r="J136" s="34" t="s">
-        <v>516</v>
+        <v>473</v>
       </c>
       <c r="K136" s="34" t="s">
-        <v>517</v>
+        <v>474</v>
       </c>
       <c r="L136" s="34"/>
       <c r="M136" s="34"/>
       <c r="N136" s="34"/>
       <c r="O136" s="2"/>
       <c r="P136" s="2" t="s">
-        <v>518</v>
+        <v>475</v>
       </c>
       <c r="Q136" s="35"/>
     </row>
@@ -11452,7 +11403,7 @@
       </c>
       <c r="D137" s="21"/>
       <c r="E137" s="21" t="s">
-        <v>519</v>
+        <v>476</v>
       </c>
       <c r="F137" s="33" t="s">
         <v>163</v>
@@ -11467,17 +11418,17 @@
         <v>1</v>
       </c>
       <c r="J137" s="34" t="s">
-        <v>520</v>
+        <v>477</v>
       </c>
       <c r="K137" s="34" t="s">
-        <v>521</v>
+        <v>478</v>
       </c>
       <c r="L137" s="34"/>
       <c r="M137" s="34"/>
       <c r="N137" s="34"/>
       <c r="O137" s="2"/>
       <c r="P137" s="2" t="s">
-        <v>522</v>
+        <v>479</v>
       </c>
       <c r="Q137" s="35"/>
     </row>
@@ -11489,7 +11440,7 @@
       </c>
       <c r="D138" s="21"/>
       <c r="E138" s="21" t="s">
-        <v>519</v>
+        <v>476</v>
       </c>
       <c r="F138" s="33" t="s">
         <v>163</v>
@@ -11506,7 +11457,7 @@
       <c r="N138" s="34"/>
       <c r="O138" s="2"/>
       <c r="P138" s="2" t="s">
-        <v>522</v>
+        <v>479</v>
       </c>
       <c r="Q138" s="35"/>
     </row>
@@ -11522,7 +11473,7 @@
       </c>
       <c r="D139" s="21"/>
       <c r="E139" s="21" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F139" s="33" t="s">
         <v>121</v>
@@ -11537,17 +11488,17 @@
         <v>1</v>
       </c>
       <c r="J139" s="34" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
       <c r="K139" s="34" t="s">
-        <v>525</v>
+        <v>482</v>
       </c>
       <c r="L139" s="34"/>
       <c r="M139" s="34"/>
       <c r="N139" s="34"/>
       <c r="O139" s="2"/>
       <c r="P139" s="2" t="s">
-        <v>526</v>
+        <v>483</v>
       </c>
       <c r="Q139" s="42"/>
     </row>
@@ -11559,7 +11510,7 @@
       </c>
       <c r="D140" s="21"/>
       <c r="E140" s="21" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F140" s="33" t="s">
         <v>121</v>
@@ -11576,7 +11527,7 @@
       <c r="N140" s="34"/>
       <c r="O140" s="2"/>
       <c r="P140" s="2" t="s">
-        <v>526</v>
+        <v>483</v>
       </c>
       <c r="Q140" s="42"/>
     </row>
@@ -11588,7 +11539,7 @@
       </c>
       <c r="D141" s="21"/>
       <c r="E141" s="21" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F141" s="33" t="s">
         <v>121</v>
@@ -11605,13 +11556,13 @@
       <c r="N141" s="34"/>
       <c r="O141" s="2"/>
       <c r="P141" s="2" t="s">
-        <v>526</v>
+        <v>483</v>
       </c>
       <c r="Q141" s="42"/>
     </row>
     <row r="142" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="B142" s="3">
         <v>72</v>
@@ -11636,27 +11587,27 @@
       <c r="N142" s="40"/>
       <c r="O142" s="1"/>
       <c r="P142" s="1" t="s">
-        <v>527</v>
+        <v>484</v>
       </c>
       <c r="Q142" s="35"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A143" s="36">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="36">
         <v>127</v>
       </c>
       <c r="D143" s="3"/>
-      <c r="E143" s="3" t="s">
-        <v>528</v>
+      <c r="E143" s="93" t="s">
+        <v>642</v>
       </c>
       <c r="F143" s="41" t="s">
         <v>164</v>
       </c>
       <c r="G143" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H143" s="36">
         <v>3</v>
@@ -11665,17 +11616,17 @@
         <v>1</v>
       </c>
       <c r="J143" s="40" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="K143" s="40" t="s">
-        <v>530</v>
+        <v>486</v>
       </c>
       <c r="L143" s="40"/>
       <c r="M143" s="40"/>
       <c r="N143" s="40"/>
       <c r="O143" s="1"/>
       <c r="P143" s="1" t="s">
-        <v>531</v>
+        <v>487</v>
       </c>
       <c r="Q143" s="42"/>
     </row>
@@ -11686,8 +11637,8 @@
         <v>128</v>
       </c>
       <c r="D144" s="3"/>
-      <c r="E144" s="3" t="s">
-        <v>528</v>
+      <c r="E144" s="93" t="s">
+        <v>642</v>
       </c>
       <c r="F144" s="41" t="s">
         <v>164</v>
@@ -11704,7 +11655,7 @@
       <c r="N144" s="40"/>
       <c r="O144" s="1"/>
       <c r="P144" s="1" t="s">
-        <v>531</v>
+        <v>487</v>
       </c>
       <c r="Q144" s="42"/>
     </row>
@@ -11715,8 +11666,8 @@
         <v>129</v>
       </c>
       <c r="D145" s="3"/>
-      <c r="E145" s="3" t="s">
-        <v>528</v>
+      <c r="E145" s="93" t="s">
+        <v>642</v>
       </c>
       <c r="F145" s="41" t="s">
         <v>164</v>
@@ -11733,7 +11684,7 @@
       <c r="N145" s="40"/>
       <c r="O145" s="1"/>
       <c r="P145" s="1" t="s">
-        <v>531</v>
+        <v>487</v>
       </c>
       <c r="Q145" s="42"/>
     </row>
@@ -11744,21 +11695,21 @@
         <v>130</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="3" t="s">
-        <v>528</v>
+      <c r="E146" s="93" t="s">
+        <v>642</v>
       </c>
       <c r="F146" s="41" t="s">
         <v>165</v>
       </c>
       <c r="G146" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H146" s="36"/>
       <c r="I146" s="36">
         <v>1</v>
       </c>
       <c r="J146" s="40" t="s">
-        <v>532</v>
+        <v>488</v>
       </c>
       <c r="K146" s="40"/>
       <c r="L146" s="40"/>
@@ -11766,7 +11717,7 @@
       <c r="N146" s="40"/>
       <c r="O146" s="1"/>
       <c r="P146" s="1" t="s">
-        <v>533</v>
+        <v>489</v>
       </c>
       <c r="Q146" s="35"/>
     </row>
@@ -11775,20 +11726,20 @@
         <v>86</v>
       </c>
       <c r="B147" s="3">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="C147" s="36">
         <v>131</v>
       </c>
       <c r="D147" s="3"/>
-      <c r="E147" s="3" t="s">
-        <v>534</v>
+      <c r="E147" s="93" t="s">
+        <v>643</v>
       </c>
       <c r="F147" s="41" t="s">
         <v>155</v>
       </c>
       <c r="G147" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H147" s="36">
         <v>2</v>
@@ -11797,17 +11748,17 @@
         <v>1</v>
       </c>
       <c r="J147" s="40" t="s">
-        <v>535</v>
+        <v>490</v>
       </c>
       <c r="K147" s="40" t="s">
-        <v>536</v>
+        <v>491</v>
       </c>
       <c r="L147" s="40"/>
       <c r="M147" s="40"/>
       <c r="N147" s="40"/>
       <c r="O147" s="1"/>
       <c r="P147" s="1" t="s">
-        <v>537</v>
+        <v>492</v>
       </c>
       <c r="Q147" s="35"/>
     </row>
@@ -11818,8 +11769,8 @@
         <v>132</v>
       </c>
       <c r="D148" s="3"/>
-      <c r="E148" s="3" t="s">
-        <v>534</v>
+      <c r="E148" s="93" t="s">
+        <v>643</v>
       </c>
       <c r="F148" s="41" t="s">
         <v>155</v>
@@ -11836,7 +11787,7 @@
       <c r="N148" s="40"/>
       <c r="O148" s="1"/>
       <c r="P148" s="1" t="s">
-        <v>537</v>
+        <v>492</v>
       </c>
       <c r="Q148" s="35"/>
     </row>
@@ -11851,14 +11802,14 @@
         <v>133</v>
       </c>
       <c r="D149" s="3"/>
-      <c r="E149" s="3" t="s">
-        <v>538</v>
+      <c r="E149" s="93" t="s">
+        <v>644</v>
       </c>
       <c r="F149" s="41" t="s">
         <v>153</v>
       </c>
       <c r="G149" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H149" s="36">
         <v>2</v>
@@ -11867,17 +11818,17 @@
         <v>1</v>
       </c>
       <c r="J149" s="40" t="s">
-        <v>539</v>
+        <v>493</v>
       </c>
       <c r="K149" s="40" t="s">
-        <v>540</v>
+        <v>494</v>
       </c>
       <c r="L149" s="40"/>
       <c r="M149" s="40"/>
       <c r="N149" s="40"/>
       <c r="O149" s="1"/>
       <c r="P149" s="1" t="s">
-        <v>541</v>
+        <v>495</v>
       </c>
       <c r="Q149" s="35"/>
     </row>
@@ -11892,14 +11843,14 @@
         <v>134</v>
       </c>
       <c r="D150" s="3"/>
-      <c r="E150" s="3" t="s">
-        <v>542</v>
+      <c r="E150" s="93" t="s">
+        <v>645</v>
       </c>
       <c r="F150" s="41" t="s">
         <v>166</v>
       </c>
       <c r="G150" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H150" s="36">
         <v>2</v>
@@ -11908,17 +11859,17 @@
         <v>1</v>
       </c>
       <c r="J150" s="40" t="s">
-        <v>543</v>
+        <v>496</v>
       </c>
       <c r="K150" s="40" t="s">
-        <v>544</v>
+        <v>497</v>
       </c>
       <c r="L150" s="40"/>
       <c r="M150" s="40"/>
       <c r="N150" s="40"/>
       <c r="O150" s="1"/>
       <c r="P150" s="1" t="s">
-        <v>545</v>
+        <v>498</v>
       </c>
       <c r="Q150" s="35"/>
     </row>
@@ -11933,14 +11884,14 @@
         <v>135</v>
       </c>
       <c r="D151" s="3"/>
-      <c r="E151" s="3" t="s">
-        <v>546</v>
+      <c r="E151" s="93" t="s">
+        <v>646</v>
       </c>
       <c r="F151" s="41" t="s">
         <v>167</v>
       </c>
       <c r="G151" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H151" s="36">
         <v>2</v>
@@ -11949,17 +11900,17 @@
         <v>1</v>
       </c>
       <c r="J151" s="40" t="s">
-        <v>547</v>
+        <v>499</v>
       </c>
       <c r="K151" s="40" t="s">
-        <v>548</v>
+        <v>500</v>
       </c>
       <c r="L151" s="40"/>
       <c r="M151" s="40"/>
       <c r="N151" s="40"/>
       <c r="O151" s="1"/>
       <c r="P151" s="1" t="s">
-        <v>549</v>
+        <v>501</v>
       </c>
       <c r="Q151" s="35"/>
     </row>
@@ -11974,14 +11925,14 @@
         <v>136</v>
       </c>
       <c r="D152" s="3"/>
-      <c r="E152" s="3" t="s">
-        <v>550</v>
+      <c r="E152" s="93" t="s">
+        <v>647</v>
       </c>
       <c r="F152" s="41" t="s">
         <v>168</v>
       </c>
       <c r="G152" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H152" s="36">
         <v>2</v>
@@ -11990,17 +11941,17 @@
         <v>1</v>
       </c>
       <c r="J152" s="40" t="s">
-        <v>551</v>
+        <v>502</v>
       </c>
       <c r="K152" s="40" t="s">
-        <v>552</v>
+        <v>503</v>
       </c>
       <c r="L152" s="40"/>
       <c r="M152" s="40"/>
       <c r="N152" s="40"/>
       <c r="O152" s="1"/>
       <c r="P152" s="1" t="s">
-        <v>553</v>
+        <v>504</v>
       </c>
       <c r="Q152" s="35"/>
     </row>
@@ -12015,14 +11966,14 @@
         <v>137</v>
       </c>
       <c r="D153" s="3"/>
-      <c r="E153" s="3" t="s">
-        <v>554</v>
+      <c r="E153" s="93" t="s">
+        <v>648</v>
       </c>
       <c r="F153" s="49" t="s">
-        <v>555</v>
+        <v>505</v>
       </c>
       <c r="G153" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H153" s="36">
         <v>2</v>
@@ -12031,17 +11982,17 @@
         <v>1</v>
       </c>
       <c r="J153" s="40" t="s">
-        <v>556</v>
+        <v>506</v>
       </c>
       <c r="K153" s="40" t="s">
-        <v>557</v>
+        <v>507</v>
       </c>
       <c r="L153" s="40"/>
       <c r="M153" s="40"/>
       <c r="N153" s="40"/>
       <c r="O153" s="1"/>
       <c r="P153" s="1" t="s">
-        <v>558</v>
+        <v>508</v>
       </c>
       <c r="Q153" s="35"/>
     </row>
@@ -12056,14 +12007,14 @@
         <v>138</v>
       </c>
       <c r="D154" s="3"/>
-      <c r="E154" s="3" t="s">
-        <v>559</v>
+      <c r="E154" s="93" t="s">
+        <v>649</v>
       </c>
       <c r="F154" s="41" t="s">
         <v>170</v>
       </c>
       <c r="G154" s="36">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="H154" s="36">
         <v>2</v>
@@ -12072,69 +12023,70 @@
         <v>1</v>
       </c>
       <c r="J154" s="40" t="s">
-        <v>560</v>
+        <v>509</v>
       </c>
       <c r="K154" s="40" t="s">
-        <v>561</v>
+        <v>510</v>
       </c>
       <c r="L154" s="40"/>
       <c r="M154" s="40"/>
       <c r="N154" s="40"/>
       <c r="O154" s="1"/>
       <c r="P154" s="1" t="s">
-        <v>562</v>
+        <v>511</v>
       </c>
       <c r="Q154" s="42"/>
     </row>
-    <row r="155" spans="1:17" s="88" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="83">
-        <v>208</v>
-      </c>
-      <c r="B155" s="84">
-        <v>72</v>
-      </c>
-      <c r="C155" s="83"/>
-      <c r="D155" s="84"/>
-      <c r="E155" s="84"/>
-      <c r="F155" s="85" t="s">
-        <v>669</v>
-      </c>
-      <c r="G155" s="83">
+    <row r="155" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A155" s="28">
+        <v>93</v>
+      </c>
+      <c r="B155" s="21">
+        <v>72.206000000000003</v>
+      </c>
+      <c r="C155" s="28">
+        <v>139</v>
+      </c>
+      <c r="D155" s="21"/>
+      <c r="E155" s="21"/>
+      <c r="F155" s="92" t="s">
+        <v>171</v>
+      </c>
+      <c r="G155" s="28">
         <v>43</v>
       </c>
-      <c r="H155" s="83"/>
-      <c r="I155" s="83"/>
-      <c r="J155" s="86"/>
-      <c r="K155" s="86"/>
-      <c r="L155" s="86"/>
-      <c r="M155" s="86"/>
-      <c r="N155" s="86"/>
-      <c r="O155" s="87"/>
-      <c r="P155" s="87"/>
+      <c r="H155" s="28">
+        <v>2</v>
+      </c>
+      <c r="I155" s="28">
+        <v>1</v>
+      </c>
+      <c r="J155" s="34"/>
+      <c r="K155" s="34"/>
+      <c r="L155" s="34"/>
+      <c r="M155" s="34"/>
+      <c r="N155" s="34"/>
+      <c r="O155" s="2"/>
+      <c r="P155" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="Q155" s="35"/>
     </row>
     <row r="156" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A156" s="28">
-        <v>93</v>
-      </c>
-      <c r="B156" s="21" t="s">
-        <v>668</v>
-      </c>
+      <c r="A156" s="28"/>
+      <c r="B156" s="21"/>
       <c r="C156" s="28">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D156" s="21"/>
       <c r="E156" s="21"/>
       <c r="F156" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="G156" s="28">
-        <v>43</v>
-      </c>
-      <c r="H156" s="28">
+      <c r="G156" s="28"/>
+      <c r="H156" s="28"/>
+      <c r="I156" s="28">
         <v>2</v>
-      </c>
-      <c r="I156" s="28">
-        <v>1</v>
       </c>
       <c r="J156" s="34"/>
       <c r="K156" s="34"/>
@@ -12143,51 +12095,65 @@
       <c r="N156" s="34"/>
       <c r="O156" s="2"/>
       <c r="P156" s="2" t="s">
-        <v>563</v>
+        <v>512</v>
       </c>
       <c r="Q156" s="35"/>
     </row>
     <row r="157" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A157" s="28"/>
+      <c r="A157" s="28">
+        <v>94</v>
+      </c>
       <c r="B157" s="21"/>
       <c r="C157" s="28">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D157" s="21"/>
-      <c r="E157" s="21"/>
-      <c r="F157" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="G157" s="28"/>
-      <c r="H157" s="28"/>
+      <c r="E157" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="F157" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="G157" s="28">
+        <v>93</v>
+      </c>
+      <c r="H157" s="28">
+        <v>2</v>
+      </c>
       <c r="I157" s="28">
-        <v>2</v>
-      </c>
-      <c r="J157" s="34"/>
-      <c r="K157" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J157" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="K157" s="34" t="s">
+        <v>515</v>
+      </c>
       <c r="L157" s="34"/>
       <c r="M157" s="34"/>
       <c r="N157" s="34"/>
       <c r="O157" s="2"/>
       <c r="P157" s="2" t="s">
-        <v>563</v>
+        <v>516</v>
       </c>
       <c r="Q157" s="35"/>
     </row>
     <row r="158" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="28">
+        <v>95</v>
+      </c>
+      <c r="B158" s="21">
         <v>94</v>
       </c>
-      <c r="B158" s="21"/>
       <c r="C158" s="28">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D158" s="21"/>
       <c r="E158" s="21" t="s">
-        <v>564</v>
+        <v>517</v>
       </c>
       <c r="F158" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G158" s="28">
         <v>93</v>
@@ -12199,36 +12165,36 @@
         <v>1</v>
       </c>
       <c r="J158" s="34" t="s">
-        <v>565</v>
+        <v>518</v>
       </c>
       <c r="K158" s="34" t="s">
-        <v>566</v>
+        <v>519</v>
       </c>
       <c r="L158" s="34"/>
       <c r="M158" s="34"/>
       <c r="N158" s="34"/>
       <c r="O158" s="2"/>
       <c r="P158" s="2" t="s">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="Q158" s="35"/>
     </row>
     <row r="159" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="28">
+        <v>96</v>
+      </c>
+      <c r="B159" s="21">
         <v>95</v>
       </c>
-      <c r="B159" s="21">
-        <v>94</v>
-      </c>
       <c r="C159" s="28">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D159" s="21"/>
       <c r="E159" s="21" t="s">
-        <v>568</v>
+        <v>521</v>
       </c>
       <c r="F159" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G159" s="28">
         <v>93</v>
@@ -12240,36 +12206,38 @@
         <v>1</v>
       </c>
       <c r="J159" s="34" t="s">
-        <v>569</v>
+        <v>522</v>
       </c>
       <c r="K159" s="34" t="s">
-        <v>570</v>
+        <v>523</v>
       </c>
       <c r="L159" s="34"/>
-      <c r="M159" s="34"/>
+      <c r="M159" s="34" t="s">
+        <v>524</v>
+      </c>
       <c r="N159" s="34"/>
       <c r="O159" s="2"/>
       <c r="P159" s="2" t="s">
-        <v>571</v>
+        <v>525</v>
       </c>
       <c r="Q159" s="35"/>
     </row>
     <row r="160" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="28">
+        <v>97</v>
+      </c>
+      <c r="B160" s="21">
         <v>96</v>
       </c>
-      <c r="B160" s="21">
-        <v>95</v>
-      </c>
       <c r="C160" s="28">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D160" s="21"/>
       <c r="E160" s="21" t="s">
-        <v>572</v>
+        <v>526</v>
       </c>
       <c r="F160" s="33" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G160" s="28">
         <v>93</v>
@@ -12281,62 +12249,50 @@
         <v>1</v>
       </c>
       <c r="J160" s="34" t="s">
-        <v>573</v>
+        <v>527</v>
       </c>
       <c r="K160" s="34" t="s">
-        <v>574</v>
+        <v>528</v>
       </c>
       <c r="L160" s="34"/>
       <c r="M160" s="34" t="s">
-        <v>575</v>
+        <v>529</v>
       </c>
       <c r="N160" s="34"/>
       <c r="O160" s="2"/>
       <c r="P160" s="2" t="s">
-        <v>576</v>
+        <v>530</v>
       </c>
       <c r="Q160" s="35"/>
     </row>
     <row r="161" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A161" s="28">
-        <v>97</v>
-      </c>
-      <c r="B161" s="21">
-        <v>96</v>
-      </c>
-      <c r="C161" s="28">
-        <v>144</v>
-      </c>
-      <c r="D161" s="21"/>
-      <c r="E161" s="21" t="s">
-        <v>577</v>
-      </c>
-      <c r="F161" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="G161" s="28">
+      <c r="A161" s="36">
+        <v>207</v>
+      </c>
+      <c r="B161" s="3">
         <v>93</v>
       </c>
-      <c r="H161" s="28">
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="93" t="s">
+        <v>657</v>
+      </c>
+      <c r="G161" s="36">
+        <v>43</v>
+      </c>
+      <c r="H161" s="36">
         <v>2</v>
       </c>
-      <c r="I161" s="28">
-        <v>1</v>
-      </c>
-      <c r="J161" s="34" t="s">
-        <v>578</v>
-      </c>
-      <c r="K161" s="34" t="s">
-        <v>579</v>
-      </c>
-      <c r="L161" s="34"/>
-      <c r="M161" s="34" t="s">
-        <v>580</v>
-      </c>
-      <c r="N161" s="34"/>
-      <c r="O161" s="2"/>
-      <c r="P161" s="2" t="s">
-        <v>581</v>
+      <c r="I161" s="36"/>
+      <c r="J161" s="40"/>
+      <c r="K161" s="40"/>
+      <c r="L161" s="40"/>
+      <c r="M161" s="40"/>
+      <c r="N161" s="40"/>
+      <c r="O161" s="1"/>
+      <c r="P161" s="1" t="s">
+        <v>533</v>
       </c>
       <c r="Q161" s="35"/>
     </row>
@@ -12344,335 +12300,346 @@
       <c r="A162" s="36">
         <v>98</v>
       </c>
-      <c r="B162" s="3">
-        <v>93</v>
-      </c>
-      <c r="C162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="36">
+        <v>145</v>
+      </c>
       <c r="D162" s="3"/>
-      <c r="E162" s="3"/>
-      <c r="F162" s="3" t="s">
-        <v>175</v>
+      <c r="E162" s="93" t="s">
+        <v>658</v>
+      </c>
+      <c r="F162" s="93" t="s">
+        <v>657</v>
       </c>
       <c r="G162" s="36">
-        <v>43</v>
-      </c>
-      <c r="H162" s="36"/>
+        <v>207</v>
+      </c>
+      <c r="H162" s="36">
+        <v>1</v>
+      </c>
       <c r="I162" s="36">
         <v>1</v>
       </c>
-      <c r="J162" s="40"/>
-      <c r="K162" s="40"/>
+      <c r="J162" s="40" t="s">
+        <v>531</v>
+      </c>
+      <c r="K162" s="40" t="s">
+        <v>532</v>
+      </c>
       <c r="L162" s="40"/>
       <c r="M162" s="40"/>
       <c r="N162" s="40"/>
       <c r="O162" s="1"/>
-      <c r="P162" s="1" t="s">
-        <v>585</v>
-      </c>
+      <c r="P162" s="1"/>
       <c r="Q162" s="35"/>
     </row>
-    <row r="163" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A163" s="36">
+        <v>99</v>
+      </c>
+      <c r="B163" s="3">
+        <v>98</v>
+      </c>
+      <c r="C163" s="36">
+        <v>146</v>
+      </c>
+      <c r="D163" s="3"/>
+      <c r="E163" s="93" t="s">
+        <v>659</v>
+      </c>
+      <c r="F163" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G163" s="36">
         <v>207</v>
       </c>
-      <c r="B163" s="3"/>
-      <c r="C163" s="36">
-        <v>145</v>
-      </c>
-      <c r="D163" s="3"/>
-      <c r="E163" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G163" s="36">
-        <v>98</v>
-      </c>
       <c r="H163" s="36">
-        <v>3</v>
-      </c>
-      <c r="I163" s="36"/>
+        <v>2</v>
+      </c>
+      <c r="I163" s="36">
+        <v>1</v>
+      </c>
       <c r="J163" s="40" t="s">
-        <v>583</v>
+        <v>534</v>
       </c>
       <c r="K163" s="40" t="s">
-        <v>584</v>
+        <v>535</v>
       </c>
       <c r="L163" s="40"/>
       <c r="M163" s="40"/>
       <c r="N163" s="40"/>
       <c r="O163" s="1"/>
-      <c r="P163" s="1"/>
-      <c r="Q163" s="35"/>
+      <c r="P163" s="1" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A164" s="36">
-        <v>99</v>
-      </c>
-      <c r="B164" s="3">
-        <v>207</v>
-      </c>
+      <c r="A164" s="36"/>
+      <c r="B164" s="3"/>
       <c r="C164" s="36">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D164" s="3"/>
-      <c r="E164" s="3" t="s">
-        <v>586</v>
+      <c r="E164" s="93" t="s">
+        <v>659</v>
       </c>
       <c r="F164" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G164" s="36">
-        <v>98</v>
-      </c>
-      <c r="H164" s="36">
+      <c r="G164" s="36"/>
+      <c r="H164" s="36"/>
+      <c r="I164" s="36">
         <v>2</v>
       </c>
-      <c r="I164" s="36">
-        <v>1</v>
-      </c>
-      <c r="J164" s="40" t="s">
-        <v>587</v>
-      </c>
-      <c r="K164" s="40" t="s">
-        <v>588</v>
-      </c>
+      <c r="J164" s="40"/>
+      <c r="K164" s="40"/>
       <c r="L164" s="40"/>
       <c r="M164" s="40"/>
       <c r="N164" s="40"/>
       <c r="O164" s="1"/>
       <c r="P164" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A165" s="36"/>
-      <c r="B165" s="3"/>
-      <c r="C165" s="36">
-        <v>147</v>
-      </c>
-      <c r="D165" s="3"/>
-      <c r="E165" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="F165" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="G165" s="36"/>
-      <c r="H165" s="36"/>
-      <c r="I165" s="36">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A165" s="28">
+        <v>100</v>
+      </c>
+      <c r="B165" s="21">
+        <v>72.102999999999994</v>
+      </c>
+      <c r="C165" s="28"/>
+      <c r="D165" s="21"/>
+      <c r="E165" s="21"/>
+      <c r="F165" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="G165" s="28">
+        <v>43</v>
+      </c>
+      <c r="H165" s="28">
         <v>2</v>
       </c>
-      <c r="J165" s="40"/>
-      <c r="K165" s="40"/>
-      <c r="L165" s="40"/>
-      <c r="M165" s="40"/>
-      <c r="N165" s="40"/>
-      <c r="O165" s="1"/>
-      <c r="P165" s="1" t="s">
-        <v>589</v>
-      </c>
+      <c r="I165" s="28"/>
+      <c r="J165" s="34"/>
+      <c r="K165" s="34"/>
+      <c r="L165" s="34"/>
+      <c r="M165" s="34"/>
+      <c r="N165" s="34"/>
+      <c r="O165" s="2"/>
+      <c r="P165" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q165" s="35"/>
     </row>
     <row r="166" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="28">
+        <v>101</v>
+      </c>
+      <c r="B166" s="21"/>
+      <c r="C166" s="28">
+        <v>148</v>
+      </c>
+      <c r="D166" s="21"/>
+      <c r="E166" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="F166" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="G166" s="28">
         <v>100</v>
-      </c>
-      <c r="B166" s="21"/>
-      <c r="C166" s="28"/>
-      <c r="D166" s="21"/>
-      <c r="E166" s="21"/>
-      <c r="F166" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="G166" s="28">
-        <v>208</v>
       </c>
       <c r="H166" s="28">
         <v>2</v>
       </c>
-      <c r="I166" s="28"/>
-      <c r="J166" s="34"/>
-      <c r="K166" s="34"/>
+      <c r="I166" s="28">
+        <v>1</v>
+      </c>
+      <c r="J166" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="K166" s="34" t="s">
+        <v>540</v>
+      </c>
       <c r="L166" s="34"/>
       <c r="M166" s="34"/>
       <c r="N166" s="34"/>
       <c r="O166" s="2"/>
       <c r="P166" s="2" t="s">
-        <v>590</v>
+        <v>541</v>
       </c>
       <c r="Q166" s="35"/>
     </row>
     <row r="167" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A167" s="28">
-        <v>101</v>
-      </c>
+      <c r="A167" s="28"/>
       <c r="B167" s="21"/>
       <c r="C167" s="28">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D167" s="21"/>
       <c r="E167" s="21" t="s">
-        <v>591</v>
+        <v>538</v>
       </c>
       <c r="F167" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="G167" s="28">
-        <v>100</v>
-      </c>
-      <c r="H167" s="28">
+      <c r="G167" s="28"/>
+      <c r="H167" s="28"/>
+      <c r="I167" s="28">
         <v>2</v>
       </c>
-      <c r="I167" s="28">
-        <v>1</v>
-      </c>
-      <c r="J167" s="34" t="s">
-        <v>592</v>
-      </c>
-      <c r="K167" s="34" t="s">
-        <v>593</v>
-      </c>
+      <c r="J167" s="34"/>
+      <c r="K167" s="34"/>
       <c r="L167" s="34"/>
       <c r="M167" s="34"/>
       <c r="N167" s="34"/>
       <c r="O167" s="2"/>
       <c r="P167" s="2" t="s">
-        <v>594</v>
+        <v>541</v>
       </c>
       <c r="Q167" s="35"/>
     </row>
     <row r="168" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A168" s="28"/>
-      <c r="B168" s="21"/>
+      <c r="A168" s="28">
+        <v>102</v>
+      </c>
+      <c r="B168" s="21">
+        <v>101</v>
+      </c>
       <c r="C168" s="28">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D168" s="21"/>
-      <c r="E168" s="21" t="s">
-        <v>591</v>
+      <c r="E168" s="92" t="s">
+        <v>656</v>
       </c>
       <c r="F168" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G168" s="28">
         <v>100</v>
       </c>
-      <c r="H168" s="28"/>
+      <c r="H168" s="28">
+        <v>2</v>
+      </c>
       <c r="I168" s="28">
-        <v>2</v>
-      </c>
-      <c r="J168" s="34"/>
-      <c r="K168" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J168" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="K168" s="34" t="s">
+        <v>543</v>
+      </c>
       <c r="L168" s="34"/>
       <c r="M168" s="34"/>
       <c r="N168" s="34"/>
       <c r="O168" s="2"/>
       <c r="P168" s="2" t="s">
-        <v>594</v>
+        <v>544</v>
       </c>
       <c r="Q168" s="35"/>
     </row>
-    <row r="169" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A169" s="28">
-        <v>102</v>
-      </c>
-      <c r="B169" s="21">
-        <v>101</v>
-      </c>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A169" s="28"/>
+      <c r="B169" s="21"/>
       <c r="C169" s="28">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D169" s="21"/>
-      <c r="E169" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="F169" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="G169" s="28">
-        <v>100</v>
-      </c>
-      <c r="H169" s="28">
-        <v>2</v>
-      </c>
+      <c r="E169" s="92" t="s">
+        <v>656</v>
+      </c>
+      <c r="F169" s="21"/>
+      <c r="G169" s="28"/>
+      <c r="H169" s="28"/>
       <c r="I169" s="28">
         <v>1</v>
       </c>
-      <c r="J169" s="34" t="s">
-        <v>596</v>
-      </c>
+      <c r="J169" s="34"/>
       <c r="K169" s="34" t="s">
-        <v>597</v>
+        <v>545</v>
       </c>
       <c r="L169" s="34"/>
-      <c r="M169" s="34"/>
+      <c r="M169" s="34" t="s">
+        <v>546</v>
+      </c>
       <c r="N169" s="34"/>
       <c r="O169" s="2"/>
       <c r="P169" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="Q169" s="35"/>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A170" s="28"/>
-      <c r="B170" s="21"/>
-      <c r="C170" s="28">
-        <v>151</v>
-      </c>
-      <c r="D170" s="21"/>
-      <c r="E170" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="F170" s="21"/>
-      <c r="G170" s="28"/>
-      <c r="H170" s="28"/>
-      <c r="I170" s="28">
-        <v>1</v>
-      </c>
-      <c r="J170" s="34"/>
-      <c r="K170" s="34" t="s">
-        <v>599</v>
-      </c>
-      <c r="L170" s="34"/>
-      <c r="M170" s="34" t="s">
-        <v>600</v>
-      </c>
-      <c r="N170" s="34"/>
-      <c r="O170" s="2"/>
-      <c r="P170" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="Q170" s="42"/>
-    </row>
-    <row r="171" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A171" s="36">
+        <v>547</v>
+      </c>
+      <c r="Q169" s="42"/>
+    </row>
+    <row r="170" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A170" s="36">
         <v>103</v>
       </c>
-      <c r="B171" s="3"/>
-      <c r="C171" s="36"/>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3">
+      <c r="B170" s="3">
+        <v>68.72</v>
+      </c>
+      <c r="C170" s="36"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="G170" s="36">
         <v>43</v>
       </c>
-      <c r="F171" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="G171" s="36">
-        <v>208</v>
-      </c>
-      <c r="H171" s="36"/>
-      <c r="I171" s="36"/>
-      <c r="J171" s="40"/>
-      <c r="K171" s="40"/>
-      <c r="L171" s="40"/>
-      <c r="M171" s="40"/>
-      <c r="N171" s="40"/>
-      <c r="O171" s="1"/>
-      <c r="P171" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="Q171" s="35"/>
+      <c r="H170" s="36">
+        <v>1</v>
+      </c>
+      <c r="I170" s="36"/>
+      <c r="J170" s="40"/>
+      <c r="K170" s="40"/>
+      <c r="L170" s="40"/>
+      <c r="M170" s="40"/>
+      <c r="N170" s="40"/>
+      <c r="O170" s="1"/>
+      <c r="P170" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="Q170" s="35"/>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A171" s="28">
+        <v>71</v>
+      </c>
+      <c r="B171" s="21"/>
+      <c r="C171" s="28">
+        <v>109</v>
+      </c>
+      <c r="D171" s="21"/>
+      <c r="E171" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="F171" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="G171" s="28">
+        <v>103</v>
+      </c>
+      <c r="H171" s="28">
+        <v>1</v>
+      </c>
+      <c r="I171" s="28">
+        <v>1</v>
+      </c>
+      <c r="J171" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="K171" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="L171" s="34"/>
+      <c r="M171" s="34"/>
+      <c r="N171" s="34"/>
+      <c r="O171" s="2"/>
+      <c r="P171" s="2" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="172" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="36">
@@ -12686,7 +12653,7 @@
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="3" t="s">
-        <v>603</v>
+        <v>549</v>
       </c>
       <c r="F172" s="41" t="s">
         <v>181</v>
@@ -12695,23 +12662,23 @@
         <v>103</v>
       </c>
       <c r="H172" s="36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I172" s="36">
         <v>1</v>
       </c>
       <c r="J172" s="40" t="s">
-        <v>604</v>
+        <v>550</v>
       </c>
       <c r="K172" s="40" t="s">
-        <v>605</v>
+        <v>551</v>
       </c>
       <c r="L172" s="40"/>
       <c r="M172" s="40"/>
       <c r="N172" s="40"/>
       <c r="O172" s="1"/>
       <c r="P172" s="1" t="s">
-        <v>606</v>
+        <v>552</v>
       </c>
       <c r="Q172" s="35"/>
     </row>
@@ -12727,7 +12694,7 @@
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="3" t="s">
-        <v>607</v>
+        <v>553</v>
       </c>
       <c r="F173" s="41" t="s">
         <v>182</v>
@@ -12736,25 +12703,25 @@
         <v>103</v>
       </c>
       <c r="H173" s="36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I173" s="36">
         <v>1</v>
       </c>
       <c r="J173" s="40" t="s">
-        <v>608</v>
+        <v>554</v>
       </c>
       <c r="K173" s="40" t="s">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="L173" s="40"/>
       <c r="M173" s="40" t="s">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="N173" s="40"/>
       <c r="O173" s="1"/>
       <c r="P173" s="1" t="s">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="Q173" s="35"/>
     </row>
@@ -12770,7 +12737,7 @@
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="3" t="s">
-        <v>612</v>
+        <v>558</v>
       </c>
       <c r="F174" s="41" t="s">
         <v>183</v>
@@ -12779,53 +12746,55 @@
         <v>103</v>
       </c>
       <c r="H174" s="36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I174" s="36">
         <v>1</v>
       </c>
       <c r="J174" s="40" t="s">
-        <v>613</v>
+        <v>559</v>
       </c>
       <c r="K174" s="40" t="s">
-        <v>614</v>
+        <v>560</v>
       </c>
       <c r="L174" s="40"/>
       <c r="M174" s="40" t="s">
-        <v>615</v>
+        <v>561</v>
       </c>
       <c r="N174" s="40"/>
       <c r="O174" s="1"/>
       <c r="P174" s="1" t="s">
-        <v>616</v>
+        <v>562</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A175" s="28">
         <v>107</v>
       </c>
-      <c r="B175" s="21"/>
+      <c r="B175" s="21">
+        <v>103</v>
+      </c>
       <c r="C175" s="28">
         <v>155</v>
       </c>
       <c r="D175" s="21"/>
       <c r="E175" s="21" t="s">
-        <v>617</v>
+        <v>563</v>
       </c>
       <c r="F175" s="21" t="s">
         <v>36</v>
       </c>
       <c r="G175" s="28">
-        <v>208</v>
+        <v>43</v>
       </c>
       <c r="H175" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I175" s="28">
         <v>1</v>
       </c>
       <c r="J175" s="34" t="s">
-        <v>618</v>
+        <v>564</v>
       </c>
       <c r="K175" s="34"/>
       <c r="L175" s="34"/>
@@ -12833,29 +12802,29 @@
       <c r="N175" s="34"/>
       <c r="O175" s="2"/>
       <c r="P175" s="2" t="s">
-        <v>619</v>
+        <v>565</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A176" s="36">
-        <v>108</v>
-      </c>
-      <c r="B176" s="3"/>
+        <v>209</v>
+      </c>
+      <c r="B176" s="3">
+        <v>107</v>
+      </c>
       <c r="C176" s="40"/>
       <c r="D176" s="3"/>
-      <c r="E176" s="3" t="s">
-        <v>620</v>
-      </c>
+      <c r="E176" s="3"/>
       <c r="F176" s="3" t="s">
         <v>184</v>
       </c>
       <c r="G176" s="36">
-        <v>208</v>
-      </c>
-      <c r="H176" s="40"/>
-      <c r="I176" s="36">
-        <v>1</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="H176" s="95">
+        <v>1</v>
+      </c>
+      <c r="I176" s="36"/>
       <c r="J176" s="40"/>
       <c r="K176" s="40"/>
       <c r="L176" s="40"/>
@@ -12863,33 +12832,35 @@
       <c r="N176" s="40"/>
       <c r="O176" s="1"/>
       <c r="P176" s="1" t="s">
-        <v>622</v>
+        <v>567</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" s="36">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="36">
         <v>156</v>
       </c>
       <c r="D177" s="3"/>
-      <c r="E177" s="3" t="s">
-        <v>620</v>
+      <c r="E177" s="93" t="s">
+        <v>650</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>184</v>
       </c>
       <c r="G177" s="36">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="H177" s="36">
-        <v>2</v>
-      </c>
-      <c r="I177" s="36"/>
+        <v>1</v>
+      </c>
+      <c r="I177" s="36">
+        <v>1</v>
+      </c>
       <c r="J177" s="40" t="s">
-        <v>621</v>
+        <v>566</v>
       </c>
       <c r="K177" s="40"/>
       <c r="L177" s="40"/>
@@ -12903,29 +12874,29 @@
         <v>109</v>
       </c>
       <c r="B178" s="3">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="C178" s="36">
         <v>157</v>
       </c>
       <c r="D178" s="3"/>
-      <c r="E178" s="3" t="s">
-        <v>623</v>
+      <c r="E178" s="93" t="s">
+        <v>651</v>
       </c>
       <c r="F178" s="41" t="s">
         <v>185</v>
       </c>
       <c r="G178" s="36">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="H178" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I178" s="36">
         <v>1</v>
       </c>
       <c r="J178" s="40" t="s">
-        <v>624</v>
+        <v>568</v>
       </c>
       <c r="K178" s="40"/>
       <c r="L178" s="40"/>
@@ -12933,7 +12904,7 @@
       <c r="N178" s="40"/>
       <c r="O178" s="1"/>
       <c r="P178" s="1" t="s">
-        <v>625</v>
+        <v>569</v>
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.2">
@@ -12997,10 +12968,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="96"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
@@ -13018,17 +12989,17 @@
         <v>3</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>626</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
+      <c r="A5" s="90"/>
+      <c r="B5" s="90"/>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>627</v>
+        <v>571</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -13043,18 +13014,18 @@
       <c r="B6" s="21"/>
       <c r="C6" s="2"/>
       <c r="E6" s="8" t="s">
-        <v>628</v>
+        <v>572</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>629</v>
+        <v>573</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>630</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="64" x14ac:dyDescent="0.2">
@@ -13063,10 +13034,10 @@
       <c r="C7" s="2"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>631</v>
+        <v>575</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>632</v>
+        <v>576</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
@@ -13080,10 +13051,10 @@
       <c r="C8" s="2"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>634</v>
+        <v>578</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
@@ -13096,7 +13067,7 @@
       <c r="B9" s="21"/>
       <c r="C9" s="2"/>
       <c r="E9" s="7" t="s">
-        <v>635</v>
+        <v>579</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="1"/>
@@ -13105,7 +13076,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>636</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -13114,7 +13085,7 @@
       <c r="C10" s="2"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>637</v>
+        <v>581</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
@@ -13124,7 +13095,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>636</v>
+        <v>580</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -13133,17 +13104,17 @@
       <c r="C11" s="2"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>638</v>
+        <v>582</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>639</v>
+        <v>583</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>640</v>
+        <v>584</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>636</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -13151,11 +13122,11 @@
       <c r="B12" s="21"/>
       <c r="C12" s="2"/>
       <c r="E12" s="8" t="s">
-        <v>641</v>
+        <v>585</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="2" t="s">
-        <v>642</v>
+        <v>586</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
@@ -13169,10 +13140,10 @@
       <c r="C13" s="2"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>643</v>
+        <v>587</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>642</v>
+        <v>586</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
@@ -13186,10 +13157,10 @@
       <c r="C14" s="2"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>644</v>
+        <v>588</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>642</v>
+        <v>586</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
@@ -13203,14 +13174,14 @@
       <c r="C15" s="2"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8" t="s">
-        <v>645</v>
+        <v>589</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>642</v>
+        <v>586</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>646</v>
+        <v>590</v>
       </c>
       <c r="J15" s="2"/>
     </row>
@@ -13219,7 +13190,7 @@
       <c r="B16" s="21"/>
       <c r="C16" s="2"/>
       <c r="E16" s="7" t="s">
-        <v>647</v>
+        <v>591</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="1"/>
@@ -13232,7 +13203,7 @@
       <c r="B17" s="21"/>
       <c r="C17" s="2"/>
       <c r="E17" s="8" t="s">
-        <v>648</v>
+        <v>592</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="2"/>
@@ -13255,13 +13226,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>649</v>
+        <v>593</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>650</v>
+        <v>594</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>83</v>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FF76D7-6411-0B46-9B67-3258444951C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB50F974-8CB0-45A5-B96E-574579D5AE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17660" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25725" yWindow="90" windowWidth="25890" windowHeight="20805" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFP" sheetId="1" r:id="rId1"/>
     <sheet name="OFP_Import" sheetId="2" r:id="rId2"/>
     <sheet name="AuD" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="661">
   <si>
     <t>Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -2049,7 +2049,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2444,14 +2444,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2469,6 +2461,14 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2661,9 +2661,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2701,7 +2701,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2807,7 +2807,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2949,7 +2949,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2958,29 +2958,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I245"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="35.6640625" customWidth="1"/>
-    <col min="3" max="4" width="7.1640625" customWidth="1"/>
+    <col min="1" max="2" width="35.7109375" customWidth="1"/>
+    <col min="3" max="4" width="7.140625" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="9" width="28.5" customWidth="1"/>
+    <col min="6" max="9" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="89" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="89"/>
+      <c r="B4" s="95"/>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
@@ -2998,11 +2998,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="90" t="s">
+    <row r="5" spans="1:9" ht="30">
+      <c r="A5" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="90"/>
+      <c r="B5" s="96"/>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
@@ -3018,11 +3018,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="87" t="s">
+    <row r="6" spans="1:9" ht="30">
+      <c r="A6" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="87"/>
+      <c r="B6" s="93"/>
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3038,11 +3038,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="88" t="s">
+    <row r="7" spans="1:9" ht="30">
+      <c r="A7" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="88"/>
+      <c r="B7" s="94"/>
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
@@ -3058,11 +3058,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="87" t="s">
+    <row r="8" spans="1:9" ht="60">
+      <c r="A8" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="87"/>
+      <c r="B8" s="93"/>
       <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="45">
       <c r="A9" s="7" t="s">
         <v>28</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="45">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
         <v>32</v>
@@ -3124,7 +3124,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="45">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
         <v>36</v>
@@ -3146,7 +3146,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="30">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
         <v>42</v>
@@ -3168,7 +3168,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="75">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
         <v>46</v>
@@ -3190,7 +3190,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="60">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>50</v>
@@ -3210,11 +3210,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="87" t="s">
+    <row r="15" spans="1:9">
+      <c r="A15" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="87"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="2" t="s">
         <v>56</v>
       </c>
@@ -3230,11 +3230,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A16" s="88" t="s">
+    <row r="16" spans="1:9" ht="45">
+      <c r="A16" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="88"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="1" t="s">
         <v>61</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="60">
       <c r="A17" s="8" t="s">
         <v>65</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8">
       <c r="A18" s="8"/>
       <c r="B18" s="2" t="s">
         <v>67</v>
@@ -3268,7 +3268,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8">
       <c r="A19" s="8"/>
       <c r="B19" s="2" t="s">
         <v>69</v>
@@ -3277,7 +3277,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8">
       <c r="A20" s="8"/>
       <c r="B20" s="2" t="s">
         <v>71</v>
@@ -3286,7 +3286,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8">
       <c r="A21" s="8"/>
       <c r="B21" s="2" t="s">
         <v>73</v>
@@ -3295,7 +3295,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8">
       <c r="A22" s="8"/>
       <c r="B22" s="2" t="s">
         <v>75</v>
@@ -3304,7 +3304,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="45">
       <c r="A24" s="5" t="s">
         <v>77</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
         <v>67</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="13" customFormat="1">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -3358,7 +3358,7 @@
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
     </row>
-    <row r="27" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="13" customFormat="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>88</v>
@@ -3372,7 +3372,7 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="13" customFormat="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="11"/>
@@ -3384,7 +3384,7 @@
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
         <v>90</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
         <v>91</v>
@@ -3426,7 +3426,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="7"/>
@@ -3438,7 +3438,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
         <v>92</v>
       </c>
@@ -3450,7 +3450,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" s="13" customFormat="1">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
@@ -3466,7 +3466,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" s="13" customFormat="1">
       <c r="A35" s="2"/>
       <c r="B35" s="17"/>
       <c r="C35" s="2"/>
@@ -3478,7 +3478,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" s="13" customFormat="1">
       <c r="A36" s="2"/>
       <c r="B36" s="17" t="s">
         <v>94</v>
@@ -3490,7 +3490,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" s="13" customFormat="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
         <v>95</v>
@@ -3504,7 +3504,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" s="13" customFormat="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3516,7 +3516,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" s="13" customFormat="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>96</v>
@@ -3530,7 +3530,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" s="13" customFormat="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3542,7 +3542,7 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" s="13" customFormat="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
         <v>97</v>
@@ -3556,7 +3556,7 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" s="13" customFormat="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3568,7 +3568,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" s="13" customFormat="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
         <v>98</v>
@@ -3582,7 +3582,7 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" s="13" customFormat="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3594,7 +3594,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" s="13" customFormat="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
         <v>99</v>
@@ -3608,7 +3608,7 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" s="13" customFormat="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3620,7 +3620,7 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" s="13" customFormat="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
         <v>100</v>
@@ -3634,7 +3634,7 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" s="13" customFormat="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3646,7 +3646,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" s="13" customFormat="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
         <v>101</v>
@@ -3660,7 +3660,7 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" s="13" customFormat="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3672,7 +3672,7 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" s="13" customFormat="1">
       <c r="A51" s="1" t="s">
         <v>102</v>
       </c>
@@ -3684,7 +3684,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" s="13" customFormat="1">
       <c r="A52" s="1" t="s">
         <v>85</v>
       </c>
@@ -3698,7 +3698,7 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
         <v>103</v>
@@ -3712,7 +3712,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3724,7 +3724,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
         <v>105</v>
@@ -3736,7 +3736,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
         <v>106</v>
@@ -3750,7 +3750,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3762,7 +3762,7 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
         <v>107</v>
@@ -3776,7 +3776,7 @@
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3788,7 +3788,7 @@
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3800,7 +3800,7 @@
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8">
       <c r="A61" s="2" t="s">
         <v>108</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
         <v>85</v>
       </c>
@@ -3828,7 +3828,7 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3840,7 +3840,7 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3852,7 +3852,7 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>109</v>
@@ -3866,7 +3866,7 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>110</v>
@@ -3880,7 +3880,7 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3892,7 +3892,7 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>111</v>
@@ -3906,7 +3906,7 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3918,7 +3918,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>112</v>
@@ -3932,7 +3932,7 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3944,7 +3944,7 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3956,7 +3956,7 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8">
       <c r="A73" s="2"/>
       <c r="B73" s="2" t="s">
         <v>113</v>
@@ -3970,7 +3970,7 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8">
       <c r="A74" s="2"/>
       <c r="B74" s="2" t="s">
         <v>114</v>
@@ -3984,7 +3984,7 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3996,7 +3996,7 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8">
       <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>73</v>
@@ -4010,7 +4010,7 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4022,7 +4022,7 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" ht="30">
       <c r="A78" s="7" t="s">
         <v>115</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8">
       <c r="A79" s="7" t="s">
         <v>85</v>
       </c>
@@ -4052,7 +4052,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
     </row>
-    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8">
       <c r="A80" s="7" t="s">
         <v>85</v>
       </c>
@@ -4068,7 +4068,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="1"/>
@@ -4080,7 +4080,7 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8">
       <c r="A82" s="8" t="s">
         <v>60</v>
       </c>
@@ -4092,7 +4092,7 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>118</v>
@@ -4106,7 +4106,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4118,7 +4118,7 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8">
       <c r="A85" s="2" t="s">
         <v>85</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4146,7 +4146,7 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4158,7 +4158,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
         <v>119</v>
@@ -4174,7 +4174,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
         <v>121</v>
       </c>
@@ -4188,7 +4188,7 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
         <v>85</v>
       </c>
@@ -4202,7 +4202,7 @@
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4214,7 +4214,7 @@
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4226,7 +4226,7 @@
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4238,7 +4238,7 @@
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4250,7 +4250,7 @@
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
         <v>109</v>
@@ -4264,7 +4264,7 @@
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4276,7 +4276,7 @@
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
         <v>122</v>
       </c>
@@ -4288,7 +4288,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8">
       <c r="A98" s="2"/>
       <c r="B98" s="2" t="s">
         <v>123</v>
@@ -4302,7 +4302,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4314,7 +4314,7 @@
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4326,7 +4326,7 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8">
       <c r="A101" s="2"/>
       <c r="B101" s="2" t="s">
         <v>124</v>
@@ -4340,7 +4340,7 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4352,7 +4352,7 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4364,7 +4364,7 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4376,7 +4376,7 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8">
       <c r="A105" s="2"/>
       <c r="B105" s="2" t="s">
         <v>125</v>
@@ -4390,7 +4390,7 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4402,7 +4402,7 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4414,7 +4414,7 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
         <v>126</v>
       </c>
@@ -4426,7 +4426,7 @@
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
         <v>85</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4454,7 +4454,7 @@
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8">
       <c r="A111" s="1"/>
       <c r="B111" s="1" t="s">
         <v>128</v>
@@ -4468,7 +4468,7 @@
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
         <v>129</v>
@@ -4482,7 +4482,7 @@
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
     </row>
-    <row r="114" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" ht="30">
       <c r="A114" s="19" t="s">
         <v>130</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8">
       <c r="A115" s="2" t="s">
         <v>131</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8">
       <c r="A116" s="3" t="s">
         <v>132</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
         <v>131</v>
       </c>
@@ -4538,7 +4538,7 @@
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
         <v>92</v>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4564,7 +4564,7 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
         <v>131</v>
       </c>
@@ -4580,7 +4580,7 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4592,7 +4592,7 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8">
       <c r="A122" s="2"/>
       <c r="B122" s="2" t="s">
         <v>134</v>
@@ -4606,7 +4606,7 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -4618,7 +4618,7 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8">
       <c r="A124" s="2"/>
       <c r="B124" s="2" t="s">
         <v>135</v>
@@ -4632,7 +4632,7 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -4644,7 +4644,7 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8">
       <c r="A126" s="2"/>
       <c r="B126" s="2" t="s">
         <v>97</v>
@@ -4658,7 +4658,7 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -4670,7 +4670,7 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8">
       <c r="A128" s="2"/>
       <c r="B128" s="2" t="s">
         <v>93</v>
@@ -4684,7 +4684,7 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -4696,7 +4696,7 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -4708,7 +4708,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8">
       <c r="A131" s="2"/>
       <c r="B131" s="2" t="s">
         <v>136</v>
@@ -4722,7 +4722,7 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -4734,7 +4734,7 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8">
       <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
         <v>137</v>
@@ -4748,7 +4748,7 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -4760,7 +4760,7 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8">
       <c r="A135" s="2"/>
       <c r="B135" s="2" t="s">
         <v>138</v>
@@ -4774,7 +4774,7 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -4786,7 +4786,7 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8">
       <c r="A137" s="2"/>
       <c r="B137" s="2" t="s">
         <v>139</v>
@@ -4800,7 +4800,7 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -4812,7 +4812,7 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
         <v>90</v>
       </c>
@@ -4826,7 +4826,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
         <v>131</v>
       </c>
@@ -4840,7 +4840,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8">
       <c r="A141" s="2" t="s">
         <v>140</v>
       </c>
@@ -4852,7 +4852,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
         <v>131</v>
       </c>
@@ -4868,7 +4868,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -4880,7 +4880,7 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8">
       <c r="A144" s="2"/>
       <c r="B144" s="2" t="s">
         <v>142</v>
@@ -4894,7 +4894,7 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -4906,7 +4906,7 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8">
       <c r="A146" s="2"/>
       <c r="B146" s="2" t="s">
         <v>143</v>
@@ -4920,7 +4920,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -4932,7 +4932,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8">
       <c r="A148" s="2"/>
       <c r="B148" s="2" t="s">
         <v>144</v>
@@ -4946,7 +4946,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -4958,7 +4958,7 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8">
       <c r="A150" s="2"/>
       <c r="B150" s="2" t="s">
         <v>145</v>
@@ -4972,7 +4972,7 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -4984,7 +4984,7 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8">
       <c r="A152" s="1" t="s">
         <v>146</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8">
       <c r="A153" s="1" t="s">
         <v>131</v>
       </c>
@@ -5012,7 +5012,7 @@
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5024,7 +5024,7 @@
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8">
       <c r="A155" s="1"/>
       <c r="B155" s="1" t="s">
         <v>147</v>
@@ -5038,7 +5038,7 @@
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5050,7 +5050,7 @@
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8">
       <c r="A157" s="1"/>
       <c r="B157" s="1" t="s">
         <v>105</v>
@@ -5064,7 +5064,7 @@
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5076,7 +5076,7 @@
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8">
       <c r="A159" s="1"/>
       <c r="B159" s="1" t="s">
         <v>106</v>
@@ -5090,7 +5090,7 @@
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5102,7 +5102,7 @@
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8">
       <c r="A161" s="1"/>
       <c r="B161" s="1" t="s">
         <v>148</v>
@@ -5116,7 +5116,7 @@
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5128,7 +5128,7 @@
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
         <v>149</v>
@@ -5142,7 +5142,7 @@
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5154,7 +5154,7 @@
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8">
       <c r="A165" s="17" t="s">
         <v>126</v>
       </c>
@@ -5166,7 +5166,7 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8">
       <c r="A166" s="2" t="s">
         <v>131</v>
       </c>
@@ -5182,7 +5182,7 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8">
       <c r="A167" s="17"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -5194,7 +5194,7 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8">
       <c r="A168" s="2"/>
       <c r="B168" s="2" t="s">
         <v>151</v>
@@ -5208,7 +5208,7 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -5220,7 +5220,7 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8">
       <c r="A170" s="2"/>
       <c r="B170" s="2" t="s">
         <v>152</v>
@@ -5234,7 +5234,7 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -5246,7 +5246,7 @@
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8">
       <c r="A172" s="1" t="s">
         <v>153</v>
       </c>
@@ -5258,7 +5258,7 @@
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8">
       <c r="A173" s="1" t="s">
         <v>131</v>
       </c>
@@ -5274,7 +5274,7 @@
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5286,7 +5286,7 @@
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8">
       <c r="A175" s="1"/>
       <c r="B175" s="1" t="s">
         <v>155</v>
@@ -5300,7 +5300,7 @@
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5312,7 +5312,7 @@
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8">
       <c r="A177" s="1"/>
       <c r="B177" s="1" t="s">
         <v>156</v>
@@ -5326,7 +5326,7 @@
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5338,7 +5338,7 @@
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8">
       <c r="A179" s="1"/>
       <c r="B179" s="1" t="s">
         <v>157</v>
@@ -5352,7 +5352,7 @@
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5364,7 +5364,7 @@
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8">
       <c r="A181" s="1"/>
       <c r="B181" s="1" t="s">
         <v>158</v>
@@ -5378,7 +5378,7 @@
       <c r="G181" s="1"/>
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5390,7 +5390,7 @@
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8">
       <c r="A183" s="1"/>
       <c r="B183" s="1" t="s">
         <v>159</v>
@@ -5404,7 +5404,7 @@
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5416,7 +5416,7 @@
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5428,7 +5428,7 @@
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8">
       <c r="A186" s="2" t="s">
         <v>160</v>
       </c>
@@ -5444,7 +5444,7 @@
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8">
       <c r="A187" s="2" t="s">
         <v>131</v>
       </c>
@@ -5458,7 +5458,7 @@
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8">
       <c r="A188" s="2"/>
       <c r="B188" s="2" t="s">
         <v>162</v>
@@ -5472,7 +5472,7 @@
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -5484,7 +5484,7 @@
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:8">
       <c r="A190" s="2"/>
       <c r="B190" s="2" t="s">
         <v>163</v>
@@ -5498,7 +5498,7 @@
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:8">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -5510,7 +5510,7 @@
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:8">
       <c r="A192" s="2"/>
       <c r="B192" s="2" t="s">
         <v>121</v>
@@ -5524,7 +5524,7 @@
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -5536,7 +5536,7 @@
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8">
       <c r="A194" s="1" t="s">
         <v>164</v>
       </c>
@@ -5552,7 +5552,7 @@
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5564,7 +5564,7 @@
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8">
       <c r="A196" s="1"/>
       <c r="B196" s="1" t="s">
         <v>165</v>
@@ -5578,7 +5578,7 @@
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5590,7 +5590,7 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8">
       <c r="A198" s="1"/>
       <c r="B198" s="1" t="s">
         <v>155</v>
@@ -5604,7 +5604,7 @@
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5616,7 +5616,7 @@
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8">
       <c r="A200" s="1"/>
       <c r="B200" s="1" t="s">
         <v>153</v>
@@ -5630,7 +5630,7 @@
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -5642,7 +5642,7 @@
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8">
       <c r="A202" s="1"/>
       <c r="B202" s="1" t="s">
         <v>166</v>
@@ -5656,7 +5656,7 @@
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -5668,7 +5668,7 @@
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8">
       <c r="A204" s="1"/>
       <c r="B204" s="1" t="s">
         <v>167</v>
@@ -5682,7 +5682,7 @@
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -5694,7 +5694,7 @@
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8">
       <c r="A206" s="1"/>
       <c r="B206" s="1" t="s">
         <v>168</v>
@@ -5708,7 +5708,7 @@
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -5720,7 +5720,7 @@
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8">
       <c r="A208" s="1"/>
       <c r="B208" s="1" t="s">
         <v>169</v>
@@ -5734,7 +5734,7 @@
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -5746,7 +5746,7 @@
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8">
       <c r="A210" s="1"/>
       <c r="B210" s="1" t="s">
         <v>170</v>
@@ -5760,7 +5760,7 @@
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -5772,7 +5772,7 @@
       <c r="G211" s="1"/>
       <c r="H211" s="1"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8">
       <c r="A212" s="2" t="s">
         <v>171</v>
       </c>
@@ -5788,7 +5788,7 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -5800,7 +5800,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
         <v>131</v>
       </c>
@@ -5816,7 +5816,7 @@
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -5828,7 +5828,7 @@
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8">
       <c r="A216" s="2" t="s">
         <v>164</v>
       </c>
@@ -5844,7 +5844,7 @@
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -5856,7 +5856,7 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -5868,7 +5868,7 @@
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8">
       <c r="A219" s="2"/>
       <c r="B219" s="2" t="s">
         <v>171</v>
@@ -5882,7 +5882,7 @@
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -5894,7 +5894,7 @@
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -5906,7 +5906,7 @@
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8">
       <c r="A222" s="1" t="s">
         <v>175</v>
       </c>
@@ -5920,7 +5920,7 @@
       <c r="G222" s="1"/>
       <c r="H222" s="1"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8">
       <c r="A223" s="1" t="s">
         <v>131</v>
       </c>
@@ -5934,7 +5934,7 @@
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8">
       <c r="A224" s="1"/>
       <c r="B224" s="1" t="s">
         <v>176</v>
@@ -5948,7 +5948,7 @@
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -5960,7 +5960,7 @@
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
         <v>177</v>
       </c>
@@ -5976,7 +5976,7 @@
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -5988,7 +5988,7 @@
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8">
       <c r="A228" s="2" t="s">
         <v>131</v>
       </c>
@@ -6004,7 +6004,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -6016,7 +6016,7 @@
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -6028,7 +6028,7 @@
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -6040,7 +6040,7 @@
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8">
       <c r="A232" s="1" t="s">
         <v>180</v>
       </c>
@@ -6052,7 +6052,7 @@
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8">
       <c r="A233" s="1"/>
       <c r="B233" s="1" t="s">
         <v>181</v>
@@ -6066,7 +6066,7 @@
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -6078,7 +6078,7 @@
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8">
       <c r="A235" s="1" t="s">
         <v>131</v>
       </c>
@@ -6094,7 +6094,7 @@
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -6106,7 +6106,7 @@
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -6118,7 +6118,7 @@
       <c r="G237" s="1"/>
       <c r="H237" s="1"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8">
       <c r="A238" s="1"/>
       <c r="B238" s="1" t="s">
         <v>183</v>
@@ -6132,7 +6132,7 @@
       <c r="G238" s="1"/>
       <c r="H238" s="1"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -6144,7 +6144,7 @@
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -6156,7 +6156,7 @@
       <c r="G240" s="1"/>
       <c r="H240" s="1"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8">
       <c r="A241" s="2" t="s">
         <v>36</v>
       </c>
@@ -6170,7 +6170,7 @@
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8">
       <c r="A242" s="2" t="s">
         <v>131</v>
       </c>
@@ -6184,7 +6184,7 @@
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8">
       <c r="A243" s="1" t="s">
         <v>184</v>
       </c>
@@ -6198,7 +6198,7 @@
       <c r="G243" s="1"/>
       <c r="H243" s="1"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8">
       <c r="A244" s="1" t="s">
         <v>131</v>
       </c>
@@ -6214,7 +6214,7 @@
       <c r="G244" s="1"/>
       <c r="H244" s="1"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -6435,29 +6435,29 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMJ180"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AMJ186"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.5" customWidth="1"/>
-    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="5" width="18.5" style="22" customWidth="1"/>
-    <col min="6" max="6" width="43.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" customWidth="1"/>
-    <col min="10" max="10" width="36.1640625" customWidth="1"/>
-    <col min="11" max="11" width="37.6640625" customWidth="1"/>
-    <col min="12" max="12" width="45.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="22" customWidth="1"/>
+    <col min="6" max="6" width="43.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" customWidth="1"/>
+    <col min="10" max="10" width="36.140625" customWidth="1"/>
+    <col min="11" max="11" width="37.7109375" customWidth="1"/>
+    <col min="12" max="12" width="45.140625" customWidth="1"/>
     <col min="13" max="13" width="41" customWidth="1"/>
-    <col min="14" max="14" width="32.6640625" customWidth="1"/>
+    <col min="14" max="14" width="32.7109375" customWidth="1"/>
     <col min="15" max="15" width="32" customWidth="1"/>
-    <col min="16" max="16" width="63.6640625" customWidth="1"/>
-    <col min="1024" max="1024" width="11.5" customWidth="1"/>
+    <col min="16" max="16" width="63.7109375" customWidth="1"/>
+    <col min="1024" max="1024" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="30">
       <c r="A1" s="5" t="s">
         <v>186</v>
       </c>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Q1" s="24"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -6536,7 +6536,7 @@
       <c r="O2" s="5"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" s="28">
         <v>4</v>
       </c>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="Q3" s="35"/>
     </row>
-    <row r="4" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18">
       <c r="A4" s="28">
         <v>5</v>
       </c>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="Q4" s="35"/>
     </row>
-    <row r="5" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18">
       <c r="A5" s="36">
         <v>6</v>
       </c>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18">
       <c r="A6" s="36">
         <v>7</v>
       </c>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="Q6" s="42"/>
     </row>
-    <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18">
       <c r="A7" s="28">
         <v>210</v>
       </c>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Q7" s="35"/>
     </row>
-    <row r="8" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18">
       <c r="A8" s="28">
         <v>8</v>
       </c>
@@ -6746,7 +6746,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="19"/>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="87" t="s">
         <v>607</v>
       </c>
       <c r="F8" s="21" t="s">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Q8" s="35"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18">
       <c r="A9" s="28">
         <v>9</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="21"/>
-      <c r="E9" s="92" t="s">
+      <c r="E9" s="88" t="s">
         <v>608</v>
       </c>
       <c r="F9" s="44" t="s">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="Q9" s="42"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18">
       <c r="A10" s="28"/>
       <c r="B10" s="21"/>
       <c r="C10" s="28">
         <v>7</v>
       </c>
       <c r="D10" s="21"/>
-      <c r="E10" s="92" t="s">
+      <c r="E10" s="88" t="s">
         <v>608</v>
       </c>
       <c r="F10" s="44" t="s">
@@ -6848,14 +6848,14 @@
       </c>
       <c r="Q10" s="42"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18">
       <c r="A11" s="28"/>
       <c r="B11" s="21"/>
       <c r="C11" s="28">
         <v>8</v>
       </c>
       <c r="D11" s="21"/>
-      <c r="E11" s="92" t="s">
+      <c r="E11" s="88" t="s">
         <v>608</v>
       </c>
       <c r="F11" s="44" t="s">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="Q11" s="42"/>
     </row>
-    <row r="12" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18">
       <c r="A12" s="28">
         <v>10</v>
       </c>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="92" t="s">
+      <c r="E12" s="88" t="s">
         <v>609</v>
       </c>
       <c r="F12" s="44" t="s">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="Q12" s="35"/>
     </row>
-    <row r="13" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18">
       <c r="A13" s="28">
         <v>11</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="21"/>
-      <c r="E13" s="92" t="s">
+      <c r="E13" s="88" t="s">
         <v>610</v>
       </c>
       <c r="F13" s="46" t="s">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="Q13" s="35"/>
     </row>
-    <row r="14" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18">
       <c r="A14" s="28">
         <v>12</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="21"/>
-      <c r="E14" s="92" t="s">
+      <c r="E14" s="88" t="s">
         <v>611</v>
       </c>
       <c r="F14" s="46" t="s">
@@ -6998,14 +6998,14 @@
       </c>
       <c r="Q14" s="35"/>
     </row>
-    <row r="15" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18">
       <c r="A15" s="28"/>
       <c r="B15" s="21"/>
       <c r="C15" s="28">
         <v>11</v>
       </c>
       <c r="D15" s="21"/>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="88" t="s">
         <v>611</v>
       </c>
       <c r="F15" s="46" t="s">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="Q15" s="35"/>
     </row>
-    <row r="16" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18">
       <c r="A16" s="28">
         <v>13</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="21"/>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="88" t="s">
         <v>612</v>
       </c>
       <c r="F16" s="46" t="s">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="Q16" s="35"/>
     </row>
-    <row r="17" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1024">
       <c r="A17" s="28">
         <v>14</v>
       </c>
@@ -7081,7 +7081,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="21"/>
-      <c r="E17" s="92" t="s">
+      <c r="E17" s="88" t="s">
         <v>613</v>
       </c>
       <c r="F17" s="46" t="s">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Q17" s="35"/>
     </row>
-    <row r="18" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1024">
       <c r="A18" s="28">
         <v>16</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>14</v>
       </c>
       <c r="D18" s="21"/>
-      <c r="E18" s="92" t="s">
+      <c r="E18" s="88" t="s">
         <v>614</v>
       </c>
       <c r="F18" s="33" t="s">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="Q18" s="35"/>
     </row>
-    <row r="19" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1024">
       <c r="A19" s="28">
         <v>17</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="21"/>
-      <c r="E19" s="92" t="s">
+      <c r="E19" s="88" t="s">
         <v>615</v>
       </c>
       <c r="F19" s="33" t="s">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="Q19" s="35"/>
     </row>
-    <row r="20" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1024">
       <c r="A20" s="28">
         <v>15</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>16</v>
       </c>
       <c r="D20" s="21"/>
-      <c r="E20" s="92" t="s">
+      <c r="E20" s="88" t="s">
         <v>616</v>
       </c>
       <c r="F20" s="46" t="s">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="Q20" s="35"/>
     </row>
-    <row r="21" spans="1:1024" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1024" s="72" customFormat="1">
       <c r="A21" s="66">
         <v>201</v>
       </c>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="Q21" s="71"/>
     </row>
-    <row r="22" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1024">
       <c r="A22" s="36">
         <v>18</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="93" t="s">
+      <c r="E22" s="89" t="s">
         <v>617</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Q22" s="35"/>
     </row>
-    <row r="23" spans="1:1024" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1024">
       <c r="A23" s="36">
         <v>19</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="93" t="s">
+      <c r="E23" s="89" t="s">
         <v>618</v>
       </c>
       <c r="F23" s="41" t="s">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="Q23" s="42"/>
     </row>
-    <row r="24" spans="1:1024" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1024">
       <c r="A24" s="36"/>
       <c r="B24" s="3"/>
       <c r="C24" s="36">
         <v>19</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="93" t="s">
+      <c r="E24" s="89" t="s">
         <v>618</v>
       </c>
       <c r="F24" s="41" t="s">
@@ -7386,14 +7386,14 @@
       </c>
       <c r="Q24" s="42"/>
     </row>
-    <row r="25" spans="1:1024" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1024">
       <c r="A25" s="36"/>
       <c r="B25" s="3"/>
       <c r="C25" s="36">
         <v>20</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="93" t="s">
+      <c r="E25" s="89" t="s">
         <v>618</v>
       </c>
       <c r="F25" s="41" t="s">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="Q25" s="42"/>
     </row>
-    <row r="26" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1024">
       <c r="A26" s="36">
         <v>20</v>
       </c>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C26" s="36"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="93" t="s">
+      <c r="E26" s="89" t="s">
         <v>619</v>
       </c>
       <c r="F26" s="41" t="s">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="Q26" s="35"/>
     </row>
-    <row r="27" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1024">
       <c r="A27" s="36">
         <v>21</v>
       </c>
@@ -7461,7 +7461,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="93" t="s">
+      <c r="E27" s="89" t="s">
         <v>620</v>
       </c>
       <c r="F27" s="49" t="s">
@@ -7493,14 +7493,14 @@
       </c>
       <c r="Q27" s="35"/>
     </row>
-    <row r="28" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1024">
       <c r="A28" s="36"/>
       <c r="B28" s="3"/>
       <c r="C28" s="36">
         <v>22</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="93" t="s">
+      <c r="E28" s="89" t="s">
         <v>620</v>
       </c>
       <c r="F28" s="49" t="s">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="Q28" s="35"/>
     </row>
-    <row r="29" spans="1:1024" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1024">
       <c r="A29" s="36">
         <v>22</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>23</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="93" t="s">
+      <c r="E29" s="89" t="s">
         <v>621</v>
       </c>
       <c r="F29" s="49" t="s">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="Q29" s="42"/>
     </row>
-    <row r="30" spans="1:1024" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1024">
       <c r="A30" s="36"/>
       <c r="B30" s="3"/>
       <c r="C30" s="36">
         <v>24</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="93" t="s">
+      <c r="E30" s="89" t="s">
         <v>621</v>
       </c>
       <c r="F30" s="49" t="s">
@@ -7598,14 +7598,14 @@
       </c>
       <c r="Q30" s="42"/>
     </row>
-    <row r="31" spans="1:1024" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1024">
       <c r="A31" s="36"/>
       <c r="B31" s="3"/>
       <c r="C31" s="36">
         <v>25</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="93" t="s">
+      <c r="E31" s="89" t="s">
         <v>621</v>
       </c>
       <c r="F31" s="49" t="s">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="Q31" s="42"/>
     </row>
-    <row r="32" spans="1:1024" s="85" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1024" s="85" customFormat="1">
       <c r="A32" s="50">
         <v>211</v>
       </c>
@@ -7663,7 +7663,7 @@
       <c r="Q32" s="84"/>
       <c r="AMJ32" s="86"/>
     </row>
-    <row r="33" spans="1:1024" s="85" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1024" s="85" customFormat="1">
       <c r="A33" s="50">
         <v>39</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>27</v>
       </c>
       <c r="D33" s="51"/>
-      <c r="E33" s="94" t="s">
+      <c r="E33" s="90" t="s">
         <v>622</v>
       </c>
       <c r="F33" s="51" t="s">
@@ -7699,7 +7699,7 @@
       <c r="Q33" s="84"/>
       <c r="AMJ33" s="86"/>
     </row>
-    <row r="34" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1024" s="55" customFormat="1">
       <c r="A34" s="50">
         <v>40</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>28</v>
       </c>
       <c r="D34" s="51"/>
-      <c r="E34" s="94" t="s">
+      <c r="E34" s="90" t="s">
         <v>623</v>
       </c>
       <c r="F34" s="56" t="s">
@@ -7743,14 +7743,14 @@
       <c r="Q34" s="57"/>
       <c r="AMJ34"/>
     </row>
-    <row r="35" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1024" s="55" customFormat="1">
       <c r="A35" s="50"/>
       <c r="B35" s="51"/>
       <c r="C35" s="50">
         <v>29</v>
       </c>
       <c r="D35" s="51"/>
-      <c r="E35" s="94" t="s">
+      <c r="E35" s="90" t="s">
         <v>623</v>
       </c>
       <c r="F35" s="56" t="s">
@@ -7775,14 +7775,14 @@
       <c r="Q35" s="57"/>
       <c r="AMJ35"/>
     </row>
-    <row r="36" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1024" s="55" customFormat="1">
       <c r="A36" s="50"/>
       <c r="B36" s="51"/>
       <c r="C36" s="50">
         <v>30</v>
       </c>
       <c r="D36" s="51"/>
-      <c r="E36" s="94" t="s">
+      <c r="E36" s="90" t="s">
         <v>623</v>
       </c>
       <c r="F36" s="56" t="s">
@@ -7807,7 +7807,7 @@
       <c r="Q36" s="57"/>
       <c r="AMJ36"/>
     </row>
-    <row r="37" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1024" s="55" customFormat="1">
       <c r="A37" s="50">
         <v>41</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>31</v>
       </c>
       <c r="D37" s="51"/>
-      <c r="E37" s="94" t="s">
+      <c r="E37" s="90" t="s">
         <v>624</v>
       </c>
       <c r="F37" s="56" t="s">
@@ -7849,14 +7849,14 @@
       <c r="Q37" s="57"/>
       <c r="AMJ37"/>
     </row>
-    <row r="38" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1024" s="55" customFormat="1">
       <c r="A38" s="50"/>
       <c r="B38" s="51"/>
       <c r="C38" s="50">
         <v>32</v>
       </c>
       <c r="D38" s="51"/>
-      <c r="E38" s="94" t="s">
+      <c r="E38" s="90" t="s">
         <v>624</v>
       </c>
       <c r="F38" s="56" t="s">
@@ -7881,7 +7881,7 @@
       <c r="Q38" s="57"/>
       <c r="AMJ38"/>
     </row>
-    <row r="39" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1024" s="55" customFormat="1">
       <c r="A39" s="50">
         <v>42</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="51"/>
-      <c r="E39" s="94" t="s">
+      <c r="E39" s="90" t="s">
         <v>625</v>
       </c>
       <c r="F39" s="56" t="s">
@@ -7923,7 +7923,7 @@
       <c r="Q39" s="57"/>
       <c r="AMJ39"/>
     </row>
-    <row r="40" spans="1:1024" s="80" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1024" s="80" customFormat="1">
       <c r="A40" s="73">
         <v>202</v>
       </c>
@@ -7953,7 +7953,7 @@
       <c r="Q40" s="79"/>
       <c r="AMJ40" s="81"/>
     </row>
-    <row r="41" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1024" s="55" customFormat="1">
       <c r="A41" s="28">
         <v>23</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="21"/>
-      <c r="E41" s="92" t="s">
+      <c r="E41" s="88" t="s">
         <v>626</v>
       </c>
       <c r="F41" s="21" t="s">
@@ -7993,14 +7993,14 @@
       <c r="Q41" s="54"/>
       <c r="AMJ41"/>
     </row>
-    <row r="42" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1024" s="55" customFormat="1">
       <c r="A42" s="28"/>
       <c r="B42" s="21"/>
       <c r="C42" s="28">
         <v>36</v>
       </c>
       <c r="D42" s="21"/>
-      <c r="E42" s="92" t="s">
+      <c r="E42" s="88" t="s">
         <v>626</v>
       </c>
       <c r="F42" s="21" t="s">
@@ -8025,14 +8025,14 @@
       <c r="Q42" s="54"/>
       <c r="AMJ42"/>
     </row>
-    <row r="43" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1024" s="55" customFormat="1">
       <c r="A43" s="28"/>
       <c r="B43" s="21"/>
       <c r="C43" s="28">
         <v>37</v>
       </c>
       <c r="D43" s="21"/>
-      <c r="E43" s="92" t="s">
+      <c r="E43" s="88" t="s">
         <v>626</v>
       </c>
       <c r="F43" s="21" t="s">
@@ -8061,7 +8061,7 @@
       <c r="Q43" s="54"/>
       <c r="AMJ43"/>
     </row>
-    <row r="44" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1024" s="55" customFormat="1">
       <c r="A44" s="28"/>
       <c r="B44" s="21"/>
       <c r="C44" s="28">
@@ -8099,7 +8099,7 @@
       <c r="Q44" s="54"/>
       <c r="AMJ44"/>
     </row>
-    <row r="45" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1024" s="55" customFormat="1">
       <c r="A45" s="28">
         <v>24</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>39</v>
       </c>
       <c r="D45" s="21"/>
-      <c r="E45" s="92" t="s">
+      <c r="E45" s="88" t="s">
         <v>627</v>
       </c>
       <c r="F45" s="33" t="s">
@@ -8143,7 +8143,7 @@
       <c r="Q45" s="54"/>
       <c r="AMJ45"/>
     </row>
-    <row r="46" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1024" s="55" customFormat="1">
       <c r="A46" s="28">
         <v>25</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>40</v>
       </c>
       <c r="D46" s="21"/>
-      <c r="E46" s="92" t="s">
+      <c r="E46" s="88" t="s">
         <v>628</v>
       </c>
       <c r="F46" s="33" t="s">
@@ -8187,14 +8187,14 @@
       <c r="Q46" s="54"/>
       <c r="AMJ46"/>
     </row>
-    <row r="47" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1024" s="55" customFormat="1">
       <c r="A47" s="28"/>
       <c r="B47" s="21"/>
       <c r="C47" s="28">
         <v>41</v>
       </c>
       <c r="D47" s="21"/>
-      <c r="E47" s="92" t="s">
+      <c r="E47" s="88" t="s">
         <v>628</v>
       </c>
       <c r="F47" s="33" t="s">
@@ -8219,14 +8219,14 @@
       <c r="Q47" s="54"/>
       <c r="AMJ47"/>
     </row>
-    <row r="48" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1024" s="55" customFormat="1">
       <c r="A48" s="28"/>
       <c r="B48" s="21"/>
       <c r="C48" s="28">
         <v>42</v>
       </c>
       <c r="D48" s="21"/>
-      <c r="E48" s="92" t="s">
+      <c r="E48" s="88" t="s">
         <v>628</v>
       </c>
       <c r="F48" s="33" t="s">
@@ -8251,7 +8251,7 @@
       <c r="Q48" s="54"/>
       <c r="AMJ48"/>
     </row>
-    <row r="49" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1024" s="55" customFormat="1">
       <c r="A49" s="28">
         <v>26</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>43</v>
       </c>
       <c r="D49" s="21"/>
-      <c r="E49" s="92" t="s">
+      <c r="E49" s="88" t="s">
         <v>629</v>
       </c>
       <c r="F49" s="58" t="s">
@@ -8296,14 +8296,14 @@
       </c>
       <c r="AMJ49"/>
     </row>
-    <row r="50" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1024" s="55" customFormat="1">
       <c r="A50" s="28"/>
       <c r="B50" s="21"/>
       <c r="C50" s="28">
         <v>44</v>
       </c>
       <c r="D50" s="21"/>
-      <c r="E50" s="92" t="s">
+      <c r="E50" s="88" t="s">
         <v>629</v>
       </c>
       <c r="F50" s="58" t="s">
@@ -8327,14 +8327,14 @@
       </c>
       <c r="AMJ50"/>
     </row>
-    <row r="51" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1024" s="55" customFormat="1">
       <c r="A51" s="28"/>
       <c r="B51" s="21"/>
       <c r="C51" s="28">
         <v>45</v>
       </c>
       <c r="D51" s="21"/>
-      <c r="E51" s="92" t="s">
+      <c r="E51" s="88" t="s">
         <v>629</v>
       </c>
       <c r="F51" s="33" t="s">
@@ -8361,7 +8361,7 @@
       <c r="Q51" s="54"/>
       <c r="AMJ51"/>
     </row>
-    <row r="52" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1024" s="55" customFormat="1">
       <c r="A52" s="28">
         <v>27</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>46</v>
       </c>
       <c r="D52" s="21"/>
-      <c r="E52" s="92" t="s">
+      <c r="E52" s="88" t="s">
         <v>630</v>
       </c>
       <c r="F52" s="33" t="s">
@@ -8405,7 +8405,7 @@
       <c r="Q52" s="54"/>
       <c r="AMJ52"/>
     </row>
-    <row r="53" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1024" s="55" customFormat="1">
       <c r="A53" s="28">
         <v>28</v>
       </c>
@@ -8416,7 +8416,7 @@
         <v>47</v>
       </c>
       <c r="D53" s="21"/>
-      <c r="E53" s="92" t="s">
+      <c r="E53" s="88" t="s">
         <v>631</v>
       </c>
       <c r="F53" s="33" t="s">
@@ -8449,14 +8449,14 @@
       <c r="Q53" s="54"/>
       <c r="AMJ53"/>
     </row>
-    <row r="54" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1024" s="55" customFormat="1">
       <c r="A54" s="28"/>
       <c r="B54" s="21"/>
       <c r="C54" s="28">
         <v>48</v>
       </c>
       <c r="D54" s="21"/>
-      <c r="E54" s="92" t="s">
+      <c r="E54" s="88" t="s">
         <v>631</v>
       </c>
       <c r="F54" s="33" t="s">
@@ -8481,14 +8481,14 @@
       <c r="Q54" s="54"/>
       <c r="AMJ54"/>
     </row>
-    <row r="55" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1024" s="55" customFormat="1">
       <c r="A55" s="28"/>
       <c r="B55" s="21"/>
       <c r="C55" s="28">
         <v>49</v>
       </c>
       <c r="D55" s="21"/>
-      <c r="E55" s="92" t="s">
+      <c r="E55" s="88" t="s">
         <v>631</v>
       </c>
       <c r="F55" s="33" t="s">
@@ -8513,7 +8513,7 @@
       <c r="Q55" s="54"/>
       <c r="AMJ55"/>
     </row>
-    <row r="56" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1024" s="55" customFormat="1" ht="30">
       <c r="A56" s="36">
         <v>212</v>
       </c>
@@ -8547,7 +8547,7 @@
       <c r="Q56" s="54"/>
       <c r="AMJ56"/>
     </row>
-    <row r="57" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1024" s="55" customFormat="1" ht="30">
       <c r="A57" s="36">
         <v>29</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3"/>
-      <c r="E57" s="93" t="s">
+      <c r="E57" s="89" t="s">
         <v>632</v>
       </c>
       <c r="F57" s="37" t="s">
@@ -8589,7 +8589,7 @@
       <c r="Q57" s="54"/>
       <c r="AMJ57"/>
     </row>
-    <row r="58" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1024" s="55" customFormat="1">
       <c r="A58" s="36">
         <v>30</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="93" t="s">
+      <c r="E58" s="89" t="s">
         <v>633</v>
       </c>
       <c r="F58" s="59" t="s">
@@ -8631,14 +8631,14 @@
       <c r="Q58" s="57"/>
       <c r="AMJ58"/>
     </row>
-    <row r="59" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1024" s="55" customFormat="1">
       <c r="A59" s="36"/>
       <c r="B59" s="3"/>
       <c r="C59" s="36">
         <v>52</v>
       </c>
       <c r="D59" s="3"/>
-      <c r="E59" s="93" t="s">
+      <c r="E59" s="89" t="s">
         <v>633</v>
       </c>
       <c r="F59" s="59" t="s">
@@ -8663,7 +8663,7 @@
       <c r="Q59" s="57"/>
       <c r="AMJ59"/>
     </row>
-    <row r="60" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1024" s="55" customFormat="1">
       <c r="A60" s="50">
         <v>34</v>
       </c>
@@ -8711,7 +8711,7 @@
       <c r="Q60" s="54"/>
       <c r="AMJ60"/>
     </row>
-    <row r="61" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1024" s="55" customFormat="1">
       <c r="A61" s="50"/>
       <c r="B61" s="51"/>
       <c r="C61" s="50">
@@ -8743,7 +8743,7 @@
       <c r="Q61" s="54"/>
       <c r="AMJ61"/>
     </row>
-    <row r="62" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1024" s="55" customFormat="1">
       <c r="A62" s="50"/>
       <c r="B62" s="51"/>
       <c r="C62" s="50">
@@ -8775,7 +8775,7 @@
       <c r="Q62" s="54"/>
       <c r="AMJ62"/>
     </row>
-    <row r="63" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1024" s="55" customFormat="1">
       <c r="A63" s="50"/>
       <c r="B63" s="51"/>
       <c r="C63" s="50">
@@ -8809,7 +8809,7 @@
       <c r="Q63" s="54"/>
       <c r="AMJ63"/>
     </row>
-    <row r="64" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1024" s="55" customFormat="1">
       <c r="A64" s="50"/>
       <c r="B64" s="51"/>
       <c r="C64" s="50">
@@ -8847,11 +8847,11 @@
       <c r="Q64" s="57"/>
       <c r="AMJ64"/>
     </row>
-    <row r="65" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1024" s="55" customFormat="1">
       <c r="A65" s="28">
         <v>31</v>
       </c>
-      <c r="B65" s="92" t="s">
+      <c r="B65" s="88" t="s">
         <v>634</v>
       </c>
       <c r="C65" s="28"/>
@@ -8879,7 +8879,7 @@
       <c r="Q65" s="54"/>
       <c r="AMJ65"/>
     </row>
-    <row r="66" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1024" s="55" customFormat="1">
       <c r="A66" s="28">
         <v>32</v>
       </c>
@@ -8921,7 +8921,7 @@
       <c r="Q66" s="54"/>
       <c r="AMJ66"/>
     </row>
-    <row r="67" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1024" s="55" customFormat="1">
       <c r="A67" s="28"/>
       <c r="B67" s="21"/>
       <c r="C67" s="28">
@@ -8953,7 +8953,7 @@
       <c r="Q67" s="54"/>
       <c r="AMJ67"/>
     </row>
-    <row r="68" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1024" s="55" customFormat="1">
       <c r="A68" s="28"/>
       <c r="B68" s="21"/>
       <c r="C68" s="28">
@@ -8991,7 +8991,7 @@
       <c r="Q68" s="57"/>
       <c r="AMJ68"/>
     </row>
-    <row r="69" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1024" s="55" customFormat="1">
       <c r="A69" s="28">
         <v>33</v>
       </c>
@@ -9033,7 +9033,7 @@
       <c r="Q69" s="54"/>
       <c r="AMJ69"/>
     </row>
-    <row r="70" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1024" s="55" customFormat="1">
       <c r="A70" s="36">
         <v>35</v>
       </c>
@@ -9067,7 +9067,7 @@
       <c r="Q70" s="54"/>
       <c r="AMJ70"/>
     </row>
-    <row r="71" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1024" s="55" customFormat="1">
       <c r="A71" s="36">
         <v>36</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>63</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="93" t="s">
+      <c r="E71" s="89" t="s">
         <v>336</v>
       </c>
       <c r="F71" s="41" t="s">
@@ -9111,7 +9111,7 @@
       <c r="Q71" s="57"/>
       <c r="AMJ71"/>
     </row>
-    <row r="72" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1024" s="55" customFormat="1">
       <c r="A72" s="36"/>
       <c r="B72" s="3"/>
       <c r="C72" s="36">
@@ -9143,7 +9143,7 @@
       <c r="Q72" s="57"/>
       <c r="AMJ72"/>
     </row>
-    <row r="73" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1024" s="55" customFormat="1">
       <c r="A73" s="36"/>
       <c r="B73" s="3"/>
       <c r="C73" s="36">
@@ -9175,7 +9175,7 @@
       <c r="Q73" s="57"/>
       <c r="AMJ73"/>
     </row>
-    <row r="74" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1024" s="55" customFormat="1">
       <c r="A74" s="36">
         <v>37</v>
       </c>
@@ -9184,7 +9184,7 @@
         <v>66</v>
       </c>
       <c r="D74" s="3"/>
-      <c r="E74" s="93" t="s">
+      <c r="E74" s="89" t="s">
         <v>343</v>
       </c>
       <c r="F74" s="41" t="s">
@@ -9215,7 +9215,7 @@
       <c r="Q74" s="57"/>
       <c r="AMJ74"/>
     </row>
-    <row r="75" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1024" s="55" customFormat="1">
       <c r="A75" s="36"/>
       <c r="B75" s="3"/>
       <c r="C75" s="36">
@@ -9247,7 +9247,7 @@
       <c r="Q75" s="57"/>
       <c r="AMJ75"/>
     </row>
-    <row r="76" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1024" s="55" customFormat="1">
       <c r="A76" s="36"/>
       <c r="B76" s="3"/>
       <c r="C76" s="36">
@@ -9279,7 +9279,7 @@
       <c r="Q76" s="57"/>
       <c r="AMJ76"/>
     </row>
-    <row r="77" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1024" s="55" customFormat="1">
       <c r="A77" s="36"/>
       <c r="B77" s="3"/>
       <c r="C77" s="36">
@@ -9311,7 +9311,7 @@
       <c r="Q77" s="54"/>
       <c r="AMJ77"/>
     </row>
-    <row r="78" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1024" s="55" customFormat="1">
       <c r="A78" s="36">
         <v>38</v>
       </c>
@@ -9355,7 +9355,7 @@
       <c r="Q78" s="57"/>
       <c r="AMJ78"/>
     </row>
-    <row r="79" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1024" s="55" customFormat="1">
       <c r="A79" s="36"/>
       <c r="B79" s="3"/>
       <c r="C79" s="36">
@@ -9387,7 +9387,7 @@
       <c r="Q79" s="57"/>
       <c r="AMJ79"/>
     </row>
-    <row r="80" spans="1:1024" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1024">
       <c r="A80" s="61">
         <v>43</v>
       </c>
@@ -9414,7 +9414,7 @@
       <c r="N80" s="63"/>
       <c r="Q80" s="42"/>
     </row>
-    <row r="81" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17">
       <c r="A81" s="28">
         <v>44</v>
       </c>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="Q81" s="42"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17">
       <c r="A82" s="36">
         <v>45</v>
       </c>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="Q82" s="42"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17">
       <c r="A83" s="28">
         <v>204</v>
       </c>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="Q83" s="42"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17">
       <c r="A84" s="28">
         <v>46</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>75</v>
       </c>
       <c r="D84" s="21"/>
-      <c r="E84" s="92" t="s">
+      <c r="E84" s="88" t="s">
         <v>635</v>
       </c>
       <c r="F84" s="21" t="s">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="Q84" s="42"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17">
       <c r="A85" s="28">
         <v>47</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>76</v>
       </c>
       <c r="D85" s="21"/>
-      <c r="E85" s="92" t="s">
+      <c r="E85" s="88" t="s">
         <v>636</v>
       </c>
       <c r="F85" s="33" t="s">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="Q85" s="42"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17">
       <c r="A86" s="28">
         <v>48</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>77</v>
       </c>
       <c r="D86" s="21"/>
-      <c r="E86" s="92" t="s">
+      <c r="E86" s="88" t="s">
         <v>637</v>
       </c>
       <c r="F86" s="33" t="s">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="Q86" s="42"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17">
       <c r="A87" s="28">
         <v>49</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>78</v>
       </c>
       <c r="D87" s="21"/>
-      <c r="E87" s="92" t="s">
+      <c r="E87" s="88" t="s">
         <v>638</v>
       </c>
       <c r="F87" s="33" t="s">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="Q87" s="42"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17">
       <c r="A88" s="28">
         <v>50</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>79</v>
       </c>
       <c r="D88" s="21"/>
-      <c r="E88" s="92" t="s">
+      <c r="E88" s="88" t="s">
         <v>639</v>
       </c>
       <c r="F88" s="33" t="s">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="Q88" s="42"/>
     </row>
-    <row r="89" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17">
       <c r="A89" s="28">
         <v>54</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>85</v>
       </c>
       <c r="D89" s="21"/>
-      <c r="E89" s="92" t="s">
+      <c r="E89" s="88" t="s">
         <v>652</v>
       </c>
       <c r="F89" s="33" t="s">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:17">
       <c r="A90" s="28">
         <v>55</v>
       </c>
@@ -9766,7 +9766,7 @@
         <v>86</v>
       </c>
       <c r="D90" s="21"/>
-      <c r="E90" s="92" t="s">
+      <c r="E90" s="88" t="s">
         <v>653</v>
       </c>
       <c r="F90" s="33" t="s">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17">
       <c r="A91" s="36">
         <v>56</v>
       </c>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="Q91" s="42"/>
     </row>
-    <row r="92" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17">
       <c r="A92" s="28">
         <v>57</v>
       </c>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17">
       <c r="A93" s="28">
         <v>58</v>
       </c>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17">
       <c r="A94" s="28">
         <v>59</v>
       </c>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17">
       <c r="A95" s="28">
         <v>60</v>
       </c>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17">
       <c r="A96" s="28">
         <v>61</v>
       </c>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="Q96" s="42"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:17">
       <c r="A97" s="28">
         <v>205</v>
       </c>
@@ -10041,7 +10041,7 @@
         <v>92</v>
       </c>
       <c r="D97" s="21"/>
-      <c r="E97" s="92" t="s">
+      <c r="E97" s="88" t="s">
         <v>641</v>
       </c>
       <c r="F97" s="33" t="s">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="Q97" s="42"/>
     </row>
-    <row r="98" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:17">
       <c r="A98" s="36">
         <v>62</v>
       </c>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17">
       <c r="A99" s="36">
         <v>63</v>
       </c>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:17">
       <c r="A100" s="36"/>
       <c r="B100" s="3"/>
       <c r="C100" s="36">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:17">
       <c r="A101" s="36"/>
       <c r="B101" s="3"/>
       <c r="C101" s="36">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:17">
       <c r="A102" s="36">
         <v>64</v>
       </c>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17">
       <c r="A103" s="36"/>
       <c r="B103" s="3"/>
       <c r="C103" s="36">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:17">
       <c r="A104" s="36">
         <v>65</v>
       </c>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:17">
       <c r="A105" s="36"/>
       <c r="B105" s="3"/>
       <c r="C105" s="36">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:17">
       <c r="A106" s="36">
         <v>66</v>
       </c>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:17">
       <c r="A107" s="36">
         <v>67</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>65</v>
       </c>
       <c r="H107" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I107" s="36">
         <v>1</v>
@@ -10419,133 +10419,123 @@
       </c>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:17">
       <c r="A108" s="36"/>
       <c r="B108" s="3"/>
       <c r="C108" s="36">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F108" s="49" t="s">
-        <v>433</v>
+        <v>256</v>
       </c>
       <c r="G108" s="36">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H108" s="36"/>
       <c r="I108" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J108" s="40"/>
-      <c r="K108" s="40" t="s">
-        <v>434</v>
-      </c>
-      <c r="L108" s="40" t="s">
-        <v>435</v>
-      </c>
+      <c r="K108" s="40"/>
+      <c r="L108" s="40"/>
       <c r="M108" s="40"/>
       <c r="N108" s="40"/>
       <c r="O108" s="1"/>
-      <c r="P108" s="1" t="s">
+      <c r="P108" s="1"/>
+      <c r="Q108" s="35"/>
+    </row>
+    <row r="109" spans="1:17">
+      <c r="A109" s="36"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="36">
+        <v>102</v>
+      </c>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F109" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="G109" s="36">
+        <v>65</v>
+      </c>
+      <c r="H109" s="36"/>
+      <c r="I109" s="36">
+        <v>1</v>
+      </c>
+      <c r="J109" s="40"/>
+      <c r="K109" s="40" t="s">
+        <v>434</v>
+      </c>
+      <c r="L109" s="40" t="s">
+        <v>435</v>
+      </c>
+      <c r="M109" s="40"/>
+      <c r="N109" s="40"/>
+      <c r="O109" s="1"/>
+      <c r="P109" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="Q108" s="42"/>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A109" s="28">
+      <c r="Q109" s="42"/>
+    </row>
+    <row r="110" spans="1:17">
+      <c r="A110" s="28">
         <v>68</v>
       </c>
-      <c r="B109" s="21">
+      <c r="B110" s="21">
         <v>204</v>
       </c>
-      <c r="C109" s="28"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="21"/>
-      <c r="F109" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="G109" s="45">
-        <v>43</v>
-      </c>
-      <c r="H109" s="28">
-        <v>3</v>
-      </c>
-      <c r="I109" s="28"/>
-      <c r="J109" s="34"/>
-      <c r="K109" s="34"/>
-      <c r="L109" s="34"/>
-      <c r="M109" s="34"/>
-      <c r="N109" s="34"/>
-      <c r="O109" s="2"/>
-      <c r="P109" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q109" s="42"/>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A110" s="28">
-        <v>203</v>
-      </c>
-      <c r="B110" s="21"/>
       <c r="C110" s="28"/>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
-      <c r="F110" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="G110" s="28">
-        <v>68</v>
+      <c r="F110" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G110" s="45">
+        <v>43</v>
       </c>
       <c r="H110" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I110" s="28"/>
-      <c r="J110" s="81"/>
-      <c r="K110" s="81"/>
-      <c r="L110" s="81"/>
-      <c r="M110" s="81"/>
+      <c r="J110" s="34"/>
+      <c r="K110" s="34"/>
+      <c r="L110" s="34"/>
+      <c r="M110" s="34"/>
       <c r="N110" s="34"/>
       <c r="O110" s="2"/>
       <c r="P110" s="2" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="Q110" s="42"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:17">
       <c r="A111" s="28">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="B111" s="21"/>
-      <c r="C111" s="28">
-        <v>80</v>
-      </c>
+      <c r="C111" s="28"/>
       <c r="D111" s="21"/>
-      <c r="E111" s="92" t="s">
-        <v>640</v>
-      </c>
+      <c r="E111" s="21"/>
       <c r="F111" s="33" t="s">
         <v>93</v>
       </c>
       <c r="G111" s="28">
-        <v>203</v>
+        <v>68</v>
       </c>
       <c r="H111" s="28">
         <v>1</v>
       </c>
-      <c r="I111" s="28">
-        <v>1</v>
-      </c>
-      <c r="J111" s="34" t="s">
-        <v>374</v>
-      </c>
-      <c r="K111" s="34"/>
-      <c r="L111" s="34"/>
-      <c r="M111" s="34" t="s">
-        <v>375</v>
-      </c>
+      <c r="I111" s="28"/>
+      <c r="J111" s="81"/>
+      <c r="K111" s="81"/>
+      <c r="L111" s="81"/>
+      <c r="M111" s="81"/>
       <c r="N111" s="34"/>
       <c r="O111" s="2"/>
       <c r="P111" s="2" t="s">
@@ -10553,64 +10543,74 @@
       </c>
       <c r="Q111" s="42"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:17">
       <c r="A112" s="28">
-        <v>52</v>
-      </c>
-      <c r="B112" s="21">
         <v>51</v>
       </c>
+      <c r="B112" s="21"/>
       <c r="C112" s="28">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D112" s="21"/>
-      <c r="E112" s="92" t="s">
-        <v>654</v>
-      </c>
-      <c r="F112" s="46" t="s">
-        <v>377</v>
+      <c r="E112" s="88" t="s">
+        <v>640</v>
+      </c>
+      <c r="F112" s="33" t="s">
+        <v>93</v>
       </c>
       <c r="G112" s="28">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H112" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I112" s="28">
         <v>1</v>
       </c>
       <c r="J112" s="34" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K112" s="34"/>
       <c r="L112" s="34"/>
-      <c r="M112" s="34"/>
+      <c r="M112" s="34" t="s">
+        <v>375</v>
+      </c>
       <c r="N112" s="34"/>
       <c r="O112" s="2"/>
       <c r="P112" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Q112" s="42"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A113" s="28"/>
-      <c r="B113" s="21"/>
+    <row r="113" spans="1:17">
+      <c r="A113" s="28">
+        <v>52</v>
+      </c>
+      <c r="B113" s="21">
+        <v>51</v>
+      </c>
       <c r="C113" s="28">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D113" s="21"/>
-      <c r="E113" s="92" t="s">
+      <c r="E113" s="88" t="s">
         <v>654</v>
       </c>
       <c r="F113" s="46" t="s">
         <v>377</v>
       </c>
-      <c r="G113" s="28"/>
-      <c r="H113" s="28"/>
+      <c r="G113" s="28">
+        <v>51</v>
+      </c>
+      <c r="H113" s="28">
+        <v>3</v>
+      </c>
       <c r="I113" s="28">
-        <v>2</v>
-      </c>
-      <c r="J113" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J113" s="34" t="s">
+        <v>378</v>
+      </c>
       <c r="K113" s="34"/>
       <c r="L113" s="34"/>
       <c r="M113" s="34"/>
@@ -10621,14 +10621,14 @@
       </c>
       <c r="Q113" s="42"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:17">
       <c r="A114" s="28"/>
       <c r="B114" s="21"/>
       <c r="C114" s="28">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D114" s="21"/>
-      <c r="E114" s="92" t="s">
+      <c r="E114" s="88" t="s">
         <v>654</v>
       </c>
       <c r="F114" s="46" t="s">
@@ -10637,7 +10637,7 @@
       <c r="G114" s="28"/>
       <c r="H114" s="28"/>
       <c r="I114" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J114" s="34"/>
       <c r="K114" s="34"/>
@@ -10650,101 +10650,93 @@
       </c>
       <c r="Q114" s="42"/>
     </row>
-    <row r="115" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A115" s="28">
-        <v>53</v>
-      </c>
-      <c r="B115" s="21">
-        <v>51</v>
-      </c>
+    <row r="115" spans="1:17">
+      <c r="A115" s="28"/>
+      <c r="B115" s="21"/>
       <c r="C115" s="28">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D115" s="21"/>
-      <c r="E115" s="92" t="s">
-        <v>655</v>
+      <c r="E115" s="88" t="s">
+        <v>654</v>
       </c>
       <c r="F115" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="G115" s="28">
-        <v>51</v>
-      </c>
-      <c r="H115" s="28">
+        <v>377</v>
+      </c>
+      <c r="G115" s="28"/>
+      <c r="H115" s="28"/>
+      <c r="I115" s="28">
         <v>3</v>
       </c>
-      <c r="I115" s="28">
-        <v>1</v>
-      </c>
-      <c r="J115" s="34" t="s">
-        <v>380</v>
-      </c>
+      <c r="J115" s="34"/>
       <c r="K115" s="34"/>
       <c r="L115" s="34"/>
       <c r="M115" s="34"/>
       <c r="N115" s="34"/>
       <c r="O115" s="2"/>
       <c r="P115" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q115" s="35"/>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+        <v>379</v>
+      </c>
+      <c r="Q115" s="42"/>
+    </row>
+    <row r="116" spans="1:17">
       <c r="A116" s="28">
-        <v>213</v>
-      </c>
-      <c r="B116" s="21"/>
-      <c r="C116" s="28"/>
+        <v>53</v>
+      </c>
+      <c r="B116" s="21">
+        <v>51</v>
+      </c>
+      <c r="C116" s="28">
+        <v>84</v>
+      </c>
       <c r="D116" s="21"/>
-      <c r="E116" s="92"/>
-      <c r="F116" s="96" t="s">
-        <v>150</v>
+      <c r="E116" s="88" t="s">
+        <v>655</v>
+      </c>
+      <c r="F116" s="46" t="s">
+        <v>160</v>
       </c>
       <c r="G116" s="28">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H116" s="28">
         <v>3</v>
       </c>
-      <c r="I116" s="28"/>
-      <c r="J116" s="34"/>
+      <c r="I116" s="28">
+        <v>1</v>
+      </c>
+      <c r="J116" s="34" t="s">
+        <v>380</v>
+      </c>
       <c r="K116" s="34"/>
       <c r="L116" s="34"/>
       <c r="M116" s="34"/>
       <c r="N116" s="34"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q116" s="42"/>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+        <v>381</v>
+      </c>
+      <c r="Q116" s="35"/>
+    </row>
+    <row r="117" spans="1:17">
       <c r="A117" s="28">
-        <v>69</v>
+        <v>213</v>
       </c>
       <c r="B117" s="21"/>
-      <c r="C117" s="28">
-        <v>103</v>
-      </c>
+      <c r="C117" s="28"/>
       <c r="D117" s="21"/>
-      <c r="E117" s="92" t="s">
-        <v>438</v>
-      </c>
-      <c r="F117" s="33" t="s">
+      <c r="E117" s="88"/>
+      <c r="F117" s="92" t="s">
         <v>150</v>
       </c>
       <c r="G117" s="28">
-        <v>213</v>
+        <v>68</v>
       </c>
       <c r="H117" s="28">
         <v>3</v>
       </c>
-      <c r="I117" s="28">
-        <v>1</v>
-      </c>
-      <c r="J117" s="34" t="s">
-        <v>439</v>
-      </c>
+      <c r="I117" s="28"/>
+      <c r="J117" s="34"/>
       <c r="K117" s="34"/>
       <c r="L117" s="34"/>
       <c r="M117" s="34"/>
@@ -10755,25 +10747,33 @@
       </c>
       <c r="Q117" s="42"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A118" s="28"/>
+    <row r="118" spans="1:17">
+      <c r="A118" s="28">
+        <v>69</v>
+      </c>
       <c r="B118" s="21"/>
       <c r="C118" s="28">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D118" s="21"/>
-      <c r="E118" s="21" t="s">
+      <c r="E118" s="88" t="s">
         <v>438</v>
       </c>
       <c r="F118" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="G118" s="28"/>
-      <c r="H118" s="28"/>
+      <c r="G118" s="28">
+        <v>213</v>
+      </c>
+      <c r="H118" s="28">
+        <v>3</v>
+      </c>
       <c r="I118" s="28">
-        <v>2</v>
-      </c>
-      <c r="J118" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J118" s="34" t="s">
+        <v>439</v>
+      </c>
       <c r="K118" s="34"/>
       <c r="L118" s="34"/>
       <c r="M118" s="34"/>
@@ -10784,11 +10784,11 @@
       </c>
       <c r="Q118" s="42"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:17">
       <c r="A119" s="28"/>
       <c r="B119" s="21"/>
       <c r="C119" s="28">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D119" s="21"/>
       <c r="E119" s="21" t="s">
@@ -10800,7 +10800,7 @@
       <c r="G119" s="28"/>
       <c r="H119" s="28"/>
       <c r="I119" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J119" s="34"/>
       <c r="K119" s="34"/>
@@ -10813,64 +10813,64 @@
       </c>
       <c r="Q119" s="42"/>
     </row>
-    <row r="120" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A120" s="28">
-        <v>70</v>
-      </c>
-      <c r="B120" s="21">
-        <v>69</v>
-      </c>
+    <row r="120" spans="1:17">
+      <c r="A120" s="28"/>
+      <c r="B120" s="21"/>
       <c r="C120" s="28">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D120" s="21"/>
       <c r="E120" s="21" t="s">
-        <v>441</v>
-      </c>
-      <c r="F120" s="96" t="s">
-        <v>660</v>
-      </c>
-      <c r="G120" s="28">
-        <v>213</v>
-      </c>
-      <c r="H120" s="28">
+        <v>438</v>
+      </c>
+      <c r="F120" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G120" s="28"/>
+      <c r="H120" s="28"/>
+      <c r="I120" s="28">
         <v>3</v>
       </c>
-      <c r="I120" s="28">
-        <v>1</v>
-      </c>
-      <c r="J120" s="34" t="s">
-        <v>442</v>
-      </c>
+      <c r="J120" s="34"/>
       <c r="K120" s="34"/>
       <c r="L120" s="34"/>
       <c r="M120" s="34"/>
       <c r="N120" s="34"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q120" s="35"/>
-    </row>
-    <row r="121" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A121" s="28"/>
-      <c r="B121" s="21"/>
+        <v>440</v>
+      </c>
+      <c r="Q120" s="42"/>
+    </row>
+    <row r="121" spans="1:17">
+      <c r="A121" s="28">
+        <v>70</v>
+      </c>
+      <c r="B121" s="21">
+        <v>69</v>
+      </c>
       <c r="C121" s="28">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D121" s="21"/>
       <c r="E121" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="F121" s="96" t="s">
+      <c r="F121" s="92" t="s">
         <v>660</v>
       </c>
-      <c r="G121" s="28"/>
-      <c r="H121" s="28"/>
+      <c r="G121" s="28">
+        <v>213</v>
+      </c>
+      <c r="H121" s="28">
+        <v>3</v>
+      </c>
       <c r="I121" s="28">
-        <v>2</v>
-      </c>
-      <c r="J121" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J121" s="34" t="s">
+        <v>442</v>
+      </c>
       <c r="K121" s="34"/>
       <c r="L121" s="34"/>
       <c r="M121" s="34"/>
@@ -10881,23 +10881,23 @@
       </c>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:17">
       <c r="A122" s="28"/>
       <c r="B122" s="21"/>
       <c r="C122" s="28">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D122" s="21"/>
       <c r="E122" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="F122" s="96" t="s">
+      <c r="F122" s="92" t="s">
         <v>660</v>
       </c>
       <c r="G122" s="28"/>
       <c r="H122" s="28"/>
       <c r="I122" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J122" s="34"/>
       <c r="K122" s="34"/>
@@ -10910,77 +10910,72 @@
       </c>
       <c r="Q122" s="35"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A123" s="36">
+    <row r="123" spans="1:17">
+      <c r="A123" s="28"/>
+      <c r="B123" s="21"/>
+      <c r="C123" s="28">
+        <v>108</v>
+      </c>
+      <c r="D123" s="21"/>
+      <c r="E123" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="F123" s="92" t="s">
+        <v>660</v>
+      </c>
+      <c r="G123" s="28"/>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28">
+        <v>3</v>
+      </c>
+      <c r="J123" s="34"/>
+      <c r="K123" s="34"/>
+      <c r="L123" s="34"/>
+      <c r="M123" s="34"/>
+      <c r="N123" s="34"/>
+      <c r="O123" s="2"/>
+      <c r="P123" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q123" s="35"/>
+    </row>
+    <row r="124" spans="1:17">
+      <c r="A124" s="36">
         <v>72</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B124" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="C123" s="36"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-      <c r="F123" s="3" t="s">
+      <c r="C124" s="36"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="G123" s="36">
+      <c r="G124" s="36">
         <v>43</v>
       </c>
-      <c r="H123" s="36">
+      <c r="H124" s="36">
         <v>3</v>
       </c>
-      <c r="I123" s="36"/>
-      <c r="J123" s="40"/>
-      <c r="K123" s="40"/>
-      <c r="L123" s="40"/>
-      <c r="M123" s="40"/>
-      <c r="N123" s="40"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A124" s="36">
-        <v>73</v>
-      </c>
-      <c r="B124" s="3"/>
-      <c r="C124" s="36">
-        <v>110</v>
-      </c>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="F124" s="41" t="s">
-        <v>596</v>
-      </c>
-      <c r="G124" s="36">
-        <v>72</v>
-      </c>
-      <c r="H124" s="36">
-        <v>2</v>
-      </c>
-      <c r="I124" s="36">
-        <v>1</v>
-      </c>
-      <c r="J124" s="40" t="s">
-        <v>450</v>
-      </c>
+      <c r="I124" s="36"/>
+      <c r="J124" s="40"/>
       <c r="K124" s="40"/>
       <c r="L124" s="40"/>
       <c r="M124" s="40"/>
       <c r="N124" s="40"/>
       <c r="O124" s="1"/>
       <c r="P124" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A125" s="36"/>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17">
+      <c r="A125" s="36">
+        <v>73</v>
+      </c>
       <c r="B125" s="3"/>
       <c r="C125" s="36">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="3" t="s">
@@ -10989,12 +10984,18 @@
       <c r="F125" s="41" t="s">
         <v>596</v>
       </c>
-      <c r="G125" s="36"/>
-      <c r="H125" s="36"/>
+      <c r="G125" s="36">
+        <v>72</v>
+      </c>
+      <c r="H125" s="36">
+        <v>2</v>
+      </c>
       <c r="I125" s="36">
-        <v>2</v>
-      </c>
-      <c r="J125" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J125" s="40" t="s">
+        <v>450</v>
+      </c>
       <c r="K125" s="40"/>
       <c r="L125" s="40"/>
       <c r="M125" s="40"/>
@@ -11004,49 +11005,43 @@
         <v>451</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A126" s="36">
-        <v>75</v>
-      </c>
-      <c r="B126" s="3">
-        <v>73</v>
-      </c>
+    <row r="126" spans="1:17">
+      <c r="A126" s="36"/>
+      <c r="B126" s="3"/>
       <c r="C126" s="36">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F126" s="41" t="s">
-        <v>598</v>
-      </c>
-      <c r="G126" s="36">
-        <v>72</v>
-      </c>
-      <c r="H126" s="36">
-        <v>3</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="G126" s="36"/>
+      <c r="H126" s="36"/>
       <c r="I126" s="36">
-        <v>1</v>
-      </c>
-      <c r="J126" s="40" t="s">
-        <v>453</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J126" s="40"/>
       <c r="K126" s="40"/>
       <c r="L126" s="40"/>
       <c r="M126" s="40"/>
       <c r="N126" s="40"/>
       <c r="O126" s="1"/>
       <c r="P126" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A127" s="36"/>
-      <c r="B127" s="3"/>
+        <v>451</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17">
+      <c r="A127" s="36">
+        <v>75</v>
+      </c>
+      <c r="B127" s="3">
+        <v>73</v>
+      </c>
       <c r="C127" s="36">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="3" t="s">
@@ -11055,12 +11050,18 @@
       <c r="F127" s="41" t="s">
         <v>598</v>
       </c>
-      <c r="G127" s="36"/>
-      <c r="H127" s="36"/>
+      <c r="G127" s="36">
+        <v>72</v>
+      </c>
+      <c r="H127" s="36">
+        <v>3</v>
+      </c>
       <c r="I127" s="36">
-        <v>2</v>
-      </c>
-      <c r="J127" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J127" s="40" t="s">
+        <v>453</v>
+      </c>
       <c r="K127" s="40"/>
       <c r="L127" s="40"/>
       <c r="M127" s="40"/>
@@ -11070,11 +11071,11 @@
         <v>454</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:17">
       <c r="A128" s="36"/>
       <c r="B128" s="3"/>
       <c r="C128" s="36">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="3" t="s">
@@ -11086,7 +11087,7 @@
       <c r="G128" s="36"/>
       <c r="H128" s="36"/>
       <c r="I128" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J128" s="40"/>
       <c r="K128" s="40"/>
@@ -11098,74 +11099,64 @@
         <v>454</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A129" s="36">
-        <v>76</v>
-      </c>
-      <c r="B129" s="3">
-        <v>75</v>
-      </c>
+    <row r="129" spans="1:17">
+      <c r="A129" s="36"/>
+      <c r="B129" s="3"/>
       <c r="C129" s="36">
-        <v>115</v>
-      </c>
-      <c r="D129" s="3">
-        <v>75</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="D129" s="3"/>
       <c r="E129" s="3" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F129" s="41" t="s">
-        <v>599</v>
-      </c>
-      <c r="G129" s="36">
-        <v>72</v>
-      </c>
-      <c r="H129" s="36">
-        <v>1</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="G129" s="36"/>
+      <c r="H129" s="36"/>
       <c r="I129" s="36">
-        <v>1</v>
-      </c>
-      <c r="J129" s="40" t="s">
-        <v>456</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J129" s="40"/>
       <c r="K129" s="40"/>
       <c r="L129" s="40"/>
       <c r="M129" s="40"/>
       <c r="N129" s="40"/>
       <c r="O129" s="1"/>
       <c r="P129" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17">
       <c r="A130" s="36">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B130" s="3">
         <v>75</v>
       </c>
       <c r="C130" s="36">
-        <v>116</v>
-      </c>
-      <c r="D130" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="D130" s="3">
+        <v>75</v>
+      </c>
       <c r="E130" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="F130" s="49" t="s">
-        <v>458</v>
+        <v>455</v>
+      </c>
+      <c r="F130" s="41" t="s">
+        <v>599</v>
       </c>
       <c r="G130" s="36">
         <v>72</v>
       </c>
       <c r="H130" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I130" s="36">
         <v>1</v>
       </c>
       <c r="J130" s="40" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="K130" s="40"/>
       <c r="L130" s="40"/>
@@ -11173,15 +11164,18 @@
       <c r="N130" s="40"/>
       <c r="O130" s="1"/>
       <c r="P130" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q130" s="35"/>
-    </row>
-    <row r="131" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A131" s="36"/>
-      <c r="B131" s="3"/>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17">
+      <c r="A131" s="36">
+        <v>78</v>
+      </c>
+      <c r="B131" s="3">
+        <v>75</v>
+      </c>
       <c r="C131" s="36">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3" t="s">
@@ -11190,12 +11184,18 @@
       <c r="F131" s="49" t="s">
         <v>458</v>
       </c>
-      <c r="G131" s="36"/>
-      <c r="H131" s="36"/>
+      <c r="G131" s="36">
+        <v>72</v>
+      </c>
+      <c r="H131" s="36">
+        <v>3</v>
+      </c>
       <c r="I131" s="36">
-        <v>2</v>
-      </c>
-      <c r="J131" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J131" s="40" t="s">
+        <v>459</v>
+      </c>
       <c r="K131" s="40"/>
       <c r="L131" s="40"/>
       <c r="M131" s="40"/>
@@ -11206,11 +11206,11 @@
       </c>
       <c r="Q131" s="35"/>
     </row>
-    <row r="132" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:17">
       <c r="A132" s="36"/>
       <c r="B132" s="3"/>
       <c r="C132" s="36">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3" t="s">
@@ -11222,7 +11222,7 @@
       <c r="G132" s="36"/>
       <c r="H132" s="36"/>
       <c r="I132" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J132" s="40"/>
       <c r="K132" s="40"/>
@@ -11235,137 +11235,125 @@
       </c>
       <c r="Q132" s="35"/>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A133" s="36">
-        <v>79</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>603</v>
-      </c>
+    <row r="133" spans="1:17">
+      <c r="A133" s="36"/>
+      <c r="B133" s="3"/>
       <c r="C133" s="36">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F133" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="G133" s="36">
-        <v>72</v>
-      </c>
-      <c r="H133" s="36">
-        <v>1</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="G133" s="36"/>
+      <c r="H133" s="36"/>
       <c r="I133" s="36">
-        <v>1</v>
-      </c>
-      <c r="J133" s="40" t="s">
-        <v>462</v>
-      </c>
-      <c r="K133" s="40" t="s">
-        <v>463</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J133" s="40"/>
+      <c r="K133" s="40"/>
       <c r="L133" s="40"/>
-      <c r="M133" s="40" t="s">
-        <v>464</v>
-      </c>
+      <c r="M133" s="40"/>
       <c r="N133" s="40"/>
       <c r="O133" s="1"/>
       <c r="P133" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q133" s="35"/>
+    </row>
+    <row r="134" spans="1:17">
+      <c r="A134" s="36">
+        <v>79</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C134" s="36">
+        <v>119</v>
+      </c>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="F134" s="49" t="s">
+        <v>461</v>
+      </c>
+      <c r="G134" s="36">
+        <v>72</v>
+      </c>
+      <c r="H134" s="36">
+        <v>1</v>
+      </c>
+      <c r="I134" s="36">
+        <v>1</v>
+      </c>
+      <c r="J134" s="40" t="s">
+        <v>462</v>
+      </c>
+      <c r="K134" s="40" t="s">
+        <v>463</v>
+      </c>
+      <c r="L134" s="40"/>
+      <c r="M134" s="40" t="s">
+        <v>464</v>
+      </c>
+      <c r="N134" s="40"/>
+      <c r="O134" s="1"/>
+      <c r="P134" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="Q133" s="42"/>
-    </row>
-    <row r="134" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A134" s="28">
+      <c r="Q134" s="42"/>
+    </row>
+    <row r="135" spans="1:17">
+      <c r="A135" s="28">
         <v>80</v>
       </c>
-      <c r="B134" s="21">
+      <c r="B135" s="21">
         <v>78</v>
       </c>
-      <c r="C134" s="28"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21" t="s">
-        <v>466</v>
-      </c>
-      <c r="F134" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="G134" s="28">
-        <v>72</v>
-      </c>
-      <c r="H134" s="28">
-        <v>3</v>
-      </c>
-      <c r="I134" s="28"/>
-      <c r="J134" s="34"/>
-      <c r="K134" s="34"/>
-      <c r="L134" s="34"/>
-      <c r="M134" s="34"/>
-      <c r="N134" s="34"/>
-      <c r="O134" s="2"/>
-      <c r="P134" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q134" s="35"/>
-    </row>
-    <row r="135" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A135" s="28">
-        <v>81</v>
-      </c>
-      <c r="B135" s="21"/>
-      <c r="C135" s="28">
-        <v>120</v>
-      </c>
+      <c r="C135" s="28"/>
       <c r="D135" s="21"/>
       <c r="E135" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="F135" s="33" t="s">
-        <v>161</v>
+        <v>466</v>
+      </c>
+      <c r="F135" s="21" t="s">
+        <v>160</v>
       </c>
       <c r="G135" s="28">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H135" s="28">
-        <v>1</v>
-      </c>
-      <c r="I135" s="28">
-        <v>1</v>
-      </c>
-      <c r="J135" s="34" t="s">
-        <v>469</v>
-      </c>
-      <c r="K135" s="34" t="s">
-        <v>470</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I135" s="28"/>
+      <c r="J135" s="34"/>
+      <c r="K135" s="34"/>
       <c r="L135" s="34"/>
       <c r="M135" s="34"/>
       <c r="N135" s="34"/>
       <c r="O135" s="2"/>
       <c r="P135" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="Q135" s="35"/>
     </row>
-    <row r="136" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:17">
       <c r="A136" s="28">
-        <v>82</v>
-      </c>
-      <c r="B136" s="21">
         <v>81</v>
       </c>
+      <c r="B136" s="21"/>
       <c r="C136" s="28">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D136" s="21"/>
       <c r="E136" s="21" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F136" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G136" s="28">
         <v>80</v>
@@ -11377,66 +11365,70 @@
         <v>1</v>
       </c>
       <c r="J136" s="34" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="K136" s="34" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L136" s="34"/>
       <c r="M136" s="34"/>
       <c r="N136" s="34"/>
       <c r="O136" s="2"/>
       <c r="P136" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="Q136" s="35"/>
     </row>
-    <row r="137" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:17">
       <c r="A137" s="28">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B137" s="21">
         <v>81</v>
       </c>
       <c r="C137" s="28">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D137" s="21"/>
       <c r="E137" s="21" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F137" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G137" s="28">
         <v>80</v>
       </c>
       <c r="H137" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I137" s="28">
         <v>1</v>
       </c>
       <c r="J137" s="34" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="K137" s="34" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="L137" s="34"/>
       <c r="M137" s="34"/>
       <c r="N137" s="34"/>
       <c r="O137" s="2"/>
       <c r="P137" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="Q137" s="35"/>
     </row>
-    <row r="138" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A138" s="28"/>
-      <c r="B138" s="21"/>
+    <row r="138" spans="1:17">
+      <c r="A138" s="28">
+        <v>83</v>
+      </c>
+      <c r="B138" s="21">
+        <v>81</v>
+      </c>
       <c r="C138" s="28">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D138" s="21"/>
       <c r="E138" s="21" t="s">
@@ -11445,13 +11437,21 @@
       <c r="F138" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="G138" s="28"/>
-      <c r="H138" s="28"/>
+      <c r="G138" s="28">
+        <v>80</v>
+      </c>
+      <c r="H138" s="28">
+        <v>2</v>
+      </c>
       <c r="I138" s="28">
-        <v>2</v>
-      </c>
-      <c r="J138" s="34"/>
-      <c r="K138" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J138" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="K138" s="34" t="s">
+        <v>478</v>
+      </c>
       <c r="L138" s="34"/>
       <c r="M138" s="34"/>
       <c r="N138" s="34"/>
@@ -11461,52 +11461,44 @@
       </c>
       <c r="Q138" s="35"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A139" s="28">
-        <v>84</v>
-      </c>
-      <c r="B139" s="21">
-        <v>81</v>
-      </c>
+    <row r="139" spans="1:17">
+      <c r="A139" s="28"/>
+      <c r="B139" s="21"/>
       <c r="C139" s="28">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D139" s="21"/>
       <c r="E139" s="21" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="F139" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="G139" s="28">
-        <v>80</v>
-      </c>
-      <c r="H139" s="28">
-        <v>3</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="G139" s="28"/>
+      <c r="H139" s="28"/>
       <c r="I139" s="28">
-        <v>1</v>
-      </c>
-      <c r="J139" s="34" t="s">
-        <v>481</v>
-      </c>
-      <c r="K139" s="34" t="s">
-        <v>482</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J139" s="34"/>
+      <c r="K139" s="34"/>
       <c r="L139" s="34"/>
       <c r="M139" s="34"/>
       <c r="N139" s="34"/>
       <c r="O139" s="2"/>
       <c r="P139" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q139" s="42"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A140" s="28"/>
-      <c r="B140" s="21"/>
+        <v>479</v>
+      </c>
+      <c r="Q139" s="35"/>
+    </row>
+    <row r="140" spans="1:17">
+      <c r="A140" s="28">
+        <v>84</v>
+      </c>
+      <c r="B140" s="21">
+        <v>81</v>
+      </c>
       <c r="C140" s="28">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D140" s="21"/>
       <c r="E140" s="21" t="s">
@@ -11515,13 +11507,21 @@
       <c r="F140" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="G140" s="28"/>
-      <c r="H140" s="28"/>
+      <c r="G140" s="28">
+        <v>80</v>
+      </c>
+      <c r="H140" s="28">
+        <v>3</v>
+      </c>
       <c r="I140" s="28">
-        <v>2</v>
-      </c>
-      <c r="J140" s="34"/>
-      <c r="K140" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J140" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="K140" s="34" t="s">
+        <v>482</v>
+      </c>
       <c r="L140" s="34"/>
       <c r="M140" s="34"/>
       <c r="N140" s="34"/>
@@ -11531,11 +11531,11 @@
       </c>
       <c r="Q140" s="42"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:17">
       <c r="A141" s="28"/>
       <c r="B141" s="21"/>
       <c r="C141" s="28">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D141" s="21"/>
       <c r="E141" s="21" t="s">
@@ -11547,7 +11547,7 @@
       <c r="G141" s="28"/>
       <c r="H141" s="28"/>
       <c r="I141" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J141" s="34"/>
       <c r="K141" s="34"/>
@@ -11560,96 +11560,96 @@
       </c>
       <c r="Q141" s="42"/>
     </row>
-    <row r="142" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A142" s="36">
+    <row r="142" spans="1:17">
+      <c r="A142" s="28"/>
+      <c r="B142" s="21"/>
+      <c r="C142" s="28">
+        <v>126</v>
+      </c>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="F142" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="G142" s="28"/>
+      <c r="H142" s="28"/>
+      <c r="I142" s="28">
+        <v>3</v>
+      </c>
+      <c r="J142" s="34"/>
+      <c r="K142" s="34"/>
+      <c r="L142" s="34"/>
+      <c r="M142" s="34"/>
+      <c r="N142" s="34"/>
+      <c r="O142" s="2"/>
+      <c r="P142" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q142" s="42"/>
+    </row>
+    <row r="143" spans="1:17">
+      <c r="A143" s="36">
         <v>206</v>
       </c>
-      <c r="B142" s="3">
+      <c r="B143" s="3">
         <v>72</v>
       </c>
-      <c r="C142" s="36"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-      <c r="F142" s="3" t="s">
+      <c r="C143" s="36"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G142" s="36">
+      <c r="G143" s="36">
         <v>43</v>
-      </c>
-      <c r="H142" s="36">
-        <v>3</v>
-      </c>
-      <c r="I142" s="36"/>
-      <c r="J142" s="40"/>
-      <c r="K142" s="40"/>
-      <c r="L142" s="40"/>
-      <c r="M142" s="40"/>
-      <c r="N142" s="40"/>
-      <c r="O142" s="1"/>
-      <c r="P142" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q142" s="35"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A143" s="36">
-        <v>85</v>
-      </c>
-      <c r="B143" s="3"/>
-      <c r="C143" s="36">
-        <v>127</v>
-      </c>
-      <c r="D143" s="3"/>
-      <c r="E143" s="93" t="s">
-        <v>642</v>
-      </c>
-      <c r="F143" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="G143" s="36">
-        <v>206</v>
       </c>
       <c r="H143" s="36">
         <v>3</v>
       </c>
-      <c r="I143" s="36">
-        <v>1</v>
-      </c>
-      <c r="J143" s="40" t="s">
-        <v>485</v>
-      </c>
-      <c r="K143" s="40" t="s">
-        <v>486</v>
-      </c>
+      <c r="I143" s="36"/>
+      <c r="J143" s="40"/>
+      <c r="K143" s="40"/>
       <c r="L143" s="40"/>
       <c r="M143" s="40"/>
       <c r="N143" s="40"/>
       <c r="O143" s="1"/>
       <c r="P143" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q143" s="42"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A144" s="36"/>
+        <v>484</v>
+      </c>
+      <c r="Q143" s="35"/>
+    </row>
+    <row r="144" spans="1:17">
+      <c r="A144" s="36">
+        <v>85</v>
+      </c>
       <c r="B144" s="3"/>
       <c r="C144" s="36">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D144" s="3"/>
-      <c r="E144" s="93" t="s">
+      <c r="E144" s="89" t="s">
         <v>642</v>
       </c>
       <c r="F144" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="G144" s="36"/>
-      <c r="H144" s="36"/>
+      <c r="G144" s="36">
+        <v>206</v>
+      </c>
+      <c r="H144" s="36">
+        <v>3</v>
+      </c>
       <c r="I144" s="36">
-        <v>2</v>
-      </c>
-      <c r="J144" s="40"/>
-      <c r="K144" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J144" s="40" t="s">
+        <v>485</v>
+      </c>
+      <c r="K144" s="40" t="s">
+        <v>486</v>
+      </c>
       <c r="L144" s="40"/>
       <c r="M144" s="40"/>
       <c r="N144" s="40"/>
@@ -11659,14 +11659,14 @@
       </c>
       <c r="Q144" s="42"/>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:17">
       <c r="A145" s="36"/>
       <c r="B145" s="3"/>
       <c r="C145" s="36">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D145" s="3"/>
-      <c r="E145" s="93" t="s">
+      <c r="E145" s="89" t="s">
         <v>642</v>
       </c>
       <c r="F145" s="41" t="s">
@@ -11675,7 +11675,7 @@
       <c r="G145" s="36"/>
       <c r="H145" s="36"/>
       <c r="I145" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J145" s="40"/>
       <c r="K145" s="40"/>
@@ -11688,100 +11688,100 @@
       </c>
       <c r="Q145" s="42"/>
     </row>
-    <row r="146" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:17">
       <c r="A146" s="36"/>
       <c r="B146" s="3"/>
       <c r="C146" s="36">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="93" t="s">
+      <c r="E146" s="89" t="s">
         <v>642</v>
       </c>
       <c r="F146" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="G146" s="36">
-        <v>206</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="G146" s="36"/>
       <c r="H146" s="36"/>
       <c r="I146" s="36">
-        <v>1</v>
-      </c>
-      <c r="J146" s="40" t="s">
-        <v>488</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J146" s="40"/>
       <c r="K146" s="40"/>
       <c r="L146" s="40"/>
       <c r="M146" s="40"/>
       <c r="N146" s="40"/>
       <c r="O146" s="1"/>
       <c r="P146" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q146" s="35"/>
-    </row>
-    <row r="147" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A147" s="36">
-        <v>86</v>
-      </c>
-      <c r="B147" s="3">
-        <v>85</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="Q146" s="42"/>
+    </row>
+    <row r="147" spans="1:17">
+      <c r="A147" s="36"/>
+      <c r="B147" s="3"/>
       <c r="C147" s="36">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D147" s="3"/>
-      <c r="E147" s="93" t="s">
-        <v>643</v>
+      <c r="E147" s="89" t="s">
+        <v>642</v>
       </c>
       <c r="F147" s="41" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G147" s="36">
         <v>206</v>
       </c>
-      <c r="H147" s="36">
-        <v>2</v>
-      </c>
+      <c r="H147" s="36"/>
       <c r="I147" s="36">
         <v>1</v>
       </c>
       <c r="J147" s="40" t="s">
-        <v>490</v>
-      </c>
-      <c r="K147" s="40" t="s">
-        <v>491</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="K147" s="40"/>
       <c r="L147" s="40"/>
       <c r="M147" s="40"/>
       <c r="N147" s="40"/>
       <c r="O147" s="1"/>
       <c r="P147" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="Q147" s="35"/>
     </row>
-    <row r="148" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A148" s="36"/>
-      <c r="B148" s="3"/>
+    <row r="148" spans="1:17">
+      <c r="A148" s="36">
+        <v>86</v>
+      </c>
+      <c r="B148" s="3">
+        <v>85</v>
+      </c>
       <c r="C148" s="36">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D148" s="3"/>
-      <c r="E148" s="93" t="s">
+      <c r="E148" s="89" t="s">
         <v>643</v>
       </c>
       <c r="F148" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="G148" s="36"/>
-      <c r="H148" s="36"/>
+      <c r="G148" s="36">
+        <v>206</v>
+      </c>
+      <c r="H148" s="36">
+        <v>2</v>
+      </c>
       <c r="I148" s="36">
-        <v>2</v>
-      </c>
-      <c r="J148" s="40"/>
-      <c r="K148" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J148" s="40" t="s">
+        <v>490</v>
+      </c>
+      <c r="K148" s="40" t="s">
+        <v>491</v>
+      </c>
       <c r="L148" s="40"/>
       <c r="M148" s="40"/>
       <c r="N148" s="40"/>
@@ -11791,63 +11791,51 @@
       </c>
       <c r="Q148" s="35"/>
     </row>
-    <row r="149" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A149" s="36">
-        <v>87</v>
-      </c>
-      <c r="B149" s="3">
-        <v>86</v>
-      </c>
+    <row r="149" spans="1:17">
+      <c r="A149" s="36"/>
+      <c r="B149" s="3"/>
       <c r="C149" s="36">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D149" s="3"/>
-      <c r="E149" s="93" t="s">
-        <v>644</v>
+      <c r="E149" s="89" t="s">
+        <v>643</v>
       </c>
       <c r="F149" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="G149" s="36">
-        <v>206</v>
-      </c>
-      <c r="H149" s="36">
+        <v>155</v>
+      </c>
+      <c r="G149" s="36"/>
+      <c r="H149" s="36"/>
+      <c r="I149" s="36">
         <v>2</v>
       </c>
-      <c r="I149" s="36">
-        <v>1</v>
-      </c>
-      <c r="J149" s="40" t="s">
-        <v>493</v>
-      </c>
-      <c r="K149" s="40" t="s">
-        <v>494</v>
-      </c>
+      <c r="J149" s="40"/>
+      <c r="K149" s="40"/>
       <c r="L149" s="40"/>
       <c r="M149" s="40"/>
       <c r="N149" s="40"/>
       <c r="O149" s="1"/>
       <c r="P149" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="Q149" s="35"/>
     </row>
-    <row r="150" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:17">
       <c r="A150" s="36">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B150" s="3">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C150" s="36">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D150" s="3"/>
-      <c r="E150" s="93" t="s">
-        <v>645</v>
+      <c r="E150" s="89" t="s">
+        <v>644</v>
       </c>
       <c r="F150" s="41" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G150" s="36">
         <v>206</v>
@@ -11859,36 +11847,36 @@
         <v>1</v>
       </c>
       <c r="J150" s="40" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="K150" s="40" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="L150" s="40"/>
       <c r="M150" s="40"/>
       <c r="N150" s="40"/>
       <c r="O150" s="1"/>
       <c r="P150" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="Q150" s="35"/>
     </row>
-    <row r="151" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:17">
       <c r="A151" s="36">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B151" s="3">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C151" s="36">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D151" s="3"/>
-      <c r="E151" s="93" t="s">
-        <v>646</v>
+      <c r="E151" s="89" t="s">
+        <v>645</v>
       </c>
       <c r="F151" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G151" s="36">
         <v>206</v>
@@ -11900,36 +11888,36 @@
         <v>1</v>
       </c>
       <c r="J151" s="40" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="K151" s="40" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L151" s="40"/>
       <c r="M151" s="40"/>
       <c r="N151" s="40"/>
       <c r="O151" s="1"/>
       <c r="P151" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="Q151" s="35"/>
     </row>
-    <row r="152" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:17">
       <c r="A152" s="36">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B152" s="3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C152" s="36">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D152" s="3"/>
-      <c r="E152" s="93" t="s">
-        <v>647</v>
+      <c r="E152" s="89" t="s">
+        <v>646</v>
       </c>
       <c r="F152" s="41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G152" s="36">
         <v>206</v>
@@ -11941,36 +11929,36 @@
         <v>1</v>
       </c>
       <c r="J152" s="40" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="K152" s="40" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="L152" s="40"/>
       <c r="M152" s="40"/>
       <c r="N152" s="40"/>
       <c r="O152" s="1"/>
       <c r="P152" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="Q152" s="35"/>
     </row>
-    <row r="153" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:17">
       <c r="A153" s="36">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B153" s="3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C153" s="36">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D153" s="3"/>
-      <c r="E153" s="93" t="s">
-        <v>648</v>
-      </c>
-      <c r="F153" s="49" t="s">
-        <v>505</v>
+      <c r="E153" s="89" t="s">
+        <v>647</v>
+      </c>
+      <c r="F153" s="41" t="s">
+        <v>168</v>
       </c>
       <c r="G153" s="36">
         <v>206</v>
@@ -11982,36 +11970,36 @@
         <v>1</v>
       </c>
       <c r="J153" s="40" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="K153" s="40" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="L153" s="40"/>
       <c r="M153" s="40"/>
       <c r="N153" s="40"/>
       <c r="O153" s="1"/>
       <c r="P153" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="Q153" s="35"/>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:17">
       <c r="A154" s="36">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B154" s="3">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C154" s="36">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D154" s="3"/>
-      <c r="E154" s="93" t="s">
-        <v>649</v>
-      </c>
-      <c r="F154" s="41" t="s">
-        <v>170</v>
+      <c r="E154" s="89" t="s">
+        <v>648</v>
+      </c>
+      <c r="F154" s="49" t="s">
+        <v>505</v>
       </c>
       <c r="G154" s="36">
         <v>206</v>
@@ -12023,70 +12011,84 @@
         <v>1</v>
       </c>
       <c r="J154" s="40" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="K154" s="40" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="L154" s="40"/>
       <c r="M154" s="40"/>
       <c r="N154" s="40"/>
       <c r="O154" s="1"/>
       <c r="P154" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q154" s="35"/>
+    </row>
+    <row r="155" spans="1:17">
+      <c r="A155" s="36">
+        <v>92</v>
+      </c>
+      <c r="B155" s="3">
+        <v>91</v>
+      </c>
+      <c r="C155" s="36">
+        <v>138</v>
+      </c>
+      <c r="D155" s="3"/>
+      <c r="E155" s="89" t="s">
+        <v>649</v>
+      </c>
+      <c r="F155" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="G155" s="36">
+        <v>206</v>
+      </c>
+      <c r="H155" s="36">
+        <v>2</v>
+      </c>
+      <c r="I155" s="36">
+        <v>1</v>
+      </c>
+      <c r="J155" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="K155" s="40" t="s">
+        <v>510</v>
+      </c>
+      <c r="L155" s="40"/>
+      <c r="M155" s="40"/>
+      <c r="N155" s="40"/>
+      <c r="O155" s="1"/>
+      <c r="P155" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="Q154" s="42"/>
-    </row>
-    <row r="155" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A155" s="28">
+      <c r="Q155" s="42"/>
+    </row>
+    <row r="156" spans="1:17">
+      <c r="A156" s="28">
         <v>93</v>
       </c>
-      <c r="B155" s="21">
+      <c r="B156" s="21">
         <v>72.206000000000003</v>
       </c>
-      <c r="C155" s="28">
+      <c r="C156" s="28">
         <v>139</v>
-      </c>
-      <c r="D155" s="21"/>
-      <c r="E155" s="21"/>
-      <c r="F155" s="92" t="s">
-        <v>171</v>
-      </c>
-      <c r="G155" s="28">
-        <v>43</v>
-      </c>
-      <c r="H155" s="28">
-        <v>2</v>
-      </c>
-      <c r="I155" s="28">
-        <v>1</v>
-      </c>
-      <c r="J155" s="34"/>
-      <c r="K155" s="34"/>
-      <c r="L155" s="34"/>
-      <c r="M155" s="34"/>
-      <c r="N155" s="34"/>
-      <c r="O155" s="2"/>
-      <c r="P155" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q155" s="35"/>
-    </row>
-    <row r="156" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A156" s="28"/>
-      <c r="B156" s="21"/>
-      <c r="C156" s="28">
-        <v>140</v>
       </c>
       <c r="D156" s="21"/>
       <c r="E156" s="21"/>
-      <c r="F156" s="21" t="s">
+      <c r="F156" s="88" t="s">
         <v>171</v>
       </c>
-      <c r="G156" s="28"/>
-      <c r="H156" s="28"/>
+      <c r="G156" s="28">
+        <v>43</v>
+      </c>
+      <c r="H156" s="28">
+        <v>2</v>
+      </c>
       <c r="I156" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J156" s="34"/>
       <c r="K156" s="34"/>
@@ -12099,61 +12101,47 @@
       </c>
       <c r="Q156" s="35"/>
     </row>
-    <row r="157" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A157" s="28">
-        <v>94</v>
-      </c>
+    <row r="157" spans="1:17">
+      <c r="A157" s="28"/>
       <c r="B157" s="21"/>
       <c r="C157" s="28">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D157" s="21"/>
-      <c r="E157" s="21" t="s">
-        <v>513</v>
-      </c>
-      <c r="F157" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="G157" s="28">
-        <v>93</v>
-      </c>
-      <c r="H157" s="28">
+      <c r="E157" s="21"/>
+      <c r="F157" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="G157" s="28"/>
+      <c r="H157" s="28"/>
+      <c r="I157" s="28">
         <v>2</v>
       </c>
-      <c r="I157" s="28">
-        <v>1</v>
-      </c>
-      <c r="J157" s="34" t="s">
-        <v>514</v>
-      </c>
-      <c r="K157" s="34" t="s">
-        <v>515</v>
-      </c>
+      <c r="J157" s="34"/>
+      <c r="K157" s="34"/>
       <c r="L157" s="34"/>
       <c r="M157" s="34"/>
       <c r="N157" s="34"/>
       <c r="O157" s="2"/>
       <c r="P157" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="Q157" s="35"/>
     </row>
-    <row r="158" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:17">
       <c r="A158" s="28">
-        <v>95</v>
-      </c>
-      <c r="B158" s="21">
         <v>94</v>
       </c>
+      <c r="B158" s="21"/>
       <c r="C158" s="28">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D158" s="21"/>
       <c r="E158" s="21" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F158" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G158" s="28">
         <v>93</v>
@@ -12165,627 +12153,587 @@
         <v>1</v>
       </c>
       <c r="J158" s="34" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="K158" s="34" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="L158" s="34"/>
       <c r="M158" s="34"/>
       <c r="N158" s="34"/>
       <c r="O158" s="2"/>
       <c r="P158" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="Q158" s="35"/>
     </row>
-    <row r="159" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:17">
       <c r="A159" s="28">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B159" s="21">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C159" s="28">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D159" s="21"/>
       <c r="E159" s="21" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F159" s="33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G159" s="28">
         <v>93</v>
       </c>
       <c r="H159" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I159" s="28">
         <v>1</v>
       </c>
       <c r="J159" s="34" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="K159" s="34" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="L159" s="34"/>
-      <c r="M159" s="34" t="s">
-        <v>524</v>
-      </c>
+      <c r="M159" s="34"/>
       <c r="N159" s="34"/>
       <c r="O159" s="2"/>
       <c r="P159" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="Q159" s="35"/>
     </row>
-    <row r="160" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A160" s="28">
-        <v>97</v>
-      </c>
-      <c r="B160" s="21">
-        <v>96</v>
-      </c>
+    <row r="160" spans="1:17">
+      <c r="A160" s="28"/>
+      <c r="B160" s="21"/>
       <c r="C160" s="28">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D160" s="21"/>
       <c r="E160" s="21" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="F160" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G160" s="28">
-        <v>93</v>
-      </c>
-      <c r="H160" s="28">
+        <v>95</v>
+      </c>
+      <c r="H160" s="28"/>
+      <c r="I160" s="28">
         <v>2</v>
       </c>
-      <c r="I160" s="28">
-        <v>1</v>
-      </c>
-      <c r="J160" s="34" t="s">
-        <v>527</v>
-      </c>
-      <c r="K160" s="34" t="s">
-        <v>528</v>
-      </c>
       <c r="L160" s="34"/>
-      <c r="M160" s="34" t="s">
-        <v>529</v>
-      </c>
+      <c r="M160" s="34"/>
       <c r="N160" s="34"/>
       <c r="O160" s="2"/>
-      <c r="P160" s="2" t="s">
+      <c r="P160" s="2"/>
+      <c r="Q160" s="35"/>
+    </row>
+    <row r="161" spans="1:17">
+      <c r="A161" s="28"/>
+      <c r="B161" s="21"/>
+      <c r="C161" s="28">
+        <v>159</v>
+      </c>
+      <c r="D161" s="21"/>
+      <c r="E161" s="21" t="s">
+        <v>517</v>
+      </c>
+      <c r="F161" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="G161" s="28">
+        <v>95</v>
+      </c>
+      <c r="H161" s="28"/>
+      <c r="I161" s="28">
+        <v>3</v>
+      </c>
+      <c r="J161" s="34"/>
+      <c r="K161" s="34"/>
+      <c r="L161" s="34"/>
+      <c r="M161" s="34"/>
+      <c r="N161" s="34"/>
+      <c r="O161" s="2"/>
+      <c r="P161" s="2"/>
+      <c r="Q161" s="35"/>
+    </row>
+    <row r="162" spans="1:17">
+      <c r="A162" s="28">
+        <v>96</v>
+      </c>
+      <c r="B162" s="21">
+        <v>95</v>
+      </c>
+      <c r="C162" s="28">
+        <v>143</v>
+      </c>
+      <c r="D162" s="21"/>
+      <c r="E162" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="F162" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="G162" s="28">
+        <v>93</v>
+      </c>
+      <c r="H162" s="28">
+        <v>2</v>
+      </c>
+      <c r="I162" s="28">
+        <v>1</v>
+      </c>
+      <c r="J162" s="34" t="s">
+        <v>522</v>
+      </c>
+      <c r="K162" s="34" t="s">
+        <v>523</v>
+      </c>
+      <c r="L162" s="34"/>
+      <c r="M162" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="N162" s="34"/>
+      <c r="O162" s="2"/>
+      <c r="P162" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q162" s="35"/>
+    </row>
+    <row r="163" spans="1:17">
+      <c r="A163" s="28">
+        <v>97</v>
+      </c>
+      <c r="B163" s="21">
+        <v>96</v>
+      </c>
+      <c r="C163" s="28">
+        <v>144</v>
+      </c>
+      <c r="D163" s="21"/>
+      <c r="E163" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="F163" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="G163" s="28">
+        <v>93</v>
+      </c>
+      <c r="H163" s="28">
+        <v>3</v>
+      </c>
+      <c r="I163" s="28">
+        <v>1</v>
+      </c>
+      <c r="J163" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="K163" s="34" t="s">
+        <v>528</v>
+      </c>
+      <c r="L163" s="34"/>
+      <c r="M163" s="34" t="s">
+        <v>529</v>
+      </c>
+      <c r="N163" s="34"/>
+      <c r="O163" s="2"/>
+      <c r="P163" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="Q160" s="35"/>
-    </row>
-    <row r="161" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A161" s="36">
+      <c r="Q163" s="35"/>
+    </row>
+    <row r="164" spans="1:17">
+      <c r="A164" s="28"/>
+      <c r="B164" s="21"/>
+      <c r="C164" s="28">
+        <v>162</v>
+      </c>
+      <c r="D164" s="21"/>
+      <c r="E164" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="F164" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="G164" s="28">
+        <v>97</v>
+      </c>
+      <c r="H164" s="28"/>
+      <c r="I164" s="28">
+        <v>3</v>
+      </c>
+      <c r="J164" s="34"/>
+      <c r="K164" s="34"/>
+      <c r="L164" s="34"/>
+      <c r="M164" s="34"/>
+      <c r="N164" s="34"/>
+      <c r="O164" s="2"/>
+      <c r="P164" s="2"/>
+      <c r="Q164" s="35"/>
+    </row>
+    <row r="165" spans="1:17">
+      <c r="A165" s="36">
         <v>207</v>
       </c>
-      <c r="B161" s="3">
+      <c r="B165" s="3">
         <v>93</v>
       </c>
-      <c r="C161" s="3"/>
-      <c r="D161" s="3"/>
-      <c r="E161" s="3"/>
-      <c r="F161" s="93" t="s">
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="89" t="s">
         <v>657</v>
       </c>
-      <c r="G161" s="36">
+      <c r="G165" s="36">
         <v>43</v>
       </c>
-      <c r="H161" s="36">
+      <c r="H165" s="36">
         <v>2</v>
       </c>
-      <c r="I161" s="36"/>
-      <c r="J161" s="40"/>
-      <c r="K161" s="40"/>
-      <c r="L161" s="40"/>
-      <c r="M161" s="40"/>
-      <c r="N161" s="40"/>
-      <c r="O161" s="1"/>
-      <c r="P161" s="1" t="s">
+      <c r="I165" s="36"/>
+      <c r="J165" s="40"/>
+      <c r="K165" s="40"/>
+      <c r="L165" s="40"/>
+      <c r="M165" s="40"/>
+      <c r="N165" s="40"/>
+      <c r="O165" s="1"/>
+      <c r="P165" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="Q161" s="35"/>
-    </row>
-    <row r="162" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A162" s="36">
+      <c r="Q165" s="35"/>
+    </row>
+    <row r="166" spans="1:17">
+      <c r="A166" s="36">
         <v>98</v>
       </c>
-      <c r="B162" s="3"/>
-      <c r="C162" s="36">
+      <c r="B166" s="3"/>
+      <c r="C166" s="36">
         <v>145</v>
       </c>
-      <c r="D162" s="3"/>
-      <c r="E162" s="93" t="s">
+      <c r="D166" s="3"/>
+      <c r="E166" s="89" t="s">
         <v>658</v>
       </c>
-      <c r="F162" s="93" t="s">
+      <c r="F166" s="89" t="s">
         <v>657</v>
       </c>
-      <c r="G162" s="36">
+      <c r="G166" s="36">
         <v>207</v>
       </c>
-      <c r="H162" s="36">
-        <v>1</v>
-      </c>
-      <c r="I162" s="36">
-        <v>1</v>
-      </c>
-      <c r="J162" s="40" t="s">
+      <c r="H166" s="36">
+        <v>1</v>
+      </c>
+      <c r="I166" s="36">
+        <v>1</v>
+      </c>
+      <c r="J166" s="40" t="s">
         <v>531</v>
       </c>
-      <c r="K162" s="40" t="s">
+      <c r="K166" s="40" t="s">
         <v>532</v>
       </c>
-      <c r="L162" s="40"/>
-      <c r="M162" s="40"/>
-      <c r="N162" s="40"/>
-      <c r="O162" s="1"/>
-      <c r="P162" s="1"/>
-      <c r="Q162" s="35"/>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A163" s="36">
+      <c r="L166" s="40"/>
+      <c r="M166" s="40"/>
+      <c r="N166" s="40"/>
+      <c r="O166" s="1"/>
+      <c r="P166" s="1"/>
+      <c r="Q166" s="35"/>
+    </row>
+    <row r="167" spans="1:17">
+      <c r="A167" s="36">
         <v>99</v>
       </c>
-      <c r="B163" s="3">
+      <c r="B167" s="3">
         <v>98</v>
       </c>
-      <c r="C163" s="36">
+      <c r="C167" s="36">
         <v>146</v>
       </c>
-      <c r="D163" s="3"/>
-      <c r="E163" s="93" t="s">
+      <c r="D167" s="3"/>
+      <c r="E167" s="89" t="s">
         <v>659</v>
       </c>
-      <c r="F163" s="41" t="s">
+      <c r="F167" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G163" s="36">
+      <c r="G167" s="36">
         <v>207</v>
       </c>
-      <c r="H163" s="36">
+      <c r="H167" s="36">
         <v>2</v>
       </c>
-      <c r="I163" s="36">
-        <v>1</v>
-      </c>
-      <c r="J163" s="40" t="s">
+      <c r="I167" s="36">
+        <v>1</v>
+      </c>
+      <c r="J167" s="40" t="s">
         <v>534</v>
       </c>
-      <c r="K163" s="40" t="s">
+      <c r="K167" s="40" t="s">
         <v>535</v>
       </c>
-      <c r="L163" s="40"/>
-      <c r="M163" s="40"/>
-      <c r="N163" s="40"/>
-      <c r="O163" s="1"/>
-      <c r="P163" s="1" t="s">
+      <c r="L167" s="40"/>
+      <c r="M167" s="40"/>
+      <c r="N167" s="40"/>
+      <c r="O167" s="1"/>
+      <c r="P167" s="1" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A164" s="36"/>
-      <c r="B164" s="3"/>
-      <c r="C164" s="36">
+    <row r="168" spans="1:17">
+      <c r="A168" s="36"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="36">
         <v>147</v>
       </c>
-      <c r="D164" s="3"/>
-      <c r="E164" s="93" t="s">
+      <c r="D168" s="3"/>
+      <c r="E168" s="89" t="s">
         <v>659</v>
       </c>
-      <c r="F164" s="41" t="s">
+      <c r="F168" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G164" s="36"/>
-      <c r="H164" s="36"/>
-      <c r="I164" s="36">
+      <c r="G168" s="36"/>
+      <c r="H168" s="36"/>
+      <c r="I168" s="36">
         <v>2</v>
       </c>
-      <c r="J164" s="40"/>
-      <c r="K164" s="40"/>
-      <c r="L164" s="40"/>
-      <c r="M164" s="40"/>
-      <c r="N164" s="40"/>
-      <c r="O164" s="1"/>
-      <c r="P164" s="1" t="s">
+      <c r="J168" s="40"/>
+      <c r="K168" s="40"/>
+      <c r="L168" s="40"/>
+      <c r="M168" s="40"/>
+      <c r="N168" s="40"/>
+      <c r="O168" s="1"/>
+      <c r="P168" s="1" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="165" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A165" s="28">
+    <row r="169" spans="1:17">
+      <c r="A169" s="28">
         <v>100</v>
       </c>
-      <c r="B165" s="21">
+      <c r="B169" s="21">
         <v>72.102999999999994</v>
       </c>
-      <c r="C165" s="28"/>
-      <c r="D165" s="21"/>
-      <c r="E165" s="21"/>
-      <c r="F165" s="21" t="s">
+      <c r="C169" s="28"/>
+      <c r="D169" s="21"/>
+      <c r="E169" s="21"/>
+      <c r="F169" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="G165" s="28">
+      <c r="G169" s="28">
         <v>43</v>
       </c>
-      <c r="H165" s="28">
+      <c r="H169" s="28">
         <v>2</v>
       </c>
-      <c r="I165" s="28"/>
-      <c r="J165" s="34"/>
-      <c r="K165" s="34"/>
-      <c r="L165" s="34"/>
-      <c r="M165" s="34"/>
-      <c r="N165" s="34"/>
-      <c r="O165" s="2"/>
-      <c r="P165" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q165" s="35"/>
-    </row>
-    <row r="166" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A166" s="28">
-        <v>101</v>
-      </c>
-      <c r="B166" s="21"/>
-      <c r="C166" s="28">
-        <v>148</v>
-      </c>
-      <c r="D166" s="21"/>
-      <c r="E166" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="F166" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="G166" s="28">
-        <v>100</v>
-      </c>
-      <c r="H166" s="28">
-        <v>2</v>
-      </c>
-      <c r="I166" s="28">
-        <v>1</v>
-      </c>
-      <c r="J166" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="K166" s="34" t="s">
-        <v>540</v>
-      </c>
-      <c r="L166" s="34"/>
-      <c r="M166" s="34"/>
-      <c r="N166" s="34"/>
-      <c r="O166" s="2"/>
-      <c r="P166" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="Q166" s="35"/>
-    </row>
-    <row r="167" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A167" s="28"/>
-      <c r="B167" s="21"/>
-      <c r="C167" s="28">
-        <v>149</v>
-      </c>
-      <c r="D167" s="21"/>
-      <c r="E167" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="F167" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="G167" s="28"/>
-      <c r="H167" s="28"/>
-      <c r="I167" s="28">
-        <v>2</v>
-      </c>
-      <c r="J167" s="34"/>
-      <c r="K167" s="34"/>
-      <c r="L167" s="34"/>
-      <c r="M167" s="34"/>
-      <c r="N167" s="34"/>
-      <c r="O167" s="2"/>
-      <c r="P167" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="Q167" s="35"/>
-    </row>
-    <row r="168" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A168" s="28">
-        <v>102</v>
-      </c>
-      <c r="B168" s="21">
-        <v>101</v>
-      </c>
-      <c r="C168" s="28">
-        <v>150</v>
-      </c>
-      <c r="D168" s="21"/>
-      <c r="E168" s="92" t="s">
-        <v>656</v>
-      </c>
-      <c r="F168" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="G168" s="28">
-        <v>100</v>
-      </c>
-      <c r="H168" s="28">
-        <v>2</v>
-      </c>
-      <c r="I168" s="28">
-        <v>1</v>
-      </c>
-      <c r="J168" s="34" t="s">
-        <v>542</v>
-      </c>
-      <c r="K168" s="34" t="s">
-        <v>543</v>
-      </c>
-      <c r="L168" s="34"/>
-      <c r="M168" s="34"/>
-      <c r="N168" s="34"/>
-      <c r="O168" s="2"/>
-      <c r="P168" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="Q168" s="35"/>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A169" s="28"/>
-      <c r="B169" s="21"/>
-      <c r="C169" s="28">
-        <v>151</v>
-      </c>
-      <c r="D169" s="21"/>
-      <c r="E169" s="92" t="s">
-        <v>656</v>
-      </c>
-      <c r="F169" s="21"/>
-      <c r="G169" s="28"/>
-      <c r="H169" s="28"/>
-      <c r="I169" s="28">
-        <v>1</v>
-      </c>
+      <c r="I169" s="28"/>
       <c r="J169" s="34"/>
-      <c r="K169" s="34" t="s">
-        <v>545</v>
-      </c>
+      <c r="K169" s="34"/>
       <c r="L169" s="34"/>
-      <c r="M169" s="34" t="s">
-        <v>546</v>
-      </c>
+      <c r="M169" s="34"/>
       <c r="N169" s="34"/>
       <c r="O169" s="2"/>
       <c r="P169" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="Q169" s="42"/>
-    </row>
-    <row r="170" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A170" s="36">
-        <v>103</v>
-      </c>
-      <c r="B170" s="3">
-        <v>68.72</v>
-      </c>
-      <c r="C170" s="36"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-      <c r="F170" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="G170" s="36">
-        <v>43</v>
-      </c>
-      <c r="H170" s="36">
-        <v>1</v>
-      </c>
-      <c r="I170" s="36"/>
-      <c r="J170" s="40"/>
-      <c r="K170" s="40"/>
-      <c r="L170" s="40"/>
-      <c r="M170" s="40"/>
-      <c r="N170" s="40"/>
-      <c r="O170" s="1"/>
-      <c r="P170" s="1" t="s">
-        <v>548</v>
+        <v>537</v>
+      </c>
+      <c r="Q169" s="35"/>
+    </row>
+    <row r="170" spans="1:17">
+      <c r="A170" s="28">
+        <v>101</v>
+      </c>
+      <c r="B170" s="21"/>
+      <c r="C170" s="28">
+        <v>148</v>
+      </c>
+      <c r="D170" s="21"/>
+      <c r="E170" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="F170" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="G170" s="28">
+        <v>100</v>
+      </c>
+      <c r="H170" s="28">
+        <v>2</v>
+      </c>
+      <c r="I170" s="28">
+        <v>1</v>
+      </c>
+      <c r="J170" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="K170" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="L170" s="34"/>
+      <c r="M170" s="34"/>
+      <c r="N170" s="34"/>
+      <c r="O170" s="2"/>
+      <c r="P170" s="2" t="s">
+        <v>541</v>
       </c>
       <c r="Q170" s="35"/>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A171" s="28">
-        <v>71</v>
-      </c>
+    <row r="171" spans="1:17">
+      <c r="A171" s="28"/>
       <c r="B171" s="21"/>
       <c r="C171" s="28">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D171" s="21"/>
       <c r="E171" s="21" t="s">
-        <v>444</v>
+        <v>538</v>
       </c>
       <c r="F171" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="G171" s="28">
-        <v>103</v>
-      </c>
-      <c r="H171" s="28">
-        <v>1</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="G171" s="28"/>
+      <c r="H171" s="28"/>
       <c r="I171" s="28">
-        <v>1</v>
-      </c>
-      <c r="J171" s="34" t="s">
-        <v>445</v>
-      </c>
-      <c r="K171" s="34" t="s">
-        <v>446</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J171" s="34"/>
+      <c r="K171" s="34"/>
       <c r="L171" s="34"/>
       <c r="M171" s="34"/>
       <c r="N171" s="34"/>
       <c r="O171" s="2"/>
       <c r="P171" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="172" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A172" s="36">
-        <v>104</v>
-      </c>
-      <c r="B172" s="3">
-        <v>71</v>
-      </c>
-      <c r="C172" s="36">
-        <v>152</v>
-      </c>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="F172" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="G172" s="36">
+        <v>541</v>
+      </c>
+      <c r="Q171" s="35"/>
+    </row>
+    <row r="172" spans="1:17">
+      <c r="A172" s="28">
+        <v>102</v>
+      </c>
+      <c r="B172" s="21">
+        <v>101</v>
+      </c>
+      <c r="C172" s="28">
+        <v>150</v>
+      </c>
+      <c r="D172" s="21"/>
+      <c r="E172" s="88" t="s">
+        <v>656</v>
+      </c>
+      <c r="F172" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="G172" s="28">
+        <v>100</v>
+      </c>
+      <c r="H172" s="28">
+        <v>2</v>
+      </c>
+      <c r="I172" s="28">
+        <v>1</v>
+      </c>
+      <c r="J172" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="K172" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="L172" s="34"/>
+      <c r="M172" s="34"/>
+      <c r="N172" s="34"/>
+      <c r="O172" s="2"/>
+      <c r="P172" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q172" s="35"/>
+    </row>
+    <row r="173" spans="1:17">
+      <c r="A173" s="28"/>
+      <c r="B173" s="21"/>
+      <c r="C173" s="28">
+        <v>151</v>
+      </c>
+      <c r="D173" s="21"/>
+      <c r="E173" s="88" t="s">
+        <v>656</v>
+      </c>
+      <c r="F173" s="21"/>
+      <c r="G173" s="28"/>
+      <c r="H173" s="28"/>
+      <c r="I173" s="28">
+        <v>1</v>
+      </c>
+      <c r="J173" s="34"/>
+      <c r="K173" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="L173" s="34"/>
+      <c r="M173" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="N173" s="34"/>
+      <c r="O173" s="2"/>
+      <c r="P173" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q173" s="42"/>
+    </row>
+    <row r="174" spans="1:17">
+      <c r="A174" s="36">
         <v>103</v>
       </c>
-      <c r="H172" s="36">
-        <v>1</v>
-      </c>
-      <c r="I172" s="36">
-        <v>1</v>
-      </c>
-      <c r="J172" s="40" t="s">
-        <v>550</v>
-      </c>
-      <c r="K172" s="40" t="s">
-        <v>551</v>
-      </c>
-      <c r="L172" s="40"/>
-      <c r="M172" s="40"/>
-      <c r="N172" s="40"/>
-      <c r="O172" s="1"/>
-      <c r="P172" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="Q172" s="35"/>
-    </row>
-    <row r="173" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A173" s="36">
-        <v>105</v>
-      </c>
-      <c r="B173" s="3">
-        <v>104</v>
-      </c>
-      <c r="C173" s="36">
-        <v>153</v>
-      </c>
-      <c r="D173" s="3"/>
-      <c r="E173" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="F173" s="41" t="s">
-        <v>182</v>
-      </c>
-      <c r="G173" s="36">
-        <v>103</v>
-      </c>
-      <c r="H173" s="36">
-        <v>1</v>
-      </c>
-      <c r="I173" s="36">
-        <v>1</v>
-      </c>
-      <c r="J173" s="40" t="s">
-        <v>554</v>
-      </c>
-      <c r="K173" s="40" t="s">
-        <v>555</v>
-      </c>
-      <c r="L173" s="40"/>
-      <c r="M173" s="40" t="s">
-        <v>556</v>
-      </c>
-      <c r="N173" s="40"/>
-      <c r="O173" s="1"/>
-      <c r="P173" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="Q173" s="35"/>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A174" s="36">
-        <v>106</v>
-      </c>
       <c r="B174" s="3">
-        <v>104</v>
-      </c>
-      <c r="C174" s="36">
-        <v>154</v>
-      </c>
+        <v>68.72</v>
+      </c>
+      <c r="C174" s="36"/>
       <c r="D174" s="3"/>
-      <c r="E174" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="F174" s="41" t="s">
-        <v>183</v>
+      <c r="E174" s="3"/>
+      <c r="F174" s="3" t="s">
+        <v>602</v>
       </c>
       <c r="G174" s="36">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="H174" s="36">
         <v>1</v>
       </c>
-      <c r="I174" s="36">
-        <v>1</v>
-      </c>
-      <c r="J174" s="40" t="s">
-        <v>559</v>
-      </c>
-      <c r="K174" s="40" t="s">
-        <v>560</v>
-      </c>
+      <c r="I174" s="36"/>
+      <c r="J174" s="40"/>
+      <c r="K174" s="40"/>
       <c r="L174" s="40"/>
-      <c r="M174" s="40" t="s">
-        <v>561</v>
-      </c>
+      <c r="M174" s="40"/>
       <c r="N174" s="40"/>
       <c r="O174" s="1"/>
       <c r="P174" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.2">
+        <v>548</v>
+      </c>
+      <c r="Q174" s="35"/>
+    </row>
+    <row r="175" spans="1:17">
       <c r="A175" s="28">
-        <v>107</v>
-      </c>
-      <c r="B175" s="21">
-        <v>103</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B175" s="21"/>
       <c r="C175" s="28">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="D175" s="21"/>
       <c r="E175" s="21" t="s">
-        <v>563</v>
-      </c>
-      <c r="F175" s="21" t="s">
-        <v>36</v>
+        <v>444</v>
+      </c>
+      <c r="F175" s="33" t="s">
+        <v>152</v>
       </c>
       <c r="G175" s="28">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="H175" s="28">
         <v>1</v>
@@ -12794,64 +12742,79 @@
         <v>1</v>
       </c>
       <c r="J175" s="34" t="s">
-        <v>564</v>
-      </c>
-      <c r="K175" s="34"/>
+        <v>445</v>
+      </c>
+      <c r="K175" s="34" t="s">
+        <v>446</v>
+      </c>
       <c r="L175" s="34"/>
       <c r="M175" s="34"/>
       <c r="N175" s="34"/>
       <c r="O175" s="2"/>
       <c r="P175" s="2" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.2">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17">
       <c r="A176" s="36">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="B176" s="3">
-        <v>107</v>
-      </c>
-      <c r="C176" s="40"/>
+        <v>71</v>
+      </c>
+      <c r="C176" s="36">
+        <v>152</v>
+      </c>
       <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-      <c r="F176" s="3" t="s">
-        <v>184</v>
+      <c r="E176" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="F176" s="41" t="s">
+        <v>181</v>
       </c>
       <c r="G176" s="36">
-        <v>43</v>
-      </c>
-      <c r="H176" s="95">
-        <v>1</v>
-      </c>
-      <c r="I176" s="36"/>
-      <c r="J176" s="40"/>
-      <c r="K176" s="40"/>
+        <v>103</v>
+      </c>
+      <c r="H176" s="36">
+        <v>1</v>
+      </c>
+      <c r="I176" s="36">
+        <v>1</v>
+      </c>
+      <c r="J176" s="40" t="s">
+        <v>550</v>
+      </c>
+      <c r="K176" s="40" t="s">
+        <v>551</v>
+      </c>
       <c r="L176" s="40"/>
       <c r="M176" s="40"/>
       <c r="N176" s="40"/>
       <c r="O176" s="1"/>
       <c r="P176" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
+        <v>552</v>
+      </c>
+      <c r="Q176" s="35"/>
+    </row>
+    <row r="177" spans="1:17">
       <c r="A177" s="36">
-        <v>108</v>
-      </c>
-      <c r="B177" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="B177" s="3">
+        <v>104</v>
+      </c>
       <c r="C177" s="36">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D177" s="3"/>
-      <c r="E177" s="93" t="s">
-        <v>650</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>184</v>
+      <c r="E177" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="F177" s="41" t="s">
+        <v>182</v>
       </c>
       <c r="G177" s="36">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="H177" s="36">
         <v>1</v>
@@ -12860,34 +12823,41 @@
         <v>1</v>
       </c>
       <c r="J177" s="40" t="s">
-        <v>566</v>
-      </c>
-      <c r="K177" s="40"/>
+        <v>554</v>
+      </c>
+      <c r="K177" s="40" t="s">
+        <v>555</v>
+      </c>
       <c r="L177" s="40"/>
-      <c r="M177" s="40"/>
+      <c r="M177" s="40" t="s">
+        <v>556</v>
+      </c>
       <c r="N177" s="40"/>
       <c r="O177" s="1"/>
-      <c r="P177" s="1"/>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P177" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q177" s="35"/>
+    </row>
+    <row r="178" spans="1:17">
       <c r="A178" s="36">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B178" s="3">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C178" s="36">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D178" s="3"/>
-      <c r="E178" s="93" t="s">
-        <v>651</v>
+      <c r="E178" s="3" t="s">
+        <v>558</v>
       </c>
       <c r="F178" s="41" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G178" s="36">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="H178" s="36">
         <v>1</v>
@@ -12896,24 +12866,224 @@
         <v>1</v>
       </c>
       <c r="J178" s="40" t="s">
-        <v>568</v>
-      </c>
-      <c r="K178" s="40"/>
+        <v>559</v>
+      </c>
+      <c r="K178" s="40" t="s">
+        <v>560</v>
+      </c>
       <c r="L178" s="40"/>
-      <c r="M178" s="40"/>
+      <c r="M178" s="40" t="s">
+        <v>561</v>
+      </c>
       <c r="N178" s="40"/>
       <c r="O178" s="1"/>
       <c r="P178" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17">
+      <c r="A179" s="28">
+        <v>107</v>
+      </c>
+      <c r="B179" s="21">
+        <v>103</v>
+      </c>
+      <c r="C179" s="28">
+        <v>155</v>
+      </c>
+      <c r="D179" s="21"/>
+      <c r="E179" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="F179" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G179" s="28">
+        <v>43</v>
+      </c>
+      <c r="H179" s="28">
+        <v>3</v>
+      </c>
+      <c r="I179" s="28">
+        <v>1</v>
+      </c>
+      <c r="J179" s="34" t="s">
+        <v>564</v>
+      </c>
+      <c r="K179" s="34"/>
+      <c r="L179" s="34"/>
+      <c r="M179" s="34"/>
+      <c r="N179" s="34"/>
+      <c r="O179" s="2"/>
+      <c r="P179" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17">
+      <c r="A180" s="28"/>
+      <c r="B180" s="21"/>
+      <c r="C180" s="28">
+        <v>160</v>
+      </c>
+      <c r="D180" s="21"/>
+      <c r="E180" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="F180" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G180" s="28">
+        <v>107</v>
+      </c>
+      <c r="H180" s="28"/>
+      <c r="I180" s="28">
+        <v>2</v>
+      </c>
+      <c r="J180" s="34"/>
+      <c r="K180" s="34"/>
+      <c r="L180" s="34"/>
+      <c r="M180" s="34"/>
+      <c r="N180" s="34"/>
+      <c r="O180" s="2"/>
+      <c r="P180" s="2"/>
+    </row>
+    <row r="181" spans="1:17">
+      <c r="A181" s="28"/>
+      <c r="B181" s="21"/>
+      <c r="C181" s="28">
+        <v>161</v>
+      </c>
+      <c r="D181" s="21"/>
+      <c r="E181" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="F181" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G181" s="28">
+        <v>107</v>
+      </c>
+      <c r="H181" s="28"/>
+      <c r="I181" s="28">
+        <v>3</v>
+      </c>
+      <c r="J181" s="34"/>
+      <c r="K181" s="34"/>
+      <c r="L181" s="34"/>
+      <c r="M181" s="34"/>
+      <c r="N181" s="34"/>
+      <c r="O181" s="2"/>
+      <c r="P181" s="2"/>
+    </row>
+    <row r="182" spans="1:17">
+      <c r="A182" s="36">
+        <v>209</v>
+      </c>
+      <c r="B182" s="3">
+        <v>107</v>
+      </c>
+      <c r="C182" s="40"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G182" s="36">
+        <v>43</v>
+      </c>
+      <c r="H182" s="91">
+        <v>1</v>
+      </c>
+      <c r="I182" s="36"/>
+      <c r="J182" s="40"/>
+      <c r="K182" s="40"/>
+      <c r="L182" s="40"/>
+      <c r="M182" s="40"/>
+      <c r="N182" s="40"/>
+      <c r="O182" s="1"/>
+      <c r="P182" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17">
+      <c r="A183" s="36">
+        <v>108</v>
+      </c>
+      <c r="B183" s="3"/>
+      <c r="C183" s="36">
+        <v>156</v>
+      </c>
+      <c r="D183" s="3"/>
+      <c r="E183" s="89" t="s">
+        <v>650</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G183" s="36">
+        <v>209</v>
+      </c>
+      <c r="H183" s="36">
+        <v>1</v>
+      </c>
+      <c r="I183" s="36">
+        <v>1</v>
+      </c>
+      <c r="J183" s="40" t="s">
+        <v>566</v>
+      </c>
+      <c r="K183" s="40"/>
+      <c r="L183" s="40"/>
+      <c r="M183" s="40"/>
+      <c r="N183" s="40"/>
+      <c r="O183" s="1"/>
+      <c r="P183" s="1"/>
+    </row>
+    <row r="184" spans="1:17">
+      <c r="A184" s="36">
+        <v>109</v>
+      </c>
+      <c r="B184" s="3">
+        <v>108</v>
+      </c>
+      <c r="C184" s="36">
+        <v>157</v>
+      </c>
+      <c r="D184" s="3"/>
+      <c r="E184" s="89" t="s">
+        <v>651</v>
+      </c>
+      <c r="F184" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="G184" s="36">
+        <v>209</v>
+      </c>
+      <c r="H184" s="36">
+        <v>1</v>
+      </c>
+      <c r="I184" s="36">
+        <v>1</v>
+      </c>
+      <c r="J184" s="40" t="s">
+        <v>568</v>
+      </c>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
+      <c r="N184" s="40"/>
+      <c r="O184" s="1"/>
+      <c r="P184" s="1" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A179" s="61"/>
-      <c r="C179" s="61"/>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A180" s="61"/>
-      <c r="C180" s="61"/>
+    <row r="185" spans="1:17">
+      <c r="A185" s="61"/>
+      <c r="C185" s="61"/>
+    </row>
+    <row r="186" spans="1:17">
+      <c r="A186" s="61"/>
+      <c r="C186" s="61"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
@@ -12922,23 +13092,23 @@
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J161:J1048576 J1:J159">
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K161:K1048576 K1:K159">
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.70069444444444395" right="0.70069444444444395" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12948,30 +13118,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="35.6640625" customWidth="1"/>
-    <col min="3" max="4" width="7.1640625" customWidth="1"/>
+    <col min="1" max="2" width="35.7109375" customWidth="1"/>
+    <col min="3" max="4" width="7.140625" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="8" width="28.5" customWidth="1"/>
-    <col min="10" max="10" width="42.83203125" customWidth="1"/>
+    <col min="6" max="8" width="28.42578125" customWidth="1"/>
+    <col min="10" max="10" width="42.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="89" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="89"/>
+      <c r="B4" s="95"/>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
@@ -12992,9 +13162,9 @@
         <v>570</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="90"/>
-      <c r="B5" s="90"/>
+    <row r="5" spans="1:10" ht="45">
+      <c r="A5" s="96"/>
+      <c r="B5" s="96"/>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
@@ -13009,7 +13179,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="45">
       <c r="A6" s="21"/>
       <c r="B6" s="21"/>
       <c r="C6" s="2"/>
@@ -13028,7 +13198,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="60">
       <c r="A7" s="21"/>
       <c r="B7" s="21"/>
       <c r="C7" s="2"/>
@@ -13045,7 +13215,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="60">
       <c r="A8" s="21"/>
       <c r="B8" s="21"/>
       <c r="C8" s="2"/>
@@ -13062,7 +13232,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="30">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="2"/>
@@ -13079,7 +13249,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="30">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="2"/>
@@ -13098,7 +13268,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="30">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="2"/>
@@ -13117,7 +13287,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="30">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="2"/>
@@ -13134,7 +13304,7 @@
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="30">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="2"/>
@@ -13151,7 +13321,7 @@
       </c>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="30">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="2"/>
@@ -13168,7 +13338,7 @@
       </c>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="30">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="2"/>
@@ -13185,7 +13355,7 @@
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="60">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="2"/>
@@ -13198,7 +13368,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="75">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="2"/>
@@ -13211,11 +13381,11 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="62"/>
       <c r="B18" s="62"/>
     </row>
-    <row r="19" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="45">
       <c r="A19" s="5" t="s">
         <v>77</v>
       </c>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB50F974-8CB0-45A5-B96E-574579D5AE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2E42F9-24C8-4946-9F73-FF746C9023AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25725" yWindow="90" windowWidth="25890" windowHeight="20805" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFP" sheetId="1" r:id="rId1"/>
@@ -2049,7 +2049,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2661,9 +2661,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2701,7 +2701,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2807,7 +2807,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2949,7 +2949,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2958,25 +2958,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I245"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="4" width="7.140625" customWidth="1"/>
+    <col min="1" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="4" width="7.1640625" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="9" width="28.42578125" customWidth="1"/>
+    <col min="6" max="9" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="95" t="s">
         <v>2</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30">
+    <row r="5" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="96" t="s">
         <v>7</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30">
+    <row r="6" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="93" t="s">
         <v>12</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30">
+    <row r="7" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="94" t="s">
         <v>17</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="60">
+    <row r="8" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="93" t="s">
         <v>22</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="45">
+    <row r="9" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>28</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="45">
+    <row r="10" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
         <v>32</v>
@@ -3124,7 +3124,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="45">
+    <row r="11" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
         <v>36</v>
@@ -3146,7 +3146,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30">
+    <row r="12" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
         <v>42</v>
@@ -3168,7 +3168,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="75">
+    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
         <v>46</v>
@@ -3190,7 +3190,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="60">
+    <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>50</v>
@@ -3210,7 +3210,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="93" t="s">
         <v>55</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="45">
+    <row r="16" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="94" t="s">
         <v>60</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="60">
+    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>65</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="2" t="s">
         <v>67</v>
@@ -3268,7 +3268,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="2" t="s">
         <v>69</v>
@@ -3277,7 +3277,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="2" t="s">
         <v>71</v>
@@ -3286,7 +3286,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="2" t="s">
         <v>73</v>
@@ -3295,7 +3295,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="2" t="s">
         <v>75</v>
@@ -3304,7 +3304,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="45">
+    <row r="24" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>77</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>67</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8" s="13" customFormat="1">
+    <row r="26" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -3358,7 +3358,7 @@
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
     </row>
-    <row r="27" spans="1:8" s="13" customFormat="1">
+    <row r="27" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>88</v>
@@ -3372,7 +3372,7 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" spans="1:8" s="13" customFormat="1">
+    <row r="28" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="11"/>
@@ -3384,7 +3384,7 @@
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>90</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
         <v>91</v>
@@ -3426,7 +3426,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="7"/>
@@ -3438,7 +3438,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>92</v>
       </c>
@@ -3450,7 +3450,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" s="13" customFormat="1">
+    <row r="34" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
@@ -3466,7 +3466,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" s="13" customFormat="1">
+    <row r="35" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="17"/>
       <c r="C35" s="2"/>
@@ -3478,7 +3478,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" s="13" customFormat="1">
+    <row r="36" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="17" t="s">
         <v>94</v>
@@ -3490,7 +3490,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" s="13" customFormat="1">
+    <row r="37" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
         <v>95</v>
@@ -3504,7 +3504,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" s="13" customFormat="1">
+    <row r="38" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3516,7 +3516,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" s="13" customFormat="1">
+    <row r="39" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>96</v>
@@ -3530,7 +3530,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" s="13" customFormat="1">
+    <row r="40" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3542,7 +3542,7 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" s="13" customFormat="1">
+    <row r="41" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
         <v>97</v>
@@ -3556,7 +3556,7 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" s="13" customFormat="1">
+    <row r="42" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3568,7 +3568,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" s="13" customFormat="1">
+    <row r="43" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
         <v>98</v>
@@ -3582,7 +3582,7 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" s="13" customFormat="1">
+    <row r="44" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3594,7 +3594,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" s="13" customFormat="1">
+    <row r="45" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
         <v>99</v>
@@ -3608,7 +3608,7 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" s="13" customFormat="1">
+    <row r="46" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3620,7 +3620,7 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" s="13" customFormat="1">
+    <row r="47" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
         <v>100</v>
@@ -3634,7 +3634,7 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" s="13" customFormat="1">
+    <row r="48" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3646,7 +3646,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" s="13" customFormat="1">
+    <row r="49" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
         <v>101</v>
@@ -3660,7 +3660,7 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" s="13" customFormat="1">
+    <row r="50" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3672,7 +3672,7 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" s="13" customFormat="1">
+    <row r="51" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>102</v>
       </c>
@@ -3684,7 +3684,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8" s="13" customFormat="1">
+    <row r="52" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>85</v>
       </c>
@@ -3698,7 +3698,7 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
         <v>103</v>
@@ -3712,7 +3712,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3724,7 +3724,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
         <v>105</v>
@@ -3736,7 +3736,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
         <v>106</v>
@@ -3750,7 +3750,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3762,7 +3762,7 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
         <v>107</v>
@@ -3776,7 +3776,7 @@
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3788,7 +3788,7 @@
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3800,7 +3800,7 @@
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>108</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>85</v>
       </c>
@@ -3828,7 +3828,7 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3840,7 +3840,7 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3852,7 +3852,7 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>109</v>
@@ -3866,7 +3866,7 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>110</v>
@@ -3880,7 +3880,7 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3892,7 +3892,7 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>111</v>
@@ -3906,7 +3906,7 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3918,7 +3918,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>112</v>
@@ -3932,7 +3932,7 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3944,7 +3944,7 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3956,7 +3956,7 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2" t="s">
         <v>113</v>
@@ -3970,7 +3970,7 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2" t="s">
         <v>114</v>
@@ -3984,7 +3984,7 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3996,7 +3996,7 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>73</v>
@@ -4010,7 +4010,7 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4022,7 +4022,7 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" ht="30">
+    <row r="78" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
         <v>115</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
         <v>85</v>
       </c>
@@ -4052,7 +4052,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
         <v>85</v>
       </c>
@@ -4068,7 +4068,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="1"/>
@@ -4080,7 +4080,7 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>60</v>
       </c>
@@ -4092,7 +4092,7 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>118</v>
@@ -4106,7 +4106,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4118,7 +4118,7 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>85</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4146,7 +4146,7 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4158,7 +4158,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
         <v>119</v>
@@ -4174,7 +4174,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>121</v>
       </c>
@@ -4188,7 +4188,7 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>85</v>
       </c>
@@ -4202,7 +4202,7 @@
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4214,7 +4214,7 @@
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4226,7 +4226,7 @@
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4238,7 +4238,7 @@
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4250,7 +4250,7 @@
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
         <v>109</v>
@@ -4264,7 +4264,7 @@
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4276,7 +4276,7 @@
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>122</v>
       </c>
@@ -4288,7 +4288,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2" t="s">
         <v>123</v>
@@ -4302,7 +4302,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4314,7 +4314,7 @@
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4326,7 +4326,7 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2" t="s">
         <v>124</v>
@@ -4340,7 +4340,7 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4352,7 +4352,7 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4364,7 +4364,7 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4376,7 +4376,7 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2" t="s">
         <v>125</v>
@@ -4390,7 +4390,7 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4402,7 +4402,7 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4414,7 +4414,7 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>126</v>
       </c>
@@ -4426,7 +4426,7 @@
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>85</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4454,7 +4454,7 @@
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1" t="s">
         <v>128</v>
@@ -4468,7 +4468,7 @@
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
         <v>129</v>
@@ -4482,7 +4482,7 @@
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
     </row>
-    <row r="114" spans="1:8" ht="30">
+    <row r="114" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="19" t="s">
         <v>130</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>131</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>132</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>131</v>
       </c>
@@ -4538,7 +4538,7 @@
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>92</v>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4564,7 +4564,7 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>131</v>
       </c>
@@ -4580,7 +4580,7 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4592,7 +4592,7 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2" t="s">
         <v>134</v>
@@ -4606,7 +4606,7 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -4618,7 +4618,7 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2" t="s">
         <v>135</v>
@@ -4632,7 +4632,7 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -4644,7 +4644,7 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2" t="s">
         <v>97</v>
@@ -4658,7 +4658,7 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -4670,7 +4670,7 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2" t="s">
         <v>93</v>
@@ -4684,7 +4684,7 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -4696,7 +4696,7 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -4708,7 +4708,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2" t="s">
         <v>136</v>
@@ -4722,7 +4722,7 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -4734,7 +4734,7 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
         <v>137</v>
@@ -4748,7 +4748,7 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -4760,7 +4760,7 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2" t="s">
         <v>138</v>
@@ -4774,7 +4774,7 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -4786,7 +4786,7 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2" t="s">
         <v>139</v>
@@ -4800,7 +4800,7 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -4812,7 +4812,7 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>90</v>
       </c>
@@ -4826,7 +4826,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>131</v>
       </c>
@@ -4840,7 +4840,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>140</v>
       </c>
@@ -4852,7 +4852,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>131</v>
       </c>
@@ -4868,7 +4868,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -4880,7 +4880,7 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2" t="s">
         <v>142</v>
@@ -4894,7 +4894,7 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -4906,7 +4906,7 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2" t="s">
         <v>143</v>
@@ -4920,7 +4920,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -4932,7 +4932,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2" t="s">
         <v>144</v>
@@ -4946,7 +4946,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -4958,7 +4958,7 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2" t="s">
         <v>145</v>
@@ -4972,7 +4972,7 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -4984,7 +4984,7 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>146</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>131</v>
       </c>
@@ -5012,7 +5012,7 @@
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5024,7 +5024,7 @@
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1" t="s">
         <v>147</v>
@@ -5038,7 +5038,7 @@
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5050,7 +5050,7 @@
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1" t="s">
         <v>105</v>
@@ -5064,7 +5064,7 @@
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5076,7 +5076,7 @@
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1" t="s">
         <v>106</v>
@@ -5090,7 +5090,7 @@
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5102,7 +5102,7 @@
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1" t="s">
         <v>148</v>
@@ -5116,7 +5116,7 @@
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5128,7 +5128,7 @@
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
         <v>149</v>
@@ -5142,7 +5142,7 @@
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5154,7 +5154,7 @@
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="17" t="s">
         <v>126</v>
       </c>
@@ -5166,7 +5166,7 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>131</v>
       </c>
@@ -5182,7 +5182,7 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="17"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -5194,7 +5194,7 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2" t="s">
         <v>151</v>
@@ -5208,7 +5208,7 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -5220,7 +5220,7 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2" t="s">
         <v>152</v>
@@ -5234,7 +5234,7 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -5246,7 +5246,7 @@
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>153</v>
       </c>
@@ -5258,7 +5258,7 @@
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>131</v>
       </c>
@@ -5274,7 +5274,7 @@
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5286,7 +5286,7 @@
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1" t="s">
         <v>155</v>
@@ -5300,7 +5300,7 @@
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5312,7 +5312,7 @@
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1" t="s">
         <v>156</v>
@@ -5326,7 +5326,7 @@
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5338,7 +5338,7 @@
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1" t="s">
         <v>157</v>
@@ -5352,7 +5352,7 @@
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5364,7 +5364,7 @@
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1" t="s">
         <v>158</v>
@@ -5378,7 +5378,7 @@
       <c r="G181" s="1"/>
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5390,7 +5390,7 @@
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1" t="s">
         <v>159</v>
@@ -5404,7 +5404,7 @@
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5416,7 +5416,7 @@
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5428,7 +5428,7 @@
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>160</v>
       </c>
@@ -5444,7 +5444,7 @@
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>131</v>
       </c>
@@ -5458,7 +5458,7 @@
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2" t="s">
         <v>162</v>
@@ -5472,7 +5472,7 @@
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -5484,7 +5484,7 @@
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2" t="s">
         <v>163</v>
@@ -5498,7 +5498,7 @@
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -5510,7 +5510,7 @@
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2" t="s">
         <v>121</v>
@@ -5524,7 +5524,7 @@
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -5536,7 +5536,7 @@
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>164</v>
       </c>
@@ -5552,7 +5552,7 @@
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5564,7 +5564,7 @@
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1" t="s">
         <v>165</v>
@@ -5578,7 +5578,7 @@
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5590,7 +5590,7 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1" t="s">
         <v>155</v>
@@ -5604,7 +5604,7 @@
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5616,7 +5616,7 @@
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1" t="s">
         <v>153</v>
@@ -5630,7 +5630,7 @@
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -5642,7 +5642,7 @@
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1" t="s">
         <v>166</v>
@@ -5656,7 +5656,7 @@
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -5668,7 +5668,7 @@
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1" t="s">
         <v>167</v>
@@ -5682,7 +5682,7 @@
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -5694,7 +5694,7 @@
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1" t="s">
         <v>168</v>
@@ -5708,7 +5708,7 @@
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -5720,7 +5720,7 @@
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1" t="s">
         <v>169</v>
@@ -5734,7 +5734,7 @@
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -5746,7 +5746,7 @@
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1" t="s">
         <v>170</v>
@@ -5760,7 +5760,7 @@
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -5772,7 +5772,7 @@
       <c r="G211" s="1"/>
       <c r="H211" s="1"/>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>171</v>
       </c>
@@ -5788,7 +5788,7 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -5800,7 +5800,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>131</v>
       </c>
@@ -5816,7 +5816,7 @@
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -5828,7 +5828,7 @@
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>164</v>
       </c>
@@ -5844,7 +5844,7 @@
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -5856,7 +5856,7 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -5868,7 +5868,7 @@
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
       <c r="B219" s="2" t="s">
         <v>171</v>
@@ -5882,7 +5882,7 @@
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -5894,7 +5894,7 @@
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -5906,7 +5906,7 @@
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>175</v>
       </c>
@@ -5920,7 +5920,7 @@
       <c r="G222" s="1"/>
       <c r="H222" s="1"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>131</v>
       </c>
@@ -5934,7 +5934,7 @@
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1" t="s">
         <v>176</v>
@@ -5948,7 +5948,7 @@
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -5960,7 +5960,7 @@
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>177</v>
       </c>
@@ -5976,7 +5976,7 @@
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -5988,7 +5988,7 @@
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>131</v>
       </c>
@@ -6004,7 +6004,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -6016,7 +6016,7 @@
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -6028,7 +6028,7 @@
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -6040,7 +6040,7 @@
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
         <v>180</v>
       </c>
@@ -6052,7 +6052,7 @@
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1" t="s">
         <v>181</v>
@@ -6066,7 +6066,7 @@
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -6078,7 +6078,7 @@
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>131</v>
       </c>
@@ -6094,7 +6094,7 @@
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -6106,7 +6106,7 @@
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -6118,7 +6118,7 @@
       <c r="G237" s="1"/>
       <c r="H237" s="1"/>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1" t="s">
         <v>183</v>
@@ -6132,7 +6132,7 @@
       <c r="G238" s="1"/>
       <c r="H238" s="1"/>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -6144,7 +6144,7 @@
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -6156,7 +6156,7 @@
       <c r="G240" s="1"/>
       <c r="H240" s="1"/>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
         <v>36</v>
       </c>
@@ -6170,7 +6170,7 @@
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>131</v>
       </c>
@@ -6184,7 +6184,7 @@
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>184</v>
       </c>
@@ -6198,7 +6198,7 @@
       <c r="G243" s="1"/>
       <c r="H243" s="1"/>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>131</v>
       </c>
@@ -6214,7 +6214,7 @@
       <c r="G244" s="1"/>
       <c r="H244" s="1"/>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -6436,28 +6436,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AMJ186"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="22" customWidth="1"/>
-    <col min="6" max="6" width="43.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" customWidth="1"/>
-    <col min="10" max="10" width="36.140625" customWidth="1"/>
-    <col min="11" max="11" width="37.7109375" customWidth="1"/>
-    <col min="12" max="12" width="45.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="18.5" style="22" customWidth="1"/>
+    <col min="6" max="6" width="43.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" customWidth="1"/>
+    <col min="10" max="10" width="36.1640625" customWidth="1"/>
+    <col min="11" max="11" width="37.6640625" customWidth="1"/>
+    <col min="12" max="12" width="45.1640625" customWidth="1"/>
     <col min="13" max="13" width="41" customWidth="1"/>
-    <col min="14" max="14" width="32.7109375" customWidth="1"/>
+    <col min="14" max="14" width="32.6640625" customWidth="1"/>
     <col min="15" max="15" width="32" customWidth="1"/>
-    <col min="16" max="16" width="63.7109375" customWidth="1"/>
-    <col min="1024" max="1024" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="63.6640625" customWidth="1"/>
+    <col min="1024" max="1024" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30">
+    <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>186</v>
       </c>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Q1" s="24"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -6536,7 +6536,7 @@
       <c r="O2" s="5"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
         <v>4</v>
       </c>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="Q3" s="35"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
         <v>5</v>
       </c>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="Q4" s="35"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
         <v>6</v>
       </c>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="36">
         <v>7</v>
       </c>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="Q6" s="42"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
         <v>210</v>
       </c>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Q7" s="35"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
         <v>8</v>
       </c>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Q8" s="35"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
         <v>9</v>
       </c>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="Q9" s="42"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="28"/>
       <c r="B10" s="21"/>
       <c r="C10" s="28">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="Q10" s="42"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="28"/>
       <c r="B11" s="21"/>
       <c r="C11" s="28">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="Q11" s="42"/>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
         <v>10</v>
       </c>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="Q12" s="35"/>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
         <v>11</v>
       </c>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="Q13" s="35"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
         <v>12</v>
       </c>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="Q14" s="35"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="28"/>
       <c r="B15" s="21"/>
       <c r="C15" s="28">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="Q15" s="35"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
         <v>13</v>
       </c>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="Q16" s="35"/>
     </row>
-    <row r="17" spans="1:1024">
+    <row r="17" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
         <v>14</v>
       </c>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Q17" s="35"/>
     </row>
-    <row r="18" spans="1:1024">
+    <row r="18" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
         <v>16</v>
       </c>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="Q18" s="35"/>
     </row>
-    <row r="19" spans="1:1024">
+    <row r="19" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
         <v>17</v>
       </c>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="Q19" s="35"/>
     </row>
-    <row r="20" spans="1:1024">
+    <row r="20" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
         <v>15</v>
       </c>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="Q20" s="35"/>
     </row>
-    <row r="21" spans="1:1024" s="72" customFormat="1">
+    <row r="21" spans="1:1024" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="66">
         <v>201</v>
       </c>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="Q21" s="71"/>
     </row>
-    <row r="22" spans="1:1024">
+    <row r="22" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="36">
         <v>18</v>
       </c>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Q22" s="35"/>
     </row>
-    <row r="23" spans="1:1024">
+    <row r="23" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A23" s="36">
         <v>19</v>
       </c>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Q23" s="42"/>
     </row>
-    <row r="24" spans="1:1024">
+    <row r="24" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A24" s="36"/>
       <c r="B24" s="3"/>
       <c r="C24" s="36">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="Q24" s="42"/>
     </row>
-    <row r="25" spans="1:1024">
+    <row r="25" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A25" s="36"/>
       <c r="B25" s="3"/>
       <c r="C25" s="36">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="Q25" s="42"/>
     </row>
-    <row r="26" spans="1:1024">
+    <row r="26" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="36">
         <v>20</v>
       </c>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="Q26" s="35"/>
     </row>
-    <row r="27" spans="1:1024">
+    <row r="27" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="36">
         <v>21</v>
       </c>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Q27" s="35"/>
     </row>
-    <row r="28" spans="1:1024">
+    <row r="28" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="36"/>
       <c r="B28" s="3"/>
       <c r="C28" s="36">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="Q28" s="35"/>
     </row>
-    <row r="29" spans="1:1024">
+    <row r="29" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A29" s="36">
         <v>22</v>
       </c>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="Q29" s="42"/>
     </row>
-    <row r="30" spans="1:1024">
+    <row r="30" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A30" s="36"/>
       <c r="B30" s="3"/>
       <c r="C30" s="36">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Q30" s="42"/>
     </row>
-    <row r="31" spans="1:1024">
+    <row r="31" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A31" s="36"/>
       <c r="B31" s="3"/>
       <c r="C31" s="36">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="Q31" s="42"/>
     </row>
-    <row r="32" spans="1:1024" s="85" customFormat="1">
+    <row r="32" spans="1:1024" s="85" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="50">
         <v>211</v>
       </c>
@@ -7663,7 +7663,7 @@
       <c r="Q32" s="84"/>
       <c r="AMJ32" s="86"/>
     </row>
-    <row r="33" spans="1:1024" s="85" customFormat="1">
+    <row r="33" spans="1:1024" s="85" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="50">
         <v>39</v>
       </c>
@@ -7699,7 +7699,7 @@
       <c r="Q33" s="84"/>
       <c r="AMJ33" s="86"/>
     </row>
-    <row r="34" spans="1:1024" s="55" customFormat="1">
+    <row r="34" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="50">
         <v>40</v>
       </c>
@@ -7743,7 +7743,7 @@
       <c r="Q34" s="57"/>
       <c r="AMJ34"/>
     </row>
-    <row r="35" spans="1:1024" s="55" customFormat="1">
+    <row r="35" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50"/>
       <c r="B35" s="51"/>
       <c r="C35" s="50">
@@ -7775,7 +7775,7 @@
       <c r="Q35" s="57"/>
       <c r="AMJ35"/>
     </row>
-    <row r="36" spans="1:1024" s="55" customFormat="1">
+    <row r="36" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="50"/>
       <c r="B36" s="51"/>
       <c r="C36" s="50">
@@ -7807,7 +7807,7 @@
       <c r="Q36" s="57"/>
       <c r="AMJ36"/>
     </row>
-    <row r="37" spans="1:1024" s="55" customFormat="1">
+    <row r="37" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="50">
         <v>41</v>
       </c>
@@ -7849,7 +7849,7 @@
       <c r="Q37" s="57"/>
       <c r="AMJ37"/>
     </row>
-    <row r="38" spans="1:1024" s="55" customFormat="1">
+    <row r="38" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="50"/>
       <c r="B38" s="51"/>
       <c r="C38" s="50">
@@ -7881,7 +7881,7 @@
       <c r="Q38" s="57"/>
       <c r="AMJ38"/>
     </row>
-    <row r="39" spans="1:1024" s="55" customFormat="1">
+    <row r="39" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="50">
         <v>42</v>
       </c>
@@ -7923,7 +7923,7 @@
       <c r="Q39" s="57"/>
       <c r="AMJ39"/>
     </row>
-    <row r="40" spans="1:1024" s="80" customFormat="1">
+    <row r="40" spans="1:1024" s="80" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="73">
         <v>202</v>
       </c>
@@ -7953,7 +7953,7 @@
       <c r="Q40" s="79"/>
       <c r="AMJ40" s="81"/>
     </row>
-    <row r="41" spans="1:1024" s="55" customFormat="1">
+    <row r="41" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="28">
         <v>23</v>
       </c>
@@ -7993,7 +7993,7 @@
       <c r="Q41" s="54"/>
       <c r="AMJ41"/>
     </row>
-    <row r="42" spans="1:1024" s="55" customFormat="1">
+    <row r="42" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="28"/>
       <c r="B42" s="21"/>
       <c r="C42" s="28">
@@ -8025,7 +8025,7 @@
       <c r="Q42" s="54"/>
       <c r="AMJ42"/>
     </row>
-    <row r="43" spans="1:1024" s="55" customFormat="1">
+    <row r="43" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="28"/>
       <c r="B43" s="21"/>
       <c r="C43" s="28">
@@ -8061,7 +8061,7 @@
       <c r="Q43" s="54"/>
       <c r="AMJ43"/>
     </row>
-    <row r="44" spans="1:1024" s="55" customFormat="1">
+    <row r="44" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="28"/>
       <c r="B44" s="21"/>
       <c r="C44" s="28">
@@ -8099,7 +8099,7 @@
       <c r="Q44" s="54"/>
       <c r="AMJ44"/>
     </row>
-    <row r="45" spans="1:1024" s="55" customFormat="1">
+    <row r="45" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="28">
         <v>24</v>
       </c>
@@ -8143,7 +8143,7 @@
       <c r="Q45" s="54"/>
       <c r="AMJ45"/>
     </row>
-    <row r="46" spans="1:1024" s="55" customFormat="1">
+    <row r="46" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="28">
         <v>25</v>
       </c>
@@ -8187,7 +8187,7 @@
       <c r="Q46" s="54"/>
       <c r="AMJ46"/>
     </row>
-    <row r="47" spans="1:1024" s="55" customFormat="1">
+    <row r="47" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="28"/>
       <c r="B47" s="21"/>
       <c r="C47" s="28">
@@ -8219,7 +8219,7 @@
       <c r="Q47" s="54"/>
       <c r="AMJ47"/>
     </row>
-    <row r="48" spans="1:1024" s="55" customFormat="1">
+    <row r="48" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="28"/>
       <c r="B48" s="21"/>
       <c r="C48" s="28">
@@ -8251,7 +8251,7 @@
       <c r="Q48" s="54"/>
       <c r="AMJ48"/>
     </row>
-    <row r="49" spans="1:1024" s="55" customFormat="1">
+    <row r="49" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="28">
         <v>26</v>
       </c>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AMJ49"/>
     </row>
-    <row r="50" spans="1:1024" s="55" customFormat="1">
+    <row r="50" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="28"/>
       <c r="B50" s="21"/>
       <c r="C50" s="28">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AMJ50"/>
     </row>
-    <row r="51" spans="1:1024" s="55" customFormat="1">
+    <row r="51" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="28"/>
       <c r="B51" s="21"/>
       <c r="C51" s="28">
@@ -8361,7 +8361,7 @@
       <c r="Q51" s="54"/>
       <c r="AMJ51"/>
     </row>
-    <row r="52" spans="1:1024" s="55" customFormat="1">
+    <row r="52" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="28">
         <v>27</v>
       </c>
@@ -8405,7 +8405,7 @@
       <c r="Q52" s="54"/>
       <c r="AMJ52"/>
     </row>
-    <row r="53" spans="1:1024" s="55" customFormat="1">
+    <row r="53" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="28">
         <v>28</v>
       </c>
@@ -8449,7 +8449,7 @@
       <c r="Q53" s="54"/>
       <c r="AMJ53"/>
     </row>
-    <row r="54" spans="1:1024" s="55" customFormat="1">
+    <row r="54" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="28"/>
       <c r="B54" s="21"/>
       <c r="C54" s="28">
@@ -8481,7 +8481,7 @@
       <c r="Q54" s="54"/>
       <c r="AMJ54"/>
     </row>
-    <row r="55" spans="1:1024" s="55" customFormat="1">
+    <row r="55" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="28"/>
       <c r="B55" s="21"/>
       <c r="C55" s="28">
@@ -8513,7 +8513,7 @@
       <c r="Q55" s="54"/>
       <c r="AMJ55"/>
     </row>
-    <row r="56" spans="1:1024" s="55" customFormat="1" ht="30">
+    <row r="56" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="36">
         <v>212</v>
       </c>
@@ -8547,7 +8547,7 @@
       <c r="Q56" s="54"/>
       <c r="AMJ56"/>
     </row>
-    <row r="57" spans="1:1024" s="55" customFormat="1" ht="30">
+    <row r="57" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="36">
         <v>29</v>
       </c>
@@ -8589,7 +8589,7 @@
       <c r="Q57" s="54"/>
       <c r="AMJ57"/>
     </row>
-    <row r="58" spans="1:1024" s="55" customFormat="1">
+    <row r="58" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="36">
         <v>30</v>
       </c>
@@ -8631,7 +8631,7 @@
       <c r="Q58" s="57"/>
       <c r="AMJ58"/>
     </row>
-    <row r="59" spans="1:1024" s="55" customFormat="1">
+    <row r="59" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="36"/>
       <c r="B59" s="3"/>
       <c r="C59" s="36">
@@ -8663,7 +8663,7 @@
       <c r="Q59" s="57"/>
       <c r="AMJ59"/>
     </row>
-    <row r="60" spans="1:1024" s="55" customFormat="1">
+    <row r="60" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="50">
         <v>34</v>
       </c>
@@ -8711,7 +8711,7 @@
       <c r="Q60" s="54"/>
       <c r="AMJ60"/>
     </row>
-    <row r="61" spans="1:1024" s="55" customFormat="1">
+    <row r="61" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="50"/>
       <c r="B61" s="51"/>
       <c r="C61" s="50">
@@ -8743,7 +8743,7 @@
       <c r="Q61" s="54"/>
       <c r="AMJ61"/>
     </row>
-    <row r="62" spans="1:1024" s="55" customFormat="1">
+    <row r="62" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="50"/>
       <c r="B62" s="51"/>
       <c r="C62" s="50">
@@ -8775,7 +8775,7 @@
       <c r="Q62" s="54"/>
       <c r="AMJ62"/>
     </row>
-    <row r="63" spans="1:1024" s="55" customFormat="1">
+    <row r="63" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="50"/>
       <c r="B63" s="51"/>
       <c r="C63" s="50">
@@ -8809,7 +8809,7 @@
       <c r="Q63" s="54"/>
       <c r="AMJ63"/>
     </row>
-    <row r="64" spans="1:1024" s="55" customFormat="1">
+    <row r="64" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="50"/>
       <c r="B64" s="51"/>
       <c r="C64" s="50">
@@ -8847,7 +8847,7 @@
       <c r="Q64" s="57"/>
       <c r="AMJ64"/>
     </row>
-    <row r="65" spans="1:1024" s="55" customFormat="1">
+    <row r="65" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="28">
         <v>31</v>
       </c>
@@ -8879,7 +8879,7 @@
       <c r="Q65" s="54"/>
       <c r="AMJ65"/>
     </row>
-    <row r="66" spans="1:1024" s="55" customFormat="1">
+    <row r="66" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="28">
         <v>32</v>
       </c>
@@ -8921,7 +8921,7 @@
       <c r="Q66" s="54"/>
       <c r="AMJ66"/>
     </row>
-    <row r="67" spans="1:1024" s="55" customFormat="1">
+    <row r="67" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="28"/>
       <c r="B67" s="21"/>
       <c r="C67" s="28">
@@ -8953,7 +8953,7 @@
       <c r="Q67" s="54"/>
       <c r="AMJ67"/>
     </row>
-    <row r="68" spans="1:1024" s="55" customFormat="1">
+    <row r="68" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="28"/>
       <c r="B68" s="21"/>
       <c r="C68" s="28">
@@ -8991,7 +8991,7 @@
       <c r="Q68" s="57"/>
       <c r="AMJ68"/>
     </row>
-    <row r="69" spans="1:1024" s="55" customFormat="1">
+    <row r="69" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="28">
         <v>33</v>
       </c>
@@ -9033,7 +9033,7 @@
       <c r="Q69" s="54"/>
       <c r="AMJ69"/>
     </row>
-    <row r="70" spans="1:1024" s="55" customFormat="1">
+    <row r="70" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="36">
         <v>35</v>
       </c>
@@ -9067,7 +9067,7 @@
       <c r="Q70" s="54"/>
       <c r="AMJ70"/>
     </row>
-    <row r="71" spans="1:1024" s="55" customFormat="1">
+    <row r="71" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="36">
         <v>36</v>
       </c>
@@ -9111,7 +9111,7 @@
       <c r="Q71" s="57"/>
       <c r="AMJ71"/>
     </row>
-    <row r="72" spans="1:1024" s="55" customFormat="1">
+    <row r="72" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="36"/>
       <c r="B72" s="3"/>
       <c r="C72" s="36">
@@ -9143,7 +9143,7 @@
       <c r="Q72" s="57"/>
       <c r="AMJ72"/>
     </row>
-    <row r="73" spans="1:1024" s="55" customFormat="1">
+    <row r="73" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="36"/>
       <c r="B73" s="3"/>
       <c r="C73" s="36">
@@ -9175,7 +9175,7 @@
       <c r="Q73" s="57"/>
       <c r="AMJ73"/>
     </row>
-    <row r="74" spans="1:1024" s="55" customFormat="1">
+    <row r="74" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="36">
         <v>37</v>
       </c>
@@ -9215,7 +9215,7 @@
       <c r="Q74" s="57"/>
       <c r="AMJ74"/>
     </row>
-    <row r="75" spans="1:1024" s="55" customFormat="1">
+    <row r="75" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="36"/>
       <c r="B75" s="3"/>
       <c r="C75" s="36">
@@ -9247,7 +9247,7 @@
       <c r="Q75" s="57"/>
       <c r="AMJ75"/>
     </row>
-    <row r="76" spans="1:1024" s="55" customFormat="1">
+    <row r="76" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="36"/>
       <c r="B76" s="3"/>
       <c r="C76" s="36">
@@ -9279,7 +9279,7 @@
       <c r="Q76" s="57"/>
       <c r="AMJ76"/>
     </row>
-    <row r="77" spans="1:1024" s="55" customFormat="1">
+    <row r="77" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="36"/>
       <c r="B77" s="3"/>
       <c r="C77" s="36">
@@ -9311,7 +9311,7 @@
       <c r="Q77" s="54"/>
       <c r="AMJ77"/>
     </row>
-    <row r="78" spans="1:1024" s="55" customFormat="1">
+    <row r="78" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="36">
         <v>38</v>
       </c>
@@ -9355,7 +9355,7 @@
       <c r="Q78" s="57"/>
       <c r="AMJ78"/>
     </row>
-    <row r="79" spans="1:1024" s="55" customFormat="1">
+    <row r="79" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="36"/>
       <c r="B79" s="3"/>
       <c r="C79" s="36">
@@ -9387,7 +9387,7 @@
       <c r="Q79" s="57"/>
       <c r="AMJ79"/>
     </row>
-    <row r="80" spans="1:1024">
+    <row r="80" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A80" s="61">
         <v>43</v>
       </c>
@@ -9414,7 +9414,7 @@
       <c r="N80" s="63"/>
       <c r="Q80" s="42"/>
     </row>
-    <row r="81" spans="1:17">
+    <row r="81" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="28">
         <v>44</v>
       </c>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="Q81" s="42"/>
     </row>
-    <row r="82" spans="1:17">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="36">
         <v>45</v>
       </c>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="Q82" s="42"/>
     </row>
-    <row r="83" spans="1:17">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="28">
         <v>204</v>
       </c>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="Q83" s="42"/>
     </row>
-    <row r="84" spans="1:17">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="28">
         <v>46</v>
       </c>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="Q84" s="42"/>
     </row>
-    <row r="85" spans="1:17">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="28">
         <v>47</v>
       </c>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="Q85" s="42"/>
     </row>
-    <row r="86" spans="1:17">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="28">
         <v>48</v>
       </c>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="Q86" s="42"/>
     </row>
-    <row r="87" spans="1:17">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="28">
         <v>49</v>
       </c>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="Q87" s="42"/>
     </row>
-    <row r="88" spans="1:17">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="28">
         <v>50</v>
       </c>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="Q88" s="42"/>
     </row>
-    <row r="89" spans="1:17">
+    <row r="89" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="28">
         <v>54</v>
       </c>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" spans="1:17">
+    <row r="90" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="28">
         <v>55</v>
       </c>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" spans="1:17">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="36">
         <v>56</v>
       </c>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="Q91" s="42"/>
     </row>
-    <row r="92" spans="1:17">
+    <row r="92" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="28">
         <v>57</v>
       </c>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" spans="1:17">
+    <row r="93" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="28">
         <v>58</v>
       </c>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" spans="1:17">
+    <row r="94" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="28">
         <v>59</v>
       </c>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" spans="1:17">
+    <row r="95" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="28">
         <v>60</v>
       </c>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" spans="1:17">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="28">
         <v>61</v>
       </c>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="Q96" s="42"/>
     </row>
-    <row r="97" spans="1:17">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="28">
         <v>205</v>
       </c>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="Q97" s="42"/>
     </row>
-    <row r="98" spans="1:17">
+    <row r="98" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="36">
         <v>62</v>
       </c>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17">
+    <row r="99" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="36">
         <v>63</v>
       </c>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" spans="1:17">
+    <row r="100" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="36"/>
       <c r="B100" s="3"/>
       <c r="C100" s="36">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="36"/>
       <c r="B101" s="3"/>
       <c r="C101" s="36">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" spans="1:17">
+    <row r="102" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="36">
         <v>64</v>
       </c>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="36"/>
       <c r="B103" s="3"/>
       <c r="C103" s="36">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" spans="1:17">
+    <row r="104" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="36">
         <v>65</v>
       </c>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" spans="1:17">
+    <row r="105" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="36"/>
       <c r="B105" s="3"/>
       <c r="C105" s="36">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" spans="1:17">
+    <row r="106" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="36">
         <v>66</v>
       </c>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" spans="1:17">
+    <row r="107" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="36">
         <v>67</v>
       </c>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" spans="1:17">
+    <row r="108" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="36"/>
       <c r="B108" s="3"/>
       <c r="C108" s="36">
@@ -10448,7 +10448,7 @@
       <c r="P108" s="1"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" spans="1:17">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="36"/>
       <c r="B109" s="3"/>
       <c r="C109" s="36">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="Q109" s="42"/>
     </row>
-    <row r="110" spans="1:17">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="28">
         <v>68</v>
       </c>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="Q110" s="42"/>
     </row>
-    <row r="111" spans="1:17">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="28">
         <v>203</v>
       </c>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="Q111" s="42"/>
     </row>
-    <row r="112" spans="1:17">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="28">
         <v>51</v>
       </c>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="Q112" s="42"/>
     </row>
-    <row r="113" spans="1:17">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="28">
         <v>52</v>
       </c>
@@ -10600,7 +10600,7 @@
         <v>377</v>
       </c>
       <c r="G113" s="28">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H113" s="28">
         <v>3</v>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="Q113" s="42"/>
     </row>
-    <row r="114" spans="1:17">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="28"/>
       <c r="B114" s="21"/>
       <c r="C114" s="28">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="Q114" s="42"/>
     </row>
-    <row r="115" spans="1:17">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="28"/>
       <c r="B115" s="21"/>
       <c r="C115" s="28">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="Q115" s="42"/>
     </row>
-    <row r="116" spans="1:17">
+    <row r="116" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="28">
         <v>53</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>160</v>
       </c>
       <c r="G116" s="28">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H116" s="28">
         <v>3</v>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="Q116" s="35"/>
     </row>
-    <row r="117" spans="1:17">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="28">
         <v>213</v>
       </c>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="Q117" s="42"/>
     </row>
-    <row r="118" spans="1:17">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="28">
         <v>69</v>
       </c>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="Q118" s="42"/>
     </row>
-    <row r="119" spans="1:17">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="28"/>
       <c r="B119" s="21"/>
       <c r="C119" s="28">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="Q119" s="42"/>
     </row>
-    <row r="120" spans="1:17">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="28"/>
       <c r="B120" s="21"/>
       <c r="C120" s="28">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="Q120" s="42"/>
     </row>
-    <row r="121" spans="1:17">
+    <row r="121" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="28">
         <v>70</v>
       </c>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17">
+    <row r="122" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="28"/>
       <c r="B122" s="21"/>
       <c r="C122" s="28">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="Q122" s="35"/>
     </row>
-    <row r="123" spans="1:17">
+    <row r="123" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="28"/>
       <c r="B123" s="21"/>
       <c r="C123" s="28">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="Q123" s="35"/>
     </row>
-    <row r="124" spans="1:17">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="36">
         <v>72</v>
       </c>
@@ -10969,7 +10969,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="125" spans="1:17">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125" s="36">
         <v>73</v>
       </c>
@@ -11005,7 +11005,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="126" spans="1:17">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="36"/>
       <c r="B126" s="3"/>
       <c r="C126" s="36">
@@ -11033,7 +11033,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="127" spans="1:17">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127" s="36">
         <v>75</v>
       </c>
@@ -11071,7 +11071,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="128" spans="1:17">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128" s="36"/>
       <c r="B128" s="3"/>
       <c r="C128" s="36">
@@ -11099,7 +11099,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="129" spans="1:17">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="36"/>
       <c r="B129" s="3"/>
       <c r="C129" s="36">
@@ -11127,7 +11127,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="130" spans="1:17">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A130" s="36">
         <v>76</v>
       </c>
@@ -11167,7 +11167,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="131" spans="1:17">
+    <row r="131" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="36">
         <v>78</v>
       </c>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="Q131" s="35"/>
     </row>
-    <row r="132" spans="1:17">
+    <row r="132" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="36"/>
       <c r="B132" s="3"/>
       <c r="C132" s="36">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="Q132" s="35"/>
     </row>
-    <row r="133" spans="1:17">
+    <row r="133" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="36"/>
       <c r="B133" s="3"/>
       <c r="C133" s="36">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="Q133" s="35"/>
     </row>
-    <row r="134" spans="1:17">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A134" s="36">
         <v>79</v>
       </c>
@@ -11307,7 +11307,7 @@
       </c>
       <c r="Q134" s="42"/>
     </row>
-    <row r="135" spans="1:17">
+    <row r="135" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="28">
         <v>80</v>
       </c>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="Q135" s="35"/>
     </row>
-    <row r="136" spans="1:17">
+    <row r="136" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="28">
         <v>81</v>
       </c>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="Q136" s="35"/>
     </row>
-    <row r="137" spans="1:17">
+    <row r="137" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="28">
         <v>82</v>
       </c>
@@ -11420,7 +11420,7 @@
       </c>
       <c r="Q137" s="35"/>
     </row>
-    <row r="138" spans="1:17">
+    <row r="138" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="28">
         <v>83</v>
       </c>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="Q138" s="35"/>
     </row>
-    <row r="139" spans="1:17">
+    <row r="139" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="28"/>
       <c r="B139" s="21"/>
       <c r="C139" s="28">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="Q139" s="35"/>
     </row>
-    <row r="140" spans="1:17">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A140" s="28">
         <v>84</v>
       </c>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="Q140" s="42"/>
     </row>
-    <row r="141" spans="1:17">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A141" s="28"/>
       <c r="B141" s="21"/>
       <c r="C141" s="28">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="Q141" s="42"/>
     </row>
-    <row r="142" spans="1:17">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A142" s="28"/>
       <c r="B142" s="21"/>
       <c r="C142" s="28">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="Q142" s="42"/>
     </row>
-    <row r="143" spans="1:17">
+    <row r="143" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="36">
         <v>206</v>
       </c>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="Q143" s="35"/>
     </row>
-    <row r="144" spans="1:17">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A144" s="36">
         <v>85</v>
       </c>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="Q144" s="42"/>
     </row>
-    <row r="145" spans="1:17">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="36"/>
       <c r="B145" s="3"/>
       <c r="C145" s="36">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="Q145" s="42"/>
     </row>
-    <row r="146" spans="1:17">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="36"/>
       <c r="B146" s="3"/>
       <c r="C146" s="36">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="Q146" s="42"/>
     </row>
-    <row r="147" spans="1:17">
+    <row r="147" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="36"/>
       <c r="B147" s="3"/>
       <c r="C147" s="36">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="Q147" s="35"/>
     </row>
-    <row r="148" spans="1:17">
+    <row r="148" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A148" s="36">
         <v>86</v>
       </c>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="Q148" s="35"/>
     </row>
-    <row r="149" spans="1:17">
+    <row r="149" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="36"/>
       <c r="B149" s="3"/>
       <c r="C149" s="36">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="Q149" s="35"/>
     </row>
-    <row r="150" spans="1:17">
+    <row r="150" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="36">
         <v>87</v>
       </c>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="Q150" s="35"/>
     </row>
-    <row r="151" spans="1:17">
+    <row r="151" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="36">
         <v>88</v>
       </c>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="Q151" s="35"/>
     </row>
-    <row r="152" spans="1:17">
+    <row r="152" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="36">
         <v>89</v>
       </c>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="Q152" s="35"/>
     </row>
-    <row r="153" spans="1:17">
+    <row r="153" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="36">
         <v>90</v>
       </c>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="Q153" s="35"/>
     </row>
-    <row r="154" spans="1:17">
+    <row r="154" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="36">
         <v>91</v>
       </c>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="Q154" s="35"/>
     </row>
-    <row r="155" spans="1:17">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A155" s="36">
         <v>92</v>
       </c>
@@ -12066,7 +12066,7 @@
       </c>
       <c r="Q155" s="42"/>
     </row>
-    <row r="156" spans="1:17">
+    <row r="156" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="28">
         <v>93</v>
       </c>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="Q156" s="35"/>
     </row>
-    <row r="157" spans="1:17">
+    <row r="157" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="28"/>
       <c r="B157" s="21"/>
       <c r="C157" s="28">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="Q157" s="35"/>
     </row>
-    <row r="158" spans="1:17">
+    <row r="158" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="28">
         <v>94</v>
       </c>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="Q158" s="35"/>
     </row>
-    <row r="159" spans="1:17">
+    <row r="159" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="28">
         <v>95</v>
       </c>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="Q159" s="35"/>
     </row>
-    <row r="160" spans="1:17">
+    <row r="160" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="28"/>
       <c r="B160" s="21"/>
       <c r="C160" s="28">
@@ -12235,7 +12235,7 @@
       <c r="P160" s="2"/>
       <c r="Q160" s="35"/>
     </row>
-    <row r="161" spans="1:17">
+    <row r="161" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="28"/>
       <c r="B161" s="21"/>
       <c r="C161" s="28">
@@ -12264,7 +12264,7 @@
       <c r="P161" s="2"/>
       <c r="Q161" s="35"/>
     </row>
-    <row r="162" spans="1:17">
+    <row r="162" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="28">
         <v>96</v>
       </c>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="Q162" s="35"/>
     </row>
-    <row r="163" spans="1:17">
+    <row r="163" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="28">
         <v>97</v>
       </c>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Q163" s="35"/>
     </row>
-    <row r="164" spans="1:17">
+    <row r="164" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="28"/>
       <c r="B164" s="21"/>
       <c r="C164" s="28">
@@ -12379,7 +12379,7 @@
       <c r="P164" s="2"/>
       <c r="Q164" s="35"/>
     </row>
-    <row r="165" spans="1:17">
+    <row r="165" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="36">
         <v>207</v>
       </c>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="Q165" s="35"/>
     </row>
-    <row r="166" spans="1:17">
+    <row r="166" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="36">
         <v>98</v>
       </c>
@@ -12447,7 +12447,7 @@
       <c r="P166" s="1"/>
       <c r="Q166" s="35"/>
     </row>
-    <row r="167" spans="1:17">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A167" s="36">
         <v>99</v>
       </c>
@@ -12487,7 +12487,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="168" spans="1:17">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A168" s="36"/>
       <c r="B168" s="3"/>
       <c r="C168" s="36">
@@ -12515,7 +12515,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="169" spans="1:17">
+    <row r="169" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="28">
         <v>100</v>
       </c>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="Q169" s="35"/>
     </row>
-    <row r="170" spans="1:17">
+    <row r="170" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="28">
         <v>101</v>
       </c>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="Q170" s="35"/>
     </row>
-    <row r="171" spans="1:17">
+    <row r="171" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="28"/>
       <c r="B171" s="21"/>
       <c r="C171" s="28">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="Q171" s="35"/>
     </row>
-    <row r="172" spans="1:17">
+    <row r="172" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="28">
         <v>102</v>
       </c>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="Q172" s="35"/>
     </row>
-    <row r="173" spans="1:17">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A173" s="28"/>
       <c r="B173" s="21"/>
       <c r="C173" s="28">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="Q173" s="42"/>
     </row>
-    <row r="174" spans="1:17">
+    <row r="174" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="36">
         <v>103</v>
       </c>
@@ -12717,7 +12717,7 @@
       </c>
       <c r="Q174" s="35"/>
     </row>
-    <row r="175" spans="1:17">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A175" s="28">
         <v>71</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="176" spans="1:17">
+    <row r="176" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" s="36">
         <v>104</v>
       </c>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="Q176" s="35"/>
     </row>
-    <row r="177" spans="1:17">
+    <row r="177" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="36">
         <v>105</v>
       </c>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="Q177" s="35"/>
     </row>
-    <row r="178" spans="1:17">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A178" s="36">
         <v>106</v>
       </c>
@@ -12881,7 +12881,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="179" spans="1:17">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A179" s="28">
         <v>107</v>
       </c>
@@ -12919,7 +12919,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="180" spans="1:17">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A180" s="28"/>
       <c r="B180" s="21"/>
       <c r="C180" s="28">
@@ -12947,7 +12947,7 @@
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
     </row>
-    <row r="181" spans="1:17">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A181" s="28"/>
       <c r="B181" s="21"/>
       <c r="C181" s="28">
@@ -12975,7 +12975,7 @@
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
     </row>
-    <row r="182" spans="1:17">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A182" s="36">
         <v>209</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="183" spans="1:17">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A183" s="36">
         <v>108</v>
       </c>
@@ -13039,7 +13039,7 @@
       <c r="O183" s="1"/>
       <c r="P183" s="1"/>
     </row>
-    <row r="184" spans="1:17">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A184" s="36">
         <v>109</v>
       </c>
@@ -13077,11 +13077,11 @@
         <v>569</v>
       </c>
     </row>
-    <row r="185" spans="1:17">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A185" s="61"/>
       <c r="C185" s="61"/>
     </row>
-    <row r="186" spans="1:17">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A186" s="61"/>
       <c r="C186" s="61"/>
     </row>
@@ -13092,23 +13092,23 @@
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J161:J1048576 J1:J159">
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K161:K1048576 K1:K159">
+    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="16"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J161:J1048576 J1:J159">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K161:K1048576 K1:K159">
-    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.70069444444444395" right="0.70069444444444395" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -13118,26 +13118,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="4" width="7.140625" customWidth="1"/>
+    <col min="1" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="4" width="7.1640625" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="8" width="28.42578125" customWidth="1"/>
-    <col min="10" max="10" width="42.85546875" customWidth="1"/>
+    <col min="6" max="8" width="28.5" customWidth="1"/>
+    <col min="10" max="10" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="95" t="s">
         <v>2</v>
       </c>
@@ -13162,7 +13162,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="45">
+    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="96"/>
       <c r="B5" s="96"/>
       <c r="C5" s="1" t="s">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="45">
+    <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="21"/>
       <c r="B6" s="21"/>
       <c r="C6" s="2"/>
@@ -13198,7 +13198,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="60">
+    <row r="7" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="21"/>
       <c r="B7" s="21"/>
       <c r="C7" s="2"/>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="60">
+    <row r="8" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" s="21"/>
       <c r="B8" s="21"/>
       <c r="C8" s="2"/>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="30">
+    <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="2"/>
@@ -13249,7 +13249,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30">
+    <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="2"/>
@@ -13268,7 +13268,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30">
+    <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="2"/>
@@ -13287,7 +13287,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="30">
+    <row r="12" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="2"/>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="30">
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="2"/>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="30">
+    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="2"/>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="30">
+    <row r="15" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="2"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="60">
+    <row r="16" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="2"/>
@@ -13368,7 +13368,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="75">
+    <row r="17" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="2"/>
@@ -13381,11 +13381,11 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="62"/>
       <c r="B18" s="62"/>
     </row>
-    <row r="19" spans="1:10" ht="45">
+    <row r="19" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>77</v>
       </c>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17D0FCB-7D0E-4365-AE44-74980EE8C6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3299AE08-9A7C-4713-B2D5-F652725C3394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="-645" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17550" yWindow="0" windowWidth="25890" windowHeight="20805" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFP" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="660">
   <si>
     <t>Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -1878,9 +1878,6 @@
   </si>
   <si>
     <t>62, 68</t>
-  </si>
-  <si>
-    <t>if/elsel</t>
   </si>
   <si>
     <t>2,8,210</t>
@@ -6438,7 +6435,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMJ191"/>
+  <dimension ref="A1:AMJ192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -6831,7 +6828,7 @@
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="87" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>92</v>
@@ -6870,7 +6867,7 @@
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="88" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F12" s="44" t="s">
         <v>93</v>
@@ -6909,7 +6906,7 @@
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="88" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F13" s="44" t="s">
         <v>93</v>
@@ -6940,7 +6937,7 @@
       </c>
       <c r="D14" s="21"/>
       <c r="E14" s="88" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F14" s="44" t="s">
         <v>93</v>
@@ -6973,7 +6970,7 @@
       <c r="C15" s="28"/>
       <c r="D15" s="21"/>
       <c r="E15" s="88" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F15" s="44" t="s">
         <v>94</v>
@@ -7008,7 +7005,7 @@
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="88" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F16" s="46" t="s">
         <v>133</v>
@@ -7051,7 +7048,7 @@
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="88" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F17" s="46" t="s">
         <v>134</v>
@@ -7090,7 +7087,7 @@
       </c>
       <c r="D18" s="21"/>
       <c r="E18" s="88" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F18" s="46" t="s">
         <v>134</v>
@@ -7123,7 +7120,7 @@
       </c>
       <c r="D19" s="21"/>
       <c r="E19" s="88" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F19" s="46" t="s">
         <v>224</v>
@@ -7166,7 +7163,7 @@
       </c>
       <c r="D20" s="21"/>
       <c r="E20" s="88" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F20" s="46" t="s">
         <v>101</v>
@@ -7175,7 +7172,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="28">
         <v>1</v>
@@ -7198,326 +7195,322 @@
       <c r="Q20" s="35"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="28">
-        <v>16</v>
-      </c>
-      <c r="B21" s="21">
-        <v>8</v>
-      </c>
+      <c r="A21" s="28"/>
+      <c r="B21" s="21"/>
       <c r="C21" s="28">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="88" t="s">
-        <v>614</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="28">
-        <v>210</v>
-      </c>
-      <c r="H21" s="28">
-        <v>1</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="28">
-        <v>1</v>
-      </c>
-      <c r="J21" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="K21" s="34" t="s">
-        <v>234</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
       <c r="N21" s="34"/>
-      <c r="O21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>235</v>
-      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
       <c r="Q21" s="35"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="28">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="21">
         <v>8</v>
       </c>
       <c r="C22" s="28">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="88" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F22" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G22" s="28">
         <v>210</v>
       </c>
       <c r="H22" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" s="28">
         <v>1</v>
       </c>
       <c r="J22" s="34" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K22" s="34" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
       <c r="N22" s="34"/>
       <c r="O22" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q22" s="35"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="28"/>
-      <c r="B23" s="21"/>
+      <c r="A23" s="28">
+        <v>17</v>
+      </c>
+      <c r="B23" s="21">
+        <v>8</v>
+      </c>
       <c r="C23" s="28">
-        <v>167</v>
+        <v>15</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="88" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F23" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="G23" s="28">
+        <v>210</v>
+      </c>
+      <c r="H23" s="28">
+        <v>3</v>
+      </c>
       <c r="I23" s="28">
-        <v>3</v>
-      </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="K23" s="34" t="s">
+        <v>237</v>
+      </c>
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
       <c r="N23" s="34"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
+      <c r="O23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="Q23" s="35"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="28">
-        <v>15</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>239</v>
-      </c>
+      <c r="A24" s="28"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="28">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="88" t="s">
-        <v>616</v>
-      </c>
-      <c r="F24" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="43">
-        <v>210</v>
-      </c>
-      <c r="H24" s="28">
+        <v>614</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28">
         <v>3</v>
       </c>
-      <c r="I24" s="28">
-        <v>1</v>
-      </c>
-      <c r="J24" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="K24" s="34" t="s">
-        <v>241</v>
-      </c>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
       <c r="L24" s="34"/>
       <c r="M24" s="34"/>
       <c r="N24" s="34"/>
-      <c r="O24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>242</v>
-      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
       <c r="Q24" s="35"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="28"/>
-      <c r="B25" s="21"/>
+      <c r="A25" s="28">
+        <v>15</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>239</v>
+      </c>
       <c r="C25" s="28">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="D25" s="21"/>
       <c r="E25" s="88" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F25" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="43"/>
-      <c r="H25" s="28"/>
+      <c r="G25" s="43">
+        <v>210</v>
+      </c>
+      <c r="H25" s="28">
+        <v>3</v>
+      </c>
       <c r="I25" s="28">
-        <v>3</v>
-      </c>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J25" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="K25" s="34" t="s">
+        <v>241</v>
+      </c>
       <c r="L25" s="34"/>
       <c r="M25" s="34"/>
       <c r="N25" s="34"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
+      <c r="O25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="Q25" s="35"/>
     </row>
-    <row r="26" spans="1:17" s="72" customFormat="1">
-      <c r="A26" s="66">
+    <row r="26" spans="1:17">
+      <c r="A26" s="28"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="28">
+        <v>168</v>
+      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="88" t="s">
+        <v>615</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G26" s="43"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28">
+        <v>3</v>
+      </c>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="35"/>
+    </row>
+    <row r="27" spans="1:17" s="72" customFormat="1">
+      <c r="A27" s="66">
         <v>201</v>
       </c>
-      <c r="B26" s="67">
+      <c r="B27" s="67">
         <v>210</v>
       </c>
-      <c r="C26" s="66"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67" t="s">
+      <c r="C27" s="66"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="G26" s="68">
+      <c r="G27" s="68">
         <v>2</v>
       </c>
-      <c r="H26" s="66">
+      <c r="H27" s="66">
         <v>3</v>
       </c>
-      <c r="I26" s="66"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="69"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q26" s="71"/>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="36">
-        <v>18</v>
-      </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="36">
-        <v>17</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="89" t="s">
-        <v>617</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G27" s="36">
-        <v>201</v>
-      </c>
-      <c r="H27" s="36">
-        <v>1</v>
-      </c>
-      <c r="I27" s="36">
-        <v>1</v>
-      </c>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="1" t="s">
-        <v>244</v>
-      </c>
+      <c r="I27" s="66"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="70"/>
       <c r="P27" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="Q27" s="35"/>
+      <c r="Q27" s="71"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="36">
-        <v>19</v>
-      </c>
-      <c r="B28" s="3">
         <v>18</v>
       </c>
+      <c r="B28" s="47"/>
       <c r="C28" s="36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="89" t="s">
-        <v>618</v>
-      </c>
-      <c r="F28" s="41" t="s">
-        <v>103</v>
+        <v>616</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="G28" s="36">
         <v>201</v>
       </c>
       <c r="H28" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" s="36">
         <v>1</v>
       </c>
-      <c r="J28" s="40" t="s">
-        <v>246</v>
-      </c>
+      <c r="J28" s="40"/>
       <c r="K28" s="40" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
       <c r="N28" s="40"/>
       <c r="O28" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q28" s="42"/>
+        <v>245</v>
+      </c>
+      <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="36"/>
-      <c r="B29" s="3"/>
+      <c r="A29" s="36">
+        <v>19</v>
+      </c>
+      <c r="B29" s="3">
+        <v>18</v>
+      </c>
       <c r="C29" s="36">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="89" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F29" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
+      <c r="G29" s="36">
+        <v>201</v>
+      </c>
+      <c r="H29" s="36">
+        <v>3</v>
+      </c>
       <c r="I29" s="36">
-        <v>2</v>
-      </c>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J29" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="K29" s="40" t="s">
+        <v>247</v>
+      </c>
       <c r="L29" s="40"/>
       <c r="M29" s="40"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="82" t="s">
-        <v>606</v>
+      <c r="O29" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>249</v>
@@ -7528,11 +7521,11 @@
       <c r="A30" s="36"/>
       <c r="B30" s="3"/>
       <c r="C30" s="36">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="89" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F30" s="41" t="s">
         <v>103</v>
@@ -7540,7 +7533,7 @@
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
       <c r="I30" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="40"/>
       <c r="K30" s="40"/>
@@ -7548,7 +7541,7 @@
       <c r="M30" s="40"/>
       <c r="N30" s="40"/>
       <c r="O30" s="82" t="s">
-        <v>606</v>
+        <v>103</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>249</v>
@@ -7556,103 +7549,103 @@
       <c r="Q30" s="42"/>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="36">
+      <c r="A31" s="36"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="36">
         <v>20</v>
       </c>
-      <c r="B31" s="3">
-        <v>19</v>
-      </c>
-      <c r="C31" s="36"/>
       <c r="D31" s="3"/>
       <c r="E31" s="89" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G31" s="36">
-        <v>201</v>
-      </c>
-      <c r="H31" s="36">
+        <v>103</v>
+      </c>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36">
         <v>3</v>
-      </c>
-      <c r="I31" s="36">
-        <v>1</v>
       </c>
       <c r="J31" s="40"/>
       <c r="K31" s="40"/>
       <c r="L31" s="40"/>
       <c r="M31" s="40"/>
       <c r="N31" s="40"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="48" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q31" s="35"/>
+      <c r="O31" s="82" t="s">
+        <v>103</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q31" s="42"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="36">
-        <v>21</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="36">
-        <v>21</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B32" s="3">
+        <v>19</v>
+      </c>
+      <c r="C32" s="36"/>
       <c r="D32" s="3"/>
       <c r="E32" s="89" t="s">
-        <v>620</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>251</v>
+        <v>618</v>
+      </c>
+      <c r="F32" s="41" t="s">
+        <v>105</v>
       </c>
       <c r="G32" s="36">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="H32" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" s="36">
         <v>1</v>
       </c>
       <c r="J32" s="40"/>
-      <c r="K32" s="40" t="s">
-        <v>252</v>
-      </c>
+      <c r="K32" s="40"/>
       <c r="L32" s="40"/>
-      <c r="M32" s="40" t="s">
-        <v>253</v>
-      </c>
+      <c r="M32" s="40"/>
       <c r="N32" s="40"/>
-      <c r="O32" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>255</v>
+      <c r="O32" s="1"/>
+      <c r="P32" s="48" t="s">
+        <v>250</v>
       </c>
       <c r="Q32" s="35"/>
     </row>
     <row r="33" spans="1:1024">
-      <c r="A33" s="36"/>
+      <c r="A33" s="36">
+        <v>21</v>
+      </c>
       <c r="B33" s="3"/>
       <c r="C33" s="36">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="89" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F33" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
+      <c r="G33" s="36">
+        <v>20</v>
+      </c>
+      <c r="H33" s="36">
+        <v>2</v>
+      </c>
       <c r="I33" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="40"/>
-      <c r="K33" s="40"/>
+      <c r="K33" s="40" t="s">
+        <v>252</v>
+      </c>
       <c r="L33" s="40"/>
-      <c r="M33" s="40"/>
+      <c r="M33" s="40" t="s">
+        <v>253</v>
+      </c>
       <c r="N33" s="40"/>
       <c r="O33" s="1" t="s">
         <v>254</v>
@@ -7663,70 +7656,70 @@
       <c r="Q33" s="35"/>
     </row>
     <row r="34" spans="1:1024">
-      <c r="A34" s="36">
-        <v>22</v>
-      </c>
+      <c r="A34" s="36"/>
       <c r="B34" s="3"/>
       <c r="C34" s="36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="89" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F34" s="49" t="s">
-        <v>256</v>
-      </c>
-      <c r="G34" s="36">
-        <v>20</v>
-      </c>
-      <c r="H34" s="36">
-        <v>3</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
       <c r="I34" s="36">
-        <v>1</v>
-      </c>
-      <c r="J34" s="40" t="s">
-        <v>257</v>
-      </c>
-      <c r="K34" s="40" t="s">
-        <v>258</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
       <c r="L34" s="40"/>
-      <c r="M34" s="40" t="s">
-        <v>259</v>
-      </c>
+      <c r="M34" s="40"/>
       <c r="N34" s="40"/>
       <c r="O34" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q34" s="42"/>
+        <v>255</v>
+      </c>
+      <c r="Q34" s="35"/>
     </row>
     <row r="35" spans="1:1024">
-      <c r="A35" s="36"/>
+      <c r="A35" s="36">
+        <v>22</v>
+      </c>
       <c r="B35" s="3"/>
       <c r="C35" s="36">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="89" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F35" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
+      <c r="G35" s="36">
+        <v>20</v>
+      </c>
+      <c r="H35" s="36">
+        <v>3</v>
+      </c>
       <c r="I35" s="36">
-        <v>2</v>
-      </c>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J35" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="K35" s="40" t="s">
+        <v>258</v>
+      </c>
       <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
+      <c r="M35" s="40" t="s">
+        <v>259</v>
+      </c>
       <c r="N35" s="40"/>
       <c r="O35" s="1" t="s">
         <v>260</v>
@@ -7740,11 +7733,11 @@
       <c r="A36" s="36"/>
       <c r="B36" s="3"/>
       <c r="C36" s="36">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="89" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F36" s="49" t="s">
         <v>256</v>
@@ -7752,7 +7745,7 @@
       <c r="G36" s="36"/>
       <c r="H36" s="36"/>
       <c r="I36" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36" s="40"/>
       <c r="K36" s="40"/>
@@ -7767,64 +7760,59 @@
       </c>
       <c r="Q36" s="42"/>
     </row>
-    <row r="37" spans="1:1024" s="85" customFormat="1">
-      <c r="A37" s="50">
-        <v>211</v>
-      </c>
-      <c r="B37" s="51">
-        <v>201</v>
-      </c>
-      <c r="C37" s="50">
-        <v>26</v>
-      </c>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="G37" s="50">
-        <v>2</v>
-      </c>
-      <c r="H37" s="50">
+    <row r="37" spans="1:1024">
+      <c r="A37" s="36"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="36">
+        <v>25</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="89" t="s">
+        <v>620</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36">
         <v>3</v>
       </c>
-      <c r="I37" s="50"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="52"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="83" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q37" s="84"/>
-      <c r="AMJ37" s="86"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="40"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q37" s="42"/>
     </row>
     <row r="38" spans="1:1024" s="85" customFormat="1">
       <c r="A38" s="50">
-        <v>39</v>
-      </c>
-      <c r="B38" s="51"/>
+        <v>211</v>
+      </c>
+      <c r="B38" s="51">
+        <v>201</v>
+      </c>
       <c r="C38" s="50">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D38" s="51"/>
-      <c r="E38" s="90" t="s">
-        <v>622</v>
-      </c>
+      <c r="E38" s="51"/>
       <c r="F38" s="51" t="s">
         <v>126</v>
       </c>
       <c r="G38" s="50">
-        <v>211</v>
+        <v>2</v>
       </c>
       <c r="H38" s="50">
-        <v>1</v>
-      </c>
-      <c r="I38" s="50">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I38" s="50"/>
       <c r="J38" s="52"/>
       <c r="K38" s="52"/>
       <c r="L38" s="52"/>
@@ -7837,72 +7825,76 @@
       <c r="Q38" s="84"/>
       <c r="AMJ38" s="86"/>
     </row>
-    <row r="39" spans="1:1024" s="55" customFormat="1">
+    <row r="39" spans="1:1024" s="85" customFormat="1">
       <c r="A39" s="50">
-        <v>40</v>
-      </c>
-      <c r="B39" s="51">
         <v>39</v>
       </c>
+      <c r="B39" s="51"/>
       <c r="C39" s="50">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39" s="51"/>
       <c r="E39" s="90" t="s">
-        <v>623</v>
-      </c>
-      <c r="F39" s="56" t="s">
-        <v>127</v>
+        <v>621</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>126</v>
       </c>
       <c r="G39" s="50">
         <v>211</v>
       </c>
       <c r="H39" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" s="50">
         <v>1</v>
       </c>
       <c r="J39" s="52"/>
-      <c r="K39" s="52" t="s">
-        <v>263</v>
-      </c>
+      <c r="K39" s="52"/>
       <c r="L39" s="52"/>
-      <c r="M39" s="52" t="s">
-        <v>264</v>
-      </c>
+      <c r="M39" s="52"/>
       <c r="N39" s="52"/>
-      <c r="O39" s="53" t="s">
-        <v>265</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q39" s="57"/>
-      <c r="AMJ39"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q39" s="84"/>
+      <c r="AMJ39" s="86"/>
     </row>
     <row r="40" spans="1:1024" s="55" customFormat="1">
-      <c r="A40" s="50"/>
-      <c r="B40" s="51"/>
+      <c r="A40" s="50">
+        <v>40</v>
+      </c>
+      <c r="B40" s="51">
+        <v>39</v>
+      </c>
       <c r="C40" s="50">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" s="51"/>
       <c r="E40" s="90" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F40" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
+      <c r="G40" s="50">
+        <v>211</v>
+      </c>
+      <c r="H40" s="50">
+        <v>3</v>
+      </c>
       <c r="I40" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
+      <c r="K40" s="52" t="s">
+        <v>263</v>
+      </c>
       <c r="L40" s="52"/>
-      <c r="M40" s="52"/>
+      <c r="M40" s="52" t="s">
+        <v>264</v>
+      </c>
       <c r="N40" s="52"/>
       <c r="O40" s="53" t="s">
         <v>265</v>
@@ -7917,11 +7909,11 @@
       <c r="A41" s="50"/>
       <c r="B41" s="51"/>
       <c r="C41" s="50">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" s="51"/>
       <c r="E41" s="90" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F41" s="56" t="s">
         <v>127</v>
@@ -7929,7 +7921,7 @@
       <c r="G41" s="50"/>
       <c r="H41" s="50"/>
       <c r="I41" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J41" s="52"/>
       <c r="K41" s="52"/>
@@ -7946,69 +7938,69 @@
       <c r="AMJ41"/>
     </row>
     <row r="42" spans="1:1024" s="55" customFormat="1">
-      <c r="A42" s="50">
-        <v>41</v>
-      </c>
-      <c r="B42" s="51">
-        <v>39</v>
-      </c>
+      <c r="A42" s="50"/>
+      <c r="B42" s="51"/>
       <c r="C42" s="50">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D42" s="51"/>
       <c r="E42" s="90" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F42" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="G42" s="50">
-        <v>211</v>
-      </c>
-      <c r="H42" s="50">
-        <v>2</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="G42" s="50"/>
+      <c r="H42" s="50"/>
       <c r="I42" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42" s="52"/>
       <c r="K42" s="52"/>
       <c r="L42" s="52"/>
-      <c r="M42" s="52" t="s">
-        <v>267</v>
-      </c>
+      <c r="M42" s="52"/>
       <c r="N42" s="52"/>
       <c r="O42" s="53" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Q42" s="57"/>
       <c r="AMJ42"/>
     </row>
     <row r="43" spans="1:1024" s="55" customFormat="1">
-      <c r="A43" s="50"/>
-      <c r="B43" s="51"/>
+      <c r="A43" s="50">
+        <v>41</v>
+      </c>
+      <c r="B43" s="51">
+        <v>39</v>
+      </c>
       <c r="C43" s="50">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D43" s="51"/>
       <c r="E43" s="90" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F43" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="G43" s="50"/>
-      <c r="H43" s="50"/>
+      <c r="G43" s="50">
+        <v>211</v>
+      </c>
+      <c r="H43" s="50">
+        <v>2</v>
+      </c>
       <c r="I43" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="52"/>
       <c r="K43" s="52"/>
       <c r="L43" s="52"/>
-      <c r="M43" s="52"/>
+      <c r="M43" s="52" t="s">
+        <v>267</v>
+      </c>
       <c r="N43" s="52"/>
       <c r="O43" s="53" t="s">
         <v>128</v>
@@ -8020,136 +8012,136 @@
       <c r="AMJ43"/>
     </row>
     <row r="44" spans="1:1024" s="55" customFormat="1">
-      <c r="A44" s="50">
-        <v>42</v>
-      </c>
-      <c r="B44" s="51">
-        <v>39</v>
-      </c>
+      <c r="A44" s="50"/>
+      <c r="B44" s="51"/>
       <c r="C44" s="50">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D44" s="51"/>
       <c r="E44" s="90" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F44" s="56" t="s">
-        <v>129</v>
-      </c>
-      <c r="G44" s="50">
-        <v>211</v>
-      </c>
-      <c r="H44" s="50">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G44" s="50"/>
+      <c r="H44" s="50"/>
       <c r="I44" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" s="52"/>
       <c r="K44" s="52"/>
       <c r="L44" s="52"/>
-      <c r="M44" s="52" t="s">
-        <v>269</v>
-      </c>
+      <c r="M44" s="52"/>
       <c r="N44" s="52"/>
       <c r="O44" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Q44" s="57"/>
       <c r="AMJ44"/>
     </row>
-    <row r="45" spans="1:1024" s="80" customFormat="1">
-      <c r="A45" s="73">
+    <row r="45" spans="1:1024" s="55" customFormat="1">
+      <c r="A45" s="50">
+        <v>42</v>
+      </c>
+      <c r="B45" s="51">
+        <v>39</v>
+      </c>
+      <c r="C45" s="50">
+        <v>33</v>
+      </c>
+      <c r="D45" s="51"/>
+      <c r="E45" s="90" t="s">
+        <v>624</v>
+      </c>
+      <c r="F45" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="G45" s="50">
+        <v>211</v>
+      </c>
+      <c r="H45" s="50">
+        <v>1</v>
+      </c>
+      <c r="I45" s="50">
+        <v>1</v>
+      </c>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="N45" s="52"/>
+      <c r="O45" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q45" s="57"/>
+      <c r="AMJ45"/>
+    </row>
+    <row r="46" spans="1:1024" s="80" customFormat="1">
+      <c r="A46" s="73">
         <v>202</v>
       </c>
-      <c r="B45" s="74">
+      <c r="B46" s="74">
         <v>201.21100000000001</v>
       </c>
-      <c r="C45" s="73"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="75" t="s">
+      <c r="C46" s="73"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="G45" s="73">
+      <c r="G46" s="73">
         <v>2</v>
       </c>
-      <c r="H45" s="73">
+      <c r="H46" s="73">
         <v>3</v>
       </c>
-      <c r="I45" s="73"/>
-      <c r="J45" s="76"/>
-      <c r="K45" s="76"/>
-      <c r="L45" s="76"/>
-      <c r="M45" s="76"/>
-      <c r="N45" s="76"/>
-      <c r="O45" s="77"/>
-      <c r="P45" s="78"/>
-      <c r="Q45" s="79"/>
-      <c r="AMJ45" s="81"/>
-    </row>
-    <row r="46" spans="1:1024" s="55" customFormat="1">
-      <c r="A46" s="28">
+      <c r="I46" s="73"/>
+      <c r="J46" s="76"/>
+      <c r="K46" s="76"/>
+      <c r="L46" s="76"/>
+      <c r="M46" s="76"/>
+      <c r="N46" s="76"/>
+      <c r="O46" s="77"/>
+      <c r="P46" s="78"/>
+      <c r="Q46" s="79"/>
+      <c r="AMJ46" s="81"/>
+    </row>
+    <row r="47" spans="1:1024" s="55" customFormat="1">
+      <c r="A47" s="28">
         <v>23</v>
       </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="28">
-        <v>34</v>
-      </c>
-      <c r="D46" s="21"/>
-      <c r="E46" s="88" t="s">
-        <v>626</v>
-      </c>
-      <c r="F46" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="G46" s="28">
-        <v>202</v>
-      </c>
-      <c r="H46" s="28">
-        <v>3</v>
-      </c>
-      <c r="I46" s="28">
-        <v>1</v>
-      </c>
-      <c r="J46" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="34"/>
-      <c r="N46" s="34"/>
-      <c r="O46" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q46" s="54"/>
-      <c r="AMJ46"/>
-    </row>
-    <row r="47" spans="1:1024" s="55" customFormat="1">
-      <c r="A47" s="28"/>
       <c r="B47" s="21"/>
       <c r="C47" s="28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D47" s="21"/>
       <c r="E47" s="88" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F47" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
+      <c r="G47" s="28">
+        <v>202</v>
+      </c>
+      <c r="H47" s="28">
+        <v>3</v>
+      </c>
       <c r="I47" s="28">
-        <v>2</v>
-      </c>
-      <c r="J47" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J47" s="34" t="s">
+        <v>271</v>
+      </c>
       <c r="K47" s="34"/>
       <c r="L47" s="34"/>
       <c r="M47" s="34"/>
@@ -8167,11 +8159,11 @@
       <c r="A48" s="28"/>
       <c r="B48" s="21"/>
       <c r="C48" s="28">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D48" s="21"/>
       <c r="E48" s="88" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F48" s="21" t="s">
         <v>108</v>
@@ -8179,22 +8171,18 @@
       <c r="G48" s="28"/>
       <c r="H48" s="28"/>
       <c r="I48" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" s="34"/>
-      <c r="K48" s="34" t="s">
-        <v>273</v>
-      </c>
+      <c r="K48" s="34"/>
       <c r="L48" s="34"/>
-      <c r="M48" s="34" t="s">
-        <v>274</v>
-      </c>
+      <c r="M48" s="34"/>
       <c r="N48" s="34"/>
       <c r="O48" s="2" t="s">
-        <v>275</v>
+        <v>108</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q48" s="54"/>
       <c r="AMJ48"/>
@@ -8203,148 +8191,152 @@
       <c r="A49" s="28"/>
       <c r="B49" s="21"/>
       <c r="C49" s="28">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D49" s="21"/>
-      <c r="E49" s="21">
-        <v>2.202</v>
-      </c>
-      <c r="F49" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="G49" s="28">
-        <v>202</v>
-      </c>
+      <c r="E49" s="88" t="s">
+        <v>625</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G49" s="28"/>
       <c r="H49" s="28"/>
       <c r="I49" s="28">
-        <v>1</v>
-      </c>
-      <c r="J49" s="34" t="s">
-        <v>277</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J49" s="34"/>
       <c r="K49" s="34" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="L49" s="34"/>
-      <c r="M49" s="34"/>
+      <c r="M49" s="34" t="s">
+        <v>274</v>
+      </c>
       <c r="N49" s="34"/>
       <c r="O49" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="Q49" s="54"/>
       <c r="AMJ49"/>
     </row>
     <row r="50" spans="1:1024" s="55" customFormat="1">
-      <c r="A50" s="28">
-        <v>24</v>
-      </c>
-      <c r="B50" s="21">
-        <v>23</v>
-      </c>
+      <c r="A50" s="28"/>
+      <c r="B50" s="21"/>
       <c r="C50" s="28">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D50" s="21"/>
-      <c r="E50" s="88" t="s">
-        <v>627</v>
+      <c r="E50" s="21">
+        <v>2.202</v>
       </c>
       <c r="F50" s="33" t="s">
-        <v>595</v>
+        <v>109</v>
       </c>
       <c r="G50" s="28">
         <v>202</v>
       </c>
-      <c r="H50" s="28">
-        <v>1</v>
-      </c>
+      <c r="H50" s="28"/>
       <c r="I50" s="28">
         <v>1</v>
       </c>
       <c r="J50" s="34" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="K50" s="34" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L50" s="34"/>
       <c r="M50" s="34"/>
       <c r="N50" s="34"/>
       <c r="O50" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="Q50" s="54"/>
       <c r="AMJ50"/>
     </row>
     <row r="51" spans="1:1024" s="55" customFormat="1">
       <c r="A51" s="28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B51" s="21">
         <v>23</v>
       </c>
       <c r="C51" s="28">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D51" s="21"/>
       <c r="E51" s="88" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>111</v>
+        <v>595</v>
       </c>
       <c r="G51" s="28">
         <v>202</v>
       </c>
       <c r="H51" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I51" s="28">
         <v>1</v>
       </c>
       <c r="J51" s="34" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="K51" s="34" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="L51" s="34"/>
       <c r="M51" s="34"/>
       <c r="N51" s="34"/>
       <c r="O51" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="Q51" s="54"/>
       <c r="AMJ51"/>
     </row>
     <row r="52" spans="1:1024" s="55" customFormat="1">
-      <c r="A52" s="28"/>
-      <c r="B52" s="21"/>
+      <c r="A52" s="28">
+        <v>25</v>
+      </c>
+      <c r="B52" s="21">
+        <v>23</v>
+      </c>
       <c r="C52" s="28">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="88" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F52" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
+      <c r="G52" s="28">
+        <v>202</v>
+      </c>
+      <c r="H52" s="28">
+        <v>3</v>
+      </c>
       <c r="I52" s="28">
-        <v>2</v>
-      </c>
-      <c r="J52" s="34"/>
-      <c r="K52" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J52" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="K52" s="34" t="s">
+        <v>286</v>
+      </c>
       <c r="L52" s="34"/>
       <c r="M52" s="34"/>
       <c r="N52" s="34"/>
@@ -8361,11 +8353,11 @@
       <c r="A53" s="28"/>
       <c r="B53" s="21"/>
       <c r="C53" s="28">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="88" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F53" s="33" t="s">
         <v>111</v>
@@ -8373,7 +8365,7 @@
       <c r="G53" s="28"/>
       <c r="H53" s="28"/>
       <c r="I53" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J53" s="34"/>
       <c r="K53" s="34"/>
@@ -8390,71 +8382,72 @@
       <c r="AMJ53"/>
     </row>
     <row r="54" spans="1:1024" s="55" customFormat="1">
-      <c r="A54" s="28">
-        <v>26</v>
-      </c>
-      <c r="B54" s="21">
-        <v>25</v>
-      </c>
+      <c r="A54" s="28"/>
+      <c r="B54" s="21"/>
       <c r="C54" s="28">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D54" s="21"/>
       <c r="E54" s="88" t="s">
-        <v>629</v>
-      </c>
-      <c r="F54" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="G54" s="43">
-        <v>202</v>
-      </c>
-      <c r="H54" s="43">
-        <v>2</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
       <c r="I54" s="28">
-        <v>1</v>
-      </c>
-      <c r="J54" s="34" t="s">
-        <v>289</v>
-      </c>
-      <c r="K54" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="L54" s="34" t="s">
-        <v>291</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="34"/>
       <c r="M54" s="34"/>
       <c r="N54" s="34"/>
       <c r="O54" s="2" t="s">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>292</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="Q54" s="54"/>
       <c r="AMJ54"/>
     </row>
     <row r="55" spans="1:1024" s="55" customFormat="1">
-      <c r="A55" s="28"/>
-      <c r="B55" s="21"/>
+      <c r="A55" s="28">
+        <v>26</v>
+      </c>
+      <c r="B55" s="21">
+        <v>25</v>
+      </c>
       <c r="C55" s="28">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D55" s="21"/>
       <c r="E55" s="88" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F55" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="G55" s="43"/>
-      <c r="H55" s="43"/>
+      <c r="G55" s="43">
+        <v>202</v>
+      </c>
+      <c r="H55" s="43">
+        <v>2</v>
+      </c>
       <c r="I55" s="28">
-        <v>2</v>
-      </c>
-      <c r="J55" s="34"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J55" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="K55" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="L55" s="34" t="s">
+        <v>291</v>
+      </c>
       <c r="M55" s="34"/>
       <c r="N55" s="34"/>
       <c r="O55" s="2" t="s">
@@ -8469,144 +8462,143 @@
       <c r="A56" s="28"/>
       <c r="B56" s="21"/>
       <c r="C56" s="28">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="88" t="s">
-        <v>629</v>
-      </c>
-      <c r="F56" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="G56" s="28">
-        <v>202</v>
-      </c>
-      <c r="H56" s="28"/>
+        <v>628</v>
+      </c>
+      <c r="F56" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
       <c r="I56" s="28">
-        <v>1</v>
-      </c>
-      <c r="J56" s="34" t="s">
-        <v>293</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J56" s="34"/>
       <c r="K56" s="34"/>
       <c r="L56" s="34"/>
       <c r="M56" s="34"/>
       <c r="N56" s="34"/>
       <c r="O56" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="54"/>
+        <v>112</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>292</v>
+      </c>
       <c r="AMJ56"/>
     </row>
     <row r="57" spans="1:1024" s="55" customFormat="1">
-      <c r="A57" s="28">
-        <v>27</v>
-      </c>
-      <c r="B57" s="21">
-        <v>23</v>
-      </c>
+      <c r="A57" s="28"/>
+      <c r="B57" s="21"/>
       <c r="C57" s="28">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="88" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G57" s="28">
         <v>202</v>
       </c>
-      <c r="H57" s="28">
-        <v>1</v>
-      </c>
+      <c r="H57" s="28"/>
       <c r="I57" s="28">
         <v>1</v>
       </c>
       <c r="J57" s="34" t="s">
-        <v>295</v>
-      </c>
-      <c r="K57" s="34" t="s">
-        <v>296</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="K57" s="34"/>
       <c r="L57" s="34"/>
       <c r="M57" s="34"/>
       <c r="N57" s="34"/>
       <c r="O57" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>297</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="P57" s="2"/>
       <c r="Q57" s="54"/>
       <c r="AMJ57"/>
     </row>
     <row r="58" spans="1:1024" s="55" customFormat="1">
       <c r="A58" s="28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B58" s="21">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C58" s="28">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="88" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="G58" s="28">
         <v>202</v>
       </c>
       <c r="H58" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58" s="28">
         <v>1</v>
       </c>
       <c r="J58" s="34" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K58" s="34" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="L58" s="34"/>
       <c r="M58" s="34"/>
       <c r="N58" s="34"/>
       <c r="O58" s="2" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q58" s="54"/>
       <c r="AMJ58"/>
     </row>
     <row r="59" spans="1:1024" s="55" customFormat="1">
-      <c r="A59" s="28"/>
-      <c r="B59" s="21"/>
+      <c r="A59" s="28">
+        <v>28</v>
+      </c>
+      <c r="B59" s="21">
+        <v>26</v>
+      </c>
       <c r="C59" s="28">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D59" s="21"/>
       <c r="E59" s="88" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F59" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
+      <c r="G59" s="28">
+        <v>202</v>
+      </c>
+      <c r="H59" s="28">
+        <v>3</v>
+      </c>
       <c r="I59" s="28">
-        <v>2</v>
-      </c>
-      <c r="J59" s="34"/>
-      <c r="K59" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J59" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="K59" s="34" t="s">
+        <v>299</v>
+      </c>
       <c r="L59" s="34"/>
       <c r="M59" s="34"/>
       <c r="N59" s="34"/>
@@ -8623,11 +8615,11 @@
       <c r="A60" s="28"/>
       <c r="B60" s="21"/>
       <c r="C60" s="28">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D60" s="21"/>
       <c r="E60" s="88" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F60" s="33" t="s">
         <v>73</v>
@@ -8635,7 +8627,7 @@
       <c r="G60" s="28"/>
       <c r="H60" s="28"/>
       <c r="I60" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="34"/>
       <c r="K60" s="34"/>
@@ -8651,70 +8643,60 @@
       <c r="Q60" s="54"/>
       <c r="AMJ60"/>
     </row>
-    <row r="61" spans="1:1024" s="55" customFormat="1" ht="30">
-      <c r="A61" s="36">
-        <v>212</v>
-      </c>
-      <c r="B61" s="3">
-        <v>202</v>
-      </c>
-      <c r="C61" s="36"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="G61" s="39">
-        <v>2</v>
-      </c>
-      <c r="H61" s="39">
-        <v>1</v>
-      </c>
-      <c r="I61" s="36"/>
-      <c r="J61" s="40"/>
-      <c r="K61" s="40"/>
-      <c r="L61" s="40"/>
-      <c r="M61" s="40"/>
-      <c r="N61" s="40"/>
-      <c r="O61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>303</v>
+    <row r="61" spans="1:1024" s="55" customFormat="1">
+      <c r="A61" s="28"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="28">
+        <v>49</v>
+      </c>
+      <c r="D61" s="21"/>
+      <c r="E61" s="88" t="s">
+        <v>630</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28">
+        <v>3</v>
+      </c>
+      <c r="J61" s="34"/>
+      <c r="K61" s="34"/>
+      <c r="L61" s="34"/>
+      <c r="M61" s="34"/>
+      <c r="N61" s="34"/>
+      <c r="O61" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="Q61" s="54"/>
       <c r="AMJ61"/>
     </row>
     <row r="62" spans="1:1024" s="55" customFormat="1" ht="30">
       <c r="A62" s="36">
-        <v>29</v>
-      </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="36">
-        <v>50</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="B62" s="3">
+        <v>202</v>
+      </c>
+      <c r="C62" s="36"/>
       <c r="D62" s="3"/>
-      <c r="E62" s="89" t="s">
-        <v>632</v>
-      </c>
+      <c r="E62" s="3"/>
       <c r="F62" s="37" t="s">
         <v>115</v>
       </c>
       <c r="G62" s="39">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="H62" s="39">
         <v>1</v>
       </c>
-      <c r="I62" s="36">
-        <v>1</v>
-      </c>
-      <c r="J62" s="40" t="s">
-        <v>301</v>
-      </c>
-      <c r="K62" s="40" t="s">
-        <v>302</v>
-      </c>
+      <c r="I62" s="36"/>
+      <c r="J62" s="40"/>
+      <c r="K62" s="40"/>
       <c r="L62" s="40"/>
       <c r="M62" s="40"/>
       <c r="N62" s="40"/>
@@ -8727,68 +8709,78 @@
       <c r="Q62" s="54"/>
       <c r="AMJ62"/>
     </row>
-    <row r="63" spans="1:1024" s="55" customFormat="1">
+    <row r="63" spans="1:1024" s="55" customFormat="1" ht="30">
       <c r="A63" s="36">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="36">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="89" t="s">
-        <v>633</v>
-      </c>
-      <c r="F63" s="59" t="s">
-        <v>117</v>
+        <v>631</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>115</v>
       </c>
       <c r="G63" s="39">
         <v>212</v>
       </c>
       <c r="H63" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="36">
         <v>1</v>
       </c>
       <c r="J63" s="40" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="K63" s="40" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L63" s="40"/>
       <c r="M63" s="40"/>
       <c r="N63" s="40"/>
       <c r="O63" s="1" t="s">
-        <v>306</v>
+        <v>115</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q63" s="57"/>
+        <v>303</v>
+      </c>
+      <c r="Q63" s="54"/>
       <c r="AMJ63"/>
     </row>
     <row r="64" spans="1:1024" s="55" customFormat="1">
-      <c r="A64" s="36"/>
+      <c r="A64" s="36">
+        <v>30</v>
+      </c>
       <c r="B64" s="3"/>
       <c r="C64" s="36">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="89" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F64" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39"/>
+      <c r="G64" s="39">
+        <v>212</v>
+      </c>
+      <c r="H64" s="39">
+        <v>2</v>
+      </c>
       <c r="I64" s="36">
-        <v>2</v>
-      </c>
-      <c r="J64" s="40"/>
-      <c r="K64" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J64" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="K64" s="40" t="s">
+        <v>305</v>
+      </c>
       <c r="L64" s="40"/>
       <c r="M64" s="40"/>
       <c r="N64" s="40"/>
@@ -8802,58 +8794,46 @@
       <c r="AMJ64"/>
     </row>
     <row r="65" spans="1:1024" s="55" customFormat="1">
-      <c r="A65" s="50">
+      <c r="A65" s="36"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="36">
+        <v>52</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="89" t="s">
+        <v>632</v>
+      </c>
+      <c r="F65" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="36">
+        <v>2</v>
+      </c>
+      <c r="J65" s="40"/>
+      <c r="K65" s="40"/>
+      <c r="L65" s="40"/>
+      <c r="M65" s="40"/>
+      <c r="N65" s="40"/>
+      <c r="O65" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q65" s="57"/>
+      <c r="AMJ65"/>
+    </row>
+    <row r="66" spans="1:1024" s="55" customFormat="1">
+      <c r="A66" s="50">
         <v>34</v>
       </c>
-      <c r="B65" s="51">
+      <c r="B66" s="51">
         <v>202</v>
       </c>
-      <c r="C65" s="50">
+      <c r="C66" s="50">
         <v>53</v>
-      </c>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51" t="s">
-        <v>308</v>
-      </c>
-      <c r="F65" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="G65" s="50">
-        <v>2</v>
-      </c>
-      <c r="H65" s="50">
-        <v>3</v>
-      </c>
-      <c r="I65" s="50">
-        <v>1</v>
-      </c>
-      <c r="J65" s="52" t="s">
-        <v>309</v>
-      </c>
-      <c r="K65" s="52" t="s">
-        <v>310</v>
-      </c>
-      <c r="L65" s="52"/>
-      <c r="M65" s="52" t="s">
-        <v>311</v>
-      </c>
-      <c r="N65" s="52" t="s">
-        <v>312</v>
-      </c>
-      <c r="O65" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="P65" s="53" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q65" s="54"/>
-      <c r="AMJ65"/>
-    </row>
-    <row r="66" spans="1:1024" s="55" customFormat="1">
-      <c r="A66" s="50"/>
-      <c r="B66" s="51"/>
-      <c r="C66" s="50">
-        <v>54</v>
       </c>
       <c r="D66" s="51"/>
       <c r="E66" s="51" t="s">
@@ -8862,16 +8842,28 @@
       <c r="F66" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="G66" s="50"/>
-      <c r="H66" s="50"/>
+      <c r="G66" s="50">
+        <v>2</v>
+      </c>
+      <c r="H66" s="50">
+        <v>3</v>
+      </c>
       <c r="I66" s="50">
-        <v>2</v>
-      </c>
-      <c r="J66" s="52"/>
-      <c r="K66" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="J66" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="K66" s="52" t="s">
+        <v>310</v>
+      </c>
       <c r="L66" s="52"/>
-      <c r="M66" s="52"/>
-      <c r="N66" s="52"/>
+      <c r="M66" s="52" t="s">
+        <v>311</v>
+      </c>
+      <c r="N66" s="52" t="s">
+        <v>312</v>
+      </c>
       <c r="O66" s="53" t="s">
         <v>121</v>
       </c>
@@ -8885,7 +8877,7 @@
       <c r="A67" s="50"/>
       <c r="B67" s="51"/>
       <c r="C67" s="50">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D67" s="51"/>
       <c r="E67" s="51" t="s">
@@ -8897,7 +8889,7 @@
       <c r="G67" s="50"/>
       <c r="H67" s="50"/>
       <c r="I67" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J67" s="52"/>
       <c r="K67" s="52"/>
@@ -8917,32 +8909,30 @@
       <c r="A68" s="50"/>
       <c r="B68" s="51"/>
       <c r="C68" s="50">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D68" s="51"/>
       <c r="E68" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="F68" s="51"/>
+      <c r="F68" s="51" t="s">
+        <v>121</v>
+      </c>
       <c r="G68" s="50"/>
       <c r="H68" s="50"/>
       <c r="I68" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J68" s="52"/>
-      <c r="K68" s="52" t="s">
-        <v>314</v>
-      </c>
+      <c r="K68" s="52"/>
       <c r="L68" s="52"/>
-      <c r="M68" s="52" t="s">
-        <v>315</v>
-      </c>
+      <c r="M68" s="52"/>
       <c r="N68" s="52"/>
       <c r="O68" s="53" t="s">
-        <v>316</v>
+        <v>121</v>
       </c>
       <c r="P68" s="53" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="Q68" s="54"/>
       <c r="AMJ68"/>
@@ -8951,119 +8941,113 @@
       <c r="A69" s="50"/>
       <c r="B69" s="51"/>
       <c r="C69" s="50">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D69" s="51"/>
       <c r="E69" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="F69" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="G69" s="50">
-        <v>34</v>
-      </c>
+      <c r="F69" s="51"/>
+      <c r="G69" s="50"/>
       <c r="H69" s="50"/>
       <c r="I69" s="50">
         <v>1</v>
       </c>
-      <c r="J69" s="52" t="s">
-        <v>318</v>
-      </c>
+      <c r="J69" s="52"/>
       <c r="K69" s="52" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L69" s="52"/>
-      <c r="M69" s="52"/>
+      <c r="M69" s="52" t="s">
+        <v>315</v>
+      </c>
       <c r="N69" s="52"/>
       <c r="O69" s="53" t="s">
+        <v>316</v>
+      </c>
+      <c r="P69" s="53" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q69" s="54"/>
+      <c r="AMJ69"/>
+    </row>
+    <row r="70" spans="1:1024" s="55" customFormat="1">
+      <c r="A70" s="50"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="50">
+        <v>57</v>
+      </c>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51" t="s">
+        <v>308</v>
+      </c>
+      <c r="F70" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="G70" s="50">
+        <v>34</v>
+      </c>
+      <c r="H70" s="50"/>
+      <c r="I70" s="50">
+        <v>1</v>
+      </c>
+      <c r="J70" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="K70" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="L70" s="52"/>
+      <c r="M70" s="52"/>
+      <c r="N70" s="52"/>
+      <c r="O70" s="53" t="s">
         <v>320</v>
       </c>
-      <c r="P69" s="53" t="s">
+      <c r="P70" s="53" t="s">
         <v>321</v>
       </c>
-      <c r="Q69" s="57"/>
-      <c r="AMJ69"/>
-    </row>
-    <row r="70" spans="1:1024" s="55" customFormat="1">
-      <c r="A70" s="28">
-        <v>31</v>
-      </c>
-      <c r="B70" s="88" t="s">
-        <v>634</v>
-      </c>
-      <c r="C70" s="28"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="60"/>
-      <c r="F70" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G70" s="43">
-        <v>2</v>
-      </c>
-      <c r="H70" s="43">
-        <v>2</v>
-      </c>
-      <c r="I70" s="28"/>
-      <c r="J70" s="34"/>
-      <c r="K70" s="34"/>
-      <c r="L70" s="34"/>
-      <c r="M70" s="34"/>
-      <c r="N70" s="34"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q70" s="54"/>
+      <c r="Q70" s="57"/>
       <c r="AMJ70"/>
     </row>
     <row r="71" spans="1:1024" s="55" customFormat="1">
       <c r="A71" s="28">
-        <v>32</v>
-      </c>
-      <c r="B71" s="21"/>
-      <c r="C71" s="28">
-        <v>58</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B71" s="88" t="s">
+        <v>633</v>
+      </c>
+      <c r="C71" s="28"/>
       <c r="D71" s="21"/>
-      <c r="E71" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="F71" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="G71" s="28">
-        <v>31</v>
-      </c>
-      <c r="H71" s="28">
+      <c r="E71" s="60"/>
+      <c r="F71" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G71" s="43">
         <v>2</v>
       </c>
-      <c r="I71" s="28">
-        <v>1</v>
-      </c>
-      <c r="J71" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="K71" s="34" t="s">
-        <v>326</v>
-      </c>
+      <c r="H71" s="43">
+        <v>2</v>
+      </c>
+      <c r="I71" s="28"/>
+      <c r="J71" s="34"/>
+      <c r="K71" s="34"/>
       <c r="L71" s="34"/>
       <c r="M71" s="34"/>
       <c r="N71" s="34"/>
-      <c r="O71" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="Q71" s="54"/>
       <c r="AMJ71"/>
     </row>
     <row r="72" spans="1:1024" s="55" customFormat="1">
-      <c r="A72" s="28"/>
+      <c r="A72" s="28">
+        <v>32</v>
+      </c>
       <c r="B72" s="21"/>
       <c r="C72" s="28">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D72" s="21"/>
       <c r="E72" s="21" t="s">
@@ -9072,13 +9056,21 @@
       <c r="F72" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="G72" s="28"/>
-      <c r="H72" s="28"/>
+      <c r="G72" s="28">
+        <v>31</v>
+      </c>
+      <c r="H72" s="28">
+        <v>2</v>
+      </c>
       <c r="I72" s="28">
-        <v>2</v>
-      </c>
-      <c r="J72" s="34"/>
-      <c r="K72" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J72" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="K72" s="34" t="s">
+        <v>326</v>
+      </c>
       <c r="L72" s="34"/>
       <c r="M72" s="34"/>
       <c r="N72" s="34"/>
@@ -9095,182 +9087,182 @@
       <c r="A73" s="28"/>
       <c r="B73" s="21"/>
       <c r="C73" s="28">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D73" s="21"/>
-      <c r="E73" s="60" t="s">
-        <v>322</v>
+      <c r="E73" s="21" t="s">
+        <v>324</v>
       </c>
       <c r="F73" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="G73" s="28">
-        <v>31</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="G73" s="28"/>
       <c r="H73" s="28"/>
       <c r="I73" s="28">
-        <v>1</v>
-      </c>
-      <c r="J73" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="K73" s="34" t="s">
-        <v>329</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J73" s="34"/>
+      <c r="K73" s="34"/>
       <c r="L73" s="34"/>
       <c r="M73" s="34"/>
       <c r="N73" s="34"/>
       <c r="O73" s="2" t="s">
-        <v>330</v>
+        <v>118</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q73" s="57"/>
+        <v>327</v>
+      </c>
+      <c r="Q73" s="54"/>
       <c r="AMJ73"/>
     </row>
     <row r="74" spans="1:1024" s="55" customFormat="1">
-      <c r="A74" s="28">
-        <v>33</v>
-      </c>
-      <c r="B74" s="21">
-        <v>32</v>
-      </c>
+      <c r="A74" s="28"/>
+      <c r="B74" s="21"/>
       <c r="C74" s="28">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D74" s="21"/>
-      <c r="E74" s="21" t="s">
-        <v>332</v>
+      <c r="E74" s="60" t="s">
+        <v>322</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G74" s="28">
         <v>31</v>
       </c>
-      <c r="H74" s="28">
-        <v>1</v>
-      </c>
+      <c r="H74" s="28"/>
       <c r="I74" s="28">
         <v>1</v>
       </c>
       <c r="J74" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="K74" s="34"/>
+        <v>328</v>
+      </c>
+      <c r="K74" s="34" t="s">
+        <v>329</v>
+      </c>
       <c r="L74" s="34"/>
       <c r="M74" s="34"/>
       <c r="N74" s="34"/>
       <c r="O74" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q74" s="57"/>
+      <c r="AMJ74"/>
+    </row>
+    <row r="75" spans="1:1024" s="55" customFormat="1">
+      <c r="A75" s="28">
+        <v>33</v>
+      </c>
+      <c r="B75" s="21">
+        <v>32</v>
+      </c>
+      <c r="C75" s="28">
+        <v>61</v>
+      </c>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F75" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="P74" s="2" t="s">
+      <c r="G75" s="28">
+        <v>31</v>
+      </c>
+      <c r="H75" s="28">
+        <v>1</v>
+      </c>
+      <c r="I75" s="28">
+        <v>1</v>
+      </c>
+      <c r="J75" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="K75" s="34"/>
+      <c r="L75" s="34"/>
+      <c r="M75" s="34"/>
+      <c r="N75" s="34"/>
+      <c r="O75" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="P75" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="Q74" s="54"/>
-      <c r="AMJ74"/>
-    </row>
-    <row r="75" spans="1:1024" s="55" customFormat="1">
-      <c r="A75" s="36">
-        <v>35</v>
-      </c>
-      <c r="B75" s="3">
-        <v>31</v>
-      </c>
-      <c r="C75" s="36">
-        <v>62</v>
-      </c>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G75" s="36">
-        <v>2</v>
-      </c>
-      <c r="H75" s="36">
-        <v>3</v>
-      </c>
-      <c r="I75" s="36"/>
-      <c r="J75" s="40"/>
-      <c r="K75" s="40"/>
-      <c r="L75" s="40"/>
-      <c r="M75" s="40"/>
-      <c r="N75" s="40"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="Q75" s="54"/>
       <c r="AMJ75"/>
     </row>
     <row r="76" spans="1:1024" s="55" customFormat="1">
       <c r="A76" s="36">
-        <v>36</v>
-      </c>
-      <c r="B76" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="B76" s="3">
+        <v>31</v>
+      </c>
       <c r="C76" s="36">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D76" s="3"/>
-      <c r="E76" s="89" t="s">
-        <v>336</v>
-      </c>
-      <c r="F76" s="41" t="s">
-        <v>123</v>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="G76" s="36">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H76" s="36">
         <v>3</v>
       </c>
-      <c r="I76" s="36">
-        <v>1</v>
-      </c>
-      <c r="J76" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="K76" s="40" t="s">
-        <v>338</v>
-      </c>
+      <c r="I76" s="36"/>
+      <c r="J76" s="40"/>
+      <c r="K76" s="40"/>
       <c r="L76" s="40"/>
-      <c r="M76" s="40" t="s">
-        <v>339</v>
-      </c>
+      <c r="M76" s="40"/>
       <c r="N76" s="40"/>
-      <c r="O76" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P76" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q76" s="57"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q76" s="54"/>
       <c r="AMJ76"/>
     </row>
     <row r="77" spans="1:1024" s="55" customFormat="1">
-      <c r="A77" s="36"/>
+      <c r="A77" s="36">
+        <v>36</v>
+      </c>
       <c r="B77" s="3"/>
       <c r="C77" s="36">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D77" s="3"/>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="89" t="s">
         <v>336</v>
       </c>
       <c r="F77" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="G77" s="36"/>
-      <c r="H77" s="36"/>
+      <c r="G77" s="36">
+        <v>35</v>
+      </c>
+      <c r="H77" s="36">
+        <v>3</v>
+      </c>
       <c r="I77" s="36">
-        <v>2</v>
-      </c>
-      <c r="J77" s="40"/>
-      <c r="K77" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J77" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="K77" s="40" t="s">
+        <v>338</v>
+      </c>
       <c r="L77" s="40"/>
-      <c r="M77" s="40"/>
+      <c r="M77" s="40" t="s">
+        <v>339</v>
+      </c>
       <c r="N77" s="40"/>
       <c r="O77" s="1" t="s">
         <v>123</v>
@@ -9285,7 +9277,7 @@
       <c r="A78" s="36"/>
       <c r="B78" s="3"/>
       <c r="C78" s="36">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3" t="s">
@@ -9297,7 +9289,7 @@
       <c r="G78" s="36"/>
       <c r="H78" s="36"/>
       <c r="I78" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J78" s="40"/>
       <c r="K78" s="40"/>
@@ -9314,70 +9306,70 @@
       <c r="AMJ78"/>
     </row>
     <row r="79" spans="1:1024" s="55" customFormat="1">
-      <c r="A79" s="36">
-        <v>37</v>
-      </c>
+      <c r="A79" s="36"/>
       <c r="B79" s="3"/>
       <c r="C79" s="36">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D79" s="3"/>
-      <c r="E79" s="89" t="s">
-        <v>343</v>
+      <c r="E79" s="3" t="s">
+        <v>336</v>
       </c>
       <c r="F79" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="G79" s="36">
-        <v>35</v>
-      </c>
-      <c r="H79" s="36">
-        <v>1</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
       <c r="I79" s="36">
-        <v>1</v>
-      </c>
-      <c r="J79" s="40" t="s">
-        <v>341</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J79" s="40"/>
       <c r="K79" s="40"/>
       <c r="L79" s="40"/>
       <c r="M79" s="40"/>
       <c r="N79" s="40"/>
       <c r="O79" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="P79" s="2" t="s">
-        <v>342</v>
+        <v>123</v>
+      </c>
+      <c r="P79" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="Q79" s="57"/>
       <c r="AMJ79"/>
     </row>
     <row r="80" spans="1:1024" s="55" customFormat="1">
-      <c r="A80" s="36"/>
+      <c r="A80" s="36">
+        <v>37</v>
+      </c>
       <c r="B80" s="3"/>
       <c r="C80" s="36">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D80" s="3"/>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="89" t="s">
         <v>343</v>
       </c>
-      <c r="F80" s="41"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
+      <c r="F80" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="G80" s="36">
+        <v>35</v>
+      </c>
+      <c r="H80" s="36">
+        <v>1</v>
+      </c>
       <c r="I80" s="36">
         <v>1</v>
       </c>
       <c r="J80" s="40" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="40"/>
       <c r="M80" s="40"/>
       <c r="N80" s="40"/>
       <c r="O80" s="1" t="s">
-        <v>345</v>
+        <v>124</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>342</v>
@@ -9389,11 +9381,11 @@
       <c r="A81" s="36"/>
       <c r="B81" s="3"/>
       <c r="C81" s="36">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F81" s="41"/>
       <c r="G81" s="36"/>
@@ -9402,14 +9394,14 @@
         <v>1</v>
       </c>
       <c r="J81" s="40" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="K81" s="40"/>
       <c r="L81" s="40"/>
       <c r="M81" s="40"/>
       <c r="N81" s="40"/>
       <c r="O81" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>342</v>
@@ -9421,11 +9413,11 @@
       <c r="A82" s="36"/>
       <c r="B82" s="3"/>
       <c r="C82" s="36">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F82" s="41"/>
       <c r="G82" s="36"/>
@@ -9434,70 +9426,60 @@
         <v>1</v>
       </c>
       <c r="J82" s="40" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="40"/>
       <c r="M82" s="40"/>
       <c r="N82" s="40"/>
       <c r="O82" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P82" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="Q82" s="54"/>
+      <c r="Q82" s="57"/>
       <c r="AMJ82"/>
     </row>
     <row r="83" spans="1:1024" s="55" customFormat="1">
-      <c r="A83" s="36">
-        <v>38</v>
-      </c>
+      <c r="A83" s="36"/>
       <c r="B83" s="3"/>
       <c r="C83" s="36">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F83" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="G83" s="36">
-        <v>35</v>
-      </c>
-      <c r="H83" s="36">
-        <v>2</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="F83" s="41"/>
+      <c r="G83" s="36"/>
+      <c r="H83" s="36"/>
       <c r="I83" s="36">
         <v>1</v>
       </c>
       <c r="J83" s="40" t="s">
-        <v>352</v>
-      </c>
-      <c r="K83" s="40" t="s">
-        <v>353</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="K83" s="40"/>
       <c r="L83" s="40"/>
-      <c r="M83" s="40" t="s">
-        <v>354</v>
-      </c>
+      <c r="M83" s="40"/>
       <c r="N83" s="40"/>
       <c r="O83" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="P83" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q83" s="57"/>
+        <v>350</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q83" s="54"/>
       <c r="AMJ83"/>
     </row>
     <row r="84" spans="1:1024" s="55" customFormat="1">
-      <c r="A84" s="36"/>
+      <c r="A84" s="36">
+        <v>38</v>
+      </c>
       <c r="B84" s="3"/>
       <c r="C84" s="36">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3" t="s">
@@ -9506,15 +9488,25 @@
       <c r="F84" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="G84" s="36"/>
-      <c r="H84" s="36"/>
+      <c r="G84" s="36">
+        <v>35</v>
+      </c>
+      <c r="H84" s="36">
+        <v>2</v>
+      </c>
       <c r="I84" s="36">
-        <v>2</v>
-      </c>
-      <c r="J84" s="40"/>
-      <c r="K84" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J84" s="40" t="s">
+        <v>352</v>
+      </c>
+      <c r="K84" s="40" t="s">
+        <v>353</v>
+      </c>
       <c r="L84" s="40"/>
-      <c r="M84" s="40"/>
+      <c r="M84" s="40" t="s">
+        <v>354</v>
+      </c>
       <c r="N84" s="40"/>
       <c r="O84" s="1" t="s">
         <v>355</v>
@@ -9525,167 +9517,162 @@
       <c r="Q84" s="57"/>
       <c r="AMJ84"/>
     </row>
-    <row r="85" spans="1:1024">
-      <c r="A85" s="61">
+    <row r="85" spans="1:1024" s="55" customFormat="1">
+      <c r="A85" s="36"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="36">
+        <v>72</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F85" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="G85" s="36"/>
+      <c r="H85" s="36"/>
+      <c r="I85" s="36">
+        <v>2</v>
+      </c>
+      <c r="J85" s="40"/>
+      <c r="K85" s="40"/>
+      <c r="L85" s="40"/>
+      <c r="M85" s="40"/>
+      <c r="N85" s="40"/>
+      <c r="O85" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="P85" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q85" s="57"/>
+      <c r="AMJ85"/>
+    </row>
+    <row r="86" spans="1:1024">
+      <c r="A86" s="61">
         <v>43</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B86" s="62">
         <v>2</v>
       </c>
-      <c r="C85" s="61"/>
-      <c r="D85" s="62"/>
-      <c r="E85" s="62"/>
-      <c r="F85" s="4" t="s">
+      <c r="C86" s="61"/>
+      <c r="D86" s="62"/>
+      <c r="E86" s="62"/>
+      <c r="F86" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="G85" s="25">
-        <v>1</v>
-      </c>
-      <c r="H85" s="61">
+      <c r="G86" s="25">
+        <v>1</v>
+      </c>
+      <c r="H86" s="61">
         <v>3</v>
       </c>
-      <c r="I85" s="61"/>
-      <c r="J85" s="63"/>
-      <c r="K85" s="63"/>
-      <c r="L85" s="63"/>
-      <c r="M85" s="63"/>
-      <c r="N85" s="63"/>
-      <c r="Q85" s="42"/>
-    </row>
-    <row r="86" spans="1:1024">
-      <c r="A86" s="28">
+      <c r="I86" s="61"/>
+      <c r="J86" s="63"/>
+      <c r="K86" s="63"/>
+      <c r="L86" s="63"/>
+      <c r="M86" s="63"/>
+      <c r="N86" s="63"/>
+      <c r="Q86" s="42"/>
+    </row>
+    <row r="87" spans="1:1024">
+      <c r="A87" s="28">
         <v>44</v>
       </c>
-      <c r="B86" s="21">
+      <c r="B87" s="21">
         <v>45</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C87" s="28">
         <v>73</v>
       </c>
-      <c r="D86" s="21"/>
-      <c r="E86" s="21" t="s">
+      <c r="D87" s="21"/>
+      <c r="E87" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="F86" s="19" t="s">
+      <c r="F87" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="G86" s="43">
+      <c r="G87" s="43">
         <v>43</v>
       </c>
-      <c r="H86" s="43">
-        <v>1</v>
-      </c>
-      <c r="I86" s="28">
-        <v>1</v>
-      </c>
-      <c r="J86" s="34" t="s">
+      <c r="H87" s="43">
+        <v>1</v>
+      </c>
+      <c r="I87" s="28">
+        <v>1</v>
+      </c>
+      <c r="J87" s="34" t="s">
         <v>359</v>
       </c>
-      <c r="K86" s="34"/>
-      <c r="L86" s="34"/>
-      <c r="M86" s="34"/>
-      <c r="N86" s="34"/>
-      <c r="O86" s="2"/>
-      <c r="P86" s="2" t="s">
+      <c r="K87" s="34"/>
+      <c r="L87" s="34"/>
+      <c r="M87" s="34"/>
+      <c r="N87" s="34"/>
+      <c r="O87" s="2"/>
+      <c r="P87" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="Q86" s="42"/>
-    </row>
-    <row r="87" spans="1:1024">
-      <c r="A87" s="36">
+      <c r="Q87" s="42"/>
+    </row>
+    <row r="88" spans="1:1024">
+      <c r="A88" s="36">
         <v>45</v>
       </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="36">
+      <c r="B88" s="3"/>
+      <c r="C88" s="36">
         <v>74</v>
       </c>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3" t="s">
+      <c r="D88" s="3"/>
+      <c r="E88" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F88" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G87" s="36">
+      <c r="G88" s="36">
         <v>43</v>
       </c>
-      <c r="H87" s="36">
-        <v>1</v>
-      </c>
-      <c r="I87" s="36">
-        <v>1</v>
-      </c>
-      <c r="J87" s="40" t="s">
+      <c r="H88" s="36">
+        <v>1</v>
+      </c>
+      <c r="I88" s="36">
+        <v>1</v>
+      </c>
+      <c r="J88" s="40" t="s">
         <v>362</v>
       </c>
-      <c r="K87" s="40"/>
-      <c r="L87" s="40"/>
-      <c r="M87" s="40"/>
-      <c r="N87" s="40"/>
-      <c r="O87" s="1"/>
-      <c r="P87" s="1" t="s">
+      <c r="K88" s="40"/>
+      <c r="L88" s="40"/>
+      <c r="M88" s="40"/>
+      <c r="N88" s="40"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="Q87" s="42"/>
-    </row>
-    <row r="88" spans="1:1024">
-      <c r="A88" s="28">
-        <v>204</v>
-      </c>
-      <c r="B88" s="21">
-        <v>56</v>
-      </c>
-      <c r="C88" s="28"/>
-      <c r="D88" s="21"/>
-      <c r="E88" s="21"/>
-      <c r="F88" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="G88" s="28">
-        <v>43</v>
-      </c>
-      <c r="H88" s="28">
-        <v>3</v>
-      </c>
-      <c r="I88" s="28"/>
-      <c r="J88" s="34"/>
-      <c r="K88" s="34"/>
-      <c r="L88" s="34"/>
-      <c r="M88" s="34"/>
-      <c r="N88" s="34"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="Q88" s="42"/>
     </row>
     <row r="89" spans="1:1024">
       <c r="A89" s="28">
-        <v>46</v>
-      </c>
-      <c r="B89" s="21"/>
-      <c r="C89" s="28">
-        <v>75</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="B89" s="21">
+        <v>56</v>
+      </c>
+      <c r="C89" s="28"/>
       <c r="D89" s="21"/>
-      <c r="E89" s="88" t="s">
-        <v>635</v>
-      </c>
+      <c r="E89" s="21"/>
       <c r="F89" s="21" t="s">
         <v>92</v>
       </c>
       <c r="G89" s="28">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="H89" s="28">
-        <v>1</v>
-      </c>
-      <c r="I89" s="28">
-        <v>1</v>
-      </c>
-      <c r="J89" s="34" t="s">
-        <v>364</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I89" s="28"/>
+      <c r="J89" s="34"/>
       <c r="K89" s="34"/>
       <c r="L89" s="34"/>
       <c r="M89" s="34"/>
@@ -9698,20 +9685,18 @@
     </row>
     <row r="90" spans="1:1024">
       <c r="A90" s="28">
-        <v>47</v>
-      </c>
-      <c r="B90" s="21">
         <v>46</v>
       </c>
+      <c r="B90" s="21"/>
       <c r="C90" s="28">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D90" s="21"/>
       <c r="E90" s="88" t="s">
-        <v>636</v>
-      </c>
-      <c r="F90" s="33" t="s">
-        <v>133</v>
+        <v>634</v>
+      </c>
+      <c r="F90" s="21" t="s">
+        <v>92</v>
       </c>
       <c r="G90" s="28">
         <v>204</v>
@@ -9723,7 +9708,7 @@
         <v>1</v>
       </c>
       <c r="J90" s="34" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K90" s="34"/>
       <c r="L90" s="34"/>
@@ -9731,26 +9716,26 @@
       <c r="N90" s="34"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q90" s="42"/>
     </row>
     <row r="91" spans="1:1024">
       <c r="A91" s="28">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B91" s="21">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C91" s="28">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D91" s="21"/>
       <c r="E91" s="88" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F91" s="33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G91" s="28">
         <v>204</v>
@@ -9762,7 +9747,7 @@
         <v>1</v>
       </c>
       <c r="J91" s="34" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K91" s="34"/>
       <c r="L91" s="34"/>
@@ -9770,26 +9755,26 @@
       <c r="N91" s="34"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="Q91" s="42"/>
     </row>
     <row r="92" spans="1:1024">
       <c r="A92" s="28">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B92" s="21">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C92" s="28">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D92" s="21"/>
       <c r="E92" s="88" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F92" s="33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G92" s="28">
         <v>204</v>
@@ -9801,7 +9786,7 @@
         <v>1</v>
       </c>
       <c r="J92" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K92" s="34"/>
       <c r="L92" s="34"/>
@@ -9809,26 +9794,26 @@
       <c r="N92" s="34"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Q92" s="42"/>
     </row>
     <row r="93" spans="1:1024">
       <c r="A93" s="28">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B93" s="21">
         <v>46</v>
       </c>
       <c r="C93" s="28">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D93" s="21"/>
       <c r="E93" s="88" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F93" s="33" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="G93" s="28">
         <v>204</v>
@@ -9840,7 +9825,7 @@
         <v>1</v>
       </c>
       <c r="J93" s="34" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K93" s="34"/>
       <c r="L93" s="34"/>
@@ -9848,26 +9833,26 @@
       <c r="N93" s="34"/>
       <c r="O93" s="2"/>
       <c r="P93" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Q93" s="42"/>
     </row>
     <row r="94" spans="1:1024">
       <c r="A94" s="28">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B94" s="21">
         <v>46</v>
       </c>
       <c r="C94" s="28">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D94" s="21"/>
       <c r="E94" s="88" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="F94" s="33" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="G94" s="28">
         <v>204</v>
@@ -9879,36 +9864,34 @@
         <v>1</v>
       </c>
       <c r="J94" s="34" t="s">
-        <v>382</v>
-      </c>
-      <c r="K94" s="34" t="s">
-        <v>383</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="K94" s="34"/>
       <c r="L94" s="34"/>
       <c r="M94" s="34"/>
       <c r="N94" s="34"/>
       <c r="O94" s="2"/>
       <c r="P94" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="Q94" s="35"/>
+        <v>373</v>
+      </c>
+      <c r="Q94" s="42"/>
     </row>
     <row r="95" spans="1:1024">
       <c r="A95" s="28">
-        <v>55</v>
-      </c>
-      <c r="B95" s="21" t="s">
-        <v>597</v>
+        <v>54</v>
+      </c>
+      <c r="B95" s="21">
+        <v>46</v>
       </c>
       <c r="C95" s="28">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D95" s="21"/>
       <c r="E95" s="88" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F95" s="33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G95" s="28">
         <v>204</v>
@@ -9920,147 +9903,147 @@
         <v>1</v>
       </c>
       <c r="J95" s="34" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="K95" s="34" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="L95" s="34"/>
       <c r="M95" s="34"/>
       <c r="N95" s="34"/>
       <c r="O95" s="2"/>
       <c r="P95" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q95" s="35"/>
+    </row>
+    <row r="96" spans="1:1024">
+      <c r="A96" s="28">
+        <v>55</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="C96" s="28">
+        <v>86</v>
+      </c>
+      <c r="D96" s="21"/>
+      <c r="E96" s="88" t="s">
+        <v>652</v>
+      </c>
+      <c r="F96" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="G96" s="28">
+        <v>204</v>
+      </c>
+      <c r="H96" s="28">
+        <v>1</v>
+      </c>
+      <c r="I96" s="28">
+        <v>1</v>
+      </c>
+      <c r="J96" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="K96" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="L96" s="34"/>
+      <c r="M96" s="34"/>
+      <c r="N96" s="34"/>
+      <c r="O96" s="2"/>
+      <c r="P96" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="Q95" s="35"/>
-    </row>
-    <row r="96" spans="1:1024">
-      <c r="A96" s="36">
+      <c r="Q96" s="35"/>
+    </row>
+    <row r="97" spans="1:17">
+      <c r="A97" s="36">
         <v>56</v>
       </c>
-      <c r="B96" s="3">
+      <c r="B97" s="3">
         <v>45</v>
       </c>
-      <c r="C96" s="36">
+      <c r="C97" s="36">
         <v>87</v>
       </c>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3" t="s">
+      <c r="D97" s="3"/>
+      <c r="E97" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F97" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G96" s="36">
+      <c r="G97" s="36">
         <v>43</v>
       </c>
-      <c r="H96" s="64">
-        <v>1</v>
-      </c>
-      <c r="I96" s="36">
-        <v>1</v>
-      </c>
-      <c r="J96" s="40" t="s">
+      <c r="H97" s="64">
+        <v>1</v>
+      </c>
+      <c r="I97" s="36">
+        <v>1</v>
+      </c>
+      <c r="J97" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="K96" s="40" t="s">
+      <c r="K97" s="40" t="s">
         <v>390</v>
       </c>
-      <c r="L96" s="40"/>
-      <c r="M96" s="40"/>
-      <c r="N96" s="40"/>
-      <c r="O96" s="1"/>
-      <c r="P96" s="1" t="s">
+      <c r="L97" s="40"/>
+      <c r="M97" s="40"/>
+      <c r="N97" s="40"/>
+      <c r="O97" s="1"/>
+      <c r="P97" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="Q96" s="42"/>
-    </row>
-    <row r="97" spans="1:17">
-      <c r="A97" s="28">
-        <v>57</v>
-      </c>
-      <c r="B97" s="21">
-        <v>204</v>
-      </c>
-      <c r="C97" s="28"/>
-      <c r="D97" s="21"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="G97" s="28">
-        <v>43</v>
-      </c>
-      <c r="H97" s="28">
-        <v>1</v>
-      </c>
-      <c r="I97" s="28"/>
-      <c r="J97" s="34"/>
-      <c r="K97" s="34"/>
-      <c r="L97" s="34"/>
-      <c r="M97" s="34"/>
-      <c r="N97" s="34"/>
-      <c r="O97" s="2"/>
-      <c r="P97" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q97" s="35"/>
+      <c r="Q97" s="42"/>
     </row>
     <row r="98" spans="1:17">
       <c r="A98" s="28">
-        <v>58</v>
-      </c>
-      <c r="B98" s="21"/>
-      <c r="C98" s="28">
-        <v>88</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B98" s="21">
+        <v>204</v>
+      </c>
+      <c r="C98" s="28"/>
       <c r="D98" s="21"/>
-      <c r="E98" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="F98" s="33" t="s">
-        <v>141</v>
+      <c r="E98" s="21"/>
+      <c r="F98" s="21" t="s">
+        <v>140</v>
       </c>
       <c r="G98" s="28">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H98" s="28">
         <v>1</v>
       </c>
-      <c r="I98" s="28">
-        <v>1</v>
-      </c>
-      <c r="J98" s="34" t="s">
-        <v>394</v>
-      </c>
-      <c r="K98" s="34" t="s">
-        <v>395</v>
-      </c>
+      <c r="I98" s="28"/>
+      <c r="J98" s="34"/>
+      <c r="K98" s="34"/>
       <c r="L98" s="34"/>
       <c r="M98" s="34"/>
       <c r="N98" s="34"/>
       <c r="O98" s="2"/>
       <c r="P98" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="Q98" s="35"/>
     </row>
     <row r="99" spans="1:17">
       <c r="A99" s="28">
-        <v>59</v>
-      </c>
-      <c r="B99" s="21">
         <v>58</v>
       </c>
+      <c r="B99" s="21"/>
       <c r="C99" s="28">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="21" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F99" s="33" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="G99" s="28">
         <v>57</v>
@@ -10072,36 +10055,36 @@
         <v>1</v>
       </c>
       <c r="J99" s="34" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="K99" s="34" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L99" s="34"/>
       <c r="M99" s="34"/>
       <c r="N99" s="34"/>
       <c r="O99" s="2"/>
       <c r="P99" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="Q99" s="35"/>
     </row>
     <row r="100" spans="1:17">
       <c r="A100" s="28">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B100" s="21">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C100" s="28">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F100" s="33" t="s">
-        <v>143</v>
+        <v>5</v>
       </c>
       <c r="G100" s="28">
         <v>57</v>
@@ -10113,36 +10096,36 @@
         <v>1</v>
       </c>
       <c r="J100" s="34" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K100" s="34" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L100" s="34"/>
       <c r="M100" s="34"/>
       <c r="N100" s="34"/>
       <c r="O100" s="2"/>
       <c r="P100" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="Q100" s="35"/>
     </row>
     <row r="101" spans="1:17">
       <c r="A101" s="28">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B101" s="21">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C101" s="28">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="21" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F101" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G101" s="28">
         <v>57</v>
@@ -10154,36 +10137,36 @@
         <v>1</v>
       </c>
       <c r="J101" s="34" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="K101" s="34" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="L101" s="34"/>
       <c r="M101" s="34"/>
       <c r="N101" s="34"/>
       <c r="O101" s="2"/>
       <c r="P101" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q101" s="42"/>
+        <v>404</v>
+      </c>
+      <c r="Q101" s="35"/>
     </row>
     <row r="102" spans="1:17">
       <c r="A102" s="28">
-        <v>205</v>
+        <v>61</v>
       </c>
       <c r="B102" s="21">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C102" s="28">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D102" s="21"/>
-      <c r="E102" s="88" t="s">
-        <v>641</v>
+      <c r="E102" s="21" t="s">
+        <v>405</v>
       </c>
       <c r="F102" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G102" s="28">
         <v>57</v>
@@ -10195,93 +10178,97 @@
         <v>1</v>
       </c>
       <c r="J102" s="34" t="s">
-        <v>409</v>
-      </c>
-      <c r="K102" s="34"/>
+        <v>406</v>
+      </c>
+      <c r="K102" s="34" t="s">
+        <v>407</v>
+      </c>
       <c r="L102" s="34"/>
       <c r="M102" s="34"/>
       <c r="N102" s="34"/>
       <c r="O102" s="2"/>
       <c r="P102" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q102" s="42"/>
+    </row>
+    <row r="103" spans="1:17">
+      <c r="A103" s="28">
+        <v>205</v>
+      </c>
+      <c r="B103" s="21">
+        <v>61</v>
+      </c>
+      <c r="C103" s="28">
+        <v>92</v>
+      </c>
+      <c r="D103" s="21"/>
+      <c r="E103" s="88" t="s">
+        <v>640</v>
+      </c>
+      <c r="F103" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="G103" s="28">
+        <v>57</v>
+      </c>
+      <c r="H103" s="28">
+        <v>1</v>
+      </c>
+      <c r="I103" s="28">
+        <v>1</v>
+      </c>
+      <c r="J103" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="K103" s="34"/>
+      <c r="L103" s="34"/>
+      <c r="M103" s="34"/>
+      <c r="N103" s="34"/>
+      <c r="O103" s="2"/>
+      <c r="P103" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="Q102" s="42"/>
-    </row>
-    <row r="103" spans="1:17">
-      <c r="A103" s="36">
-        <v>62</v>
-      </c>
-      <c r="B103" s="3">
-        <v>57</v>
-      </c>
-      <c r="C103" s="36"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G103" s="36">
-        <v>43</v>
-      </c>
-      <c r="H103" s="36">
-        <v>3</v>
-      </c>
-      <c r="I103" s="36"/>
-      <c r="J103" s="40"/>
-      <c r="K103" s="40"/>
-      <c r="L103" s="40"/>
-      <c r="M103" s="40"/>
-      <c r="N103" s="40"/>
-      <c r="O103" s="1"/>
-      <c r="P103" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q103" s="35"/>
+      <c r="Q103" s="42"/>
     </row>
     <row r="104" spans="1:17">
       <c r="A104" s="36">
-        <v>63</v>
-      </c>
-      <c r="B104" s="3"/>
-      <c r="C104" s="36">
-        <v>93</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B104" s="3">
+        <v>57</v>
+      </c>
+      <c r="C104" s="36"/>
       <c r="D104" s="3"/>
-      <c r="E104" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F104" s="41" t="s">
-        <v>103</v>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="G104" s="36">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="H104" s="36">
         <v>3</v>
       </c>
-      <c r="I104" s="36">
-        <v>1</v>
-      </c>
-      <c r="J104" s="40" t="s">
-        <v>413</v>
-      </c>
-      <c r="K104" s="40" t="s">
-        <v>414</v>
-      </c>
+      <c r="I104" s="36"/>
+      <c r="J104" s="40"/>
+      <c r="K104" s="40"/>
       <c r="L104" s="40"/>
       <c r="M104" s="40"/>
       <c r="N104" s="40"/>
       <c r="O104" s="1"/>
       <c r="P104" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="Q104" s="35"/>
     </row>
     <row r="105" spans="1:17">
-      <c r="A105" s="36"/>
+      <c r="A105" s="36">
+        <v>63</v>
+      </c>
       <c r="B105" s="3"/>
       <c r="C105" s="36">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="3" t="s">
@@ -10290,13 +10277,21 @@
       <c r="F105" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="G105" s="36"/>
-      <c r="H105" s="36"/>
+      <c r="G105" s="36">
+        <v>62</v>
+      </c>
+      <c r="H105" s="36">
+        <v>3</v>
+      </c>
       <c r="I105" s="36">
-        <v>2</v>
-      </c>
-      <c r="J105" s="40"/>
-      <c r="K105" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J105" s="40" t="s">
+        <v>413</v>
+      </c>
+      <c r="K105" s="40" t="s">
+        <v>414</v>
+      </c>
       <c r="L105" s="40"/>
       <c r="M105" s="40"/>
       <c r="N105" s="40"/>
@@ -10310,7 +10305,7 @@
       <c r="A106" s="36"/>
       <c r="B106" s="3"/>
       <c r="C106" s="36">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="3" t="s">
@@ -10322,7 +10317,7 @@
       <c r="G106" s="36"/>
       <c r="H106" s="36"/>
       <c r="I106" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J106" s="40"/>
       <c r="K106" s="40"/>
@@ -10336,51 +10331,43 @@
       <c r="Q106" s="35"/>
     </row>
     <row r="107" spans="1:17">
-      <c r="A107" s="36">
-        <v>64</v>
-      </c>
-      <c r="B107" s="3">
-        <v>63</v>
-      </c>
+      <c r="A107" s="36"/>
+      <c r="B107" s="3"/>
       <c r="C107" s="36">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F107" s="41" t="s">
-        <v>147</v>
-      </c>
-      <c r="G107" s="36">
-        <v>62</v>
-      </c>
-      <c r="H107" s="36">
-        <v>2</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G107" s="36"/>
+      <c r="H107" s="36"/>
       <c r="I107" s="36">
-        <v>1</v>
-      </c>
-      <c r="J107" s="40" t="s">
-        <v>417</v>
-      </c>
-      <c r="K107" s="40" t="s">
-        <v>418</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J107" s="40"/>
+      <c r="K107" s="40"/>
       <c r="L107" s="40"/>
       <c r="M107" s="40"/>
       <c r="N107" s="40"/>
       <c r="O107" s="1"/>
       <c r="P107" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="Q107" s="35"/>
     </row>
     <row r="108" spans="1:17">
-      <c r="A108" s="36"/>
-      <c r="B108" s="3"/>
+      <c r="A108" s="36">
+        <v>64</v>
+      </c>
+      <c r="B108" s="3">
+        <v>63</v>
+      </c>
       <c r="C108" s="36">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3" t="s">
@@ -10389,13 +10376,21 @@
       <c r="F108" s="41" t="s">
         <v>147</v>
       </c>
-      <c r="G108" s="36"/>
-      <c r="H108" s="36"/>
+      <c r="G108" s="36">
+        <v>62</v>
+      </c>
+      <c r="H108" s="36">
+        <v>2</v>
+      </c>
       <c r="I108" s="36">
-        <v>2</v>
-      </c>
-      <c r="J108" s="40"/>
-      <c r="K108" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J108" s="40" t="s">
+        <v>417</v>
+      </c>
+      <c r="K108" s="40" t="s">
+        <v>418</v>
+      </c>
       <c r="L108" s="40"/>
       <c r="M108" s="40"/>
       <c r="N108" s="40"/>
@@ -10406,70 +10401,68 @@
       <c r="Q108" s="35"/>
     </row>
     <row r="109" spans="1:17">
-      <c r="A109" s="36">
-        <v>65</v>
-      </c>
-      <c r="B109" s="3">
-        <v>63</v>
-      </c>
+      <c r="A109" s="36"/>
+      <c r="B109" s="3"/>
       <c r="C109" s="36">
-        <v>98</v>
-      </c>
-      <c r="D109" s="3">
-        <v>63</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D109" s="3"/>
       <c r="E109" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F109" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G109" s="36">
-        <v>62</v>
-      </c>
-      <c r="H109" s="36">
+        <v>147</v>
+      </c>
+      <c r="G109" s="36"/>
+      <c r="H109" s="36"/>
+      <c r="I109" s="36">
         <v>2</v>
       </c>
-      <c r="I109" s="36">
-        <v>1</v>
-      </c>
-      <c r="J109" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="K109" s="40" t="s">
-        <v>422</v>
-      </c>
+      <c r="J109" s="40"/>
+      <c r="K109" s="40"/>
       <c r="L109" s="40"/>
       <c r="M109" s="40"/>
       <c r="N109" s="40"/>
       <c r="O109" s="1"/>
       <c r="P109" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="Q109" s="35"/>
     </row>
     <row r="110" spans="1:17">
-      <c r="A110" s="36"/>
-      <c r="B110" s="3"/>
+      <c r="A110" s="36">
+        <v>65</v>
+      </c>
+      <c r="B110" s="3">
+        <v>63</v>
+      </c>
       <c r="C110" s="36">
-        <v>99</v>
-      </c>
-      <c r="D110" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="D110" s="3">
+        <v>63</v>
+      </c>
       <c r="E110" s="3" t="s">
         <v>420</v>
       </c>
       <c r="F110" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G110" s="36"/>
+      <c r="G110" s="36">
+        <v>62</v>
+      </c>
       <c r="H110" s="36">
         <v>2</v>
       </c>
       <c r="I110" s="36">
-        <v>2</v>
-      </c>
-      <c r="J110" s="40"/>
-      <c r="K110" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J110" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="K110" s="40" t="s">
+        <v>422</v>
+      </c>
       <c r="L110" s="40"/>
       <c r="M110" s="40"/>
       <c r="N110" s="40"/>
@@ -10480,88 +10473,82 @@
       <c r="Q110" s="35"/>
     </row>
     <row r="111" spans="1:17">
-      <c r="A111" s="36">
-        <v>66</v>
-      </c>
+      <c r="A111" s="36"/>
       <c r="B111" s="3"/>
       <c r="C111" s="36">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="F111" s="49" t="s">
-        <v>251</v>
-      </c>
-      <c r="G111" s="36">
-        <v>65</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="F111" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="G111" s="36"/>
       <c r="H111" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I111" s="36">
-        <v>1</v>
-      </c>
-      <c r="J111" s="40" t="s">
-        <v>425</v>
-      </c>
-      <c r="K111" s="40" t="s">
-        <v>426</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J111" s="40"/>
+      <c r="K111" s="40"/>
       <c r="L111" s="40"/>
       <c r="M111" s="40"/>
       <c r="N111" s="40"/>
       <c r="O111" s="1"/>
       <c r="P111" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="Q111" s="35"/>
     </row>
     <row r="112" spans="1:17">
       <c r="A112" s="36">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="36">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F112" s="49" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G112" s="36">
         <v>65</v>
       </c>
       <c r="H112" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I112" s="36">
         <v>1</v>
       </c>
       <c r="J112" s="40" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="K112" s="40" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L112" s="40"/>
       <c r="M112" s="40"/>
       <c r="N112" s="40"/>
       <c r="O112" s="1"/>
       <c r="P112" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="Q112" s="35"/>
     </row>
     <row r="113" spans="1:17">
-      <c r="A113" s="36"/>
+      <c r="A113" s="36">
+        <v>67</v>
+      </c>
       <c r="B113" s="3"/>
       <c r="C113" s="36">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="3" t="s">
@@ -10571,148 +10558,146 @@
         <v>256</v>
       </c>
       <c r="G113" s="36">
-        <v>67</v>
-      </c>
-      <c r="H113" s="36"/>
+        <v>65</v>
+      </c>
+      <c r="H113" s="36">
+        <v>3</v>
+      </c>
       <c r="I113" s="36">
-        <v>3</v>
-      </c>
-      <c r="J113" s="40"/>
-      <c r="K113" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J113" s="40" t="s">
+        <v>429</v>
+      </c>
+      <c r="K113" s="40" t="s">
+        <v>430</v>
+      </c>
       <c r="L113" s="40"/>
       <c r="M113" s="40"/>
       <c r="N113" s="40"/>
       <c r="O113" s="1"/>
-      <c r="P113" s="1"/>
+      <c r="P113" s="1" t="s">
+        <v>431</v>
+      </c>
       <c r="Q113" s="35"/>
     </row>
     <row r="114" spans="1:17">
       <c r="A114" s="36"/>
       <c r="B114" s="3"/>
       <c r="C114" s="36">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F114" s="49" t="s">
-        <v>433</v>
+        <v>256</v>
       </c>
       <c r="G114" s="36">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H114" s="36"/>
       <c r="I114" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J114" s="40"/>
-      <c r="K114" s="40" t="s">
-        <v>434</v>
-      </c>
-      <c r="L114" s="40" t="s">
-        <v>435</v>
-      </c>
+      <c r="K114" s="40"/>
+      <c r="L114" s="40"/>
       <c r="M114" s="40"/>
       <c r="N114" s="40"/>
       <c r="O114" s="1"/>
-      <c r="P114" s="1" t="s">
+      <c r="P114" s="1"/>
+      <c r="Q114" s="35"/>
+    </row>
+    <row r="115" spans="1:17">
+      <c r="A115" s="36"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="36">
+        <v>102</v>
+      </c>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F115" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="G115" s="36">
+        <v>65</v>
+      </c>
+      <c r="H115" s="36"/>
+      <c r="I115" s="36">
+        <v>1</v>
+      </c>
+      <c r="J115" s="40"/>
+      <c r="K115" s="40" t="s">
+        <v>434</v>
+      </c>
+      <c r="L115" s="40" t="s">
+        <v>435</v>
+      </c>
+      <c r="M115" s="40"/>
+      <c r="N115" s="40"/>
+      <c r="O115" s="1"/>
+      <c r="P115" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="Q114" s="42"/>
-    </row>
-    <row r="115" spans="1:17">
-      <c r="A115" s="28">
-        <v>68</v>
-      </c>
-      <c r="B115" s="21">
-        <v>204</v>
-      </c>
-      <c r="C115" s="28"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21"/>
-      <c r="F115" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="G115" s="45">
-        <v>43</v>
-      </c>
-      <c r="H115" s="28">
-        <v>3</v>
-      </c>
-      <c r="I115" s="28"/>
-      <c r="J115" s="34"/>
-      <c r="K115" s="34"/>
-      <c r="L115" s="34"/>
-      <c r="M115" s="34"/>
-      <c r="N115" s="34"/>
-      <c r="O115" s="2"/>
-      <c r="P115" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="Q115" s="42"/>
     </row>
     <row r="116" spans="1:17">
       <c r="A116" s="28">
-        <v>203</v>
-      </c>
-      <c r="B116" s="21"/>
+        <v>68</v>
+      </c>
+      <c r="B116" s="21">
+        <v>204</v>
+      </c>
       <c r="C116" s="28"/>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
-      <c r="F116" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="G116" s="28">
-        <v>68</v>
+      <c r="F116" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G116" s="45">
+        <v>43</v>
       </c>
       <c r="H116" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I116" s="28"/>
-      <c r="J116" s="81"/>
-      <c r="K116" s="81"/>
-      <c r="L116" s="81"/>
-      <c r="M116" s="81"/>
+      <c r="J116" s="34"/>
+      <c r="K116" s="34"/>
+      <c r="L116" s="34"/>
+      <c r="M116" s="34"/>
       <c r="N116" s="34"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="Q116" s="42"/>
     </row>
     <row r="117" spans="1:17">
       <c r="A117" s="28">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="B117" s="21"/>
-      <c r="C117" s="28">
-        <v>80</v>
-      </c>
+      <c r="C117" s="28"/>
       <c r="D117" s="21"/>
-      <c r="E117" s="88" t="s">
-        <v>640</v>
-      </c>
+      <c r="E117" s="21"/>
       <c r="F117" s="33" t="s">
         <v>93</v>
       </c>
       <c r="G117" s="28">
-        <v>203</v>
+        <v>68</v>
       </c>
       <c r="H117" s="28">
         <v>1</v>
       </c>
-      <c r="I117" s="28">
-        <v>1</v>
-      </c>
-      <c r="J117" s="34" t="s">
-        <v>374</v>
-      </c>
-      <c r="K117" s="34"/>
-      <c r="L117" s="34"/>
-      <c r="M117" s="34" t="s">
-        <v>375</v>
-      </c>
+      <c r="I117" s="28"/>
+      <c r="J117" s="81"/>
+      <c r="K117" s="81"/>
+      <c r="L117" s="81"/>
+      <c r="M117" s="81"/>
       <c r="N117" s="34"/>
       <c r="O117" s="2"/>
       <c r="P117" s="2" t="s">
@@ -10722,62 +10707,72 @@
     </row>
     <row r="118" spans="1:17">
       <c r="A118" s="28">
-        <v>52</v>
-      </c>
-      <c r="B118" s="21">
         <v>51</v>
       </c>
+      <c r="B118" s="21"/>
       <c r="C118" s="28">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="88" t="s">
-        <v>654</v>
-      </c>
-      <c r="F118" s="46" t="s">
-        <v>377</v>
+        <v>639</v>
+      </c>
+      <c r="F118" s="33" t="s">
+        <v>93</v>
       </c>
       <c r="G118" s="28">
         <v>203</v>
       </c>
       <c r="H118" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I118" s="28">
         <v>1</v>
       </c>
       <c r="J118" s="34" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K118" s="34"/>
       <c r="L118" s="34"/>
-      <c r="M118" s="34"/>
+      <c r="M118" s="34" t="s">
+        <v>375</v>
+      </c>
       <c r="N118" s="34"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Q118" s="42"/>
     </row>
     <row r="119" spans="1:17">
-      <c r="A119" s="28"/>
-      <c r="B119" s="21"/>
+      <c r="A119" s="28">
+        <v>52</v>
+      </c>
+      <c r="B119" s="21">
+        <v>51</v>
+      </c>
       <c r="C119" s="28">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D119" s="21"/>
       <c r="E119" s="88" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F119" s="46" t="s">
         <v>377</v>
       </c>
-      <c r="G119" s="28"/>
-      <c r="H119" s="28"/>
+      <c r="G119" s="28">
+        <v>203</v>
+      </c>
+      <c r="H119" s="28">
+        <v>3</v>
+      </c>
       <c r="I119" s="28">
-        <v>2</v>
-      </c>
-      <c r="J119" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J119" s="34" t="s">
+        <v>378</v>
+      </c>
       <c r="K119" s="34"/>
       <c r="L119" s="34"/>
       <c r="M119" s="34"/>
@@ -10792,11 +10787,11 @@
       <c r="A120" s="28"/>
       <c r="B120" s="21"/>
       <c r="C120" s="28">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D120" s="21"/>
       <c r="E120" s="88" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F120" s="46" t="s">
         <v>377</v>
@@ -10804,7 +10799,7 @@
       <c r="G120" s="28"/>
       <c r="H120" s="28"/>
       <c r="I120" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J120" s="34"/>
       <c r="K120" s="34"/>
@@ -10818,100 +10813,92 @@
       <c r="Q120" s="42"/>
     </row>
     <row r="121" spans="1:17">
-      <c r="A121" s="28">
-        <v>53</v>
-      </c>
-      <c r="B121" s="21">
-        <v>51</v>
-      </c>
+      <c r="A121" s="28"/>
+      <c r="B121" s="21"/>
       <c r="C121" s="28">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D121" s="21"/>
       <c r="E121" s="88" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F121" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="G121" s="28">
-        <v>203</v>
-      </c>
-      <c r="H121" s="28">
+        <v>377</v>
+      </c>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="28">
         <v>3</v>
       </c>
-      <c r="I121" s="28">
-        <v>1</v>
-      </c>
-      <c r="J121" s="34" t="s">
-        <v>380</v>
-      </c>
+      <c r="J121" s="34"/>
       <c r="K121" s="34"/>
       <c r="L121" s="34"/>
       <c r="M121" s="34"/>
       <c r="N121" s="34"/>
       <c r="O121" s="2"/>
       <c r="P121" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q121" s="35"/>
+        <v>379</v>
+      </c>
+      <c r="Q121" s="42"/>
     </row>
     <row r="122" spans="1:17">
       <c r="A122" s="28">
-        <v>213</v>
-      </c>
-      <c r="B122" s="21"/>
-      <c r="C122" s="28"/>
+        <v>53</v>
+      </c>
+      <c r="B122" s="21">
+        <v>51</v>
+      </c>
+      <c r="C122" s="28">
+        <v>84</v>
+      </c>
       <c r="D122" s="21"/>
-      <c r="E122" s="88"/>
-      <c r="F122" s="92" t="s">
-        <v>150</v>
+      <c r="E122" s="88" t="s">
+        <v>654</v>
+      </c>
+      <c r="F122" s="46" t="s">
+        <v>160</v>
       </c>
       <c r="G122" s="28">
-        <v>68</v>
+        <v>203</v>
       </c>
       <c r="H122" s="28">
         <v>3</v>
       </c>
-      <c r="I122" s="28"/>
-      <c r="J122" s="34"/>
+      <c r="I122" s="28">
+        <v>1</v>
+      </c>
+      <c r="J122" s="34" t="s">
+        <v>380</v>
+      </c>
       <c r="K122" s="34"/>
       <c r="L122" s="34"/>
       <c r="M122" s="34"/>
       <c r="N122" s="34"/>
       <c r="O122" s="2"/>
       <c r="P122" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q122" s="42"/>
+        <v>381</v>
+      </c>
+      <c r="Q122" s="35"/>
     </row>
     <row r="123" spans="1:17">
       <c r="A123" s="28">
-        <v>69</v>
+        <v>213</v>
       </c>
       <c r="B123" s="21"/>
-      <c r="C123" s="28">
-        <v>103</v>
-      </c>
+      <c r="C123" s="28"/>
       <c r="D123" s="21"/>
-      <c r="E123" s="88" t="s">
-        <v>438</v>
-      </c>
-      <c r="F123" s="33" t="s">
+      <c r="E123" s="88"/>
+      <c r="F123" s="92" t="s">
         <v>150</v>
       </c>
       <c r="G123" s="28">
-        <v>213</v>
+        <v>68</v>
       </c>
       <c r="H123" s="28">
         <v>3</v>
       </c>
-      <c r="I123" s="28">
-        <v>1</v>
-      </c>
-      <c r="J123" s="34" t="s">
-        <v>439</v>
-      </c>
+      <c r="I123" s="28"/>
+      <c r="J123" s="34"/>
       <c r="K123" s="34"/>
       <c r="L123" s="34"/>
       <c r="M123" s="34"/>
@@ -10923,24 +10910,32 @@
       <c r="Q123" s="42"/>
     </row>
     <row r="124" spans="1:17">
-      <c r="A124" s="28"/>
+      <c r="A124" s="28">
+        <v>69</v>
+      </c>
       <c r="B124" s="21"/>
       <c r="C124" s="28">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D124" s="21"/>
-      <c r="E124" s="21" t="s">
+      <c r="E124" s="88" t="s">
         <v>438</v>
       </c>
       <c r="F124" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="G124" s="28"/>
-      <c r="H124" s="28"/>
+      <c r="G124" s="28">
+        <v>213</v>
+      </c>
+      <c r="H124" s="28">
+        <v>3</v>
+      </c>
       <c r="I124" s="28">
-        <v>2</v>
-      </c>
-      <c r="J124" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J124" s="34" t="s">
+        <v>439</v>
+      </c>
       <c r="K124" s="34"/>
       <c r="L124" s="34"/>
       <c r="M124" s="34"/>
@@ -10955,7 +10950,7 @@
       <c r="A125" s="28"/>
       <c r="B125" s="21"/>
       <c r="C125" s="28">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D125" s="21"/>
       <c r="E125" s="21" t="s">
@@ -10967,7 +10962,7 @@
       <c r="G125" s="28"/>
       <c r="H125" s="28"/>
       <c r="I125" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J125" s="34"/>
       <c r="K125" s="34"/>
@@ -10981,63 +10976,63 @@
       <c r="Q125" s="42"/>
     </row>
     <row r="126" spans="1:17">
-      <c r="A126" s="28">
-        <v>70</v>
-      </c>
-      <c r="B126" s="21">
-        <v>69</v>
-      </c>
+      <c r="A126" s="28"/>
+      <c r="B126" s="21"/>
       <c r="C126" s="28">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D126" s="21"/>
       <c r="E126" s="21" t="s">
-        <v>441</v>
-      </c>
-      <c r="F126" s="92" t="s">
-        <v>660</v>
-      </c>
-      <c r="G126" s="28">
-        <v>213</v>
-      </c>
-      <c r="H126" s="28">
+        <v>438</v>
+      </c>
+      <c r="F126" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G126" s="28"/>
+      <c r="H126" s="28"/>
+      <c r="I126" s="28">
         <v>3</v>
       </c>
-      <c r="I126" s="28">
-        <v>1</v>
-      </c>
-      <c r="J126" s="34" t="s">
-        <v>442</v>
-      </c>
+      <c r="J126" s="34"/>
       <c r="K126" s="34"/>
       <c r="L126" s="34"/>
       <c r="M126" s="34"/>
       <c r="N126" s="34"/>
       <c r="O126" s="2"/>
       <c r="P126" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q126" s="35"/>
+        <v>440</v>
+      </c>
+      <c r="Q126" s="42"/>
     </row>
     <row r="127" spans="1:17">
-      <c r="A127" s="28"/>
-      <c r="B127" s="21"/>
+      <c r="A127" s="28">
+        <v>70</v>
+      </c>
+      <c r="B127" s="21">
+        <v>69</v>
+      </c>
       <c r="C127" s="28">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D127" s="21"/>
       <c r="E127" s="21" t="s">
         <v>441</v>
       </c>
       <c r="F127" s="92" t="s">
-        <v>660</v>
-      </c>
-      <c r="G127" s="28"/>
-      <c r="H127" s="28"/>
+        <v>659</v>
+      </c>
+      <c r="G127" s="28">
+        <v>213</v>
+      </c>
+      <c r="H127" s="28">
+        <v>3</v>
+      </c>
       <c r="I127" s="28">
-        <v>2</v>
-      </c>
-      <c r="J127" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J127" s="34" t="s">
+        <v>442</v>
+      </c>
       <c r="K127" s="34"/>
       <c r="L127" s="34"/>
       <c r="M127" s="34"/>
@@ -11052,19 +11047,19 @@
       <c r="A128" s="28"/>
       <c r="B128" s="21"/>
       <c r="C128" s="28">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D128" s="21"/>
       <c r="E128" s="21" t="s">
         <v>441</v>
       </c>
       <c r="F128" s="92" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G128" s="28"/>
       <c r="H128" s="28"/>
       <c r="I128" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J128" s="34"/>
       <c r="K128" s="34"/>
@@ -11078,76 +11073,71 @@
       <c r="Q128" s="35"/>
     </row>
     <row r="129" spans="1:17">
-      <c r="A129" s="36">
-        <v>72</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="C129" s="36"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="G129" s="36">
-        <v>43</v>
-      </c>
-      <c r="H129" s="36">
+      <c r="A129" s="28"/>
+      <c r="B129" s="21"/>
+      <c r="C129" s="28">
+        <v>108</v>
+      </c>
+      <c r="D129" s="21"/>
+      <c r="E129" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="F129" s="92" t="s">
+        <v>659</v>
+      </c>
+      <c r="G129" s="28"/>
+      <c r="H129" s="28"/>
+      <c r="I129" s="28">
         <v>3</v>
       </c>
-      <c r="I129" s="36"/>
-      <c r="J129" s="40"/>
-      <c r="K129" s="40"/>
-      <c r="L129" s="40"/>
-      <c r="M129" s="40"/>
-      <c r="N129" s="40"/>
-      <c r="O129" s="1"/>
-      <c r="P129" s="1" t="s">
-        <v>448</v>
-      </c>
+      <c r="J129" s="34"/>
+      <c r="K129" s="34"/>
+      <c r="L129" s="34"/>
+      <c r="M129" s="34"/>
+      <c r="N129" s="34"/>
+      <c r="O129" s="2"/>
+      <c r="P129" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q129" s="35"/>
     </row>
     <row r="130" spans="1:17">
       <c r="A130" s="36">
-        <v>73</v>
-      </c>
-      <c r="B130" s="3"/>
-      <c r="C130" s="36">
-        <v>110</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C130" s="36"/>
       <c r="D130" s="3"/>
-      <c r="E130" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="F130" s="41" t="s">
-        <v>596</v>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3" t="s">
+        <v>604</v>
       </c>
       <c r="G130" s="36">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="H130" s="36">
-        <v>2</v>
-      </c>
-      <c r="I130" s="36">
-        <v>1</v>
-      </c>
-      <c r="J130" s="40" t="s">
-        <v>450</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I130" s="36"/>
+      <c r="J130" s="40"/>
       <c r="K130" s="40"/>
       <c r="L130" s="40"/>
       <c r="M130" s="40"/>
       <c r="N130" s="40"/>
       <c r="O130" s="1"/>
       <c r="P130" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="131" spans="1:17">
-      <c r="A131" s="36"/>
+      <c r="A131" s="36">
+        <v>73</v>
+      </c>
       <c r="B131" s="3"/>
       <c r="C131" s="36">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3" t="s">
@@ -11156,12 +11146,18 @@
       <c r="F131" s="41" t="s">
         <v>596</v>
       </c>
-      <c r="G131" s="36"/>
-      <c r="H131" s="36"/>
+      <c r="G131" s="36">
+        <v>72</v>
+      </c>
+      <c r="H131" s="36">
+        <v>2</v>
+      </c>
       <c r="I131" s="36">
-        <v>2</v>
-      </c>
-      <c r="J131" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J131" s="40" t="s">
+        <v>450</v>
+      </c>
       <c r="K131" s="40"/>
       <c r="L131" s="40"/>
       <c r="M131" s="40"/>
@@ -11172,48 +11168,42 @@
       </c>
     </row>
     <row r="132" spans="1:17">
-      <c r="A132" s="36">
-        <v>75</v>
-      </c>
-      <c r="B132" s="3">
-        <v>73</v>
-      </c>
+      <c r="A132" s="36"/>
+      <c r="B132" s="3"/>
       <c r="C132" s="36">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F132" s="41" t="s">
-        <v>598</v>
-      </c>
-      <c r="G132" s="36">
-        <v>72</v>
-      </c>
-      <c r="H132" s="36">
-        <v>3</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="G132" s="36"/>
+      <c r="H132" s="36"/>
       <c r="I132" s="36">
-        <v>1</v>
-      </c>
-      <c r="J132" s="40" t="s">
-        <v>453</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J132" s="40"/>
       <c r="K132" s="40"/>
       <c r="L132" s="40"/>
       <c r="M132" s="40"/>
       <c r="N132" s="40"/>
       <c r="O132" s="1"/>
       <c r="P132" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="133" spans="1:17">
-      <c r="A133" s="36"/>
-      <c r="B133" s="3"/>
+      <c r="A133" s="36">
+        <v>75</v>
+      </c>
+      <c r="B133" s="3">
+        <v>73</v>
+      </c>
       <c r="C133" s="36">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="3" t="s">
@@ -11222,12 +11212,18 @@
       <c r="F133" s="41" t="s">
         <v>598</v>
       </c>
-      <c r="G133" s="36"/>
-      <c r="H133" s="36"/>
+      <c r="G133" s="36">
+        <v>72</v>
+      </c>
+      <c r="H133" s="36">
+        <v>3</v>
+      </c>
       <c r="I133" s="36">
-        <v>2</v>
-      </c>
-      <c r="J133" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J133" s="40" t="s">
+        <v>453</v>
+      </c>
       <c r="K133" s="40"/>
       <c r="L133" s="40"/>
       <c r="M133" s="40"/>
@@ -11241,7 +11237,7 @@
       <c r="A134" s="36"/>
       <c r="B134" s="3"/>
       <c r="C134" s="36">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="3" t="s">
@@ -11253,7 +11249,7 @@
       <c r="G134" s="36"/>
       <c r="H134" s="36"/>
       <c r="I134" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J134" s="40"/>
       <c r="K134" s="40"/>
@@ -11266,73 +11262,63 @@
       </c>
     </row>
     <row r="135" spans="1:17">
-      <c r="A135" s="36">
-        <v>76</v>
-      </c>
-      <c r="B135" s="3">
-        <v>75</v>
-      </c>
+      <c r="A135" s="36"/>
+      <c r="B135" s="3"/>
       <c r="C135" s="36">
-        <v>115</v>
-      </c>
-      <c r="D135" s="3">
-        <v>75</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="D135" s="3"/>
       <c r="E135" s="3" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F135" s="41" t="s">
-        <v>599</v>
-      </c>
-      <c r="G135" s="36">
-        <v>72</v>
-      </c>
-      <c r="H135" s="36">
-        <v>1</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="G135" s="36"/>
+      <c r="H135" s="36"/>
       <c r="I135" s="36">
-        <v>1</v>
-      </c>
-      <c r="J135" s="40" t="s">
-        <v>456</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J135" s="40"/>
       <c r="K135" s="40"/>
       <c r="L135" s="40"/>
       <c r="M135" s="40"/>
       <c r="N135" s="40"/>
       <c r="O135" s="1"/>
       <c r="P135" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136" spans="1:17">
       <c r="A136" s="36">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B136" s="3">
         <v>75</v>
       </c>
       <c r="C136" s="36">
-        <v>116</v>
-      </c>
-      <c r="D136" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="D136" s="3">
+        <v>75</v>
+      </c>
       <c r="E136" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="F136" s="49" t="s">
-        <v>458</v>
+        <v>455</v>
+      </c>
+      <c r="F136" s="41" t="s">
+        <v>599</v>
       </c>
       <c r="G136" s="36">
         <v>72</v>
       </c>
       <c r="H136" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I136" s="36">
         <v>1</v>
       </c>
       <c r="J136" s="40" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="K136" s="40"/>
       <c r="L136" s="40"/>
@@ -11340,15 +11326,18 @@
       <c r="N136" s="40"/>
       <c r="O136" s="1"/>
       <c r="P136" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q136" s="35"/>
+        <v>457</v>
+      </c>
     </row>
     <row r="137" spans="1:17">
-      <c r="A137" s="36"/>
-      <c r="B137" s="3"/>
+      <c r="A137" s="36">
+        <v>78</v>
+      </c>
+      <c r="B137" s="3">
+        <v>75</v>
+      </c>
       <c r="C137" s="36">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="3" t="s">
@@ -11357,12 +11346,18 @@
       <c r="F137" s="49" t="s">
         <v>458</v>
       </c>
-      <c r="G137" s="36"/>
-      <c r="H137" s="36"/>
+      <c r="G137" s="36">
+        <v>72</v>
+      </c>
+      <c r="H137" s="36">
+        <v>3</v>
+      </c>
       <c r="I137" s="36">
-        <v>2</v>
-      </c>
-      <c r="J137" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J137" s="40" t="s">
+        <v>459</v>
+      </c>
       <c r="K137" s="40"/>
       <c r="L137" s="40"/>
       <c r="M137" s="40"/>
@@ -11377,7 +11372,7 @@
       <c r="A138" s="36"/>
       <c r="B138" s="3"/>
       <c r="C138" s="36">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="3" t="s">
@@ -11389,7 +11384,7 @@
       <c r="G138" s="36"/>
       <c r="H138" s="36"/>
       <c r="I138" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J138" s="40"/>
       <c r="K138" s="40"/>
@@ -11403,136 +11398,124 @@
       <c r="Q138" s="35"/>
     </row>
     <row r="139" spans="1:17">
-      <c r="A139" s="36">
-        <v>79</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>603</v>
-      </c>
+      <c r="A139" s="36"/>
+      <c r="B139" s="3"/>
       <c r="C139" s="36">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F139" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="G139" s="36">
-        <v>72</v>
-      </c>
-      <c r="H139" s="36">
-        <v>1</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="G139" s="36"/>
+      <c r="H139" s="36"/>
       <c r="I139" s="36">
-        <v>1</v>
-      </c>
-      <c r="J139" s="40" t="s">
-        <v>462</v>
-      </c>
-      <c r="K139" s="40" t="s">
-        <v>463</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J139" s="40"/>
+      <c r="K139" s="40"/>
       <c r="L139" s="40"/>
-      <c r="M139" s="40" t="s">
-        <v>464</v>
-      </c>
+      <c r="M139" s="40"/>
       <c r="N139" s="40"/>
       <c r="O139" s="1"/>
       <c r="P139" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q139" s="35"/>
+    </row>
+    <row r="140" spans="1:17">
+      <c r="A140" s="36">
+        <v>79</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C140" s="36">
+        <v>119</v>
+      </c>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="F140" s="49" t="s">
+        <v>461</v>
+      </c>
+      <c r="G140" s="36">
+        <v>72</v>
+      </c>
+      <c r="H140" s="36">
+        <v>1</v>
+      </c>
+      <c r="I140" s="36">
+        <v>1</v>
+      </c>
+      <c r="J140" s="40" t="s">
+        <v>462</v>
+      </c>
+      <c r="K140" s="40" t="s">
+        <v>463</v>
+      </c>
+      <c r="L140" s="40"/>
+      <c r="M140" s="40" t="s">
+        <v>464</v>
+      </c>
+      <c r="N140" s="40"/>
+      <c r="O140" s="1"/>
+      <c r="P140" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="Q139" s="42"/>
-    </row>
-    <row r="140" spans="1:17">
-      <c r="A140" s="28">
-        <v>80</v>
-      </c>
-      <c r="B140" s="21">
-        <v>78</v>
-      </c>
-      <c r="C140" s="28"/>
-      <c r="D140" s="21"/>
-      <c r="E140" s="21" t="s">
-        <v>466</v>
-      </c>
-      <c r="F140" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="G140" s="28">
-        <v>72</v>
-      </c>
-      <c r="H140" s="28">
-        <v>3</v>
-      </c>
-      <c r="I140" s="28"/>
-      <c r="J140" s="34"/>
-      <c r="K140" s="34"/>
-      <c r="L140" s="34"/>
-      <c r="M140" s="34"/>
-      <c r="N140" s="34"/>
-      <c r="O140" s="2"/>
-      <c r="P140" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q140" s="35"/>
+      <c r="Q140" s="42"/>
     </row>
     <row r="141" spans="1:17">
       <c r="A141" s="28">
-        <v>81</v>
-      </c>
-      <c r="B141" s="21"/>
-      <c r="C141" s="28">
-        <v>120</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="B141" s="21">
+        <v>78</v>
+      </c>
+      <c r="C141" s="28"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="F141" s="33" t="s">
-        <v>161</v>
+        <v>466</v>
+      </c>
+      <c r="F141" s="21" t="s">
+        <v>160</v>
       </c>
       <c r="G141" s="28">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H141" s="28">
-        <v>1</v>
-      </c>
-      <c r="I141" s="28">
-        <v>1</v>
-      </c>
-      <c r="J141" s="34" t="s">
-        <v>469</v>
-      </c>
-      <c r="K141" s="34" t="s">
-        <v>470</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I141" s="28"/>
+      <c r="J141" s="34"/>
+      <c r="K141" s="34"/>
       <c r="L141" s="34"/>
       <c r="M141" s="34"/>
       <c r="N141" s="34"/>
       <c r="O141" s="2"/>
       <c r="P141" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="Q141" s="35"/>
     </row>
     <row r="142" spans="1:17">
       <c r="A142" s="28">
-        <v>82</v>
-      </c>
-      <c r="B142" s="21">
         <v>81</v>
       </c>
+      <c r="B142" s="21"/>
       <c r="C142" s="28">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D142" s="21"/>
       <c r="E142" s="21" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F142" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G142" s="28">
         <v>80</v>
@@ -11544,66 +11527,70 @@
         <v>1</v>
       </c>
       <c r="J142" s="34" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="K142" s="34" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L142" s="34"/>
       <c r="M142" s="34"/>
       <c r="N142" s="34"/>
       <c r="O142" s="2"/>
       <c r="P142" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="Q142" s="35"/>
     </row>
     <row r="143" spans="1:17">
       <c r="A143" s="28">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B143" s="21">
         <v>81</v>
       </c>
       <c r="C143" s="28">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D143" s="21"/>
       <c r="E143" s="21" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F143" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G143" s="28">
         <v>80</v>
       </c>
       <c r="H143" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I143" s="28">
         <v>1</v>
       </c>
       <c r="J143" s="34" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="K143" s="34" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="L143" s="34"/>
       <c r="M143" s="34"/>
       <c r="N143" s="34"/>
       <c r="O143" s="2"/>
       <c r="P143" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="Q143" s="35"/>
     </row>
     <row r="144" spans="1:17">
-      <c r="A144" s="28"/>
-      <c r="B144" s="21"/>
+      <c r="A144" s="28">
+        <v>83</v>
+      </c>
+      <c r="B144" s="21">
+        <v>81</v>
+      </c>
       <c r="C144" s="28">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D144" s="21"/>
       <c r="E144" s="21" t="s">
@@ -11612,13 +11599,21 @@
       <c r="F144" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="G144" s="28"/>
-      <c r="H144" s="28"/>
+      <c r="G144" s="28">
+        <v>80</v>
+      </c>
+      <c r="H144" s="28">
+        <v>2</v>
+      </c>
       <c r="I144" s="28">
-        <v>2</v>
-      </c>
-      <c r="J144" s="34"/>
-      <c r="K144" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J144" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="K144" s="34" t="s">
+        <v>478</v>
+      </c>
       <c r="L144" s="34"/>
       <c r="M144" s="34"/>
       <c r="N144" s="34"/>
@@ -11629,51 +11624,43 @@
       <c r="Q144" s="35"/>
     </row>
     <row r="145" spans="1:17">
-      <c r="A145" s="28">
-        <v>84</v>
-      </c>
-      <c r="B145" s="21">
-        <v>81</v>
-      </c>
+      <c r="A145" s="28"/>
+      <c r="B145" s="21"/>
       <c r="C145" s="28">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D145" s="21"/>
       <c r="E145" s="21" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="F145" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="G145" s="28">
-        <v>80</v>
-      </c>
-      <c r="H145" s="28">
-        <v>3</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="G145" s="28"/>
+      <c r="H145" s="28"/>
       <c r="I145" s="28">
-        <v>1</v>
-      </c>
-      <c r="J145" s="34" t="s">
-        <v>481</v>
-      </c>
-      <c r="K145" s="34" t="s">
-        <v>482</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J145" s="34"/>
+      <c r="K145" s="34"/>
       <c r="L145" s="34"/>
       <c r="M145" s="34"/>
       <c r="N145" s="34"/>
       <c r="O145" s="2"/>
       <c r="P145" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q145" s="42"/>
+        <v>479</v>
+      </c>
+      <c r="Q145" s="35"/>
     </row>
     <row r="146" spans="1:17">
-      <c r="A146" s="28"/>
-      <c r="B146" s="21"/>
+      <c r="A146" s="28">
+        <v>84</v>
+      </c>
+      <c r="B146" s="21">
+        <v>81</v>
+      </c>
       <c r="C146" s="28">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D146" s="21"/>
       <c r="E146" s="21" t="s">
@@ -11682,13 +11669,21 @@
       <c r="F146" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="G146" s="28"/>
-      <c r="H146" s="28"/>
+      <c r="G146" s="28">
+        <v>80</v>
+      </c>
+      <c r="H146" s="28">
+        <v>3</v>
+      </c>
       <c r="I146" s="28">
-        <v>2</v>
-      </c>
-      <c r="J146" s="34"/>
-      <c r="K146" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J146" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="K146" s="34" t="s">
+        <v>482</v>
+      </c>
       <c r="L146" s="34"/>
       <c r="M146" s="34"/>
       <c r="N146" s="34"/>
@@ -11702,7 +11697,7 @@
       <c r="A147" s="28"/>
       <c r="B147" s="21"/>
       <c r="C147" s="28">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D147" s="21"/>
       <c r="E147" s="21" t="s">
@@ -11714,7 +11709,7 @@
       <c r="G147" s="28"/>
       <c r="H147" s="28"/>
       <c r="I147" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J147" s="34"/>
       <c r="K147" s="34"/>
@@ -11728,95 +11723,95 @@
       <c r="Q147" s="42"/>
     </row>
     <row r="148" spans="1:17">
-      <c r="A148" s="36">
-        <v>206</v>
-      </c>
-      <c r="B148" s="3">
-        <v>72</v>
-      </c>
-      <c r="C148" s="36"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-      <c r="F148" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G148" s="36">
-        <v>43</v>
-      </c>
-      <c r="H148" s="36">
+      <c r="A148" s="28"/>
+      <c r="B148" s="21"/>
+      <c r="C148" s="28">
+        <v>126</v>
+      </c>
+      <c r="D148" s="21"/>
+      <c r="E148" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="F148" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="G148" s="28"/>
+      <c r="H148" s="28"/>
+      <c r="I148" s="28">
         <v>3</v>
       </c>
-      <c r="I148" s="36"/>
-      <c r="J148" s="40"/>
-      <c r="K148" s="40"/>
-      <c r="L148" s="40"/>
-      <c r="M148" s="40"/>
-      <c r="N148" s="40"/>
-      <c r="O148" s="1"/>
-      <c r="P148" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q148" s="35"/>
+      <c r="J148" s="34"/>
+      <c r="K148" s="34"/>
+      <c r="L148" s="34"/>
+      <c r="M148" s="34"/>
+      <c r="N148" s="34"/>
+      <c r="O148" s="2"/>
+      <c r="P148" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q148" s="42"/>
     </row>
     <row r="149" spans="1:17">
       <c r="A149" s="36">
-        <v>85</v>
-      </c>
-      <c r="B149" s="3"/>
-      <c r="C149" s="36">
-        <v>127</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="B149" s="3">
+        <v>72</v>
+      </c>
+      <c r="C149" s="36"/>
       <c r="D149" s="3"/>
-      <c r="E149" s="89" t="s">
-        <v>642</v>
-      </c>
-      <c r="F149" s="41" t="s">
+      <c r="E149" s="3"/>
+      <c r="F149" s="3" t="s">
         <v>164</v>
       </c>
       <c r="G149" s="36">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="H149" s="36">
         <v>3</v>
       </c>
-      <c r="I149" s="36">
-        <v>1</v>
-      </c>
-      <c r="J149" s="40" t="s">
-        <v>485</v>
-      </c>
-      <c r="K149" s="40" t="s">
-        <v>486</v>
-      </c>
+      <c r="I149" s="36"/>
+      <c r="J149" s="40"/>
+      <c r="K149" s="40"/>
       <c r="L149" s="40"/>
       <c r="M149" s="40"/>
       <c r="N149" s="40"/>
       <c r="O149" s="1"/>
       <c r="P149" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q149" s="42"/>
+        <v>484</v>
+      </c>
+      <c r="Q149" s="35"/>
     </row>
     <row r="150" spans="1:17">
-      <c r="A150" s="36"/>
+      <c r="A150" s="36">
+        <v>85</v>
+      </c>
       <c r="B150" s="3"/>
       <c r="C150" s="36">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="89" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F150" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="G150" s="36"/>
-      <c r="H150" s="36"/>
+      <c r="G150" s="36">
+        <v>206</v>
+      </c>
+      <c r="H150" s="36">
+        <v>3</v>
+      </c>
       <c r="I150" s="36">
-        <v>2</v>
-      </c>
-      <c r="J150" s="40"/>
-      <c r="K150" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J150" s="40" t="s">
+        <v>485</v>
+      </c>
+      <c r="K150" s="40" t="s">
+        <v>486</v>
+      </c>
       <c r="L150" s="40"/>
       <c r="M150" s="40"/>
       <c r="N150" s="40"/>
@@ -11830,11 +11825,11 @@
       <c r="A151" s="36"/>
       <c r="B151" s="3"/>
       <c r="C151" s="36">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="89" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F151" s="41" t="s">
         <v>164</v>
@@ -11842,7 +11837,7 @@
       <c r="G151" s="36"/>
       <c r="H151" s="36"/>
       <c r="I151" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J151" s="40"/>
       <c r="K151" s="40"/>
@@ -11859,96 +11854,96 @@
       <c r="A152" s="36"/>
       <c r="B152" s="3"/>
       <c r="C152" s="36">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="89" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F152" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="G152" s="36">
-        <v>206</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="G152" s="36"/>
       <c r="H152" s="36"/>
       <c r="I152" s="36">
-        <v>1</v>
-      </c>
-      <c r="J152" s="40" t="s">
-        <v>488</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J152" s="40"/>
       <c r="K152" s="40"/>
       <c r="L152" s="40"/>
       <c r="M152" s="40"/>
       <c r="N152" s="40"/>
       <c r="O152" s="1"/>
       <c r="P152" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q152" s="35"/>
+        <v>487</v>
+      </c>
+      <c r="Q152" s="42"/>
     </row>
     <row r="153" spans="1:17">
-      <c r="A153" s="36">
-        <v>86</v>
-      </c>
-      <c r="B153" s="3">
-        <v>85</v>
-      </c>
+      <c r="A153" s="36"/>
+      <c r="B153" s="3"/>
       <c r="C153" s="36">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="89" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F153" s="41" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G153" s="36">
         <v>206</v>
       </c>
-      <c r="H153" s="36">
-        <v>2</v>
-      </c>
+      <c r="H153" s="36"/>
       <c r="I153" s="36">
         <v>1</v>
       </c>
       <c r="J153" s="40" t="s">
-        <v>490</v>
-      </c>
-      <c r="K153" s="40" t="s">
-        <v>491</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="K153" s="40"/>
       <c r="L153" s="40"/>
       <c r="M153" s="40"/>
       <c r="N153" s="40"/>
       <c r="O153" s="1"/>
       <c r="P153" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="Q153" s="35"/>
     </row>
     <row r="154" spans="1:17">
-      <c r="A154" s="36"/>
-      <c r="B154" s="3"/>
+      <c r="A154" s="36">
+        <v>86</v>
+      </c>
+      <c r="B154" s="3">
+        <v>85</v>
+      </c>
       <c r="C154" s="36">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="89" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F154" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="G154" s="36"/>
-      <c r="H154" s="36"/>
+      <c r="G154" s="36">
+        <v>206</v>
+      </c>
+      <c r="H154" s="36">
+        <v>2</v>
+      </c>
       <c r="I154" s="36">
-        <v>2</v>
-      </c>
-      <c r="J154" s="40"/>
-      <c r="K154" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J154" s="40" t="s">
+        <v>490</v>
+      </c>
+      <c r="K154" s="40" t="s">
+        <v>491</v>
+      </c>
       <c r="L154" s="40"/>
       <c r="M154" s="40"/>
       <c r="N154" s="40"/>
@@ -11959,62 +11954,50 @@
       <c r="Q154" s="35"/>
     </row>
     <row r="155" spans="1:17">
-      <c r="A155" s="36">
-        <v>87</v>
-      </c>
-      <c r="B155" s="3">
-        <v>86</v>
-      </c>
+      <c r="A155" s="36"/>
+      <c r="B155" s="3"/>
       <c r="C155" s="36">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D155" s="3"/>
       <c r="E155" s="89" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F155" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="G155" s="36">
-        <v>206</v>
-      </c>
-      <c r="H155" s="36">
+        <v>155</v>
+      </c>
+      <c r="G155" s="36"/>
+      <c r="H155" s="36"/>
+      <c r="I155" s="36">
         <v>2</v>
       </c>
-      <c r="I155" s="36">
-        <v>1</v>
-      </c>
-      <c r="J155" s="40" t="s">
-        <v>493</v>
-      </c>
-      <c r="K155" s="40" t="s">
-        <v>494</v>
-      </c>
+      <c r="J155" s="40"/>
+      <c r="K155" s="40"/>
       <c r="L155" s="40"/>
       <c r="M155" s="40"/>
       <c r="N155" s="40"/>
       <c r="O155" s="1"/>
       <c r="P155" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="Q155" s="35"/>
     </row>
     <row r="156" spans="1:17">
       <c r="A156" s="36">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B156" s="3">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C156" s="36">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D156" s="3"/>
       <c r="E156" s="89" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F156" s="41" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G156" s="36">
         <v>206</v>
@@ -12026,36 +12009,36 @@
         <v>1</v>
       </c>
       <c r="J156" s="40" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="K156" s="40" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="L156" s="40"/>
       <c r="M156" s="40"/>
       <c r="N156" s="40"/>
       <c r="O156" s="1"/>
       <c r="P156" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="Q156" s="35"/>
     </row>
     <row r="157" spans="1:17">
       <c r="A157" s="36">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B157" s="3">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C157" s="36">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D157" s="3"/>
       <c r="E157" s="89" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F157" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G157" s="36">
         <v>206</v>
@@ -12067,36 +12050,36 @@
         <v>1</v>
       </c>
       <c r="J157" s="40" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="K157" s="40" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L157" s="40"/>
       <c r="M157" s="40"/>
       <c r="N157" s="40"/>
       <c r="O157" s="1"/>
       <c r="P157" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="Q157" s="35"/>
     </row>
     <row r="158" spans="1:17">
       <c r="A158" s="36">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B158" s="3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C158" s="36">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="89" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F158" s="41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G158" s="36">
         <v>206</v>
@@ -12108,36 +12091,36 @@
         <v>1</v>
       </c>
       <c r="J158" s="40" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="K158" s="40" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="L158" s="40"/>
       <c r="M158" s="40"/>
       <c r="N158" s="40"/>
       <c r="O158" s="1"/>
       <c r="P158" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="Q158" s="35"/>
     </row>
     <row r="159" spans="1:17">
       <c r="A159" s="36">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B159" s="3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C159" s="36">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D159" s="3"/>
       <c r="E159" s="89" t="s">
-        <v>648</v>
-      </c>
-      <c r="F159" s="49" t="s">
-        <v>505</v>
+        <v>646</v>
+      </c>
+      <c r="F159" s="41" t="s">
+        <v>168</v>
       </c>
       <c r="G159" s="36">
         <v>206</v>
@@ -12149,36 +12132,36 @@
         <v>1</v>
       </c>
       <c r="J159" s="40" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="K159" s="40" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="L159" s="40"/>
       <c r="M159" s="40"/>
       <c r="N159" s="40"/>
       <c r="O159" s="1"/>
       <c r="P159" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="Q159" s="35"/>
     </row>
     <row r="160" spans="1:17">
       <c r="A160" s="36">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B160" s="3">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C160" s="36">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D160" s="3"/>
       <c r="E160" s="89" t="s">
-        <v>649</v>
-      </c>
-      <c r="F160" s="41" t="s">
-        <v>170</v>
+        <v>647</v>
+      </c>
+      <c r="F160" s="49" t="s">
+        <v>505</v>
       </c>
       <c r="G160" s="36">
         <v>206</v>
@@ -12190,70 +12173,84 @@
         <v>1</v>
       </c>
       <c r="J160" s="40" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="K160" s="40" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="L160" s="40"/>
       <c r="M160" s="40"/>
       <c r="N160" s="40"/>
       <c r="O160" s="1"/>
       <c r="P160" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q160" s="35"/>
+    </row>
+    <row r="161" spans="1:17">
+      <c r="A161" s="36">
+        <v>92</v>
+      </c>
+      <c r="B161" s="3">
+        <v>91</v>
+      </c>
+      <c r="C161" s="36">
+        <v>138</v>
+      </c>
+      <c r="D161" s="3"/>
+      <c r="E161" s="89" t="s">
+        <v>648</v>
+      </c>
+      <c r="F161" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="G161" s="36">
+        <v>206</v>
+      </c>
+      <c r="H161" s="36">
+        <v>2</v>
+      </c>
+      <c r="I161" s="36">
+        <v>1</v>
+      </c>
+      <c r="J161" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="K161" s="40" t="s">
+        <v>510</v>
+      </c>
+      <c r="L161" s="40"/>
+      <c r="M161" s="40"/>
+      <c r="N161" s="40"/>
+      <c r="O161" s="1"/>
+      <c r="P161" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="Q160" s="42"/>
-    </row>
-    <row r="161" spans="1:17">
-      <c r="A161" s="28">
+      <c r="Q161" s="42"/>
+    </row>
+    <row r="162" spans="1:17">
+      <c r="A162" s="28">
         <v>93</v>
       </c>
-      <c r="B161" s="21">
+      <c r="B162" s="21">
         <v>72.206000000000003</v>
       </c>
-      <c r="C161" s="28">
+      <c r="C162" s="28">
         <v>139</v>
-      </c>
-      <c r="D161" s="21"/>
-      <c r="E161" s="21"/>
-      <c r="F161" s="88" t="s">
-        <v>171</v>
-      </c>
-      <c r="G161" s="28">
-        <v>43</v>
-      </c>
-      <c r="H161" s="28">
-        <v>2</v>
-      </c>
-      <c r="I161" s="28">
-        <v>1</v>
-      </c>
-      <c r="J161" s="34"/>
-      <c r="K161" s="34"/>
-      <c r="L161" s="34"/>
-      <c r="M161" s="34"/>
-      <c r="N161" s="34"/>
-      <c r="O161" s="2"/>
-      <c r="P161" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q161" s="35"/>
-    </row>
-    <row r="162" spans="1:17">
-      <c r="A162" s="28"/>
-      <c r="B162" s="21"/>
-      <c r="C162" s="28">
-        <v>140</v>
       </c>
       <c r="D162" s="21"/>
       <c r="E162" s="21"/>
-      <c r="F162" s="21" t="s">
+      <c r="F162" s="88" t="s">
         <v>171</v>
       </c>
-      <c r="G162" s="28"/>
-      <c r="H162" s="28"/>
+      <c r="G162" s="28">
+        <v>43</v>
+      </c>
+      <c r="H162" s="28">
+        <v>2</v>
+      </c>
       <c r="I162" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J162" s="34"/>
       <c r="K162" s="34"/>
@@ -12267,90 +12264,80 @@
       <c r="Q162" s="35"/>
     </row>
     <row r="163" spans="1:17">
-      <c r="A163" s="28">
-        <v>94</v>
-      </c>
+      <c r="A163" s="28"/>
       <c r="B163" s="21"/>
       <c r="C163" s="28">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D163" s="21"/>
-      <c r="E163" s="21" t="s">
-        <v>513</v>
-      </c>
-      <c r="F163" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="G163" s="28">
-        <v>93</v>
-      </c>
-      <c r="H163" s="28">
+      <c r="E163" s="21"/>
+      <c r="F163" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="G163" s="28"/>
+      <c r="H163" s="28"/>
+      <c r="I163" s="28">
         <v>2</v>
       </c>
-      <c r="I163" s="28">
-        <v>1</v>
-      </c>
-      <c r="J163" s="34" t="s">
-        <v>514</v>
-      </c>
-      <c r="K163" s="34" t="s">
-        <v>515</v>
-      </c>
+      <c r="J163" s="34"/>
+      <c r="K163" s="34"/>
       <c r="L163" s="34"/>
       <c r="M163" s="34"/>
       <c r="N163" s="34"/>
       <c r="O163" s="2"/>
       <c r="P163" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="Q163" s="35"/>
     </row>
     <row r="164" spans="1:17">
       <c r="A164" s="28">
-        <v>95</v>
-      </c>
-      <c r="B164" s="21">
         <v>94</v>
       </c>
+      <c r="B164" s="21"/>
       <c r="C164" s="28">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D164" s="21"/>
       <c r="E164" s="21" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F164" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G164" s="28">
         <v>93</v>
       </c>
       <c r="H164" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I164" s="28">
         <v>1</v>
       </c>
       <c r="J164" s="34" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="K164" s="34" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="L164" s="34"/>
       <c r="M164" s="34"/>
       <c r="N164" s="34"/>
       <c r="O164" s="2"/>
       <c r="P164" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="Q164" s="35"/>
     </row>
     <row r="165" spans="1:17">
-      <c r="A165" s="28"/>
-      <c r="B165" s="21"/>
+      <c r="A165" s="28">
+        <v>95</v>
+      </c>
+      <c r="B165" s="21">
+        <v>94</v>
+      </c>
       <c r="C165" s="28">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="D165" s="21"/>
       <c r="E165" s="21" t="s">
@@ -12360,24 +12347,34 @@
         <v>173</v>
       </c>
       <c r="G165" s="28">
-        <v>95</v>
-      </c>
-      <c r="H165" s="28"/>
+        <v>93</v>
+      </c>
+      <c r="H165" s="28">
+        <v>3</v>
+      </c>
       <c r="I165" s="28">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J165" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="K165" s="34" t="s">
+        <v>519</v>
       </c>
       <c r="L165" s="34"/>
       <c r="M165" s="34"/>
       <c r="N165" s="34"/>
       <c r="O165" s="2"/>
-      <c r="P165" s="2"/>
+      <c r="P165" s="2" t="s">
+        <v>520</v>
+      </c>
       <c r="Q165" s="35"/>
     </row>
     <row r="166" spans="1:17">
       <c r="A166" s="28"/>
       <c r="B166" s="21"/>
       <c r="C166" s="28">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D166" s="21"/>
       <c r="E166" s="21" t="s">
@@ -12391,10 +12388,8 @@
       </c>
       <c r="H166" s="28"/>
       <c r="I166" s="28">
-        <v>3</v>
-      </c>
-      <c r="J166" s="34"/>
-      <c r="K166" s="34"/>
+        <v>2</v>
+      </c>
       <c r="L166" s="34"/>
       <c r="M166" s="34"/>
       <c r="N166" s="34"/>
@@ -12403,96 +12398,86 @@
       <c r="Q166" s="35"/>
     </row>
     <row r="167" spans="1:17">
-      <c r="A167" s="28">
-        <v>96</v>
-      </c>
-      <c r="B167" s="21">
-        <v>95</v>
-      </c>
+      <c r="A167" s="28"/>
+      <c r="B167" s="21"/>
       <c r="C167" s="28">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D167" s="21"/>
       <c r="E167" s="21" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F167" s="33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G167" s="28">
-        <v>93</v>
-      </c>
-      <c r="H167" s="28">
-        <v>2</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H167" s="28"/>
       <c r="I167" s="28">
-        <v>1</v>
-      </c>
-      <c r="J167" s="34" t="s">
-        <v>522</v>
-      </c>
-      <c r="K167" s="34" t="s">
-        <v>523</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J167" s="34"/>
+      <c r="K167" s="34"/>
       <c r="L167" s="34"/>
-      <c r="M167" s="34" t="s">
-        <v>524</v>
-      </c>
+      <c r="M167" s="34"/>
       <c r="N167" s="34"/>
       <c r="O167" s="2"/>
-      <c r="P167" s="2" t="s">
-        <v>525</v>
-      </c>
+      <c r="P167" s="2"/>
       <c r="Q167" s="35"/>
     </row>
     <row r="168" spans="1:17">
       <c r="A168" s="28">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B168" s="21">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C168" s="28">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D168" s="21"/>
       <c r="E168" s="21" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F168" s="33" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G168" s="28">
         <v>93</v>
       </c>
       <c r="H168" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I168" s="28">
         <v>1</v>
       </c>
       <c r="J168" s="34" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="K168" s="34" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="L168" s="34"/>
       <c r="M168" s="34" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="N168" s="34"/>
       <c r="O168" s="2"/>
       <c r="P168" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="Q168" s="35"/>
     </row>
     <row r="169" spans="1:17">
-      <c r="A169" s="28"/>
-      <c r="B169" s="21"/>
+      <c r="A169" s="28">
+        <v>97</v>
+      </c>
+      <c r="B169" s="21">
+        <v>96</v>
+      </c>
       <c r="C169" s="28">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="D169" s="21"/>
       <c r="E169" s="21" t="s">
@@ -12502,149 +12487,160 @@
         <v>171</v>
       </c>
       <c r="G169" s="28">
-        <v>97</v>
-      </c>
-      <c r="H169" s="28"/>
+        <v>93</v>
+      </c>
+      <c r="H169" s="28">
+        <v>3</v>
+      </c>
       <c r="I169" s="28">
-        <v>3</v>
-      </c>
-      <c r="J169" s="34"/>
-      <c r="K169" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J169" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="K169" s="34" t="s">
+        <v>528</v>
+      </c>
       <c r="L169" s="34"/>
-      <c r="M169" s="34"/>
+      <c r="M169" s="34" t="s">
+        <v>529</v>
+      </c>
       <c r="N169" s="34"/>
       <c r="O169" s="2"/>
-      <c r="P169" s="2"/>
+      <c r="P169" s="2" t="s">
+        <v>530</v>
+      </c>
       <c r="Q169" s="35"/>
     </row>
     <row r="170" spans="1:17">
-      <c r="A170" s="36">
-        <v>207</v>
-      </c>
-      <c r="B170" s="3">
-        <v>93</v>
-      </c>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-      <c r="F170" s="89" t="s">
-        <v>657</v>
-      </c>
-      <c r="G170" s="36">
-        <v>43</v>
-      </c>
-      <c r="H170" s="36">
-        <v>2</v>
-      </c>
-      <c r="I170" s="36"/>
-      <c r="J170" s="40"/>
-      <c r="K170" s="40"/>
-      <c r="L170" s="40"/>
-      <c r="M170" s="40"/>
-      <c r="N170" s="40"/>
-      <c r="O170" s="1"/>
-      <c r="P170" s="1" t="s">
-        <v>533</v>
-      </c>
+      <c r="A170" s="28"/>
+      <c r="B170" s="21"/>
+      <c r="C170" s="28">
+        <v>162</v>
+      </c>
+      <c r="D170" s="21"/>
+      <c r="E170" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="F170" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="G170" s="28">
+        <v>97</v>
+      </c>
+      <c r="H170" s="28"/>
+      <c r="I170" s="28">
+        <v>3</v>
+      </c>
+      <c r="J170" s="34"/>
+      <c r="K170" s="34"/>
+      <c r="L170" s="34"/>
+      <c r="M170" s="34"/>
+      <c r="N170" s="34"/>
+      <c r="O170" s="2"/>
+      <c r="P170" s="2"/>
       <c r="Q170" s="35"/>
     </row>
     <row r="171" spans="1:17">
       <c r="A171" s="36">
-        <v>98</v>
-      </c>
-      <c r="B171" s="3"/>
-      <c r="C171" s="36">
-        <v>145</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="B171" s="3">
+        <v>93</v>
+      </c>
+      <c r="C171" s="3"/>
       <c r="D171" s="3"/>
-      <c r="E171" s="89" t="s">
-        <v>658</v>
-      </c>
+      <c r="E171" s="3"/>
       <c r="F171" s="89" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G171" s="36">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="H171" s="36">
-        <v>1</v>
-      </c>
-      <c r="I171" s="36">
-        <v>1</v>
-      </c>
-      <c r="J171" s="40" t="s">
-        <v>531</v>
-      </c>
-      <c r="K171" s="40" t="s">
-        <v>532</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I171" s="36"/>
+      <c r="J171" s="40"/>
+      <c r="K171" s="40"/>
       <c r="L171" s="40"/>
       <c r="M171" s="40"/>
       <c r="N171" s="40"/>
       <c r="O171" s="1"/>
-      <c r="P171" s="1"/>
+      <c r="P171" s="1" t="s">
+        <v>533</v>
+      </c>
       <c r="Q171" s="35"/>
     </row>
     <row r="172" spans="1:17">
       <c r="A172" s="36">
-        <v>99</v>
-      </c>
-      <c r="B172" s="3">
         <v>98</v>
       </c>
+      <c r="B172" s="3"/>
       <c r="C172" s="36">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="89" t="s">
-        <v>659</v>
-      </c>
-      <c r="F172" s="41" t="s">
-        <v>176</v>
+        <v>657</v>
+      </c>
+      <c r="F172" s="89" t="s">
+        <v>656</v>
       </c>
       <c r="G172" s="36">
         <v>207</v>
       </c>
       <c r="H172" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I172" s="36">
         <v>1</v>
       </c>
       <c r="J172" s="40" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="K172" s="40" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="L172" s="40"/>
       <c r="M172" s="40"/>
       <c r="N172" s="40"/>
       <c r="O172" s="1"/>
-      <c r="P172" s="1" t="s">
-        <v>536</v>
-      </c>
+      <c r="P172" s="1"/>
+      <c r="Q172" s="35"/>
     </row>
     <row r="173" spans="1:17">
-      <c r="A173" s="36"/>
-      <c r="B173" s="3"/>
+      <c r="A173" s="36">
+        <v>99</v>
+      </c>
+      <c r="B173" s="3">
+        <v>98</v>
+      </c>
       <c r="C173" s="36">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="89" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F173" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G173" s="36"/>
-      <c r="H173" s="36"/>
+      <c r="G173" s="36">
+        <v>207</v>
+      </c>
+      <c r="H173" s="36">
+        <v>2</v>
+      </c>
       <c r="I173" s="36">
-        <v>2</v>
-      </c>
-      <c r="J173" s="40"/>
-      <c r="K173" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="J173" s="40" t="s">
+        <v>534</v>
+      </c>
+      <c r="K173" s="40" t="s">
+        <v>535</v>
+      </c>
       <c r="L173" s="40"/>
       <c r="M173" s="40"/>
       <c r="N173" s="40"/>
@@ -12654,80 +12650,71 @@
       </c>
     </row>
     <row r="174" spans="1:17">
-      <c r="A174" s="28">
-        <v>100</v>
-      </c>
-      <c r="B174" s="21">
-        <v>72.102999999999994</v>
-      </c>
-      <c r="C174" s="28"/>
-      <c r="D174" s="21"/>
-      <c r="E174" s="21"/>
-      <c r="F174" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="G174" s="28">
-        <v>43</v>
-      </c>
-      <c r="H174" s="28">
+      <c r="A174" s="36"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="36">
+        <v>147</v>
+      </c>
+      <c r="D174" s="3"/>
+      <c r="E174" s="89" t="s">
+        <v>658</v>
+      </c>
+      <c r="F174" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G174" s="36"/>
+      <c r="H174" s="36"/>
+      <c r="I174" s="36">
         <v>2</v>
       </c>
-      <c r="I174" s="28"/>
-      <c r="J174" s="34"/>
-      <c r="K174" s="34"/>
-      <c r="L174" s="34"/>
-      <c r="M174" s="34"/>
-      <c r="N174" s="34"/>
-      <c r="O174" s="2"/>
-      <c r="P174" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q174" s="35"/>
+      <c r="J174" s="40"/>
+      <c r="K174" s="40"/>
+      <c r="L174" s="40"/>
+      <c r="M174" s="40"/>
+      <c r="N174" s="40"/>
+      <c r="O174" s="1"/>
+      <c r="P174" s="1" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="175" spans="1:17">
       <c r="A175" s="28">
-        <v>101</v>
-      </c>
-      <c r="B175" s="21"/>
-      <c r="C175" s="28">
-        <v>148</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B175" s="21">
+        <v>72.102999999999994</v>
+      </c>
+      <c r="C175" s="28"/>
       <c r="D175" s="21"/>
-      <c r="E175" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="F175" s="33" t="s">
-        <v>178</v>
+      <c r="E175" s="21"/>
+      <c r="F175" s="21" t="s">
+        <v>177</v>
       </c>
       <c r="G175" s="28">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="H175" s="28">
         <v>2</v>
       </c>
-      <c r="I175" s="28">
-        <v>1</v>
-      </c>
-      <c r="J175" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="K175" s="34" t="s">
-        <v>540</v>
-      </c>
+      <c r="I175" s="28"/>
+      <c r="J175" s="34"/>
+      <c r="K175" s="34"/>
       <c r="L175" s="34"/>
       <c r="M175" s="34"/>
       <c r="N175" s="34"/>
       <c r="O175" s="2"/>
       <c r="P175" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="Q175" s="35"/>
     </row>
     <row r="176" spans="1:17">
-      <c r="A176" s="28"/>
+      <c r="A176" s="28">
+        <v>101</v>
+      </c>
       <c r="B176" s="21"/>
       <c r="C176" s="28">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D176" s="21"/>
       <c r="E176" s="21" t="s">
@@ -12736,13 +12723,21 @@
       <c r="F176" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="G176" s="28"/>
-      <c r="H176" s="28"/>
+      <c r="G176" s="28">
+        <v>100</v>
+      </c>
+      <c r="H176" s="28">
+        <v>2</v>
+      </c>
       <c r="I176" s="28">
-        <v>2</v>
-      </c>
-      <c r="J176" s="34"/>
-      <c r="K176" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J176" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="K176" s="34" t="s">
+        <v>540</v>
+      </c>
       <c r="L176" s="34"/>
       <c r="M176" s="34"/>
       <c r="N176" s="34"/>
@@ -12753,203 +12748,191 @@
       <c r="Q176" s="35"/>
     </row>
     <row r="177" spans="1:17">
-      <c r="A177" s="28">
-        <v>102</v>
-      </c>
-      <c r="B177" s="21">
-        <v>101</v>
-      </c>
+      <c r="A177" s="28"/>
+      <c r="B177" s="21"/>
       <c r="C177" s="28">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D177" s="21"/>
-      <c r="E177" s="88" t="s">
-        <v>656</v>
+      <c r="E177" s="21" t="s">
+        <v>538</v>
       </c>
       <c r="F177" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="G177" s="28">
-        <v>100</v>
-      </c>
-      <c r="H177" s="28">
+        <v>178</v>
+      </c>
+      <c r="G177" s="28"/>
+      <c r="H177" s="28"/>
+      <c r="I177" s="28">
         <v>2</v>
       </c>
-      <c r="I177" s="28">
-        <v>1</v>
-      </c>
-      <c r="J177" s="34" t="s">
-        <v>542</v>
-      </c>
-      <c r="K177" s="34" t="s">
-        <v>543</v>
-      </c>
+      <c r="J177" s="34"/>
+      <c r="K177" s="34"/>
       <c r="L177" s="34"/>
       <c r="M177" s="34"/>
       <c r="N177" s="34"/>
       <c r="O177" s="2"/>
       <c r="P177" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="Q177" s="35"/>
     </row>
     <row r="178" spans="1:17">
-      <c r="A178" s="28"/>
-      <c r="B178" s="21"/>
+      <c r="A178" s="28">
+        <v>102</v>
+      </c>
+      <c r="B178" s="21">
+        <v>101</v>
+      </c>
       <c r="C178" s="28">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D178" s="21"/>
       <c r="E178" s="88" t="s">
-        <v>656</v>
-      </c>
-      <c r="F178" s="21"/>
-      <c r="G178" s="28"/>
-      <c r="H178" s="28"/>
+        <v>655</v>
+      </c>
+      <c r="F178" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="G178" s="28">
+        <v>100</v>
+      </c>
+      <c r="H178" s="28">
+        <v>2</v>
+      </c>
       <c r="I178" s="28">
         <v>1</v>
       </c>
-      <c r="J178" s="34"/>
+      <c r="J178" s="34" t="s">
+        <v>542</v>
+      </c>
       <c r="K178" s="34" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="L178" s="34"/>
-      <c r="M178" s="34" t="s">
-        <v>546</v>
-      </c>
+      <c r="M178" s="34"/>
       <c r="N178" s="34"/>
       <c r="O178" s="2"/>
       <c r="P178" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q178" s="35"/>
+    </row>
+    <row r="179" spans="1:17">
+      <c r="A179" s="28"/>
+      <c r="B179" s="21"/>
+      <c r="C179" s="28">
+        <v>151</v>
+      </c>
+      <c r="D179" s="21"/>
+      <c r="E179" s="88" t="s">
+        <v>655</v>
+      </c>
+      <c r="F179" s="21"/>
+      <c r="G179" s="28"/>
+      <c r="H179" s="28"/>
+      <c r="I179" s="28">
+        <v>1</v>
+      </c>
+      <c r="J179" s="34"/>
+      <c r="K179" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="L179" s="34"/>
+      <c r="M179" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="N179" s="34"/>
+      <c r="O179" s="2"/>
+      <c r="P179" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="Q178" s="42"/>
-    </row>
-    <row r="179" spans="1:17">
-      <c r="A179" s="36">
+      <c r="Q179" s="42"/>
+    </row>
+    <row r="180" spans="1:17">
+      <c r="A180" s="36">
         <v>103</v>
       </c>
-      <c r="B179" s="3">
+      <c r="B180" s="3">
         <v>68.72</v>
       </c>
-      <c r="C179" s="36"/>
-      <c r="D179" s="3"/>
-      <c r="E179" s="3"/>
-      <c r="F179" s="3" t="s">
+      <c r="C180" s="36"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="G179" s="36">
+      <c r="G180" s="36">
         <v>43</v>
       </c>
-      <c r="H179" s="36">
-        <v>1</v>
-      </c>
-      <c r="I179" s="36"/>
-      <c r="J179" s="40"/>
-      <c r="K179" s="40"/>
-      <c r="L179" s="40"/>
-      <c r="M179" s="40"/>
-      <c r="N179" s="40"/>
-      <c r="O179" s="1"/>
-      <c r="P179" s="1" t="s">
+      <c r="H180" s="36">
+        <v>1</v>
+      </c>
+      <c r="I180" s="36"/>
+      <c r="J180" s="40"/>
+      <c r="K180" s="40"/>
+      <c r="L180" s="40"/>
+      <c r="M180" s="40"/>
+      <c r="N180" s="40"/>
+      <c r="O180" s="1"/>
+      <c r="P180" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="Q179" s="35"/>
-    </row>
-    <row r="180" spans="1:17">
-      <c r="A180" s="28">
+      <c r="Q180" s="35"/>
+    </row>
+    <row r="181" spans="1:17">
+      <c r="A181" s="28">
         <v>71</v>
       </c>
-      <c r="B180" s="21"/>
-      <c r="C180" s="28">
+      <c r="B181" s="21"/>
+      <c r="C181" s="28">
         <v>109</v>
       </c>
-      <c r="D180" s="21"/>
-      <c r="E180" s="21" t="s">
+      <c r="D181" s="21"/>
+      <c r="E181" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="F180" s="33" t="s">
+      <c r="F181" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="G180" s="28">
+      <c r="G181" s="28">
         <v>103</v>
       </c>
-      <c r="H180" s="28">
-        <v>1</v>
-      </c>
-      <c r="I180" s="28">
-        <v>1</v>
-      </c>
-      <c r="J180" s="34" t="s">
+      <c r="H181" s="28">
+        <v>1</v>
+      </c>
+      <c r="I181" s="28">
+        <v>1</v>
+      </c>
+      <c r="J181" s="34" t="s">
         <v>445</v>
       </c>
-      <c r="K180" s="34" t="s">
+      <c r="K181" s="34" t="s">
         <v>446</v>
       </c>
-      <c r="L180" s="34"/>
-      <c r="M180" s="34"/>
-      <c r="N180" s="34"/>
-      <c r="O180" s="2"/>
-      <c r="P180" s="2" t="s">
+      <c r="L181" s="34"/>
+      <c r="M181" s="34"/>
+      <c r="N181" s="34"/>
+      <c r="O181" s="2"/>
+      <c r="P181" s="2" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="181" spans="1:17">
-      <c r="A181" s="36">
-        <v>104</v>
-      </c>
-      <c r="B181" s="3">
-        <v>71</v>
-      </c>
-      <c r="C181" s="36">
-        <v>152</v>
-      </c>
-      <c r="D181" s="3"/>
-      <c r="E181" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="F181" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="G181" s="36">
-        <v>103</v>
-      </c>
-      <c r="H181" s="36">
-        <v>1</v>
-      </c>
-      <c r="I181" s="36">
-        <v>1</v>
-      </c>
-      <c r="J181" s="40" t="s">
-        <v>550</v>
-      </c>
-      <c r="K181" s="40" t="s">
-        <v>551</v>
-      </c>
-      <c r="L181" s="40"/>
-      <c r="M181" s="40"/>
-      <c r="N181" s="40"/>
-      <c r="O181" s="1"/>
-      <c r="P181" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="Q181" s="35"/>
     </row>
     <row r="182" spans="1:17">
       <c r="A182" s="36">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B182" s="3">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C182" s="36">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="3" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F182" s="41" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G182" s="36">
         <v>103</v>
@@ -12961,38 +12944,36 @@
         <v>1</v>
       </c>
       <c r="J182" s="40" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="K182" s="40" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="L182" s="40"/>
-      <c r="M182" s="40" t="s">
-        <v>556</v>
-      </c>
+      <c r="M182" s="40"/>
       <c r="N182" s="40"/>
       <c r="O182" s="1"/>
       <c r="P182" s="1" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="Q182" s="35"/>
     </row>
     <row r="183" spans="1:17">
       <c r="A183" s="36">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B183" s="3">
         <v>104</v>
       </c>
       <c r="C183" s="36">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="3" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="F183" s="41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G183" s="36">
         <v>103</v>
@@ -13004,64 +12985,73 @@
         <v>1</v>
       </c>
       <c r="J183" s="40" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="K183" s="40" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="L183" s="40"/>
       <c r="M183" s="40" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="N183" s="40"/>
       <c r="O183" s="1"/>
       <c r="P183" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q183" s="35"/>
+    </row>
+    <row r="184" spans="1:17">
+      <c r="A184" s="36">
+        <v>106</v>
+      </c>
+      <c r="B184" s="3">
+        <v>104</v>
+      </c>
+      <c r="C184" s="36">
+        <v>154</v>
+      </c>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="F184" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="G184" s="36">
+        <v>103</v>
+      </c>
+      <c r="H184" s="36">
+        <v>1</v>
+      </c>
+      <c r="I184" s="36">
+        <v>1</v>
+      </c>
+      <c r="J184" s="40" t="s">
+        <v>559</v>
+      </c>
+      <c r="K184" s="40" t="s">
+        <v>560</v>
+      </c>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40" t="s">
+        <v>561</v>
+      </c>
+      <c r="N184" s="40"/>
+      <c r="O184" s="1"/>
+      <c r="P184" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="184" spans="1:17">
-      <c r="A184" s="28">
+    <row r="185" spans="1:17">
+      <c r="A185" s="28">
         <v>107</v>
       </c>
-      <c r="B184" s="21">
+      <c r="B185" s="21">
         <v>103</v>
       </c>
-      <c r="C184" s="28">
+      <c r="C185" s="28">
         <v>155</v>
-      </c>
-      <c r="D184" s="21"/>
-      <c r="E184" s="21" t="s">
-        <v>563</v>
-      </c>
-      <c r="F184" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G184" s="28">
-        <v>43</v>
-      </c>
-      <c r="H184" s="28">
-        <v>3</v>
-      </c>
-      <c r="I184" s="28">
-        <v>1</v>
-      </c>
-      <c r="J184" s="34" t="s">
-        <v>564</v>
-      </c>
-      <c r="K184" s="34"/>
-      <c r="L184" s="34"/>
-      <c r="M184" s="34"/>
-      <c r="N184" s="34"/>
-      <c r="O184" s="2"/>
-      <c r="P184" s="2" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="185" spans="1:17">
-      <c r="A185" s="28"/>
-      <c r="B185" s="21"/>
-      <c r="C185" s="28">
-        <v>160</v>
       </c>
       <c r="D185" s="21"/>
       <c r="E185" s="21" t="s">
@@ -13071,25 +13061,31 @@
         <v>36</v>
       </c>
       <c r="G185" s="28">
-        <v>107</v>
-      </c>
-      <c r="H185" s="28"/>
+        <v>43</v>
+      </c>
+      <c r="H185" s="28">
+        <v>3</v>
+      </c>
       <c r="I185" s="28">
-        <v>2</v>
-      </c>
-      <c r="J185" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="J185" s="34" t="s">
+        <v>564</v>
+      </c>
       <c r="K185" s="34"/>
       <c r="L185" s="34"/>
       <c r="M185" s="34"/>
       <c r="N185" s="34"/>
       <c r="O185" s="2"/>
-      <c r="P185" s="2"/>
+      <c r="P185" s="2" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="186" spans="1:17">
       <c r="A186" s="28"/>
       <c r="B186" s="21"/>
       <c r="C186" s="28">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D186" s="21"/>
       <c r="E186" s="21" t="s">
@@ -13103,7 +13099,7 @@
       </c>
       <c r="H186" s="28"/>
       <c r="I186" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J186" s="34"/>
       <c r="K186" s="34"/>
@@ -13114,85 +13110,77 @@
       <c r="P186" s="2"/>
     </row>
     <row r="187" spans="1:17">
-      <c r="A187" s="36">
-        <v>209</v>
-      </c>
-      <c r="B187" s="3">
+      <c r="A187" s="28"/>
+      <c r="B187" s="21"/>
+      <c r="C187" s="28">
+        <v>161</v>
+      </c>
+      <c r="D187" s="21"/>
+      <c r="E187" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="F187" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G187" s="28">
         <v>107</v>
       </c>
-      <c r="C187" s="40"/>
-      <c r="D187" s="3"/>
-      <c r="E187" s="3"/>
-      <c r="F187" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G187" s="36">
-        <v>43</v>
-      </c>
-      <c r="H187" s="91">
-        <v>1</v>
-      </c>
-      <c r="I187" s="36"/>
-      <c r="J187" s="40"/>
-      <c r="K187" s="40"/>
-      <c r="L187" s="40"/>
-      <c r="M187" s="40"/>
-      <c r="N187" s="40"/>
-      <c r="O187" s="1"/>
-      <c r="P187" s="1" t="s">
-        <v>567</v>
-      </c>
+      <c r="H187" s="28"/>
+      <c r="I187" s="28">
+        <v>3</v>
+      </c>
+      <c r="J187" s="34"/>
+      <c r="K187" s="34"/>
+      <c r="L187" s="34"/>
+      <c r="M187" s="34"/>
+      <c r="N187" s="34"/>
+      <c r="O187" s="2"/>
+      <c r="P187" s="2"/>
     </row>
     <row r="188" spans="1:17">
       <c r="A188" s="36">
-        <v>108</v>
-      </c>
-      <c r="B188" s="3"/>
-      <c r="C188" s="36">
-        <v>156</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="B188" s="3">
+        <v>107</v>
+      </c>
+      <c r="C188" s="40"/>
       <c r="D188" s="3"/>
-      <c r="E188" s="89" t="s">
-        <v>650</v>
-      </c>
+      <c r="E188" s="3"/>
       <c r="F188" s="3" t="s">
         <v>184</v>
       </c>
       <c r="G188" s="36">
-        <v>209</v>
-      </c>
-      <c r="H188" s="36">
-        <v>1</v>
-      </c>
-      <c r="I188" s="36">
-        <v>1</v>
-      </c>
-      <c r="J188" s="40" t="s">
-        <v>566</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="H188" s="91">
+        <v>1</v>
+      </c>
+      <c r="I188" s="36"/>
+      <c r="J188" s="40"/>
       <c r="K188" s="40"/>
       <c r="L188" s="40"/>
       <c r="M188" s="40"/>
       <c r="N188" s="40"/>
       <c r="O188" s="1"/>
-      <c r="P188" s="1"/>
+      <c r="P188" s="1" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="189" spans="1:17">
       <c r="A189" s="36">
-        <v>109</v>
-      </c>
-      <c r="B189" s="3">
         <v>108</v>
       </c>
+      <c r="B189" s="3"/>
       <c r="C189" s="36">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D189" s="3"/>
       <c r="E189" s="89" t="s">
-        <v>651</v>
-      </c>
-      <c r="F189" s="41" t="s">
-        <v>185</v>
+        <v>649</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="G189" s="36">
         <v>209</v>
@@ -13204,24 +13192,60 @@
         <v>1</v>
       </c>
       <c r="J189" s="40" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="K189" s="40"/>
       <c r="L189" s="40"/>
       <c r="M189" s="40"/>
       <c r="N189" s="40"/>
       <c r="O189" s="1"/>
-      <c r="P189" s="1" t="s">
+      <c r="P189" s="1"/>
+    </row>
+    <row r="190" spans="1:17">
+      <c r="A190" s="36">
+        <v>109</v>
+      </c>
+      <c r="B190" s="3">
+        <v>108</v>
+      </c>
+      <c r="C190" s="36">
+        <v>157</v>
+      </c>
+      <c r="D190" s="3"/>
+      <c r="E190" s="89" t="s">
+        <v>650</v>
+      </c>
+      <c r="F190" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="G190" s="36">
+        <v>209</v>
+      </c>
+      <c r="H190" s="36">
+        <v>1</v>
+      </c>
+      <c r="I190" s="36">
+        <v>1</v>
+      </c>
+      <c r="J190" s="40" t="s">
+        <v>568</v>
+      </c>
+      <c r="K190" s="40"/>
+      <c r="L190" s="40"/>
+      <c r="M190" s="40"/>
+      <c r="N190" s="40"/>
+      <c r="O190" s="1"/>
+      <c r="P190" s="1" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="190" spans="1:17">
-      <c r="A190" s="61"/>
-      <c r="C190" s="61"/>
     </row>
     <row r="191" spans="1:17">
       <c r="A191" s="61"/>
       <c r="C191" s="61"/>
+    </row>
+    <row r="192" spans="1:17">
+      <c r="A192" s="61"/>
+      <c r="C192" s="61"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
@@ -13230,10 +13254,10 @@
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J166:J1048576 J1:J164">
+  <conditionalFormatting sqref="J167:J1048576 J1:J165">
     <cfRule type="duplicateValues" dxfId="7" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K166:K1048576 K1:K164">
+  <conditionalFormatting sqref="K167:K1048576 K1:K165">
     <cfRule type="duplicateValues" dxfId="6" priority="16"/>
     <cfRule type="duplicateValues" dxfId="5" priority="17"/>
   </conditionalFormatting>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A937983-5877-41CD-B8D2-B6E9DA066118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B615E0CC-F4DC-7146-8A27-1B5B8737AAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFP" sheetId="1" r:id="rId1"/>
@@ -1907,9 +1907,6 @@
     <t>2,17,210</t>
   </si>
   <si>
-    <t>2,10,11,12,13,15,210</t>
-  </si>
-  <si>
     <t>2,18,201</t>
   </si>
   <si>
@@ -2040,13 +2037,16 @@
   </si>
   <si>
     <t>mehrdimensionales Array</t>
+  </si>
+  <si>
+    <t>2,15,210</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2661,9 +2661,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2701,7 +2701,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2807,7 +2807,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2949,7 +2949,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2958,25 +2958,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I245"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="4" width="7.140625" customWidth="1"/>
+    <col min="1" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="4" width="7.1640625" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="9" width="28.42578125" customWidth="1"/>
+    <col min="6" max="9" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="96" t="s">
         <v>2</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30">
+    <row r="5" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="97" t="s">
         <v>7</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30">
+    <row r="6" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="94" t="s">
         <v>12</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30">
+    <row r="7" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="95" t="s">
         <v>17</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="60">
+    <row r="8" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="94" t="s">
         <v>22</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="45">
+    <row r="9" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>28</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="45">
+    <row r="10" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
         <v>32</v>
@@ -3124,7 +3124,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="45">
+    <row r="11" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
         <v>36</v>
@@ -3146,7 +3146,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30">
+    <row r="12" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
         <v>42</v>
@@ -3168,7 +3168,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="75">
+    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
         <v>46</v>
@@ -3190,7 +3190,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="60">
+    <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>50</v>
@@ -3210,7 +3210,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="94" t="s">
         <v>55</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="45">
+    <row r="16" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="95" t="s">
         <v>60</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="60">
+    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>65</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="2" t="s">
         <v>67</v>
@@ -3268,7 +3268,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="2" t="s">
         <v>69</v>
@@ -3277,7 +3277,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="2" t="s">
         <v>71</v>
@@ -3286,7 +3286,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="2" t="s">
         <v>73</v>
@@ -3295,7 +3295,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="2" t="s">
         <v>75</v>
@@ -3304,7 +3304,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="45">
+    <row r="24" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>77</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>67</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8" s="13" customFormat="1">
+    <row r="26" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -3358,7 +3358,7 @@
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
     </row>
-    <row r="27" spans="1:8" s="13" customFormat="1">
+    <row r="27" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>88</v>
@@ -3372,7 +3372,7 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" spans="1:8" s="13" customFormat="1">
+    <row r="28" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="11"/>
@@ -3384,7 +3384,7 @@
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>90</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
         <v>91</v>
@@ -3426,7 +3426,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="7"/>
@@ -3438,7 +3438,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>92</v>
       </c>
@@ -3450,7 +3450,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" s="13" customFormat="1">
+    <row r="34" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
@@ -3466,7 +3466,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" s="13" customFormat="1">
+    <row r="35" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="17"/>
       <c r="C35" s="2"/>
@@ -3478,7 +3478,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" s="13" customFormat="1">
+    <row r="36" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="17" t="s">
         <v>94</v>
@@ -3490,7 +3490,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" s="13" customFormat="1">
+    <row r="37" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
         <v>95</v>
@@ -3504,7 +3504,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" s="13" customFormat="1">
+    <row r="38" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3516,7 +3516,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" s="13" customFormat="1">
+    <row r="39" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>96</v>
@@ -3530,7 +3530,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" s="13" customFormat="1">
+    <row r="40" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3542,7 +3542,7 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" s="13" customFormat="1">
+    <row r="41" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
         <v>97</v>
@@ -3556,7 +3556,7 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" s="13" customFormat="1">
+    <row r="42" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3568,7 +3568,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" s="13" customFormat="1">
+    <row r="43" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
         <v>98</v>
@@ -3582,7 +3582,7 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" s="13" customFormat="1">
+    <row r="44" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3594,7 +3594,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" s="13" customFormat="1">
+    <row r="45" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
         <v>99</v>
@@ -3608,7 +3608,7 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" s="13" customFormat="1">
+    <row r="46" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3620,7 +3620,7 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" s="13" customFormat="1">
+    <row r="47" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
         <v>100</v>
@@ -3634,7 +3634,7 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" s="13" customFormat="1">
+    <row r="48" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3646,7 +3646,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" s="13" customFormat="1">
+    <row r="49" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
         <v>101</v>
@@ -3660,7 +3660,7 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" s="13" customFormat="1">
+    <row r="50" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3672,7 +3672,7 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" s="13" customFormat="1">
+    <row r="51" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>102</v>
       </c>
@@ -3684,7 +3684,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8" s="13" customFormat="1">
+    <row r="52" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>85</v>
       </c>
@@ -3698,7 +3698,7 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
         <v>103</v>
@@ -3712,7 +3712,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3724,7 +3724,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
         <v>105</v>
@@ -3736,7 +3736,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
         <v>106</v>
@@ -3750,7 +3750,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3762,7 +3762,7 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
         <v>107</v>
@@ -3776,7 +3776,7 @@
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3788,7 +3788,7 @@
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3800,7 +3800,7 @@
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>108</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>85</v>
       </c>
@@ -3828,7 +3828,7 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3840,7 +3840,7 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3852,7 +3852,7 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>109</v>
@@ -3866,7 +3866,7 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>110</v>
@@ -3880,7 +3880,7 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3892,7 +3892,7 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>111</v>
@@ -3906,7 +3906,7 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3918,7 +3918,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>112</v>
@@ -3932,7 +3932,7 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3944,7 +3944,7 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3956,7 +3956,7 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2" t="s">
         <v>113</v>
@@ -3970,7 +3970,7 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2" t="s">
         <v>114</v>
@@ -3984,7 +3984,7 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3996,7 +3996,7 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>73</v>
@@ -4010,7 +4010,7 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4022,7 +4022,7 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" ht="30">
+    <row r="78" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
         <v>115</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
         <v>85</v>
       </c>
@@ -4052,7 +4052,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
         <v>85</v>
       </c>
@@ -4068,7 +4068,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="1"/>
@@ -4080,7 +4080,7 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>60</v>
       </c>
@@ -4092,7 +4092,7 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>118</v>
@@ -4106,7 +4106,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4118,7 +4118,7 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>85</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4146,7 +4146,7 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4158,7 +4158,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
         <v>119</v>
@@ -4174,7 +4174,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>121</v>
       </c>
@@ -4188,7 +4188,7 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>85</v>
       </c>
@@ -4202,7 +4202,7 @@
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4214,7 +4214,7 @@
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4226,7 +4226,7 @@
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4238,7 +4238,7 @@
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4250,7 +4250,7 @@
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
         <v>109</v>
@@ -4264,7 +4264,7 @@
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4276,7 +4276,7 @@
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>122</v>
       </c>
@@ -4288,7 +4288,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2" t="s">
         <v>123</v>
@@ -4302,7 +4302,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4314,7 +4314,7 @@
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4326,7 +4326,7 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2" t="s">
         <v>124</v>
@@ -4340,7 +4340,7 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4352,7 +4352,7 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4364,7 +4364,7 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4376,7 +4376,7 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2" t="s">
         <v>125</v>
@@ -4390,7 +4390,7 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4402,7 +4402,7 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4414,7 +4414,7 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>126</v>
       </c>
@@ -4426,7 +4426,7 @@
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>85</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4454,7 +4454,7 @@
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1" t="s">
         <v>128</v>
@@ -4468,7 +4468,7 @@
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
         <v>129</v>
@@ -4482,7 +4482,7 @@
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
     </row>
-    <row r="114" spans="1:8" ht="30">
+    <row r="114" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="19" t="s">
         <v>130</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>131</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>132</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>131</v>
       </c>
@@ -4538,7 +4538,7 @@
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>92</v>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4564,7 +4564,7 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>131</v>
       </c>
@@ -4580,7 +4580,7 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4592,7 +4592,7 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2" t="s">
         <v>134</v>
@@ -4606,7 +4606,7 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -4618,7 +4618,7 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2" t="s">
         <v>135</v>
@@ -4632,7 +4632,7 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -4644,7 +4644,7 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2" t="s">
         <v>97</v>
@@ -4658,7 +4658,7 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -4670,7 +4670,7 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2" t="s">
         <v>93</v>
@@ -4684,7 +4684,7 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -4696,7 +4696,7 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -4708,7 +4708,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2" t="s">
         <v>136</v>
@@ -4722,7 +4722,7 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -4734,7 +4734,7 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
         <v>137</v>
@@ -4748,7 +4748,7 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -4760,7 +4760,7 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2" t="s">
         <v>138</v>
@@ -4774,7 +4774,7 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -4786,7 +4786,7 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2" t="s">
         <v>139</v>
@@ -4800,7 +4800,7 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -4812,7 +4812,7 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>90</v>
       </c>
@@ -4826,7 +4826,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>131</v>
       </c>
@@ -4840,7 +4840,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>140</v>
       </c>
@@ -4852,7 +4852,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>131</v>
       </c>
@@ -4868,7 +4868,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -4880,7 +4880,7 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2" t="s">
         <v>142</v>
@@ -4894,7 +4894,7 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -4906,7 +4906,7 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2" t="s">
         <v>143</v>
@@ -4920,7 +4920,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -4932,7 +4932,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2" t="s">
         <v>144</v>
@@ -4946,7 +4946,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -4958,7 +4958,7 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2" t="s">
         <v>145</v>
@@ -4972,7 +4972,7 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -4984,7 +4984,7 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>146</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>131</v>
       </c>
@@ -5012,7 +5012,7 @@
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5024,7 +5024,7 @@
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1" t="s">
         <v>147</v>
@@ -5038,7 +5038,7 @@
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5050,7 +5050,7 @@
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1" t="s">
         <v>105</v>
@@ -5064,7 +5064,7 @@
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5076,7 +5076,7 @@
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1" t="s">
         <v>106</v>
@@ -5090,7 +5090,7 @@
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5102,7 +5102,7 @@
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1" t="s">
         <v>148</v>
@@ -5116,7 +5116,7 @@
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5128,7 +5128,7 @@
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
         <v>149</v>
@@ -5142,7 +5142,7 @@
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5154,7 +5154,7 @@
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="17" t="s">
         <v>126</v>
       </c>
@@ -5166,7 +5166,7 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>131</v>
       </c>
@@ -5182,7 +5182,7 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="17"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -5194,7 +5194,7 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2" t="s">
         <v>151</v>
@@ -5208,7 +5208,7 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -5220,7 +5220,7 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2" t="s">
         <v>152</v>
@@ -5234,7 +5234,7 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -5246,7 +5246,7 @@
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>153</v>
       </c>
@@ -5258,7 +5258,7 @@
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>131</v>
       </c>
@@ -5274,7 +5274,7 @@
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5286,7 +5286,7 @@
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1" t="s">
         <v>155</v>
@@ -5300,7 +5300,7 @@
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5312,7 +5312,7 @@
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1" t="s">
         <v>156</v>
@@ -5326,7 +5326,7 @@
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5338,7 +5338,7 @@
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1" t="s">
         <v>157</v>
@@ -5352,7 +5352,7 @@
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5364,7 +5364,7 @@
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1" t="s">
         <v>158</v>
@@ -5378,7 +5378,7 @@
       <c r="G181" s="1"/>
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5390,7 +5390,7 @@
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1" t="s">
         <v>159</v>
@@ -5404,7 +5404,7 @@
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5416,7 +5416,7 @@
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5428,7 +5428,7 @@
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>160</v>
       </c>
@@ -5444,7 +5444,7 @@
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>131</v>
       </c>
@@ -5458,7 +5458,7 @@
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2" t="s">
         <v>162</v>
@@ -5472,7 +5472,7 @@
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -5484,7 +5484,7 @@
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2" t="s">
         <v>163</v>
@@ -5498,7 +5498,7 @@
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -5510,7 +5510,7 @@
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2" t="s">
         <v>121</v>
@@ -5524,7 +5524,7 @@
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -5536,7 +5536,7 @@
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>164</v>
       </c>
@@ -5552,7 +5552,7 @@
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5564,7 +5564,7 @@
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1" t="s">
         <v>165</v>
@@ -5578,7 +5578,7 @@
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5590,7 +5590,7 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1" t="s">
         <v>155</v>
@@ -5604,7 +5604,7 @@
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5616,7 +5616,7 @@
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1" t="s">
         <v>153</v>
@@ -5630,7 +5630,7 @@
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -5642,7 +5642,7 @@
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1" t="s">
         <v>166</v>
@@ -5656,7 +5656,7 @@
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -5668,7 +5668,7 @@
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1" t="s">
         <v>167</v>
@@ -5682,7 +5682,7 @@
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -5694,7 +5694,7 @@
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1" t="s">
         <v>168</v>
@@ -5708,7 +5708,7 @@
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -5720,7 +5720,7 @@
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1" t="s">
         <v>169</v>
@@ -5734,7 +5734,7 @@
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -5746,7 +5746,7 @@
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1" t="s">
         <v>170</v>
@@ -5760,7 +5760,7 @@
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -5772,7 +5772,7 @@
       <c r="G211" s="1"/>
       <c r="H211" s="1"/>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>171</v>
       </c>
@@ -5788,7 +5788,7 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -5800,7 +5800,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>131</v>
       </c>
@@ -5816,7 +5816,7 @@
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -5828,7 +5828,7 @@
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>164</v>
       </c>
@@ -5844,7 +5844,7 @@
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -5856,7 +5856,7 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -5868,7 +5868,7 @@
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
       <c r="B219" s="2" t="s">
         <v>171</v>
@@ -5882,7 +5882,7 @@
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -5894,7 +5894,7 @@
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -5906,7 +5906,7 @@
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>175</v>
       </c>
@@ -5920,7 +5920,7 @@
       <c r="G222" s="1"/>
       <c r="H222" s="1"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>131</v>
       </c>
@@ -5934,7 +5934,7 @@
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1" t="s">
         <v>176</v>
@@ -5948,7 +5948,7 @@
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -5960,7 +5960,7 @@
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>177</v>
       </c>
@@ -5976,7 +5976,7 @@
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -5988,7 +5988,7 @@
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>131</v>
       </c>
@@ -6004,7 +6004,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -6016,7 +6016,7 @@
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -6028,7 +6028,7 @@
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -6040,7 +6040,7 @@
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
         <v>180</v>
       </c>
@@ -6052,7 +6052,7 @@
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1" t="s">
         <v>181</v>
@@ -6066,7 +6066,7 @@
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -6078,7 +6078,7 @@
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>131</v>
       </c>
@@ -6094,7 +6094,7 @@
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -6106,7 +6106,7 @@
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -6118,7 +6118,7 @@
       <c r="G237" s="1"/>
       <c r="H237" s="1"/>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1" t="s">
         <v>183</v>
@@ -6132,7 +6132,7 @@
       <c r="G238" s="1"/>
       <c r="H238" s="1"/>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -6144,7 +6144,7 @@
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -6156,7 +6156,7 @@
       <c r="G240" s="1"/>
       <c r="H240" s="1"/>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
         <v>36</v>
       </c>
@@ -6170,7 +6170,7 @@
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>131</v>
       </c>
@@ -6184,7 +6184,7 @@
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>184</v>
       </c>
@@ -6198,7 +6198,7 @@
       <c r="G243" s="1"/>
       <c r="H243" s="1"/>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>131</v>
       </c>
@@ -6214,7 +6214,7 @@
       <c r="G244" s="1"/>
       <c r="H244" s="1"/>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -6436,28 +6436,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AMJ195"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="22" customWidth="1"/>
-    <col min="6" max="6" width="43.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" customWidth="1"/>
-    <col min="10" max="10" width="36.140625" customWidth="1"/>
-    <col min="11" max="11" width="37.7109375" customWidth="1"/>
-    <col min="12" max="12" width="45.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="18.5" style="22" customWidth="1"/>
+    <col min="6" max="6" width="43.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" customWidth="1"/>
+    <col min="10" max="10" width="36.1640625" customWidth="1"/>
+    <col min="11" max="11" width="37.6640625" customWidth="1"/>
+    <col min="12" max="12" width="45.1640625" customWidth="1"/>
     <col min="13" max="13" width="41" customWidth="1"/>
-    <col min="14" max="14" width="32.7109375" customWidth="1"/>
+    <col min="14" max="14" width="32.6640625" customWidth="1"/>
     <col min="15" max="15" width="32" customWidth="1"/>
-    <col min="16" max="16" width="63.7109375" customWidth="1"/>
-    <col min="1024" max="1024" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="63.6640625" customWidth="1"/>
+    <col min="1024" max="1024" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30">
+    <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>186</v>
       </c>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Q1" s="24"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -6536,7 +6536,7 @@
       <c r="O2" s="5"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
         <v>4</v>
       </c>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="Q3" s="35"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
         <v>5</v>
       </c>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="Q4" s="35"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="28"/>
       <c r="B5" s="21"/>
       <c r="C5" s="28">
@@ -6645,7 +6645,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="36">
         <v>6</v>
       </c>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="Q6" s="35"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="36"/>
       <c r="B7" s="3"/>
       <c r="C7" s="36">
@@ -6715,7 +6715,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="35"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="36"/>
       <c r="B8" s="3"/>
       <c r="C8" s="36">
@@ -6742,7 +6742,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="35"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="36">
         <v>7</v>
       </c>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="Q9" s="42"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="36"/>
       <c r="B10" s="3"/>
       <c r="C10" s="36">
@@ -6812,7 +6812,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="42"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="36"/>
       <c r="B11" s="3"/>
       <c r="C11" s="36">
@@ -6839,7 +6839,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="42"/>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
         <v>210</v>
       </c>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="Q12" s="35"/>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
         <v>8</v>
       </c>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="Q13" s="35"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
         <v>9</v>
       </c>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="Q14" s="42"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="28"/>
       <c r="B15" s="21"/>
       <c r="C15" s="28">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Q15" s="42"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="28"/>
       <c r="B16" s="21"/>
       <c r="C16" s="28">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="Q16" s="42"/>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
         <v>10</v>
       </c>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="Q17" s="35"/>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
         <v>11</v>
       </c>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Q18" s="35"/>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
         <v>12</v>
       </c>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Q19" s="35"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="28"/>
       <c r="B20" s="21"/>
       <c r="C20" s="28">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="Q20" s="35"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
         <v>13</v>
       </c>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
         <v>14</v>
       </c>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Q22" s="35"/>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="28"/>
       <c r="B23" s="21"/>
       <c r="C23" s="28">
@@ -7275,7 +7275,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="35"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
         <v>16</v>
       </c>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="Q24" s="35"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="28">
         <v>17</v>
       </c>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="Q25" s="35"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="28"/>
       <c r="B26" s="21"/>
       <c r="C26" s="28">
@@ -7388,7 +7388,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="35"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
         <v>15</v>
       </c>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="88" t="s">
-        <v>615</v>
+        <v>659</v>
       </c>
       <c r="F27" s="46" t="s">
         <v>100</v>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="Q27" s="35"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="28"/>
       <c r="B28" s="21"/>
       <c r="C28" s="28">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="D28" s="21"/>
       <c r="E28" s="88" t="s">
-        <v>615</v>
+        <v>659</v>
       </c>
       <c r="F28" s="46" t="s">
         <v>100</v>
@@ -7458,7 +7458,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="35"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="28"/>
       <c r="B29" s="21"/>
       <c r="C29" s="28">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="D29" s="21"/>
       <c r="E29" s="88" t="s">
-        <v>615</v>
+        <v>659</v>
       </c>
       <c r="F29" s="46" t="s">
         <v>100</v>
@@ -7485,7 +7485,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="35"/>
     </row>
-    <row r="30" spans="1:17" s="72" customFormat="1">
+    <row r="30" spans="1:17" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="66">
         <v>201</v>
       </c>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="Q30" s="71"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="36">
         <v>18</v>
       </c>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="89" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>102</v>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="Q31" s="35"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="36">
         <v>19</v>
       </c>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="89" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F32" s="41" t="s">
         <v>103</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Q32" s="42"/>
     </row>
-    <row r="33" spans="1:1024">
+    <row r="33" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A33" s="36"/>
       <c r="B33" s="3"/>
       <c r="C33" s="36">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="89" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F33" s="41" t="s">
         <v>103</v>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="Q33" s="42"/>
     </row>
-    <row r="34" spans="1:1024">
+    <row r="34" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A34" s="36"/>
       <c r="B34" s="3"/>
       <c r="C34" s="36">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="89" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F34" s="41" t="s">
         <v>103</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="Q34" s="42"/>
     </row>
-    <row r="35" spans="1:1024">
+    <row r="35" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="36">
         <v>20</v>
       </c>
@@ -7670,7 +7670,7 @@
       <c r="C35" s="36"/>
       <c r="D35" s="3"/>
       <c r="E35" s="89" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F35" s="41" t="s">
         <v>105</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Q35" s="35"/>
     </row>
-    <row r="36" spans="1:1024">
+    <row r="36" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="36">
         <v>21</v>
       </c>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="89" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F36" s="49" t="s">
         <v>251</v>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="Q36" s="35"/>
     </row>
-    <row r="37" spans="1:1024">
+    <row r="37" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="36"/>
       <c r="B37" s="3"/>
       <c r="C37" s="36">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="89" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F37" s="49" t="s">
         <v>251</v>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="Q37" s="35"/>
     </row>
-    <row r="38" spans="1:1024">
+    <row r="38" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A38" s="36">
         <v>22</v>
       </c>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="89" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F38" s="49" t="s">
         <v>256</v>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="Q38" s="42"/>
     </row>
-    <row r="39" spans="1:1024">
+    <row r="39" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A39" s="36"/>
       <c r="B39" s="3"/>
       <c r="C39" s="36">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="89" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F39" s="49" t="s">
         <v>256</v>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="Q39" s="42"/>
     </row>
-    <row r="40" spans="1:1024">
+    <row r="40" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A40" s="36"/>
       <c r="B40" s="3"/>
       <c r="C40" s="36">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="89" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F40" s="49" t="s">
         <v>256</v>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="Q40" s="42"/>
     </row>
-    <row r="41" spans="1:1024" s="85" customFormat="1">
+    <row r="41" spans="1:1024" s="85" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="50">
         <v>211</v>
       </c>
@@ -7906,7 +7906,7 @@
       <c r="Q41" s="84"/>
       <c r="AMJ41" s="86"/>
     </row>
-    <row r="42" spans="1:1024" s="85" customFormat="1">
+    <row r="42" spans="1:1024" s="85" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="50">
         <v>39</v>
       </c>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="D42" s="51"/>
       <c r="E42" s="90" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F42" s="51" t="s">
         <v>126</v>
@@ -7942,7 +7942,7 @@
       <c r="Q42" s="84"/>
       <c r="AMJ42" s="86"/>
     </row>
-    <row r="43" spans="1:1024" s="55" customFormat="1">
+    <row r="43" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50">
         <v>40</v>
       </c>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="D43" s="51"/>
       <c r="E43" s="90" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F43" s="56" t="s">
         <v>127</v>
@@ -7986,7 +7986,7 @@
       <c r="Q43" s="57"/>
       <c r="AMJ43"/>
     </row>
-    <row r="44" spans="1:1024" s="55" customFormat="1">
+    <row r="44" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="50"/>
       <c r="B44" s="51"/>
       <c r="C44" s="50">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="D44" s="51"/>
       <c r="E44" s="90" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F44" s="56" t="s">
         <v>127</v>
@@ -8018,7 +8018,7 @@
       <c r="Q44" s="57"/>
       <c r="AMJ44"/>
     </row>
-    <row r="45" spans="1:1024" s="55" customFormat="1">
+    <row r="45" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="50"/>
       <c r="B45" s="51"/>
       <c r="C45" s="50">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D45" s="51"/>
       <c r="E45" s="90" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F45" s="56" t="s">
         <v>127</v>
@@ -8050,7 +8050,7 @@
       <c r="Q45" s="57"/>
       <c r="AMJ45"/>
     </row>
-    <row r="46" spans="1:1024" s="55" customFormat="1">
+    <row r="46" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="50">
         <v>41</v>
       </c>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="D46" s="51"/>
       <c r="E46" s="90" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F46" s="56" t="s">
         <v>128</v>
@@ -8092,7 +8092,7 @@
       <c r="Q46" s="57"/>
       <c r="AMJ46"/>
     </row>
-    <row r="47" spans="1:1024" s="55" customFormat="1">
+    <row r="47" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="50"/>
       <c r="B47" s="51"/>
       <c r="C47" s="50">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="D47" s="51"/>
       <c r="E47" s="90" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F47" s="56" t="s">
         <v>128</v>
@@ -8124,7 +8124,7 @@
       <c r="Q47" s="57"/>
       <c r="AMJ47"/>
     </row>
-    <row r="48" spans="1:1024" s="55" customFormat="1">
+    <row r="48" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="50">
         <v>42</v>
       </c>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="D48" s="51"/>
       <c r="E48" s="90" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F48" s="56" t="s">
         <v>129</v>
@@ -8166,7 +8166,7 @@
       <c r="Q48" s="57"/>
       <c r="AMJ48"/>
     </row>
-    <row r="49" spans="1:1024" s="80" customFormat="1">
+    <row r="49" spans="1:1024" s="80" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="73">
         <v>202</v>
       </c>
@@ -8196,7 +8196,7 @@
       <c r="Q49" s="79"/>
       <c r="AMJ49" s="81"/>
     </row>
-    <row r="50" spans="1:1024" s="55" customFormat="1">
+    <row r="50" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="28">
         <v>23</v>
       </c>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="D50" s="21"/>
       <c r="E50" s="88" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F50" s="21" t="s">
         <v>108</v>
@@ -8236,7 +8236,7 @@
       <c r="Q50" s="54"/>
       <c r="AMJ50"/>
     </row>
-    <row r="51" spans="1:1024" s="55" customFormat="1">
+    <row r="51" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="28"/>
       <c r="B51" s="21"/>
       <c r="C51" s="28">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="D51" s="21"/>
       <c r="E51" s="88" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F51" s="21" t="s">
         <v>108</v>
@@ -8268,7 +8268,7 @@
       <c r="Q51" s="54"/>
       <c r="AMJ51"/>
     </row>
-    <row r="52" spans="1:1024" s="55" customFormat="1">
+    <row r="52" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="28"/>
       <c r="B52" s="21"/>
       <c r="C52" s="28">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="88" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F52" s="21" t="s">
         <v>108</v>
@@ -8304,7 +8304,7 @@
       <c r="Q52" s="54"/>
       <c r="AMJ52"/>
     </row>
-    <row r="53" spans="1:1024" s="55" customFormat="1">
+    <row r="53" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="28"/>
       <c r="B53" s="21"/>
       <c r="C53" s="28">
@@ -8342,7 +8342,7 @@
       <c r="Q53" s="54"/>
       <c r="AMJ53"/>
     </row>
-    <row r="54" spans="1:1024" s="55" customFormat="1">
+    <row r="54" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="28">
         <v>24</v>
       </c>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="D54" s="21"/>
       <c r="E54" s="88" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F54" s="33" t="s">
         <v>595</v>
@@ -8386,7 +8386,7 @@
       <c r="Q54" s="54"/>
       <c r="AMJ54"/>
     </row>
-    <row r="55" spans="1:1024" s="55" customFormat="1">
+    <row r="55" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="28">
         <v>25</v>
       </c>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D55" s="21"/>
       <c r="E55" s="88" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F55" s="33" t="s">
         <v>111</v>
@@ -8430,7 +8430,7 @@
       <c r="Q55" s="54"/>
       <c r="AMJ55"/>
     </row>
-    <row r="56" spans="1:1024" s="55" customFormat="1">
+    <row r="56" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="28"/>
       <c r="B56" s="21"/>
       <c r="C56" s="28">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="88" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F56" s="33" t="s">
         <v>111</v>
@@ -8462,7 +8462,7 @@
       <c r="Q56" s="54"/>
       <c r="AMJ56"/>
     </row>
-    <row r="57" spans="1:1024" s="55" customFormat="1">
+    <row r="57" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="28"/>
       <c r="B57" s="21"/>
       <c r="C57" s="28">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="88" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F57" s="33" t="s">
         <v>111</v>
@@ -8494,7 +8494,7 @@
       <c r="Q57" s="54"/>
       <c r="AMJ57"/>
     </row>
-    <row r="58" spans="1:1024" s="55" customFormat="1">
+    <row r="58" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="28">
         <v>26</v>
       </c>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="88" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F58" s="58" t="s">
         <v>112</v>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="AMJ58"/>
     </row>
-    <row r="59" spans="1:1024" s="55" customFormat="1">
+    <row r="59" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="28"/>
       <c r="B59" s="21"/>
       <c r="C59" s="28">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="D59" s="21"/>
       <c r="E59" s="88" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F59" s="58" t="s">
         <v>112</v>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="AMJ59"/>
     </row>
-    <row r="60" spans="1:1024" s="55" customFormat="1">
+    <row r="60" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="28"/>
       <c r="B60" s="21"/>
       <c r="C60" s="28">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="D60" s="21"/>
       <c r="E60" s="88" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F60" s="33" t="s">
         <v>113</v>
@@ -8604,7 +8604,7 @@
       <c r="Q60" s="54"/>
       <c r="AMJ60"/>
     </row>
-    <row r="61" spans="1:1024" s="55" customFormat="1">
+    <row r="61" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="28">
         <v>27</v>
       </c>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D61" s="21"/>
       <c r="E61" s="88" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F61" s="33" t="s">
         <v>114</v>
@@ -8648,7 +8648,7 @@
       <c r="Q61" s="54"/>
       <c r="AMJ61"/>
     </row>
-    <row r="62" spans="1:1024" s="55" customFormat="1">
+    <row r="62" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="28">
         <v>28</v>
       </c>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="D62" s="21"/>
       <c r="E62" s="88" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F62" s="33" t="s">
         <v>73</v>
@@ -8692,7 +8692,7 @@
       <c r="Q62" s="54"/>
       <c r="AMJ62"/>
     </row>
-    <row r="63" spans="1:1024" s="55" customFormat="1">
+    <row r="63" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="28"/>
       <c r="B63" s="21"/>
       <c r="C63" s="28">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="D63" s="21"/>
       <c r="E63" s="88" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F63" s="33" t="s">
         <v>73</v>
@@ -8724,7 +8724,7 @@
       <c r="Q63" s="54"/>
       <c r="AMJ63"/>
     </row>
-    <row r="64" spans="1:1024" s="55" customFormat="1">
+    <row r="64" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="28"/>
       <c r="B64" s="21"/>
       <c r="C64" s="28">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D64" s="21"/>
       <c r="E64" s="88" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F64" s="33" t="s">
         <v>73</v>
@@ -8756,7 +8756,7 @@
       <c r="Q64" s="54"/>
       <c r="AMJ64"/>
     </row>
-    <row r="65" spans="1:1024" s="55" customFormat="1" ht="30">
+    <row r="65" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="36">
         <v>212</v>
       </c>
@@ -8790,7 +8790,7 @@
       <c r="Q65" s="54"/>
       <c r="AMJ65"/>
     </row>
-    <row r="66" spans="1:1024" s="55" customFormat="1" ht="30">
+    <row r="66" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="36">
         <v>29</v>
       </c>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="89" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F66" s="37" t="s">
         <v>115</v>
@@ -8832,7 +8832,7 @@
       <c r="Q66" s="54"/>
       <c r="AMJ66"/>
     </row>
-    <row r="67" spans="1:1024" s="55" customFormat="1">
+    <row r="67" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="36">
         <v>30</v>
       </c>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="89" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F67" s="59" t="s">
         <v>117</v>
@@ -8874,7 +8874,7 @@
       <c r="Q67" s="57"/>
       <c r="AMJ67"/>
     </row>
-    <row r="68" spans="1:1024" s="55" customFormat="1">
+    <row r="68" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="36"/>
       <c r="B68" s="3"/>
       <c r="C68" s="36">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="89" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F68" s="59" t="s">
         <v>117</v>
@@ -8906,7 +8906,7 @@
       <c r="Q68" s="57"/>
       <c r="AMJ68"/>
     </row>
-    <row r="69" spans="1:1024" s="55" customFormat="1">
+    <row r="69" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="50">
         <v>34</v>
       </c>
@@ -8954,7 +8954,7 @@
       <c r="Q69" s="54"/>
       <c r="AMJ69"/>
     </row>
-    <row r="70" spans="1:1024" s="55" customFormat="1">
+    <row r="70" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="50"/>
       <c r="B70" s="51"/>
       <c r="C70" s="50">
@@ -8986,7 +8986,7 @@
       <c r="Q70" s="54"/>
       <c r="AMJ70"/>
     </row>
-    <row r="71" spans="1:1024" s="55" customFormat="1">
+    <row r="71" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="50"/>
       <c r="B71" s="51"/>
       <c r="C71" s="50">
@@ -9018,7 +9018,7 @@
       <c r="Q71" s="54"/>
       <c r="AMJ71"/>
     </row>
-    <row r="72" spans="1:1024" s="55" customFormat="1">
+    <row r="72" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="50"/>
       <c r="B72" s="51"/>
       <c r="C72" s="50">
@@ -9052,7 +9052,7 @@
       <c r="Q72" s="54"/>
       <c r="AMJ72"/>
     </row>
-    <row r="73" spans="1:1024" s="55" customFormat="1">
+    <row r="73" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="50"/>
       <c r="B73" s="51"/>
       <c r="C73" s="50">
@@ -9090,12 +9090,12 @@
       <c r="Q73" s="57"/>
       <c r="AMJ73"/>
     </row>
-    <row r="74" spans="1:1024" s="55" customFormat="1">
+    <row r="74" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="28">
         <v>31</v>
       </c>
       <c r="B74" s="88" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C74" s="28"/>
       <c r="D74" s="21"/>
@@ -9122,7 +9122,7 @@
       <c r="Q74" s="54"/>
       <c r="AMJ74"/>
     </row>
-    <row r="75" spans="1:1024" s="55" customFormat="1">
+    <row r="75" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="28">
         <v>32</v>
       </c>
@@ -9164,7 +9164,7 @@
       <c r="Q75" s="54"/>
       <c r="AMJ75"/>
     </row>
-    <row r="76" spans="1:1024" s="55" customFormat="1">
+    <row r="76" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="28"/>
       <c r="B76" s="21"/>
       <c r="C76" s="28">
@@ -9196,7 +9196,7 @@
       <c r="Q76" s="54"/>
       <c r="AMJ76"/>
     </row>
-    <row r="77" spans="1:1024" s="55" customFormat="1">
+    <row r="77" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="28"/>
       <c r="B77" s="21"/>
       <c r="C77" s="28">
@@ -9234,7 +9234,7 @@
       <c r="Q77" s="57"/>
       <c r="AMJ77"/>
     </row>
-    <row r="78" spans="1:1024" s="55" customFormat="1">
+    <row r="78" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="28">
         <v>33</v>
       </c>
@@ -9276,7 +9276,7 @@
       <c r="Q78" s="54"/>
       <c r="AMJ78"/>
     </row>
-    <row r="79" spans="1:1024" s="55" customFormat="1">
+    <row r="79" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="36">
         <v>35</v>
       </c>
@@ -9310,7 +9310,7 @@
       <c r="Q79" s="54"/>
       <c r="AMJ79"/>
     </row>
-    <row r="80" spans="1:1024" s="55" customFormat="1">
+    <row r="80" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="36">
         <v>36</v>
       </c>
@@ -9354,7 +9354,7 @@
       <c r="Q80" s="57"/>
       <c r="AMJ80"/>
     </row>
-    <row r="81" spans="1:1024" s="55" customFormat="1">
+    <row r="81" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="36"/>
       <c r="B81" s="3"/>
       <c r="C81" s="36">
@@ -9386,7 +9386,7 @@
       <c r="Q81" s="57"/>
       <c r="AMJ81"/>
     </row>
-    <row r="82" spans="1:1024" s="55" customFormat="1">
+    <row r="82" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="36"/>
       <c r="B82" s="3"/>
       <c r="C82" s="36">
@@ -9418,7 +9418,7 @@
       <c r="Q82" s="57"/>
       <c r="AMJ82"/>
     </row>
-    <row r="83" spans="1:1024" s="55" customFormat="1">
+    <row r="83" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="36">
         <v>37</v>
       </c>
@@ -9458,7 +9458,7 @@
       <c r="Q83" s="57"/>
       <c r="AMJ83"/>
     </row>
-    <row r="84" spans="1:1024" s="55" customFormat="1">
+    <row r="84" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="36"/>
       <c r="B84" s="3"/>
       <c r="C84" s="36">
@@ -9490,7 +9490,7 @@
       <c r="Q84" s="57"/>
       <c r="AMJ84"/>
     </row>
-    <row r="85" spans="1:1024" s="55" customFormat="1">
+    <row r="85" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="36"/>
       <c r="B85" s="3"/>
       <c r="C85" s="36">
@@ -9522,7 +9522,7 @@
       <c r="Q85" s="57"/>
       <c r="AMJ85"/>
     </row>
-    <row r="86" spans="1:1024" s="55" customFormat="1">
+    <row r="86" spans="1:1024" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="36"/>
       <c r="B86" s="3"/>
       <c r="C86" s="36">
@@ -9554,7 +9554,7 @@
       <c r="Q86" s="54"/>
       <c r="AMJ86"/>
     </row>
-    <row r="87" spans="1:1024" s="55" customFormat="1">
+    <row r="87" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="36">
         <v>38</v>
       </c>
@@ -9598,7 +9598,7 @@
       <c r="Q87" s="57"/>
       <c r="AMJ87"/>
     </row>
-    <row r="88" spans="1:1024" s="55" customFormat="1">
+    <row r="88" spans="1:1024" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="36"/>
       <c r="B88" s="3"/>
       <c r="C88" s="36">
@@ -9630,7 +9630,7 @@
       <c r="Q88" s="57"/>
       <c r="AMJ88"/>
     </row>
-    <row r="89" spans="1:1024">
+    <row r="89" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A89" s="61">
         <v>43</v>
       </c>
@@ -9657,7 +9657,7 @@
       <c r="N89" s="63"/>
       <c r="Q89" s="42"/>
     </row>
-    <row r="90" spans="1:1024">
+    <row r="90" spans="1:1024" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="28">
         <v>44</v>
       </c>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="Q90" s="42"/>
     </row>
-    <row r="91" spans="1:1024">
+    <row r="91" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A91" s="36">
         <v>45</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="Q91" s="42"/>
     </row>
-    <row r="92" spans="1:1024">
+    <row r="92" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A92" s="28">
         <v>204</v>
       </c>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="Q92" s="42"/>
     </row>
-    <row r="93" spans="1:1024">
+    <row r="93" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A93" s="28">
         <v>46</v>
       </c>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D93" s="21"/>
       <c r="E93" s="88" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F93" s="21" t="s">
         <v>92</v>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="Q93" s="42"/>
     </row>
-    <row r="94" spans="1:1024">
+    <row r="94" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A94" s="28">
         <v>47</v>
       </c>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D94" s="21"/>
       <c r="E94" s="88" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F94" s="33" t="s">
         <v>133</v>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="Q94" s="42"/>
     </row>
-    <row r="95" spans="1:1024">
+    <row r="95" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A95" s="28">
         <v>48</v>
       </c>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="D95" s="21"/>
       <c r="E95" s="88" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F95" s="33" t="s">
         <v>134</v>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="Q95" s="42"/>
     </row>
-    <row r="96" spans="1:1024">
+    <row r="96" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A96" s="28">
         <v>49</v>
       </c>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="D96" s="21"/>
       <c r="E96" s="88" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F96" s="33" t="s">
         <v>135</v>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="Q96" s="42"/>
     </row>
-    <row r="97" spans="1:17">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="28">
         <v>50</v>
       </c>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="D97" s="21"/>
       <c r="E97" s="88" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F97" s="33" t="s">
         <v>97</v>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="Q97" s="42"/>
     </row>
-    <row r="98" spans="1:17">
+    <row r="98" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="28">
         <v>54</v>
       </c>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="D98" s="21"/>
       <c r="E98" s="88" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F98" s="33" t="s">
         <v>138</v>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17">
+    <row r="99" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="28">
         <v>55</v>
       </c>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="88" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F99" s="33" t="s">
         <v>139</v>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" spans="1:17">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="36">
         <v>56</v>
       </c>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="Q100" s="42"/>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="28">
         <v>57</v>
       </c>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" spans="1:17">
+    <row r="102" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="28">
         <v>58</v>
       </c>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="28">
         <v>59</v>
       </c>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" spans="1:17">
+    <row r="104" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="28">
         <v>60</v>
       </c>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" spans="1:17">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="28">
         <v>61</v>
       </c>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="Q105" s="42"/>
     </row>
-    <row r="106" spans="1:17">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="28">
         <v>205</v>
       </c>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="D106" s="21"/>
       <c r="E106" s="88" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F106" s="33" t="s">
         <v>145</v>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="Q106" s="42"/>
     </row>
-    <row r="107" spans="1:17">
+    <row r="107" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="36">
         <v>62</v>
       </c>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" spans="1:17">
+    <row r="108" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="36">
         <v>63</v>
       </c>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" spans="1:17">
+    <row r="109" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="36"/>
       <c r="B109" s="3"/>
       <c r="C109" s="36">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="Q109" s="35"/>
     </row>
-    <row r="110" spans="1:17">
+    <row r="110" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="36"/>
       <c r="B110" s="3"/>
       <c r="C110" s="36">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Q110" s="35"/>
     </row>
-    <row r="111" spans="1:17">
+    <row r="111" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="36">
         <v>64</v>
       </c>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="Q111" s="35"/>
     </row>
-    <row r="112" spans="1:17">
+    <row r="112" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="36"/>
       <c r="B112" s="3"/>
       <c r="C112" s="36">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Q112" s="35"/>
     </row>
-    <row r="113" spans="1:17">
+    <row r="113" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="36">
         <v>65</v>
       </c>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="Q113" s="35"/>
     </row>
-    <row r="114" spans="1:17">
+    <row r="114" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="36"/>
       <c r="B114" s="3"/>
       <c r="C114" s="36">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="Q114" s="35"/>
     </row>
-    <row r="115" spans="1:17">
+    <row r="115" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="36">
         <v>66</v>
       </c>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="Q115" s="35"/>
     </row>
-    <row r="116" spans="1:17">
+    <row r="116" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="36">
         <v>67</v>
       </c>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="Q116" s="35"/>
     </row>
-    <row r="117" spans="1:17">
+    <row r="117" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="36"/>
       <c r="B117" s="3"/>
       <c r="C117" s="36">
@@ -10691,7 +10691,7 @@
       <c r="P117" s="1"/>
       <c r="Q117" s="35"/>
     </row>
-    <row r="118" spans="1:17">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="36"/>
       <c r="B118" s="3"/>
       <c r="C118" s="36">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="Q118" s="42"/>
     </row>
-    <row r="119" spans="1:17">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="28">
         <v>68</v>
       </c>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="Q119" s="42"/>
     </row>
-    <row r="120" spans="1:17">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="28">
         <v>203</v>
       </c>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="Q120" s="42"/>
     </row>
-    <row r="121" spans="1:17">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="28">
         <v>51</v>
       </c>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="D121" s="21"/>
       <c r="E121" s="88" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F121" s="33" t="s">
         <v>93</v>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="Q121" s="42"/>
     </row>
-    <row r="122" spans="1:17">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="28">
         <v>52</v>
       </c>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="D122" s="21"/>
       <c r="E122" s="88" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F122" s="46" t="s">
         <v>377</v>
@@ -10864,7 +10864,7 @@
       </c>
       <c r="Q122" s="42"/>
     </row>
-    <row r="123" spans="1:17">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="28"/>
       <c r="B123" s="21"/>
       <c r="C123" s="28">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="D123" s="21"/>
       <c r="E123" s="88" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F123" s="46" t="s">
         <v>377</v>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="Q123" s="42"/>
     </row>
-    <row r="124" spans="1:17">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="28"/>
       <c r="B124" s="21"/>
       <c r="C124" s="28">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="D124" s="21"/>
       <c r="E124" s="88" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F124" s="46" t="s">
         <v>377</v>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="Q124" s="42"/>
     </row>
-    <row r="125" spans="1:17">
+    <row r="125" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="28">
         <v>53</v>
       </c>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D125" s="21"/>
       <c r="E125" s="88" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F125" s="46" t="s">
         <v>160</v>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="Q125" s="35"/>
     </row>
-    <row r="126" spans="1:17">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="28">
         <v>213</v>
       </c>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="Q126" s="42"/>
     </row>
-    <row r="127" spans="1:17">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127" s="28">
         <v>69</v>
       </c>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="Q127" s="42"/>
     </row>
-    <row r="128" spans="1:17">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128" s="28"/>
       <c r="B128" s="21"/>
       <c r="C128" s="28">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="Q128" s="42"/>
     </row>
-    <row r="129" spans="1:17">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="28"/>
       <c r="B129" s="21"/>
       <c r="C129" s="28">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="Q129" s="42"/>
     </row>
-    <row r="130" spans="1:17">
+    <row r="130" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="28">
         <v>70</v>
       </c>
@@ -11100,7 +11100,7 @@
         <v>441</v>
       </c>
       <c r="F130" s="92" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G130" s="28">
         <v>213</v>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="Q130" s="35"/>
     </row>
-    <row r="131" spans="1:17">
+    <row r="131" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="28"/>
       <c r="B131" s="21"/>
       <c r="C131" s="28">
@@ -11135,7 +11135,7 @@
         <v>441</v>
       </c>
       <c r="F131" s="92" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G131" s="28"/>
       <c r="H131" s="28"/>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="Q131" s="35"/>
     </row>
-    <row r="132" spans="1:17">
+    <row r="132" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="28"/>
       <c r="B132" s="21"/>
       <c r="C132" s="28">
@@ -11164,7 +11164,7 @@
         <v>441</v>
       </c>
       <c r="F132" s="92" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G132" s="28"/>
       <c r="H132" s="28"/>
@@ -11182,7 +11182,7 @@
       </c>
       <c r="Q132" s="35"/>
     </row>
-    <row r="133" spans="1:17">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A133" s="36">
         <v>72</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="134" spans="1:17">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A134" s="36">
         <v>73</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="135" spans="1:17">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A135" s="36"/>
       <c r="B135" s="3"/>
       <c r="C135" s="36">
@@ -11276,7 +11276,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="136" spans="1:17">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A136" s="36">
         <v>75</v>
       </c>
@@ -11314,7 +11314,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="137" spans="1:17">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A137" s="36"/>
       <c r="B137" s="3"/>
       <c r="C137" s="36">
@@ -11342,7 +11342,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="138" spans="1:17">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A138" s="36"/>
       <c r="B138" s="3"/>
       <c r="C138" s="36">
@@ -11370,7 +11370,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="139" spans="1:17">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A139" s="36">
         <v>76</v>
       </c>
@@ -11410,7 +11410,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="140" spans="1:17">
+    <row r="140" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="36">
         <v>78</v>
       </c>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="Q140" s="35"/>
     </row>
-    <row r="141" spans="1:17">
+    <row r="141" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="36"/>
       <c r="B141" s="3"/>
       <c r="C141" s="36">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="Q141" s="35"/>
     </row>
-    <row r="142" spans="1:17">
+    <row r="142" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="36"/>
       <c r="B142" s="3"/>
       <c r="C142" s="36">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="Q142" s="35"/>
     </row>
-    <row r="143" spans="1:17">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A143" s="36">
         <v>79</v>
       </c>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="Q143" s="42"/>
     </row>
-    <row r="144" spans="1:17">
+    <row r="144" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="28">
         <v>80</v>
       </c>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="Q144" s="35"/>
     </row>
-    <row r="145" spans="1:17">
+    <row r="145" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="28">
         <v>81</v>
       </c>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="Q145" s="35"/>
     </row>
-    <row r="146" spans="1:17">
+    <row r="146" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="28">
         <v>82</v>
       </c>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="Q146" s="35"/>
     </row>
-    <row r="147" spans="1:17">
+    <row r="147" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="28">
         <v>83</v>
       </c>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="Q147" s="35"/>
     </row>
-    <row r="148" spans="1:17">
+    <row r="148" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A148" s="28"/>
       <c r="B148" s="21"/>
       <c r="C148" s="28">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="Q148" s="35"/>
     </row>
-    <row r="149" spans="1:17">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A149" s="28">
         <v>84</v>
       </c>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="Q149" s="42"/>
     </row>
-    <row r="150" spans="1:17">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A150" s="28"/>
       <c r="B150" s="21"/>
       <c r="C150" s="28">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="Q150" s="42"/>
     </row>
-    <row r="151" spans="1:17">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A151" s="28"/>
       <c r="B151" s="21"/>
       <c r="C151" s="28">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Q151" s="42"/>
     </row>
-    <row r="152" spans="1:17">
+    <row r="152" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="36">
         <v>206</v>
       </c>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="Q152" s="35"/>
     </row>
-    <row r="153" spans="1:17">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A153" s="36">
         <v>85</v>
       </c>
@@ -11873,7 +11873,7 @@
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="89" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F153" s="41" t="s">
         <v>164</v>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="Q153" s="42"/>
     </row>
-    <row r="154" spans="1:17">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A154" s="36"/>
       <c r="B154" s="3"/>
       <c r="C154" s="36">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="89" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F154" s="41" t="s">
         <v>164</v>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="Q154" s="42"/>
     </row>
-    <row r="155" spans="1:17">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A155" s="36"/>
       <c r="B155" s="3"/>
       <c r="C155" s="36">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="D155" s="3"/>
       <c r="E155" s="89" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F155" s="41" t="s">
         <v>164</v>
@@ -11960,7 +11960,7 @@
       </c>
       <c r="Q155" s="42"/>
     </row>
-    <row r="156" spans="1:17">
+    <row r="156" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="36"/>
       <c r="B156" s="3"/>
       <c r="C156" s="36">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="D156" s="3"/>
       <c r="E156" s="89" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F156" s="41" t="s">
         <v>165</v>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="Q156" s="35"/>
     </row>
-    <row r="157" spans="1:17">
+    <row r="157" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="36">
         <v>86</v>
       </c>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="D157" s="3"/>
       <c r="E157" s="89" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F157" s="41" t="s">
         <v>155</v>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="Q157" s="35"/>
     </row>
-    <row r="158" spans="1:17">
+    <row r="158" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="36"/>
       <c r="B158" s="3"/>
       <c r="C158" s="36">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="89" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F158" s="41" t="s">
         <v>155</v>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="Q158" s="35"/>
     </row>
-    <row r="159" spans="1:17">
+    <row r="159" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="36">
         <v>87</v>
       </c>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="D159" s="3"/>
       <c r="E159" s="89" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F159" s="41" t="s">
         <v>153</v>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="Q159" s="35"/>
     </row>
-    <row r="160" spans="1:17">
+    <row r="160" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="36">
         <v>88</v>
       </c>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="D160" s="3"/>
       <c r="E160" s="89" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F160" s="41" t="s">
         <v>166</v>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="Q160" s="35"/>
     </row>
-    <row r="161" spans="1:17">
+    <row r="161" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="36">
         <v>89</v>
       </c>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="D161" s="3"/>
       <c r="E161" s="89" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F161" s="41" t="s">
         <v>167</v>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="Q161" s="35"/>
     </row>
-    <row r="162" spans="1:17">
+    <row r="162" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="36">
         <v>90</v>
       </c>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="89" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F162" s="41" t="s">
         <v>168</v>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="Q162" s="35"/>
     </row>
-    <row r="163" spans="1:17">
+    <row r="163" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="36">
         <v>91</v>
       </c>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="D163" s="3"/>
       <c r="E163" s="89" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F163" s="49" t="s">
         <v>505</v>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="Q163" s="35"/>
     </row>
-    <row r="164" spans="1:17">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A164" s="36">
         <v>92</v>
       </c>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="89" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F164" s="41" t="s">
         <v>170</v>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="Q164" s="42"/>
     </row>
-    <row r="165" spans="1:17">
+    <row r="165" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="28">
         <v>93</v>
       </c>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="Q165" s="35"/>
     </row>
-    <row r="166" spans="1:17">
+    <row r="166" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="28"/>
       <c r="B166" s="21"/>
       <c r="C166" s="28">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="Q166" s="35"/>
     </row>
-    <row r="167" spans="1:17">
+    <row r="167" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="28">
         <v>94</v>
       </c>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="Q167" s="35"/>
     </row>
-    <row r="168" spans="1:17">
+    <row r="168" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="28">
         <v>95</v>
       </c>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="Q168" s="35"/>
     </row>
-    <row r="169" spans="1:17">
+    <row r="169" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="28"/>
       <c r="B169" s="21"/>
       <c r="C169" s="28">
@@ -12478,7 +12478,7 @@
       <c r="P169" s="2"/>
       <c r="Q169" s="35"/>
     </row>
-    <row r="170" spans="1:17">
+    <row r="170" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="28"/>
       <c r="B170" s="21"/>
       <c r="C170" s="28">
@@ -12507,7 +12507,7 @@
       <c r="P170" s="2"/>
       <c r="Q170" s="35"/>
     </row>
-    <row r="171" spans="1:17">
+    <row r="171" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="28">
         <v>96</v>
       </c>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="Q171" s="35"/>
     </row>
-    <row r="172" spans="1:17">
+    <row r="172" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="28">
         <v>97</v>
       </c>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="Q172" s="35"/>
     </row>
-    <row r="173" spans="1:17">
+    <row r="173" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="28"/>
       <c r="B173" s="21"/>
       <c r="C173" s="28">
@@ -12622,7 +12622,7 @@
       <c r="P173" s="2"/>
       <c r="Q173" s="35"/>
     </row>
-    <row r="174" spans="1:17">
+    <row r="174" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="36">
         <v>207</v>
       </c>
@@ -12633,7 +12633,7 @@
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
       <c r="F174" s="89" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G174" s="36">
         <v>43</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="Q174" s="35"/>
     </row>
-    <row r="175" spans="1:17">
+    <row r="175" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="36">
         <v>98</v>
       </c>
@@ -12663,10 +12663,10 @@
       </c>
       <c r="D175" s="3"/>
       <c r="E175" s="89" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F175" s="89" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G175" s="36">
         <v>207</v>
@@ -12690,7 +12690,7 @@
       <c r="P175" s="1"/>
       <c r="Q175" s="35"/>
     </row>
-    <row r="176" spans="1:17">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A176" s="36">
         <v>99</v>
       </c>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="D176" s="3"/>
       <c r="E176" s="89" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F176" s="41" t="s">
         <v>176</v>
@@ -12730,7 +12730,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="177" spans="1:17">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A177" s="36"/>
       <c r="B177" s="3"/>
       <c r="C177" s="36">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="89" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F177" s="41" t="s">
         <v>176</v>
@@ -12758,7 +12758,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="178" spans="1:17">
+    <row r="178" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="28">
         <v>100</v>
       </c>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="Q178" s="35"/>
     </row>
-    <row r="179" spans="1:17">
+    <row r="179" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="28">
         <v>101</v>
       </c>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="Q179" s="35"/>
     </row>
-    <row r="180" spans="1:17">
+    <row r="180" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="28"/>
       <c r="B180" s="21"/>
       <c r="C180" s="28">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="Q180" s="35"/>
     </row>
-    <row r="181" spans="1:17">
+    <row r="181" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="28">
         <v>102</v>
       </c>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="D181" s="21"/>
       <c r="E181" s="88" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F181" s="33" t="s">
         <v>179</v>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="Q181" s="35"/>
     </row>
-    <row r="182" spans="1:17">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A182" s="28"/>
       <c r="B182" s="21"/>
       <c r="C182" s="28">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="D182" s="21"/>
       <c r="E182" s="88" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F182" s="21"/>
       <c r="G182" s="28"/>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="Q182" s="42"/>
     </row>
-    <row r="183" spans="1:17">
+    <row r="183" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A183" s="36">
         <v>103</v>
       </c>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="Q183" s="35"/>
     </row>
-    <row r="184" spans="1:17">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A184" s="28">
         <v>71</v>
       </c>
@@ -12998,7 +12998,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="185" spans="1:17">
+    <row r="185" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A185" s="36">
         <v>104</v>
       </c>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="Q185" s="35"/>
     </row>
-    <row r="186" spans="1:17">
+    <row r="186" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="36">
         <v>105</v>
       </c>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="Q186" s="35"/>
     </row>
-    <row r="187" spans="1:17">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A187" s="36">
         <v>106</v>
       </c>
@@ -13124,7 +13124,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="188" spans="1:17">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A188" s="28">
         <v>107</v>
       </c>
@@ -13162,7 +13162,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="189" spans="1:17">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A189" s="28"/>
       <c r="B189" s="21"/>
       <c r="C189" s="28">
@@ -13190,7 +13190,7 @@
       <c r="O189" s="2"/>
       <c r="P189" s="2"/>
     </row>
-    <row r="190" spans="1:17">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A190" s="28"/>
       <c r="B190" s="21"/>
       <c r="C190" s="28">
@@ -13218,7 +13218,7 @@
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
     </row>
-    <row r="191" spans="1:17">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A191" s="36">
         <v>209</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="192" spans="1:17">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A192" s="36">
         <v>108</v>
       </c>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="89" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>184</v>
@@ -13282,7 +13282,7 @@
       <c r="O192" s="1"/>
       <c r="P192" s="1"/>
     </row>
-    <row r="193" spans="1:16">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" s="36">
         <v>109</v>
       </c>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="89" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F193" s="41" t="s">
         <v>185</v>
@@ -13320,11 +13320,11 @@
         <v>569</v>
       </c>
     </row>
-    <row r="194" spans="1:16">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" s="61"/>
       <c r="C194" s="61"/>
     </row>
-    <row r="195" spans="1:16">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195" s="61"/>
       <c r="C195" s="61"/>
     </row>
@@ -13361,26 +13361,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="4" width="7.140625" customWidth="1"/>
+    <col min="1" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="4" width="7.1640625" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="8" width="28.42578125" customWidth="1"/>
-    <col min="10" max="10" width="42.85546875" customWidth="1"/>
+    <col min="6" max="8" width="28.5" customWidth="1"/>
+    <col min="10" max="10" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="96" t="s">
         <v>2</v>
       </c>
@@ -13405,7 +13405,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="45">
+    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="97"/>
       <c r="B5" s="97"/>
       <c r="C5" s="1" t="s">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="45">
+    <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="21"/>
       <c r="B6" s="21"/>
       <c r="C6" s="2"/>
@@ -13441,7 +13441,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="60">
+    <row r="7" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="21"/>
       <c r="B7" s="21"/>
       <c r="C7" s="2"/>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="60">
+    <row r="8" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" s="21"/>
       <c r="B8" s="21"/>
       <c r="C8" s="2"/>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="30">
+    <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="2"/>
@@ -13492,7 +13492,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30">
+    <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="2"/>
@@ -13511,7 +13511,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30">
+    <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="2"/>
@@ -13530,7 +13530,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="30">
+    <row r="12" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="2"/>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="30">
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="2"/>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="30">
+    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="2"/>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="30">
+    <row r="15" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="2"/>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="60">
+    <row r="16" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="2"/>
@@ -13611,7 +13611,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="75">
+    <row r="17" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="2"/>
@@ -13624,11 +13624,11 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="62"/>
       <c r="B18" s="62"/>
     </row>
-    <row r="19" spans="1:10" ht="45">
+    <row r="19" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>77</v>
       </c>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E320A827-D8B3-3D4C-8A4C-54B08AF1B1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94294FCB-CC82-6445-8851-BA2C5A083473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6978,9 +6978,7 @@
       <c r="A15" s="28">
         <v>10</v>
       </c>
-      <c r="B15" s="21">
-        <v>8</v>
-      </c>
+      <c r="B15" s="21"/>
       <c r="C15" s="28"/>
       <c r="D15" s="21"/>
       <c r="E15" s="87" t="s">
@@ -7239,9 +7237,7 @@
       <c r="A22" s="28">
         <v>16</v>
       </c>
-      <c r="B22" s="21">
-        <v>8</v>
-      </c>
+      <c r="B22" s="21"/>
       <c r="C22" s="28">
         <v>14</v>
       </c>
@@ -7282,9 +7278,7 @@
       <c r="A23" s="28">
         <v>17</v>
       </c>
-      <c r="B23" s="21">
-        <v>8</v>
-      </c>
+      <c r="B23" s="21"/>
       <c r="C23" s="28">
         <v>15</v>
       </c>
@@ -7450,7 +7444,7 @@
         <v>201</v>
       </c>
       <c r="B28" s="67">
-        <v>210</v>
+        <v>8</v>
       </c>
       <c r="C28" s="66"/>
       <c r="D28" s="67"/>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94294FCB-CC82-6445-8851-BA2C5A083473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E64A08-9F2B-C348-B337-1B0C4B3A3815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6873,9 +6873,7 @@
       <c r="A12" s="28">
         <v>9</v>
       </c>
-      <c r="B12" s="21">
-        <v>8</v>
-      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="28">
         <v>6</v>
       </c>

--- a/files/Kompetenzraster.xlsx
+++ b/files/Kompetenzraster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsauer/GitHub/hefl/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D39B6AB-A399-4A4D-8EA8-09FB0051E9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A2D9EF-8E33-2A48-8614-3D70E6901550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="760" windowWidth="30240" windowHeight="17480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFP" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="632">
   <si>
     <t>Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -1032,9 +1032,6 @@
     <t>Funktionale Programmierung ist ein Paradigma, das mathematische Funktionen zur Strukturierung von Code verwendet und Konzepte wie Unveränderlichkeit von Daten und Funktionen höherer Ordnung betont. In Python ermöglicht es die Verwendung von Funktionen wie `map`, `filter`, `reduce` und Lambda-Ausdrücken, um Code zu schreiben, der klar, konzise und oft leichter zu verstehen ist.</t>
   </si>
   <si>
-    <t>2,31,32</t>
-  </si>
-  <si>
     <t>658c43ba-f341-44ec-acf7-ef3da6b292bf</t>
   </si>
   <si>
@@ -1044,24 +1041,15 @@
     <t>In Python können Variablen, die außerhalb einer Funktion definiert wurden, innerhalb der Funktion verwendet werden, sofern sie vor der Funktionsdefinition initialisiert wurden; sie gelten dann als globale Variablen. Lokale Variablen hingegen sind nur innerhalb der Funktion bekannt und Änderungen an ihnen sind außerhalb der Funktion nicht sichtbar, es sei denn, sie werden explizit als global innerhalb der Funktion deklariert.</t>
   </si>
   <si>
-    <t>2,31</t>
-  </si>
-  <si>
     <t>f294a4fc-c912-40ab-9d2c-9e341d79ab3b</t>
   </si>
   <si>
     <t>50cc4e39-6613-441c-bee2-60883a0ce4b7</t>
   </si>
   <si>
-    <t>Goofspiel funktionaler machen</t>
-  </si>
-  <si>
     <t>Das Transkript behandelt die Unterscheidung zwischen lokalen und globalen Variablen in Python und wie sie innerhalb von Funktionen verwendet werden können. Globale Variablen können innerhalb von Funktionen gelesen werden, wenn sie vorher definiert wurden, während lokale Variablen nur innerhalb der Funktion existieren und außerhalb nicht sichtbar sind. Es wird auch erklärt, wie man mit dem Schlüsselwort `global` eine lokale Variable in einer Funktion als global deklarieren kann, sodass Änderungen an ihr auch außerhalb der Funktion sichtbar sind.</t>
   </si>
   <si>
-    <t>2,31,33</t>
-  </si>
-  <si>
     <t>fdaf9cbc-2335-4b93-92d2-cae6c8e8c366</t>
   </si>
   <si>
@@ -1314,9 +1302,6 @@
     <t>Die Switch-Anweisung in Java ermöglicht es, einen Wert gegen eine Reihe von Konstanten zu prüfen und entsprechend unterschiedliche Blöcke von Anweisungen auszuführen. Jeder Block wird durch das Schlüsselwort "case" eingeleitet und muss mit einem "break" enden, um die Ausführung der Switch-Anweisung zu beenden; andernfalls wird die Ausführung fortgesetzt, bis ein "break" erreicht wird oder die gesamte Anweisung abgearbeitet ist, wobei "default" für alle nicht explizit aufgeführten Fälle verwendet wird.</t>
   </si>
   <si>
-    <t>43,62,65</t>
-  </si>
-  <si>
     <t>746c83ca-40a6-46ef-a6f5-8a229767ab50</t>
   </si>
   <si>
@@ -1326,9 +1311,6 @@
     <t>Java bietet verschiedene Schleifentypen für unterschiedliche Anwendungsfälle: Die for-Schleife eignet sich besonders, wenn die Anzahl der Durchläufe bekannt ist, wie etwa das Durchlaufen von Zahlenbereichen. Die while- und do-while-Schleifen sind hingegen nützlich, wenn die Anzahl der Wiederholungen nicht im Voraus bekannt ist, wobei die do-while-Schleife den Schleifenblock mindestens einmal ausführt, bevor die Bedingung geprüft wird, im Gegensatz zur while-Schleife, die die Bedingung vor dem ersten Durchlauf prüft.</t>
   </si>
   <si>
-    <t>43,62,65,66</t>
-  </si>
-  <si>
     <t>15d2c1fa-c6cf-4096-8ec7-c403ce84e552</t>
   </si>
   <si>
@@ -1338,9 +1320,6 @@
     <t>Die while-Schleife in Java beginnt mit dem Keyword "while", gefolgt von einer Bedingung in runden Klammern; wenn diese Bedingung wahr ist, werden die in geschweiften Klammern eingeschlossenen Anweisungen ausgeführt. Die do-while-Schleife hingegen führt die Anweisungen mindestens einmal aus, bevor die Bedingung am Ende der Schleife geprüft wird, und wiederholt den Vorgang, solange die Bedingung wahr ist.</t>
   </si>
   <si>
-    <t>43,62,65,67</t>
-  </si>
-  <si>
     <t>acf82bde-ab5e-4f91-9613-3cb9e339abf0</t>
   </si>
   <si>
@@ -1350,39 +1329,24 @@
     <t>Java bietet mit der For-Schleife eine Kontrollstruktur, die aus drei Teilen in runden Klammern besteht: Initialisierung (z.B. `int i = 0`), Bedingung (z.B. `i &lt;= 10`) und Inkrementierung (z.B. `i++`), die es ermöglichen, einen Codeblock wiederholt auszuführen, solange die Bedingung wahr ist. Es ist möglich, mehrere Operationen in den einzelnen Teilen der For-Schleife durchzuführen, aber üblicherweise wird sie für einfache Iterationen verwendet, wobei manchmal auch Befehle wie `continue` und `break` genutzt werden können, um die Schleifenausführung zu steuern.</t>
   </si>
   <si>
-    <t>43,62,65,66,67</t>
-  </si>
-  <si>
-    <t>Beispiele</t>
-  </si>
-  <si>
     <t>2fc1faa3-550a-4714-a93c-eabeacdae78f</t>
   </si>
   <si>
     <t>f6e07b01-b881-497c-b9fe-edf3ed625ca0</t>
   </si>
   <si>
-    <t>In dem Beispiel BigX wird gezeigt, wie man mit Java Kontrollstrukturen wie for-Schleifen und if-Anweisungen ein großes "X" in der Konsole darstellen kann. Die Größe des "X" wird durch eine Variable bestimmt, und durch geschachtelte for-Schleifen und Bedingungen wird für jede Zeile und Spalte entschieden, ob ein "X" oder ein Leerzeichen ausgegeben wird, um die Form des "X" zu erzeugen.</t>
-  </si>
-  <si>
     <t>Datenstrukturen sind Sammlungen von Datenwerten, die Beziehungen untereinander aufweisen und ermöglichen es, Daten effizient zu organisieren, zu verarbeiten und zu speichern. Zu den grundlegenden Datenstrukturen gehören Arrays, Listen, Stacks, Queues, Bäume und Graphen, die jeweils unterschiedliche Operationen wie Einfügen, Löschen und Suchen von Daten optimieren.</t>
   </si>
   <si>
     <t>Ein String in der Programmierung ist eine Sequenz von Zeichen, die als Datentyp in vielen Programmiersprachen, einschließlich Java, verwendet wird, um Text zu repräsentieren. In Java ist String eine Klasse, die Methoden zur Manipulation von Text, wie das Suchen von Zeichen, das Vergleichen von Strings oder das Ändern von Textinhalten, bereitstellt und aufgrund ihrer Unveränderlichkeit besondere Überlegungen im Hinblick auf Speichereffizienz und Performance erfordert.</t>
   </si>
   <si>
-    <t>43,51,68,203,204</t>
-  </si>
-  <si>
     <t>7f4461ab-864c-4531-8656-4616b739f5fa</t>
   </si>
   <si>
     <t>6168e707-a273-4cf4-9144-9f8ef201e775</t>
   </si>
   <si>
-    <t>43,52,68,203,204</t>
-  </si>
-  <si>
     <t>Operationen auf Strings</t>
   </si>
   <si>
@@ -1392,9 +1356,6 @@
     <t>Operationen auf Strings in der Programmierung ermöglichen es, Textdaten zu manipulieren, indem Funktionen wie das Verketten, Teilen, Suchen und Ersetzen von Teilstrings sowie das Umwandeln von Groß- und Kleinschreibung angewendet werden. In Java werden diese Operationen durch Methoden der Klasse `String` bereitgestellt, die unveränderliche Objekte repräsentiert, wobei jede Änderung an einem String ein neues Objekt erzeugt.</t>
   </si>
   <si>
-    <t>43,53,68,203,204</t>
-  </si>
-  <si>
     <t>2960e92b-b82d-443a-8b32-ed87447c76e1</t>
   </si>
   <si>
@@ -1404,15 +1365,9 @@
     <t>Ein Array in Java ist eine Datenstruktur, die es ermöglicht, mehrere Werte eines bestimmten Typs in einer einzigen Variablen zu speichern, wobei jeder Wert über einen Index zugänglich ist. Arrays sind nützlich, um Sammlungen von Daten wie Zahlenreihen oder Zeichenketten effizient zu verwalten und zu manipulieren, und sind ein grundlegendes Konzept in der objektorientierten Programmierung.</t>
   </si>
   <si>
-    <t>43,68,69</t>
-  </si>
-  <si>
     <t>9f2444dc-c1c9-4daa-82b9-26b916f003ae</t>
   </si>
   <si>
-    <t>43,68,69,70</t>
-  </si>
-  <si>
     <t>mehrdimensionales Array</t>
   </si>
   <si>
@@ -1500,15 +1455,9 @@
     <t>In Java können Arrays nicht nur primitive Datentypen wie Integers oder Doubles enthalten, sondern auch Objekte, wie zum Beispiel Instanzen der Klasse String oder benutzerdefinierte Klassen wie Enemies in einem Spiel. Um ein Array von Objekten zu verwenden, muss zuerst Speicherplatz für das Array reserviert werden, und anschließend müssen die einzelnen Objekte im Array mit dem Schlüsselwort 'new' tatsächlich erstellt werden, da anfänglich nur Referenzen ohne zugewiesene Objekte existieren.</t>
   </si>
   <si>
-    <t>43,80</t>
-  </si>
-  <si>
     <t>Es werden grundlegende Konzepte der objektorientierten Programmierung wie Klassen, Objekte, Vererbung, Polymorphismus und Kapselung vermittelt. Methoden in Java sind dabei essenzielle Bausteine, die Verhalten und Funktionalitäten von Objekten definieren und es ermöglichen, wiederverwendbaren und gut strukturierten Code zu schreiben.</t>
   </si>
   <si>
-    <t>43,80,81</t>
-  </si>
-  <si>
     <t>2d3d318f-4e05-4874-8e7f-d14921296fb2</t>
   </si>
   <si>
@@ -1518,9 +1467,6 @@
     <t>In Java werden Methoden aufgerufen, indem man ihnen Parameter übergibt, die als Call-by-Value kopiert werden, wodurch die ursprünglichen Variablen unverändert bleiben. Beim Methodenaufruf werden die Parameterwerte auf den Stack kopiert und die Methode ausgeführt, wobei nach Beendigung der Methode die temporären Variablen auf dem Stack gelöscht werden und die ursprünglichen Variablen unverändert bleiben.</t>
   </si>
   <si>
-    <t>43,80,82</t>
-  </si>
-  <si>
     <t>ab7afeb0-e17f-44e9-8be8-b17cbc8f94b9</t>
   </si>
   <si>
@@ -1530,9 +1476,6 @@
     <t>In Java werden Objekte und Arrays als Referenzen an Methoden übergeben (Call-by-Reference), was bedeutet, dass Änderungen an den Objekten innerhalb der Methode auch außerhalb sichtbar sind, da nicht die Werte, sondern die Referenzen auf die Speicherorte der Objekte übergeben werden. Im Gegensatz dazu werden primitive Datentypen wie int als Werte übergeben (Call-by-Value), sodass Änderungen an diesen Parametern innerhalb der Methode nicht außerhalb der Methode sichtbar sind, da Kopien der Werte übergeben werden.</t>
   </si>
   <si>
-    <t>43,80,83</t>
-  </si>
-  <si>
     <t>36266628-c243-4351-9c54-72dbf08b903d</t>
   </si>
   <si>
@@ -1542,9 +1485,6 @@
     <t>In Java können Methoden überladen werden, indem man mehrere Methoden mit demselben Namen, aber unterschiedlichen Parametertypen oder -anzahlen definiert, sodass der Compiler anhand der übergebenen Argumente die richtige Methode auswählen kann. Überladene Methoden müssen sich in der Parameterliste unterscheiden, da der Rückgabetyp allein nicht ausreicht, um für den Compiler eine eindeutige Unterscheidung zu ermöglichen, was sonst zu Fehlern führen würde.</t>
   </si>
   <si>
-    <t>43,80,84</t>
-  </si>
-  <si>
     <t>7821b45e-3488-4818-930f-be6bde95f277</t>
   </si>
   <si>
@@ -1572,9 +1512,6 @@
     <t>b681b280-c818-4970-a531-2aafcf5b49c8</t>
   </si>
   <si>
-    <t>Die Unified Modeling Language (UML) ist eine standardisierte Modellierungssprache, die verwendet wird, um die Struktur und das Design von Software-Systemen visuell darzustellen. In einem UML-Beispiel könnten Diagramme wie Klassendiagramme, Sequenzdiagramme und Zustandsdiagramme genutzt werden, um die Beziehungen zwischen Objekten, deren Verhalten und Lebenszyklen in einem objektorientierten Programm zu veranschaulichen.</t>
-  </si>
-  <si>
     <t>43,86,206</t>
   </si>
   <si>
@@ -1635,9 +1572,6 @@
     <t>Java UML Assoziationen beschreiben die Beziehungen zwischen verschiedenen Klassen in einem Klassendiagramm, wobei Assoziationen die Verbindungen zwischen Objekten darstellen und durch Linien repräsentiert werden. Diese Assoziationen können verschiedene Multiplizitäten aufweisen, die angeben, wie viele Instanzen einer Klasse mit Instanzen einer anderen Klasse in Beziehung stehen können, und können auch Rollennamen enthalten, die die Art der Beziehung näher spezifizieren.</t>
   </si>
   <si>
-    <t>43,90,91,206</t>
-  </si>
-  <si>
     <t>Navigierbarkeit</t>
   </si>
   <si>
@@ -1689,9 +1623,6 @@
     <t>In Java können Klassen und Operationen als abstrakt definiert werden, wobei abstrakte Klassen als Vorlage dienen, von denen andere Klassen Attribute und Methoden erben, ohne dass von der abstrakten Klasse selbst Objekte instanziiert werden. UML visualisiert abstrakte Klassen und Operationen durch Kursivschrift oder das Schlüsselwort "abstrakt", und in Java wird das Schlüsselwort `abstract` verwendet, um zu kennzeichnen, dass eine Klasse oder Methode abstrakt ist und von abgeleiteten Klassen implementiert werden muss.</t>
   </si>
   <si>
-    <t>43,85,93,96</t>
-  </si>
-  <si>
     <t>46fd92aa-34de-4782-bf0c-3e5e4279c427</t>
   </si>
   <si>
@@ -1704,9 +1635,6 @@
     <t>Java UML Interfaces repräsentieren abstrakte Klassen mit ausschließlich abstrakten Methoden, die als Schnittstellen dienen und die vollständige Abkapselung von Funktionalitäten ermöglichen. Sie legen fest, welche Methoden von implementierenden Klassen definiert werden müssen, ohne selbst Instanzen zu erzeugen, und dienen als Verträge zwischen verschiedenen Entwicklern, um die Interaktion zwischen verschiedenen Teilen eines Programms zu koordinieren.</t>
   </si>
   <si>
-    <t>43,85,93,97</t>
-  </si>
-  <si>
     <t>6aeac450-f0f5-4235-b7df-cafcc9ae555f</t>
   </si>
   <si>
@@ -1776,21 +1704,12 @@
     <t>21699b3f-2e32-45e2-a0a5-f671a0f98694</t>
   </si>
   <si>
-    <t>0c24b88b-ea6b-49f5-b6e2-a2ba29305814</t>
-  </si>
-  <si>
-    <t>In Java können Ausnahmen mit Try-Catch-Blöcken behandelt werden, um Fehler während der Laufzeit zu handhaben, wie im Beispiel des WURTLE-Spiels gezeigt, bei dem Wörter aus einer Datei geladen werden. Wenn beim Laden der Datei ein Fehler auftritt, fängt der Catch-Block die Ausnahme ab und ermöglicht es dem Programm, mit einem Fallback-Wörterarray fortzufahren, ohne dass der Benutzer einen Fehler bemerkt.</t>
-  </si>
-  <si>
     <t>Dateien und Ströme</t>
   </si>
   <si>
     <t>Dateien sind digitale Container, die Daten auf Speichermedien wie Festplatten oder SSDs speichern und es ermöglichen, Informationen dauerhaft zu bewahren und zu übertragen. In der objektorientierten Programmierung, wie in Java, werden Dateien mithilfe von Klassen und Methoden gelesen, geschrieben und verwaltet, wobei die Abstraktion und Kapselung von Dateioperationen die Interaktion mit dem Dateisystem vereinfacht und sicherer macht.</t>
   </si>
   <si>
-    <t>43,68,71</t>
-  </si>
-  <si>
     <t>a900435c-ff38-4581-b0b5-ea7a8bb19f5b</t>
   </si>
   <si>
@@ -1860,9 +1779,6 @@
     <t>cd49aafd-4a0a-4670-b4d7-83ba456fcfd3</t>
   </si>
   <si>
-    <t>43,108,109,209</t>
-  </si>
-  <si>
     <t>fe681e57-e984-4ef6-9bbc-0c6ddc6fc85e</t>
   </si>
   <si>
@@ -1975,6 +1891,72 @@
   </si>
   <si>
     <t>2,208,15</t>
+  </si>
+  <si>
+    <t>2,31,210</t>
+  </si>
+  <si>
+    <t>2,210,32</t>
+  </si>
+  <si>
+    <t>2,210,33</t>
+  </si>
+  <si>
+    <t>43,51,68,203</t>
+  </si>
+  <si>
+    <t>43,52,68,203</t>
+  </si>
+  <si>
+    <t>43,53,68,203</t>
+  </si>
+  <si>
+    <t>61,60,59,58</t>
+  </si>
+  <si>
+    <t>43,68,69,213</t>
+  </si>
+  <si>
+    <t>43,68,70,213</t>
+  </si>
+  <si>
+    <t>43,71,103</t>
+  </si>
+  <si>
+    <t>43,62,65,211</t>
+  </si>
+  <si>
+    <t>43,62,211,66</t>
+  </si>
+  <si>
+    <t>43,62,211,67</t>
+  </si>
+  <si>
+    <t>43,109,209</t>
+  </si>
+  <si>
+    <t>43,80,72</t>
+  </si>
+  <si>
+    <t>43,80,81,72</t>
+  </si>
+  <si>
+    <t>43,80,82,72</t>
+  </si>
+  <si>
+    <t>43,80,83,72</t>
+  </si>
+  <si>
+    <t>43,80,84,72</t>
+  </si>
+  <si>
+    <t>43,93,96</t>
+  </si>
+  <si>
+    <t>43,93,97</t>
+  </si>
+  <si>
+    <t>43,91,206</t>
   </si>
 </sst>
 </file>
@@ -2133,7 +2115,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -2336,12 +2318,88 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Excel Built-in Bad" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6428,7 +6486,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMJ181"/>
+  <dimension ref="A1:AMJ168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -6705,7 +6763,9 @@
       <c r="M7" s="39"/>
       <c r="N7" s="39"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
+      <c r="P7" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="Q7" s="34"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -6775,7 +6835,9 @@
       <c r="M9" s="39"/>
       <c r="N9" s="39"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
+      <c r="P9" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="Q9" s="41"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -6802,7 +6864,9 @@
       <c r="M10" s="39"/>
       <c r="N10" s="39"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
+      <c r="P10" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="Q10" s="41"/>
     </row>
     <row r="11" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -6846,7 +6910,7 @@
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="81" t="s">
-        <v>629</v>
+        <v>601</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>92</v>
@@ -6883,7 +6947,7 @@
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="43" t="s">
-        <v>630</v>
+        <v>602</v>
       </c>
       <c r="F13" s="44" t="s">
         <v>93</v>
@@ -6922,7 +6986,7 @@
       </c>
       <c r="D14" s="21"/>
       <c r="E14" s="43" t="s">
-        <v>630</v>
+        <v>602</v>
       </c>
       <c r="F14" s="44" t="s">
         <v>93</v>
@@ -6953,7 +7017,7 @@
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="43" t="s">
-        <v>630</v>
+        <v>602</v>
       </c>
       <c r="F15" s="44" t="s">
         <v>93</v>
@@ -7019,7 +7083,7 @@
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="43" t="s">
-        <v>632</v>
+        <v>604</v>
       </c>
       <c r="F17" s="46" t="s">
         <v>133</v>
@@ -7062,7 +7126,7 @@
       </c>
       <c r="D18" s="21"/>
       <c r="E18" s="43" t="s">
-        <v>631</v>
+        <v>603</v>
       </c>
       <c r="F18" s="46" t="s">
         <v>134</v>
@@ -7101,7 +7165,7 @@
       </c>
       <c r="D19" s="21"/>
       <c r="E19" s="43" t="s">
-        <v>631</v>
+        <v>603</v>
       </c>
       <c r="F19" s="46" t="s">
         <v>134</v>
@@ -7134,7 +7198,7 @@
       </c>
       <c r="D20" s="21"/>
       <c r="E20" s="43" t="s">
-        <v>633</v>
+        <v>605</v>
       </c>
       <c r="F20" s="46" t="s">
         <v>224</v>
@@ -7177,7 +7241,7 @@
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="43" t="s">
-        <v>634</v>
+        <v>606</v>
       </c>
       <c r="F21" s="46" t="s">
         <v>101</v>
@@ -7216,7 +7280,7 @@
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="43" t="s">
-        <v>634</v>
+        <v>606</v>
       </c>
       <c r="F22" s="46" t="s">
         <v>101</v>
@@ -7232,7 +7296,9 @@
       <c r="M22" s="31"/>
       <c r="N22" s="31"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
+      <c r="P22" s="2" t="s">
+        <v>232</v>
+      </c>
       <c r="Q22" s="34"/>
     </row>
     <row r="23" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -7247,7 +7313,7 @@
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="43" t="s">
-        <v>635</v>
+        <v>607</v>
       </c>
       <c r="F23" s="29" t="s">
         <v>97</v>
@@ -7290,7 +7356,7 @@
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="43" t="s">
-        <v>636</v>
+        <v>608</v>
       </c>
       <c r="F24" s="29" t="s">
         <v>98</v>
@@ -7329,7 +7395,7 @@
       </c>
       <c r="D25" s="21"/>
       <c r="E25" s="43" t="s">
-        <v>636</v>
+        <v>608</v>
       </c>
       <c r="F25" s="29" t="s">
         <v>98</v>
@@ -7345,7 +7411,9 @@
       <c r="M25" s="31"/>
       <c r="N25" s="31"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
+      <c r="P25" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="Q25" s="34"/>
     </row>
     <row r="26" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -7360,7 +7428,7 @@
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="43" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="F26" s="46" t="s">
         <v>100</v>
@@ -7399,7 +7467,7 @@
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="43" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="F27" s="46" t="s">
         <v>100</v>
@@ -7415,7 +7483,9 @@
       <c r="M27" s="31"/>
       <c r="N27" s="31"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
+      <c r="P27" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="Q27" s="34"/>
     </row>
     <row r="28" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -7426,7 +7496,7 @@
       </c>
       <c r="D28" s="21"/>
       <c r="E28" s="43" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="F28" s="46" t="s">
         <v>100</v>
@@ -7442,7 +7512,9 @@
       <c r="M28" s="31"/>
       <c r="N28" s="31"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
+      <c r="P28" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="Q28" s="34"/>
     </row>
     <row r="29" spans="1:17" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -7813,7 +7885,7 @@
       </c>
       <c r="D39" s="54"/>
       <c r="E39" s="59" t="s">
-        <v>627</v>
+        <v>599</v>
       </c>
       <c r="F39" s="60" t="s">
         <v>127</v>
@@ -7852,7 +7924,7 @@
       </c>
       <c r="D40" s="54"/>
       <c r="E40" s="59" t="s">
-        <v>627</v>
+        <v>599</v>
       </c>
       <c r="F40" s="60" t="s">
         <v>127</v>
@@ -7883,7 +7955,7 @@
       </c>
       <c r="D41" s="54"/>
       <c r="E41" s="59" t="s">
-        <v>627</v>
+        <v>599</v>
       </c>
       <c r="F41" s="60" t="s">
         <v>127</v>
@@ -7916,7 +7988,7 @@
       </c>
       <c r="D42" s="54"/>
       <c r="E42" s="59" t="s">
-        <v>628</v>
+        <v>600</v>
       </c>
       <c r="F42" s="60" t="s">
         <v>128</v>
@@ -7953,7 +8025,7 @@
       </c>
       <c r="D43" s="54"/>
       <c r="E43" s="59" t="s">
-        <v>628</v>
+        <v>600</v>
       </c>
       <c r="F43" s="60" t="s">
         <v>128</v>
@@ -8002,7 +8074,9 @@
       <c r="M44" s="31"/>
       <c r="N44" s="31"/>
       <c r="O44" s="2"/>
-      <c r="P44" s="2"/>
+      <c r="P44" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="Q44" s="63"/>
       <c r="AMJ44" s="2"/>
     </row>
@@ -8715,7 +8789,7 @@
     </row>
     <row r="64" spans="1:17" s="62" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="27">
-        <v>31</v>
+        <v>210</v>
       </c>
       <c r="B64" s="43" t="s">
         <v>321</v>
@@ -8746,65 +8820,73 @@
     </row>
     <row r="65" spans="1:17" s="62" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="27">
-        <v>32</v>
-      </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="27">
-        <v>58</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B65" s="43"/>
+      <c r="C65" s="27"/>
       <c r="D65" s="21"/>
-      <c r="E65" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="F65" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="G65" s="27">
-        <v>31</v>
-      </c>
-      <c r="H65" s="27">
-        <v>2</v>
+      <c r="E65" s="82" t="s">
+        <v>610</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G65" s="42">
+        <v>210</v>
+      </c>
+      <c r="H65" s="42">
+        <v>1</v>
       </c>
       <c r="I65" s="27">
         <v>1</v>
       </c>
       <c r="J65" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K65" s="31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L65" s="31"/>
       <c r="M65" s="31"/>
       <c r="N65" s="31"/>
-      <c r="O65" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q65" s="65"/>
+        <v>328</v>
+      </c>
+      <c r="Q65" s="61"/>
     </row>
     <row r="66" spans="1:17" s="62" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="27"/>
-      <c r="B66" s="21"/>
+      <c r="A66" s="27">
+        <v>32</v>
+      </c>
+      <c r="B66" s="21">
+        <v>31</v>
+      </c>
       <c r="C66" s="27">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D66" s="21"/>
-      <c r="E66" s="21" t="s">
-        <v>323</v>
+      <c r="E66" s="80" t="s">
+        <v>611</v>
       </c>
       <c r="F66" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
+      <c r="G66" s="27">
+        <v>210</v>
+      </c>
+      <c r="H66" s="27">
+        <v>2</v>
+      </c>
       <c r="I66" s="27">
-        <v>2</v>
-      </c>
-      <c r="J66" s="31"/>
-      <c r="K66" s="31"/>
+        <v>1</v>
+      </c>
+      <c r="J66" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="K66" s="31" t="s">
+        <v>324</v>
+      </c>
       <c r="L66" s="31"/>
       <c r="M66" s="31"/>
       <c r="N66" s="31"/>
@@ -8812,46 +8894,40 @@
         <v>118</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q66" s="65"/>
     </row>
-    <row r="67" spans="1:17" s="62" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" s="62" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="27"/>
       <c r="B67" s="21"/>
       <c r="C67" s="27">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D67" s="21"/>
-      <c r="E67" s="68" t="s">
-        <v>327</v>
+      <c r="E67" s="80" t="s">
+        <v>611</v>
       </c>
       <c r="F67" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="G67" s="27">
-        <v>31</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="G67" s="27"/>
       <c r="H67" s="27"/>
       <c r="I67" s="27">
-        <v>1</v>
-      </c>
-      <c r="J67" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="K67" s="31" t="s">
-        <v>329</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
       <c r="L67" s="31"/>
       <c r="M67" s="31"/>
       <c r="N67" s="31"/>
       <c r="O67" s="2" t="s">
-        <v>330</v>
+        <v>118</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q67" s="61"/>
+        <v>325</v>
+      </c>
+      <c r="Q67" s="65"/>
     </row>
     <row r="68" spans="1:17" s="62" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="27">
@@ -8864,14 +8940,14 @@
         <v>61</v>
       </c>
       <c r="D68" s="21"/>
-      <c r="E68" s="21" t="s">
-        <v>332</v>
+      <c r="E68" s="80" t="s">
+        <v>612</v>
       </c>
       <c r="F68" s="29" t="s">
         <v>119</v>
       </c>
       <c r="G68" s="27">
-        <v>31</v>
+        <v>210</v>
       </c>
       <c r="H68" s="27">
         <v>1</v>
@@ -8880,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="J68" s="31" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="K68" s="31"/>
       <c r="L68" s="31"/>
@@ -8890,7 +8966,7 @@
         <v>119</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="Q68" s="65"/>
     </row>
@@ -8899,7 +8975,7 @@
         <v>35</v>
       </c>
       <c r="B69" s="3">
-        <v>31</v>
+        <v>210</v>
       </c>
       <c r="C69" s="35">
         <v>62</v>
@@ -8923,7 +8999,7 @@
       <c r="N69" s="39"/>
       <c r="O69" s="1"/>
       <c r="P69" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="Q69" s="65"/>
     </row>
@@ -8937,7 +9013,7 @@
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="49" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>123</v>
@@ -8952,21 +9028,21 @@
         <v>1</v>
       </c>
       <c r="J70" s="39" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K70" s="39" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="L70" s="39"/>
       <c r="M70" s="39" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N70" s="39"/>
       <c r="O70" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="Q70" s="61"/>
     </row>
@@ -8978,7 +9054,7 @@
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>123</v>
@@ -8997,7 +9073,7 @@
         <v>123</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="Q71" s="61"/>
     </row>
@@ -9009,7 +9085,7 @@
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>123</v>
@@ -9028,7 +9104,7 @@
         <v>123</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="Q72" s="61"/>
     </row>
@@ -9042,7 +9118,7 @@
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="49" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>124</v>
@@ -9057,23 +9133,23 @@
         <v>1</v>
       </c>
       <c r="J73" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="K73" s="39" t="s">
         <v>342</v>
-      </c>
-      <c r="K73" s="39" t="s">
-        <v>346</v>
       </c>
       <c r="L73" s="39"/>
       <c r="M73" s="39" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="N73" s="39" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>124</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="Q73" s="61"/>
     </row>
@@ -9087,7 +9163,7 @@
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>125</v>
@@ -9102,21 +9178,21 @@
         <v>1</v>
       </c>
       <c r="J74" s="39" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="K74" s="39" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L74" s="39"/>
       <c r="M74" s="39" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N74" s="39"/>
       <c r="O74" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="Q74" s="61"/>
     </row>
@@ -9131,7 +9207,7 @@
       <c r="D75" s="70"/>
       <c r="E75" s="70"/>
       <c r="F75" s="4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G75" s="24">
         <v>1</v>
@@ -9159,7 +9235,7 @@
       </c>
       <c r="D76" s="21"/>
       <c r="E76" s="21" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F76" s="19" t="s">
         <v>130</v>
@@ -9174,7 +9250,7 @@
         <v>1</v>
       </c>
       <c r="J76" s="31" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K76" s="31"/>
       <c r="L76" s="31"/>
@@ -9182,7 +9258,7 @@
       <c r="N76" s="31"/>
       <c r="O76" s="2"/>
       <c r="P76" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="Q76" s="41"/>
     </row>
@@ -9196,7 +9272,7 @@
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>132</v>
@@ -9211,7 +9287,7 @@
         <v>1</v>
       </c>
       <c r="J77" s="39" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="K77" s="39"/>
       <c r="L77" s="39"/>
@@ -9219,7 +9295,7 @@
       <c r="N77" s="39"/>
       <c r="O77" s="1"/>
       <c r="P77" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="Q77" s="41"/>
     </row>
@@ -9250,7 +9326,7 @@
       <c r="N78" s="31"/>
       <c r="O78" s="2"/>
       <c r="P78" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="Q78" s="41"/>
     </row>
@@ -9264,7 +9340,7 @@
       </c>
       <c r="D79" s="21"/>
       <c r="E79" s="43" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F79" s="21" t="s">
         <v>92</v>
@@ -9279,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="J79" s="31" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="K79" s="31"/>
       <c r="L79" s="31"/>
@@ -9287,7 +9363,7 @@
       <c r="N79" s="31"/>
       <c r="O79" s="2"/>
       <c r="P79" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="Q79" s="41"/>
     </row>
@@ -9303,7 +9379,7 @@
       </c>
       <c r="D80" s="21"/>
       <c r="E80" s="43" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F80" s="29" t="s">
         <v>133</v>
@@ -9318,7 +9394,7 @@
         <v>1</v>
       </c>
       <c r="J80" s="31" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K80" s="31"/>
       <c r="L80" s="31"/>
@@ -9326,7 +9402,7 @@
       <c r="N80" s="31"/>
       <c r="O80" s="2"/>
       <c r="P80" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="Q80" s="41"/>
     </row>
@@ -9342,7 +9418,7 @@
       </c>
       <c r="D81" s="21"/>
       <c r="E81" s="43" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F81" s="29" t="s">
         <v>134</v>
@@ -9357,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="J81" s="31" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="K81" s="31"/>
       <c r="L81" s="31"/>
@@ -9365,7 +9441,7 @@
       <c r="N81" s="31"/>
       <c r="O81" s="2"/>
       <c r="P81" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="Q81" s="41"/>
     </row>
@@ -9381,7 +9457,7 @@
       </c>
       <c r="D82" s="21"/>
       <c r="E82" s="43" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F82" s="29" t="s">
         <v>135</v>
@@ -9396,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="J82" s="31" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K82" s="31"/>
       <c r="L82" s="31"/>
@@ -9404,7 +9480,7 @@
       <c r="N82" s="31"/>
       <c r="O82" s="2"/>
       <c r="P82" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="Q82" s="41"/>
     </row>
@@ -9420,7 +9496,7 @@
       </c>
       <c r="D83" s="21"/>
       <c r="E83" s="43" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F83" s="29" t="s">
         <v>97</v>
@@ -9435,7 +9511,7 @@
         <v>1</v>
       </c>
       <c r="J83" s="31" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="K83" s="31"/>
       <c r="L83" s="31"/>
@@ -9443,7 +9519,7 @@
       <c r="N83" s="31"/>
       <c r="O83" s="2"/>
       <c r="P83" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="Q83" s="41"/>
     </row>
@@ -9459,7 +9535,7 @@
       </c>
       <c r="D84" s="21"/>
       <c r="E84" s="43" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F84" s="29" t="s">
         <v>138</v>
@@ -9474,17 +9550,17 @@
         <v>1</v>
       </c>
       <c r="J84" s="31" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="K84" s="31" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="L84" s="31"/>
       <c r="M84" s="31"/>
       <c r="N84" s="31"/>
       <c r="O84" s="2"/>
       <c r="P84" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="Q84" s="34"/>
     </row>
@@ -9493,14 +9569,14 @@
         <v>55</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C85" s="27">
         <v>86</v>
       </c>
       <c r="D85" s="21"/>
       <c r="E85" s="43" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F85" s="29" t="s">
         <v>139</v>
@@ -9515,17 +9591,17 @@
         <v>1</v>
       </c>
       <c r="J85" s="31" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K85" s="31" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="L85" s="31"/>
       <c r="M85" s="31"/>
       <c r="N85" s="31"/>
       <c r="O85" s="2"/>
       <c r="P85" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="Q85" s="34"/>
     </row>
@@ -9541,7 +9617,7 @@
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>90</v>
@@ -9556,17 +9632,17 @@
         <v>1</v>
       </c>
       <c r="J86" s="39" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K86" s="39" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="L86" s="39"/>
       <c r="M86" s="39"/>
       <c r="N86" s="39"/>
       <c r="O86" s="1"/>
       <c r="P86" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="Q86" s="41"/>
     </row>
@@ -9597,7 +9673,7 @@
       <c r="N87" s="31"/>
       <c r="O87" s="2"/>
       <c r="P87" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="Q87" s="34"/>
     </row>
@@ -9611,7 +9687,7 @@
       </c>
       <c r="D88" s="21"/>
       <c r="E88" s="21" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F88" s="29" t="s">
         <v>141</v>
@@ -9626,17 +9702,17 @@
         <v>1</v>
       </c>
       <c r="J88" s="31" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="K88" s="31" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="L88" s="31"/>
       <c r="M88" s="31"/>
       <c r="N88" s="31"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="Q88" s="34"/>
     </row>
@@ -9652,7 +9728,7 @@
       </c>
       <c r="D89" s="21"/>
       <c r="E89" s="21" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F89" s="29" t="s">
         <v>5</v>
@@ -9667,17 +9743,17 @@
         <v>1</v>
       </c>
       <c r="J89" s="31" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="K89" s="31" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="L89" s="31"/>
       <c r="M89" s="31"/>
       <c r="N89" s="31"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="Q89" s="34"/>
     </row>
@@ -9693,7 +9769,7 @@
       </c>
       <c r="D90" s="21"/>
       <c r="E90" s="21" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F90" s="29" t="s">
         <v>143</v>
@@ -9708,17 +9784,17 @@
         <v>1</v>
       </c>
       <c r="J90" s="31" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="K90" s="31" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L90" s="31"/>
       <c r="M90" s="31"/>
       <c r="N90" s="31"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="Q90" s="34"/>
     </row>
@@ -9734,7 +9810,7 @@
       </c>
       <c r="D91" s="21"/>
       <c r="E91" s="21" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F91" s="29" t="s">
         <v>144</v>
@@ -9749,17 +9825,17 @@
         <v>1</v>
       </c>
       <c r="J91" s="31" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K91" s="31" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L91" s="31"/>
       <c r="M91" s="31"/>
       <c r="N91" s="31"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="Q91" s="41"/>
     </row>
@@ -9767,15 +9843,15 @@
       <c r="A92" s="27">
         <v>205</v>
       </c>
-      <c r="B92" s="21">
-        <v>61</v>
+      <c r="B92" s="80" t="s">
+        <v>616</v>
       </c>
       <c r="C92" s="27">
         <v>92</v>
       </c>
       <c r="D92" s="21"/>
       <c r="E92" s="43" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F92" s="29" t="s">
         <v>145</v>
@@ -9790,7 +9866,7 @@
         <v>1</v>
       </c>
       <c r="J92" s="31" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="K92" s="31"/>
       <c r="L92" s="31"/>
@@ -9798,7 +9874,7 @@
       <c r="N92" s="31"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="Q92" s="41"/>
     </row>
@@ -9829,7 +9905,7 @@
       <c r="N93" s="39"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="Q93" s="34"/>
     </row>
@@ -9843,7 +9919,7 @@
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F94" s="50" t="s">
         <v>103</v>
@@ -9858,17 +9934,17 @@
         <v>1</v>
       </c>
       <c r="J94" s="39" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="K94" s="39" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="L94" s="39"/>
       <c r="M94" s="39"/>
       <c r="N94" s="39"/>
       <c r="O94" s="1"/>
       <c r="P94" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="Q94" s="34"/>
     </row>
@@ -9876,11 +9952,11 @@
       <c r="A95" s="35"/>
       <c r="B95" s="3"/>
       <c r="C95" s="35">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F95" s="50" t="s">
         <v>103</v>
@@ -9888,7 +9964,7 @@
       <c r="G95" s="35"/>
       <c r="H95" s="35"/>
       <c r="I95" s="35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J95" s="39"/>
       <c r="K95" s="39"/>
@@ -9897,30 +9973,42 @@
       <c r="N95" s="39"/>
       <c r="O95" s="1"/>
       <c r="P95" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="Q95" s="34"/>
     </row>
     <row r="96" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="35"/>
-      <c r="B96" s="3"/>
+      <c r="A96" s="35">
+        <v>64</v>
+      </c>
+      <c r="B96" s="3">
+        <v>63</v>
+      </c>
       <c r="C96" s="35">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
         <v>409</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="G96" s="35"/>
-      <c r="H96" s="35"/>
+        <v>147</v>
+      </c>
+      <c r="G96" s="35">
+        <v>62</v>
+      </c>
+      <c r="H96" s="35">
+        <v>2</v>
+      </c>
       <c r="I96" s="35">
-        <v>3</v>
-      </c>
-      <c r="J96" s="39"/>
-      <c r="K96" s="39"/>
+        <v>1</v>
+      </c>
+      <c r="J96" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="K96" s="39" t="s">
+        <v>411</v>
+      </c>
       <c r="L96" s="39"/>
       <c r="M96" s="39"/>
       <c r="N96" s="39"/>
@@ -9931,64 +10019,54 @@
       <c r="Q96" s="34"/>
     </row>
     <row r="97" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="35">
-        <v>64</v>
-      </c>
-      <c r="B97" s="3">
-        <v>63</v>
-      </c>
+      <c r="A97" s="35"/>
+      <c r="B97" s="3"/>
       <c r="C97" s="35">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F97" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="G97" s="35">
-        <v>62</v>
-      </c>
-      <c r="H97" s="35">
+      <c r="G97" s="35"/>
+      <c r="H97" s="35"/>
+      <c r="I97" s="35">
         <v>2</v>
       </c>
-      <c r="I97" s="35">
-        <v>1</v>
-      </c>
-      <c r="J97" s="39" t="s">
-        <v>414</v>
-      </c>
-      <c r="K97" s="39" t="s">
-        <v>415</v>
-      </c>
+      <c r="J97" s="39"/>
+      <c r="K97" s="39"/>
       <c r="L97" s="39"/>
       <c r="M97" s="39"/>
       <c r="N97" s="39"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="Q97" s="34"/>
     </row>
     <row r="98" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A98" s="35"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="35">
-        <v>97</v>
-      </c>
+      <c r="A98" s="35">
+        <v>211</v>
+      </c>
+      <c r="B98" s="3">
+        <v>63</v>
+      </c>
+      <c r="C98" s="35"/>
       <c r="D98" s="3"/>
-      <c r="E98" s="3" t="s">
-        <v>413</v>
-      </c>
+      <c r="E98" s="3"/>
       <c r="F98" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="G98" s="35"/>
-      <c r="H98" s="35"/>
-      <c r="I98" s="35">
-        <v>2</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G98" s="35">
+        <v>62</v>
+      </c>
+      <c r="H98" s="35">
+        <v>3</v>
+      </c>
+      <c r="I98" s="35"/>
       <c r="J98" s="39"/>
       <c r="K98" s="39"/>
       <c r="L98" s="39"/>
@@ -9996,7 +10074,7 @@
       <c r="N98" s="39"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q98" s="34"/>
     </row>
@@ -10004,345 +10082,359 @@
       <c r="A99" s="35">
         <v>65</v>
       </c>
-      <c r="B99" s="3">
-        <v>63</v>
-      </c>
+      <c r="B99" s="3"/>
       <c r="C99" s="35">
         <v>98</v>
       </c>
       <c r="D99" s="3">
         <v>63</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>417</v>
+      <c r="E99" s="83" t="s">
+        <v>620</v>
       </c>
       <c r="F99" s="50" t="s">
         <v>105</v>
       </c>
       <c r="G99" s="35">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="H99" s="35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="35">
         <v>1</v>
       </c>
       <c r="J99" s="39" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="K99" s="39" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="L99" s="39"/>
       <c r="M99" s="39"/>
       <c r="N99" s="39"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="Q99" s="34"/>
     </row>
     <row r="100" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A100" s="35"/>
-      <c r="B100" s="3"/>
+      <c r="A100" s="35">
+        <v>66</v>
+      </c>
+      <c r="B100" s="3">
+        <v>65</v>
+      </c>
       <c r="C100" s="35">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D100" s="3"/>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="83" t="s">
+        <v>621</v>
+      </c>
+      <c r="F100" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="G100" s="35">
+        <v>211</v>
+      </c>
+      <c r="H100" s="35">
+        <v>1</v>
+      </c>
+      <c r="I100" s="35">
+        <v>1</v>
+      </c>
+      <c r="J100" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="K100" s="39" t="s">
         <v>417</v>
       </c>
-      <c r="F100" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="G100" s="35"/>
-      <c r="H100" s="35">
-        <v>2</v>
-      </c>
-      <c r="I100" s="35">
-        <v>2</v>
-      </c>
-      <c r="J100" s="39"/>
-      <c r="K100" s="39"/>
-      <c r="L100" s="39"/>
-      <c r="M100" s="39"/>
+      <c r="L100" s="39" t="s">
+        <v>422</v>
+      </c>
+      <c r="M100" s="39" t="s">
+        <v>423</v>
+      </c>
       <c r="N100" s="39"/>
       <c r="O100" s="1"/>
       <c r="P100" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="Q100" s="34"/>
     </row>
     <row r="101" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="35">
-        <v>66</v>
-      </c>
-      <c r="B101" s="3"/>
+        <v>67</v>
+      </c>
+      <c r="B101" s="3">
+        <v>65</v>
+      </c>
       <c r="C101" s="35">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D101" s="3"/>
-      <c r="E101" s="3" t="s">
-        <v>421</v>
+      <c r="E101" s="83" t="s">
+        <v>622</v>
       </c>
       <c r="F101" s="52" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G101" s="35">
-        <v>65</v>
+        <v>211</v>
       </c>
       <c r="H101" s="35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I101" s="35">
         <v>1</v>
       </c>
       <c r="J101" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="K101" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="L101" s="39" t="s">
         <v>422</v>
       </c>
-      <c r="K101" s="39" t="s">
+      <c r="M101" s="39" t="s">
         <v>423</v>
       </c>
-      <c r="L101" s="39"/>
-      <c r="M101" s="39"/>
       <c r="N101" s="39"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="Q101" s="34"/>
     </row>
     <row r="102" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A102" s="35">
-        <v>67</v>
-      </c>
+      <c r="A102" s="35"/>
       <c r="B102" s="3"/>
       <c r="C102" s="35">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="D102" s="3"/>
-      <c r="E102" s="3" t="s">
-        <v>425</v>
+      <c r="E102" s="83" t="s">
+        <v>622</v>
       </c>
       <c r="F102" s="52" t="s">
         <v>259</v>
       </c>
       <c r="G102" s="35">
-        <v>65</v>
-      </c>
-      <c r="H102" s="35">
+        <v>211</v>
+      </c>
+      <c r="H102" s="35"/>
+      <c r="I102" s="35">
         <v>3</v>
       </c>
-      <c r="I102" s="35">
-        <v>1</v>
-      </c>
-      <c r="J102" s="39" t="s">
-        <v>426</v>
-      </c>
-      <c r="K102" s="39" t="s">
-        <v>427</v>
-      </c>
+      <c r="J102" s="39"/>
+      <c r="K102" s="39"/>
       <c r="L102" s="39"/>
       <c r="M102" s="39"/>
       <c r="N102" s="39"/>
       <c r="O102" s="1"/>
       <c r="P102" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="Q102" s="34"/>
     </row>
-    <row r="103" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A103" s="35"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="35">
-        <v>163</v>
-      </c>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3" t="s">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A103" s="27">
+        <v>68</v>
+      </c>
+      <c r="B103" s="21">
+        <v>204</v>
+      </c>
+      <c r="C103" s="27"/>
+      <c r="D103" s="21"/>
+      <c r="E103" s="21"/>
+      <c r="F103" s="73" t="s">
+        <v>126</v>
+      </c>
+      <c r="G103" s="45">
+        <v>43</v>
+      </c>
+      <c r="H103" s="27">
+        <v>3</v>
+      </c>
+      <c r="I103" s="27"/>
+      <c r="J103" s="31"/>
+      <c r="K103" s="31"/>
+      <c r="L103" s="31"/>
+      <c r="M103" s="31"/>
+      <c r="N103" s="31"/>
+      <c r="O103" s="2"/>
+      <c r="P103" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q103" s="41"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A104" s="27">
+        <v>203</v>
+      </c>
+      <c r="B104" s="21"/>
+      <c r="C104" s="27"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="21"/>
+      <c r="F104" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="G104" s="27">
+        <v>68</v>
+      </c>
+      <c r="H104" s="27">
+        <v>1</v>
+      </c>
+      <c r="I104" s="27"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2"/>
+      <c r="N104" s="31"/>
+      <c r="O104" s="2"/>
+      <c r="P104" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="F103" s="52" t="s">
-        <v>259</v>
-      </c>
-      <c r="G103" s="35">
-        <v>67</v>
-      </c>
-      <c r="H103" s="35"/>
-      <c r="I103" s="35">
-        <v>3</v>
-      </c>
-      <c r="J103" s="39"/>
-      <c r="K103" s="39"/>
-      <c r="L103" s="39"/>
-      <c r="M103" s="39"/>
-      <c r="N103" s="39"/>
-      <c r="O103" s="1"/>
-      <c r="P103" s="1"/>
-      <c r="Q103" s="34"/>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A104" s="35"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="35">
-        <v>102</v>
-      </c>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="F104" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="G104" s="35">
-        <v>65</v>
-      </c>
-      <c r="H104" s="35"/>
-      <c r="I104" s="35">
-        <v>1</v>
-      </c>
-      <c r="J104" s="39"/>
-      <c r="K104" s="39" t="s">
-        <v>431</v>
-      </c>
-      <c r="L104" s="39" t="s">
-        <v>432</v>
-      </c>
-      <c r="M104" s="39"/>
-      <c r="N104" s="39"/>
-      <c r="O104" s="1"/>
-      <c r="P104" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="Q104" s="41"/>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="27">
-        <v>68</v>
-      </c>
-      <c r="B105" s="21">
-        <v>204</v>
-      </c>
-      <c r="C105" s="27"/>
+        <v>51</v>
+      </c>
+      <c r="B105" s="21"/>
+      <c r="C105" s="27">
+        <v>80</v>
+      </c>
       <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="G105" s="45">
-        <v>43</v>
+      <c r="E105" s="43" t="s">
+        <v>613</v>
+      </c>
+      <c r="F105" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="G105" s="27">
+        <v>203</v>
       </c>
       <c r="H105" s="27">
-        <v>3</v>
-      </c>
-      <c r="I105" s="27"/>
-      <c r="J105" s="31"/>
+        <v>1</v>
+      </c>
+      <c r="I105" s="27">
+        <v>1</v>
+      </c>
+      <c r="J105" s="31" t="s">
+        <v>426</v>
+      </c>
       <c r="K105" s="31"/>
       <c r="L105" s="31"/>
-      <c r="M105" s="31"/>
+      <c r="M105" s="31" t="s">
+        <v>427</v>
+      </c>
       <c r="N105" s="31"/>
       <c r="O105" s="2"/>
       <c r="P105" s="2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="Q105" s="41"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="27">
+        <v>52</v>
+      </c>
+      <c r="B106" s="21">
+        <v>51</v>
+      </c>
+      <c r="C106" s="27">
+        <v>81</v>
+      </c>
+      <c r="D106" s="21"/>
+      <c r="E106" s="43" t="s">
+        <v>614</v>
+      </c>
+      <c r="F106" s="46" t="s">
+        <v>428</v>
+      </c>
+      <c r="G106" s="27">
         <v>203</v>
       </c>
-      <c r="B106" s="21"/>
-      <c r="C106" s="27"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="G106" s="27">
-        <v>68</v>
-      </c>
       <c r="H106" s="27">
-        <v>1</v>
-      </c>
-      <c r="I106" s="27"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
-      <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="I106" s="27">
+        <v>1</v>
+      </c>
+      <c r="J106" s="31" t="s">
+        <v>429</v>
+      </c>
+      <c r="K106" s="31"/>
+      <c r="L106" s="31"/>
+      <c r="M106" s="31"/>
       <c r="N106" s="31"/>
       <c r="O106" s="2"/>
       <c r="P106" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Q106" s="41"/>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A107" s="27">
-        <v>51</v>
-      </c>
+      <c r="A107" s="27"/>
       <c r="B107" s="21"/>
       <c r="C107" s="27">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="43" t="s">
-        <v>436</v>
-      </c>
-      <c r="F107" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="G107" s="27">
-        <v>203</v>
-      </c>
-      <c r="H107" s="27">
-        <v>1</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="F107" s="46" t="s">
+        <v>428</v>
+      </c>
+      <c r="G107" s="27"/>
+      <c r="H107" s="27"/>
       <c r="I107" s="27">
-        <v>1</v>
-      </c>
-      <c r="J107" s="31" t="s">
-        <v>437</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J107" s="31"/>
       <c r="K107" s="31"/>
       <c r="L107" s="31"/>
-      <c r="M107" s="31" t="s">
-        <v>438</v>
-      </c>
+      <c r="M107" s="31"/>
       <c r="N107" s="31"/>
       <c r="O107" s="2"/>
       <c r="P107" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Q107" s="41"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="27">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B108" s="21">
         <v>51</v>
       </c>
       <c r="C108" s="27">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D108" s="21"/>
       <c r="E108" s="43" t="s">
-        <v>439</v>
+        <v>615</v>
       </c>
       <c r="F108" s="46" t="s">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="G108" s="27">
         <v>203</v>
       </c>
       <c r="H108" s="27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I108" s="27">
         <v>1</v>
       </c>
       <c r="J108" s="31" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K108" s="31"/>
       <c r="L108" s="31"/>
@@ -10350,28 +10442,28 @@
       <c r="N108" s="31"/>
       <c r="O108" s="2"/>
       <c r="P108" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="Q108" s="41"/>
+        <v>432</v>
+      </c>
+      <c r="Q108" s="34"/>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A109" s="27"/>
+      <c r="A109" s="27">
+        <v>213</v>
+      </c>
       <c r="B109" s="21"/>
-      <c r="C109" s="27">
-        <v>82</v>
-      </c>
+      <c r="C109" s="27"/>
       <c r="D109" s="21"/>
-      <c r="E109" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="F109" s="46" t="s">
-        <v>440</v>
-      </c>
-      <c r="G109" s="27"/>
-      <c r="H109" s="27"/>
-      <c r="I109" s="27">
-        <v>2</v>
-      </c>
+      <c r="E109" s="43"/>
+      <c r="F109" s="74" t="s">
+        <v>150</v>
+      </c>
+      <c r="G109" s="27">
+        <v>68</v>
+      </c>
+      <c r="H109" s="27">
+        <v>3</v>
+      </c>
+      <c r="I109" s="27"/>
       <c r="J109" s="31"/>
       <c r="K109" s="31"/>
       <c r="L109" s="31"/>
@@ -10379,355 +10471,372 @@
       <c r="N109" s="31"/>
       <c r="O109" s="2"/>
       <c r="P109" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="Q109" s="41"/>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A110" s="27"/>
+      <c r="A110" s="27">
+        <v>69</v>
+      </c>
       <c r="B110" s="21"/>
       <c r="C110" s="27">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D110" s="21"/>
       <c r="E110" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="F110" s="46" t="s">
-        <v>440</v>
-      </c>
-      <c r="G110" s="27"/>
-      <c r="H110" s="27"/>
+        <v>617</v>
+      </c>
+      <c r="F110" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G110" s="27">
+        <v>213</v>
+      </c>
+      <c r="H110" s="27">
+        <v>3</v>
+      </c>
       <c r="I110" s="27">
-        <v>3</v>
-      </c>
-      <c r="J110" s="31"/>
+        <v>1</v>
+      </c>
+      <c r="J110" s="31" t="s">
+        <v>434</v>
+      </c>
       <c r="K110" s="31"/>
       <c r="L110" s="31"/>
       <c r="M110" s="31"/>
       <c r="N110" s="31"/>
       <c r="O110" s="2"/>
       <c r="P110" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="Q110" s="41"/>
     </row>
-    <row r="111" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A111" s="27">
-        <v>53</v>
-      </c>
-      <c r="B111" s="21">
-        <v>51</v>
-      </c>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A111" s="27"/>
+      <c r="B111" s="21"/>
       <c r="C111" s="27">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D111" s="21"/>
-      <c r="E111" s="43" t="s">
-        <v>443</v>
-      </c>
-      <c r="F111" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="G111" s="27">
-        <v>203</v>
-      </c>
-      <c r="H111" s="27">
+      <c r="E111" s="80" t="s">
+        <v>617</v>
+      </c>
+      <c r="F111" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G111" s="27"/>
+      <c r="H111" s="27"/>
+      <c r="I111" s="27">
         <v>3</v>
       </c>
-      <c r="I111" s="27">
-        <v>1</v>
-      </c>
-      <c r="J111" s="31" t="s">
-        <v>444</v>
-      </c>
+      <c r="J111" s="31"/>
       <c r="K111" s="31"/>
       <c r="L111" s="31"/>
       <c r="M111" s="31"/>
       <c r="N111" s="31"/>
       <c r="O111" s="2"/>
       <c r="P111" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q111" s="34"/>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+      <c r="Q111" s="41"/>
+    </row>
+    <row r="112" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="27">
+        <v>70</v>
+      </c>
+      <c r="B112" s="21">
+        <v>69</v>
+      </c>
+      <c r="C112" s="27">
+        <v>106</v>
+      </c>
+      <c r="D112" s="21"/>
+      <c r="E112" s="80" t="s">
+        <v>618</v>
+      </c>
+      <c r="F112" s="74" t="s">
+        <v>435</v>
+      </c>
+      <c r="G112" s="27">
         <v>213</v>
-      </c>
-      <c r="B112" s="21"/>
-      <c r="C112" s="27"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="43"/>
-      <c r="F112" s="74" t="s">
-        <v>150</v>
-      </c>
-      <c r="G112" s="27">
-        <v>68</v>
       </c>
       <c r="H112" s="27">
         <v>3</v>
       </c>
-      <c r="I112" s="27"/>
-      <c r="J112" s="31"/>
+      <c r="I112" s="27">
+        <v>1</v>
+      </c>
+      <c r="J112" s="31" t="s">
+        <v>436</v>
+      </c>
       <c r="K112" s="31"/>
       <c r="L112" s="31"/>
       <c r="M112" s="31"/>
       <c r="N112" s="31"/>
       <c r="O112" s="2"/>
       <c r="P112" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q112" s="41"/>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A113" s="27">
-        <v>69</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="Q112" s="34"/>
+    </row>
+    <row r="113" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A113" s="27"/>
       <c r="B113" s="21"/>
       <c r="C113" s="27">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D113" s="21"/>
-      <c r="E113" s="43" t="s">
-        <v>447</v>
-      </c>
-      <c r="F113" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="G113" s="27">
-        <v>213</v>
-      </c>
-      <c r="H113" s="27">
+      <c r="E113" s="80" t="s">
+        <v>618</v>
+      </c>
+      <c r="F113" s="74" t="s">
+        <v>435</v>
+      </c>
+      <c r="G113" s="27"/>
+      <c r="H113" s="27"/>
+      <c r="I113" s="27">
         <v>3</v>
       </c>
-      <c r="I113" s="27">
-        <v>1</v>
-      </c>
-      <c r="J113" s="31" t="s">
-        <v>448</v>
-      </c>
+      <c r="J113" s="31"/>
       <c r="K113" s="31"/>
       <c r="L113" s="31"/>
       <c r="M113" s="31"/>
       <c r="N113" s="31"/>
       <c r="O113" s="2"/>
       <c r="P113" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q113" s="34"/>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A114" s="35">
+        <v>72</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C114" s="35"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G114" s="35">
+        <v>43</v>
+      </c>
+      <c r="H114" s="35">
+        <v>3</v>
+      </c>
+      <c r="I114" s="35"/>
+      <c r="J114" s="39"/>
+      <c r="K114" s="39"/>
+      <c r="L114" s="39"/>
+      <c r="M114" s="39"/>
+      <c r="N114" s="39"/>
+      <c r="O114" s="1"/>
+      <c r="P114" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A115" s="35">
+        <v>73</v>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="35">
+        <v>110</v>
+      </c>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F115" s="50" t="s">
+        <v>442</v>
+      </c>
+      <c r="G115" s="35">
+        <v>72</v>
+      </c>
+      <c r="H115" s="35">
+        <v>2</v>
+      </c>
+      <c r="I115" s="35">
+        <v>1</v>
+      </c>
+      <c r="J115" s="39" t="s">
+        <v>443</v>
+      </c>
+      <c r="K115" s="39"/>
+      <c r="L115" s="39"/>
+      <c r="M115" s="39"/>
+      <c r="N115" s="39"/>
+      <c r="O115" s="1"/>
+      <c r="P115" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A116" s="35"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="35">
+        <v>111</v>
+      </c>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F116" s="50" t="s">
+        <v>442</v>
+      </c>
+      <c r="G116" s="35"/>
+      <c r="H116" s="35"/>
+      <c r="I116" s="35">
+        <v>2</v>
+      </c>
+      <c r="J116" s="39"/>
+      <c r="K116" s="39"/>
+      <c r="L116" s="39"/>
+      <c r="M116" s="39"/>
+      <c r="N116" s="39"/>
+      <c r="O116" s="1"/>
+      <c r="P116" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A117" s="35">
+        <v>75</v>
+      </c>
+      <c r="B117" s="3">
+        <v>73</v>
+      </c>
+      <c r="C117" s="35">
+        <v>112</v>
+      </c>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F117" s="50" t="s">
         <v>446</v>
       </c>
-      <c r="Q113" s="41"/>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A114" s="27"/>
-      <c r="B114" s="21"/>
-      <c r="C114" s="27">
-        <v>104</v>
-      </c>
-      <c r="D114" s="21"/>
-      <c r="E114" s="21" t="s">
+      <c r="G117" s="35">
+        <v>72</v>
+      </c>
+      <c r="H117" s="35">
+        <v>3</v>
+      </c>
+      <c r="I117" s="35">
+        <v>1</v>
+      </c>
+      <c r="J117" s="39" t="s">
         <v>447</v>
       </c>
-      <c r="F114" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="G114" s="27"/>
-      <c r="H114" s="27"/>
-      <c r="I114" s="27">
-        <v>2</v>
-      </c>
-      <c r="J114" s="31"/>
-      <c r="K114" s="31"/>
-      <c r="L114" s="31"/>
-      <c r="M114" s="31"/>
-      <c r="N114" s="31"/>
-      <c r="O114" s="2"/>
-      <c r="P114" s="2" t="s">
+      <c r="K117" s="39"/>
+      <c r="L117" s="39"/>
+      <c r="M117" s="39"/>
+      <c r="N117" s="39"/>
+      <c r="O117" s="1"/>
+      <c r="P117" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A118" s="35"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="35">
+        <v>114</v>
+      </c>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F118" s="50" t="s">
         <v>446</v>
       </c>
-      <c r="Q114" s="41"/>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A115" s="27"/>
-      <c r="B115" s="21"/>
-      <c r="C115" s="27">
-        <v>105</v>
-      </c>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21" t="s">
-        <v>447</v>
-      </c>
-      <c r="F115" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="G115" s="27"/>
-      <c r="H115" s="27"/>
-      <c r="I115" s="27">
+      <c r="G118" s="35"/>
+      <c r="H118" s="35"/>
+      <c r="I118" s="35">
         <v>3</v>
       </c>
-      <c r="J115" s="31"/>
-      <c r="K115" s="31"/>
-      <c r="L115" s="31"/>
-      <c r="M115" s="31"/>
-      <c r="N115" s="31"/>
-      <c r="O115" s="2"/>
-      <c r="P115" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q115" s="41"/>
-    </row>
-    <row r="116" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A116" s="27">
-        <v>70</v>
-      </c>
-      <c r="B116" s="21">
-        <v>69</v>
-      </c>
-      <c r="C116" s="27">
-        <v>106</v>
-      </c>
-      <c r="D116" s="21"/>
-      <c r="E116" s="21" t="s">
-        <v>449</v>
-      </c>
-      <c r="F116" s="74" t="s">
-        <v>450</v>
-      </c>
-      <c r="G116" s="27">
-        <v>213</v>
-      </c>
-      <c r="H116" s="27">
-        <v>3</v>
-      </c>
-      <c r="I116" s="27">
-        <v>1</v>
-      </c>
-      <c r="J116" s="31" t="s">
-        <v>451</v>
-      </c>
-      <c r="K116" s="31"/>
-      <c r="L116" s="31"/>
-      <c r="M116" s="31"/>
-      <c r="N116" s="31"/>
-      <c r="O116" s="2"/>
-      <c r="P116" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q116" s="34"/>
-    </row>
-    <row r="117" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A117" s="27"/>
-      <c r="B117" s="21"/>
-      <c r="C117" s="27">
-        <v>107</v>
-      </c>
-      <c r="D117" s="21"/>
-      <c r="E117" s="21" t="s">
-        <v>449</v>
-      </c>
-      <c r="F117" s="74" t="s">
-        <v>450</v>
-      </c>
-      <c r="G117" s="27"/>
-      <c r="H117" s="27"/>
-      <c r="I117" s="27">
-        <v>2</v>
-      </c>
-      <c r="J117" s="31"/>
-      <c r="K117" s="31"/>
-      <c r="L117" s="31"/>
-      <c r="M117" s="31"/>
-      <c r="N117" s="31"/>
-      <c r="O117" s="2"/>
-      <c r="P117" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q117" s="34"/>
-    </row>
-    <row r="118" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A118" s="27"/>
-      <c r="B118" s="21"/>
-      <c r="C118" s="27">
-        <v>108</v>
-      </c>
-      <c r="D118" s="21"/>
-      <c r="E118" s="21" t="s">
-        <v>449</v>
-      </c>
-      <c r="F118" s="74" t="s">
-        <v>450</v>
-      </c>
-      <c r="G118" s="27"/>
-      <c r="H118" s="27"/>
-      <c r="I118" s="27">
-        <v>3</v>
-      </c>
-      <c r="J118" s="31"/>
-      <c r="K118" s="31"/>
-      <c r="L118" s="31"/>
-      <c r="M118" s="31"/>
-      <c r="N118" s="31"/>
-      <c r="O118" s="2"/>
-      <c r="P118" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q118" s="34"/>
+      <c r="J118" s="39"/>
+      <c r="K118" s="39"/>
+      <c r="L118" s="39"/>
+      <c r="M118" s="39"/>
+      <c r="N118" s="39"/>
+      <c r="O118" s="1"/>
+      <c r="P118" s="1" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="35">
+        <v>76</v>
+      </c>
+      <c r="B119" s="3">
+        <v>75</v>
+      </c>
+      <c r="C119" s="35">
+        <v>115</v>
+      </c>
+      <c r="D119" s="3">
+        <v>75</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F119" s="50" t="s">
+        <v>450</v>
+      </c>
+      <c r="G119" s="35">
         <v>72</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="C119" s="35"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="G119" s="35">
-        <v>43</v>
-      </c>
       <c r="H119" s="35">
-        <v>3</v>
-      </c>
-      <c r="I119" s="35"/>
-      <c r="J119" s="39"/>
+        <v>1</v>
+      </c>
+      <c r="I119" s="35">
+        <v>1</v>
+      </c>
+      <c r="J119" s="39" t="s">
+        <v>451</v>
+      </c>
       <c r="K119" s="39"/>
       <c r="L119" s="39"/>
       <c r="M119" s="39"/>
       <c r="N119" s="39"/>
       <c r="O119" s="1"/>
       <c r="P119" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="35">
-        <v>73</v>
-      </c>
-      <c r="B120" s="3"/>
+        <v>78</v>
+      </c>
+      <c r="B120" s="3">
+        <v>75</v>
+      </c>
       <c r="C120" s="35">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="F120" s="50" t="s">
-        <v>457</v>
+        <v>453</v>
+      </c>
+      <c r="F120" s="52" t="s">
+        <v>454</v>
       </c>
       <c r="G120" s="35">
         <v>72</v>
       </c>
       <c r="H120" s="35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I120" s="35">
         <v>1</v>
       </c>
       <c r="J120" s="39" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K120" s="39"/>
       <c r="L120" s="39"/>
@@ -10735,26 +10844,27 @@
       <c r="N120" s="39"/>
       <c r="O120" s="1"/>
       <c r="P120" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+      <c r="Q120" s="34"/>
+    </row>
+    <row r="121" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="35"/>
       <c r="B121" s="3"/>
       <c r="C121" s="35">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="F121" s="50" t="s">
-        <v>457</v>
+        <v>453</v>
+      </c>
+      <c r="F121" s="52" t="s">
+        <v>454</v>
       </c>
       <c r="G121" s="35"/>
       <c r="H121" s="35"/>
       <c r="I121" s="35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J121" s="39"/>
       <c r="K121" s="39"/>
@@ -10763,1134 +10873,1173 @@
       <c r="N121" s="39"/>
       <c r="O121" s="1"/>
       <c r="P121" s="1" t="s">
-        <v>459</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="Q121" s="34"/>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="35">
-        <v>75</v>
-      </c>
-      <c r="B122" s="3">
-        <v>73</v>
+        <v>79</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="C122" s="35">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F122" s="50" t="s">
-        <v>461</v>
+        <v>458</v>
+      </c>
+      <c r="F122" s="52" t="s">
+        <v>459</v>
       </c>
       <c r="G122" s="35">
         <v>72</v>
       </c>
       <c r="H122" s="35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I122" s="35">
         <v>1</v>
       </c>
       <c r="J122" s="39" t="s">
+        <v>460</v>
+      </c>
+      <c r="K122" s="39" t="s">
+        <v>461</v>
+      </c>
+      <c r="L122" s="39"/>
+      <c r="M122" s="39" t="s">
         <v>462</v>
       </c>
-      <c r="K122" s="39"/>
-      <c r="L122" s="39"/>
-      <c r="M122" s="39"/>
       <c r="N122" s="39"/>
       <c r="O122" s="1"/>
       <c r="P122" s="1" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A123" s="35"/>
-      <c r="B123" s="3"/>
-      <c r="C123" s="35">
-        <v>113</v>
-      </c>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F123" s="50" t="s">
-        <v>461</v>
-      </c>
-      <c r="G123" s="35"/>
-      <c r="H123" s="35"/>
-      <c r="I123" s="35">
+      <c r="Q122" s="41"/>
+    </row>
+    <row r="123" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A123" s="27">
+        <v>80</v>
+      </c>
+      <c r="B123" s="21">
+        <v>78</v>
+      </c>
+      <c r="C123" s="27"/>
+      <c r="D123" s="21"/>
+      <c r="E123" s="80" t="s">
+        <v>624</v>
+      </c>
+      <c r="F123" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="G123" s="27">
+        <v>72</v>
+      </c>
+      <c r="H123" s="27">
+        <v>3</v>
+      </c>
+      <c r="I123" s="27"/>
+      <c r="J123" s="31"/>
+      <c r="K123" s="31"/>
+      <c r="L123" s="31"/>
+      <c r="M123" s="31"/>
+      <c r="N123" s="31"/>
+      <c r="O123" s="2"/>
+      <c r="P123" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q123" s="34"/>
+    </row>
+    <row r="124" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A124" s="27">
+        <v>81</v>
+      </c>
+      <c r="B124" s="21"/>
+      <c r="C124" s="27">
+        <v>120</v>
+      </c>
+      <c r="D124" s="21"/>
+      <c r="E124" s="80" t="s">
+        <v>625</v>
+      </c>
+      <c r="F124" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="G124" s="27">
+        <v>80</v>
+      </c>
+      <c r="H124" s="27">
+        <v>1</v>
+      </c>
+      <c r="I124" s="27">
+        <v>1</v>
+      </c>
+      <c r="J124" s="31" t="s">
+        <v>465</v>
+      </c>
+      <c r="K124" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="L124" s="31"/>
+      <c r="M124" s="31"/>
+      <c r="N124" s="31"/>
+      <c r="O124" s="2"/>
+      <c r="P124" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q124" s="34"/>
+    </row>
+    <row r="125" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A125" s="27">
+        <v>82</v>
+      </c>
+      <c r="B125" s="21">
+        <v>81</v>
+      </c>
+      <c r="C125" s="27">
+        <v>121</v>
+      </c>
+      <c r="D125" s="21"/>
+      <c r="E125" s="80" t="s">
+        <v>626</v>
+      </c>
+      <c r="F125" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="G125" s="27">
+        <v>80</v>
+      </c>
+      <c r="H125" s="27">
+        <v>1</v>
+      </c>
+      <c r="I125" s="27">
+        <v>1</v>
+      </c>
+      <c r="J125" s="31" t="s">
+        <v>468</v>
+      </c>
+      <c r="K125" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="L125" s="31"/>
+      <c r="M125" s="31"/>
+      <c r="N125" s="31"/>
+      <c r="O125" s="2"/>
+      <c r="P125" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q125" s="34"/>
+    </row>
+    <row r="126" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A126" s="27">
+        <v>83</v>
+      </c>
+      <c r="B126" s="21">
+        <v>81</v>
+      </c>
+      <c r="C126" s="27">
+        <v>122</v>
+      </c>
+      <c r="D126" s="21"/>
+      <c r="E126" s="80" t="s">
+        <v>627</v>
+      </c>
+      <c r="F126" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="G126" s="27">
+        <v>80</v>
+      </c>
+      <c r="H126" s="27">
         <v>2</v>
       </c>
-      <c r="J123" s="39"/>
-      <c r="K123" s="39"/>
-      <c r="L123" s="39"/>
-      <c r="M123" s="39"/>
-      <c r="N123" s="39"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A124" s="35"/>
-      <c r="B124" s="3"/>
-      <c r="C124" s="35">
-        <v>114</v>
-      </c>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F124" s="50" t="s">
-        <v>461</v>
-      </c>
-      <c r="G124" s="35"/>
-      <c r="H124" s="35"/>
-      <c r="I124" s="35">
+      <c r="I126" s="27">
+        <v>1</v>
+      </c>
+      <c r="J126" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="K126" s="31" t="s">
+        <v>472</v>
+      </c>
+      <c r="L126" s="31"/>
+      <c r="M126" s="31"/>
+      <c r="N126" s="31"/>
+      <c r="O126" s="2"/>
+      <c r="P126" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q126" s="34"/>
+    </row>
+    <row r="127" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A127" s="27"/>
+      <c r="B127" s="21"/>
+      <c r="C127" s="27">
+        <v>123</v>
+      </c>
+      <c r="D127" s="21"/>
+      <c r="E127" s="80" t="s">
+        <v>627</v>
+      </c>
+      <c r="F127" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="G127" s="27"/>
+      <c r="H127" s="27"/>
+      <c r="I127" s="27">
+        <v>2</v>
+      </c>
+      <c r="J127" s="31"/>
+      <c r="K127" s="31"/>
+      <c r="L127" s="31"/>
+      <c r="M127" s="31"/>
+      <c r="N127" s="31"/>
+      <c r="O127" s="2"/>
+      <c r="P127" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q127" s="34"/>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A128" s="27">
+        <v>84</v>
+      </c>
+      <c r="B128" s="21">
+        <v>81</v>
+      </c>
+      <c r="C128" s="27">
+        <v>124</v>
+      </c>
+      <c r="D128" s="21"/>
+      <c r="E128" s="80" t="s">
+        <v>628</v>
+      </c>
+      <c r="F128" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="G128" s="27">
+        <v>80</v>
+      </c>
+      <c r="H128" s="27">
         <v>3</v>
       </c>
-      <c r="J124" s="39"/>
-      <c r="K124" s="39"/>
-      <c r="L124" s="39"/>
-      <c r="M124" s="39"/>
-      <c r="N124" s="39"/>
-      <c r="O124" s="1"/>
-      <c r="P124" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A125" s="35">
-        <v>76</v>
-      </c>
-      <c r="B125" s="3">
-        <v>75</v>
-      </c>
-      <c r="C125" s="35">
-        <v>115</v>
-      </c>
-      <c r="D125" s="3">
-        <v>75</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="F125" s="50" t="s">
-        <v>465</v>
-      </c>
-      <c r="G125" s="35">
+      <c r="I128" s="27">
+        <v>1</v>
+      </c>
+      <c r="J128" s="31" t="s">
+        <v>474</v>
+      </c>
+      <c r="K128" s="31" t="s">
+        <v>475</v>
+      </c>
+      <c r="L128" s="31"/>
+      <c r="M128" s="31"/>
+      <c r="N128" s="31"/>
+      <c r="O128" s="2"/>
+      <c r="P128" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q128" s="41"/>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A129" s="27"/>
+      <c r="B129" s="21"/>
+      <c r="C129" s="27">
+        <v>126</v>
+      </c>
+      <c r="D129" s="21"/>
+      <c r="E129" s="80" t="s">
+        <v>628</v>
+      </c>
+      <c r="F129" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="G129" s="27"/>
+      <c r="H129" s="27"/>
+      <c r="I129" s="27">
+        <v>3</v>
+      </c>
+      <c r="J129" s="31"/>
+      <c r="K129" s="31"/>
+      <c r="L129" s="31"/>
+      <c r="M129" s="31"/>
+      <c r="N129" s="31"/>
+      <c r="O129" s="2"/>
+      <c r="P129" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q129" s="41"/>
+    </row>
+    <row r="130" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A130" s="35">
+        <v>206</v>
+      </c>
+      <c r="B130" s="3">
         <v>72</v>
       </c>
-      <c r="H125" s="35">
-        <v>1</v>
-      </c>
-      <c r="I125" s="35">
-        <v>1</v>
-      </c>
-      <c r="J125" s="39" t="s">
-        <v>466</v>
-      </c>
-      <c r="K125" s="39"/>
-      <c r="L125" s="39"/>
-      <c r="M125" s="39"/>
-      <c r="N125" s="39"/>
-      <c r="O125" s="1"/>
-      <c r="P125" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A126" s="35">
-        <v>78</v>
-      </c>
-      <c r="B126" s="3">
-        <v>75</v>
-      </c>
-      <c r="C126" s="35">
-        <v>116</v>
-      </c>
-      <c r="D126" s="3"/>
-      <c r="E126" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="F126" s="52" t="s">
-        <v>469</v>
-      </c>
-      <c r="G126" s="35">
-        <v>72</v>
-      </c>
-      <c r="H126" s="35">
+      <c r="C130" s="35"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G130" s="35">
+        <v>43</v>
+      </c>
+      <c r="H130" s="35">
         <v>3</v>
       </c>
-      <c r="I126" s="35">
-        <v>1</v>
-      </c>
-      <c r="J126" s="39" t="s">
-        <v>470</v>
-      </c>
-      <c r="K126" s="39"/>
-      <c r="L126" s="39"/>
-      <c r="M126" s="39"/>
-      <c r="N126" s="39"/>
-      <c r="O126" s="1"/>
-      <c r="P126" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q126" s="34"/>
-    </row>
-    <row r="127" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A127" s="35"/>
-      <c r="B127" s="3"/>
-      <c r="C127" s="35">
-        <v>117</v>
-      </c>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="F127" s="52" t="s">
-        <v>469</v>
-      </c>
-      <c r="G127" s="35"/>
-      <c r="H127" s="35"/>
-      <c r="I127" s="35">
+      <c r="I130" s="35"/>
+      <c r="J130" s="39"/>
+      <c r="K130" s="39"/>
+      <c r="L130" s="39"/>
+      <c r="M130" s="39"/>
+      <c r="N130" s="39"/>
+      <c r="O130" s="1"/>
+      <c r="P130" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q130" s="34"/>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A131" s="35">
+        <v>85</v>
+      </c>
+      <c r="B131" s="3"/>
+      <c r="C131" s="35">
+        <v>127</v>
+      </c>
+      <c r="D131" s="3"/>
+      <c r="E131" s="49" t="s">
+        <v>478</v>
+      </c>
+      <c r="F131" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="G131" s="35">
+        <v>206</v>
+      </c>
+      <c r="H131" s="35">
+        <v>3</v>
+      </c>
+      <c r="I131" s="35">
+        <v>1</v>
+      </c>
+      <c r="J131" s="39" t="s">
+        <v>479</v>
+      </c>
+      <c r="K131" s="39" t="s">
+        <v>480</v>
+      </c>
+      <c r="L131" s="39" t="s">
+        <v>482</v>
+      </c>
+      <c r="M131" s="39"/>
+      <c r="N131" s="39"/>
+      <c r="O131" s="1"/>
+      <c r="P131" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q131" s="41"/>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A132" s="35"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="35">
+        <v>129</v>
+      </c>
+      <c r="D132" s="3"/>
+      <c r="E132" s="49" t="s">
+        <v>478</v>
+      </c>
+      <c r="F132" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="G132" s="35"/>
+      <c r="H132" s="35"/>
+      <c r="I132" s="35">
+        <v>3</v>
+      </c>
+      <c r="J132" s="39"/>
+      <c r="K132" s="39"/>
+      <c r="L132" s="39"/>
+      <c r="M132" s="39"/>
+      <c r="N132" s="39"/>
+      <c r="O132" s="1"/>
+      <c r="P132" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q132" s="41"/>
+    </row>
+    <row r="133" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A133" s="35">
+        <v>86</v>
+      </c>
+      <c r="B133" s="3">
+        <v>85</v>
+      </c>
+      <c r="C133" s="35">
+        <v>131</v>
+      </c>
+      <c r="D133" s="3"/>
+      <c r="E133" s="49" t="s">
+        <v>483</v>
+      </c>
+      <c r="F133" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="G133" s="35">
+        <v>206</v>
+      </c>
+      <c r="H133" s="35">
         <v>2</v>
       </c>
-      <c r="J127" s="39"/>
-      <c r="K127" s="39"/>
-      <c r="L127" s="39"/>
-      <c r="M127" s="39"/>
-      <c r="N127" s="39"/>
-      <c r="O127" s="1"/>
-      <c r="P127" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q127" s="34"/>
-    </row>
-    <row r="128" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A128" s="35"/>
-      <c r="B128" s="3"/>
-      <c r="C128" s="35">
-        <v>118</v>
-      </c>
-      <c r="D128" s="3"/>
-      <c r="E128" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="F128" s="52" t="s">
-        <v>469</v>
-      </c>
-      <c r="G128" s="35"/>
-      <c r="H128" s="35"/>
-      <c r="I128" s="35">
-        <v>3</v>
-      </c>
-      <c r="J128" s="39"/>
-      <c r="K128" s="39"/>
-      <c r="L128" s="39"/>
-      <c r="M128" s="39"/>
-      <c r="N128" s="39"/>
-      <c r="O128" s="1"/>
-      <c r="P128" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q128" s="34"/>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A129" s="35">
-        <v>79</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="C129" s="35">
-        <v>119</v>
-      </c>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="F129" s="52" t="s">
-        <v>474</v>
-      </c>
-      <c r="G129" s="35">
-        <v>72</v>
-      </c>
-      <c r="H129" s="35">
-        <v>1</v>
-      </c>
-      <c r="I129" s="35">
-        <v>1</v>
-      </c>
-      <c r="J129" s="39" t="s">
-        <v>475</v>
-      </c>
-      <c r="K129" s="39" t="s">
-        <v>476</v>
-      </c>
-      <c r="L129" s="39"/>
-      <c r="M129" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="N129" s="39"/>
-      <c r="O129" s="1"/>
-      <c r="P129" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q129" s="41"/>
-    </row>
-    <row r="130" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A130" s="27">
-        <v>80</v>
-      </c>
-      <c r="B130" s="21">
-        <v>78</v>
-      </c>
-      <c r="C130" s="27"/>
-      <c r="D130" s="21"/>
-      <c r="E130" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="F130" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="G130" s="27">
-        <v>72</v>
-      </c>
-      <c r="H130" s="27">
-        <v>3</v>
-      </c>
-      <c r="I130" s="27"/>
-      <c r="J130" s="31"/>
-      <c r="K130" s="31"/>
-      <c r="L130" s="31"/>
-      <c r="M130" s="31"/>
-      <c r="N130" s="31"/>
-      <c r="O130" s="2"/>
-      <c r="P130" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q130" s="34"/>
-    </row>
-    <row r="131" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A131" s="27">
-        <v>81</v>
-      </c>
-      <c r="B131" s="21"/>
-      <c r="C131" s="27">
-        <v>120</v>
-      </c>
-      <c r="D131" s="21"/>
-      <c r="E131" s="21" t="s">
-        <v>481</v>
-      </c>
-      <c r="F131" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="G131" s="27">
-        <v>80</v>
-      </c>
-      <c r="H131" s="27">
-        <v>1</v>
-      </c>
-      <c r="I131" s="27">
-        <v>1</v>
-      </c>
-      <c r="J131" s="31" t="s">
-        <v>482</v>
-      </c>
-      <c r="K131" s="31" t="s">
+      <c r="I133" s="35">
+        <v>1</v>
+      </c>
+      <c r="J133" s="39" t="s">
+        <v>484</v>
+      </c>
+      <c r="K133" s="39" t="s">
+        <v>485</v>
+      </c>
+      <c r="L133" s="39"/>
+      <c r="M133" s="39"/>
+      <c r="N133" s="39"/>
+      <c r="O133" s="1"/>
+      <c r="P133" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q133" s="34"/>
+    </row>
+    <row r="134" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A134" s="35"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="35">
+        <v>132</v>
+      </c>
+      <c r="D134" s="3"/>
+      <c r="E134" s="49" t="s">
         <v>483</v>
       </c>
-      <c r="L131" s="31"/>
-      <c r="M131" s="31"/>
-      <c r="N131" s="31"/>
-      <c r="O131" s="2"/>
-      <c r="P131" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q131" s="34"/>
-    </row>
-    <row r="132" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A132" s="27">
-        <v>82</v>
-      </c>
-      <c r="B132" s="21">
-        <v>81</v>
-      </c>
-      <c r="C132" s="27">
-        <v>121</v>
-      </c>
-      <c r="D132" s="21"/>
-      <c r="E132" s="21" t="s">
-        <v>485</v>
-      </c>
-      <c r="F132" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="G132" s="27">
-        <v>80</v>
-      </c>
-      <c r="H132" s="27">
-        <v>1</v>
-      </c>
-      <c r="I132" s="27">
-        <v>1</v>
-      </c>
-      <c r="J132" s="31" t="s">
+      <c r="F134" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="G134" s="35"/>
+      <c r="H134" s="35"/>
+      <c r="I134" s="35">
+        <v>2</v>
+      </c>
+      <c r="J134" s="39"/>
+      <c r="K134" s="39"/>
+      <c r="L134" s="39"/>
+      <c r="M134" s="39"/>
+      <c r="N134" s="39"/>
+      <c r="O134" s="1"/>
+      <c r="P134" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="K132" s="31" t="s">
+      <c r="Q134" s="34"/>
+    </row>
+    <row r="135" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A135" s="35">
+        <v>87</v>
+      </c>
+      <c r="B135" s="3">
+        <v>86</v>
+      </c>
+      <c r="C135" s="35">
+        <v>133</v>
+      </c>
+      <c r="D135" s="3"/>
+      <c r="E135" s="49" t="s">
         <v>487</v>
       </c>
-      <c r="L132" s="31"/>
-      <c r="M132" s="31"/>
-      <c r="N132" s="31"/>
-      <c r="O132" s="2"/>
-      <c r="P132" s="2" t="s">
+      <c r="F135" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="G135" s="35">
+        <v>206</v>
+      </c>
+      <c r="H135" s="35">
+        <v>1</v>
+      </c>
+      <c r="I135" s="35">
+        <v>1</v>
+      </c>
+      <c r="J135" s="39" t="s">
         <v>488</v>
       </c>
-      <c r="Q132" s="34"/>
-    </row>
-    <row r="133" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A133" s="27">
-        <v>83</v>
-      </c>
-      <c r="B133" s="21">
-        <v>81</v>
-      </c>
-      <c r="C133" s="27">
-        <v>122</v>
-      </c>
-      <c r="D133" s="21"/>
-      <c r="E133" s="21" t="s">
+      <c r="K135" s="39" t="s">
         <v>489</v>
       </c>
-      <c r="F133" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="G133" s="27">
-        <v>80</v>
-      </c>
-      <c r="H133" s="27">
-        <v>2</v>
-      </c>
-      <c r="I133" s="27">
-        <v>1</v>
-      </c>
-      <c r="J133" s="31" t="s">
+      <c r="L135" s="39"/>
+      <c r="M135" s="39"/>
+      <c r="N135" s="39"/>
+      <c r="O135" s="1"/>
+      <c r="P135" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="K133" s="31" t="s">
+      <c r="Q135" s="34"/>
+    </row>
+    <row r="136" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A136" s="35">
+        <v>88</v>
+      </c>
+      <c r="B136" s="3">
+        <v>87</v>
+      </c>
+      <c r="C136" s="35">
+        <v>134</v>
+      </c>
+      <c r="D136" s="3"/>
+      <c r="E136" s="49" t="s">
         <v>491</v>
       </c>
-      <c r="L133" s="31"/>
-      <c r="M133" s="31"/>
-      <c r="N133" s="31"/>
-      <c r="O133" s="2"/>
-      <c r="P133" s="2" t="s">
+      <c r="F136" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="G136" s="35">
+        <v>206</v>
+      </c>
+      <c r="H136" s="35">
+        <v>1</v>
+      </c>
+      <c r="I136" s="35">
+        <v>1</v>
+      </c>
+      <c r="J136" s="39" t="s">
         <v>492</v>
       </c>
-      <c r="Q133" s="34"/>
-    </row>
-    <row r="134" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A134" s="27"/>
-      <c r="B134" s="21"/>
-      <c r="C134" s="27">
-        <v>123</v>
-      </c>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21" t="s">
-        <v>489</v>
-      </c>
-      <c r="F134" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="G134" s="27"/>
-      <c r="H134" s="27"/>
-      <c r="I134" s="27">
-        <v>2</v>
-      </c>
-      <c r="J134" s="31"/>
-      <c r="K134" s="31"/>
-      <c r="L134" s="31"/>
-      <c r="M134" s="31"/>
-      <c r="N134" s="31"/>
-      <c r="O134" s="2"/>
-      <c r="P134" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="Q134" s="34"/>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A135" s="27">
-        <v>84</v>
-      </c>
-      <c r="B135" s="21">
-        <v>81</v>
-      </c>
-      <c r="C135" s="27">
-        <v>124</v>
-      </c>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21" t="s">
+      <c r="K136" s="39" t="s">
         <v>493</v>
       </c>
-      <c r="F135" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="G135" s="27">
-        <v>80</v>
-      </c>
-      <c r="H135" s="27">
-        <v>3</v>
-      </c>
-      <c r="I135" s="27">
-        <v>1</v>
-      </c>
-      <c r="J135" s="31" t="s">
+      <c r="L136" s="39"/>
+      <c r="M136" s="39"/>
+      <c r="N136" s="39"/>
+      <c r="O136" s="1"/>
+      <c r="P136" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="K135" s="31" t="s">
+      <c r="Q136" s="34"/>
+    </row>
+    <row r="137" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A137" s="35">
+        <v>89</v>
+      </c>
+      <c r="B137" s="3">
+        <v>88</v>
+      </c>
+      <c r="C137" s="35">
+        <v>135</v>
+      </c>
+      <c r="D137" s="3"/>
+      <c r="E137" s="49" t="s">
         <v>495</v>
       </c>
-      <c r="L135" s="31"/>
-      <c r="M135" s="31"/>
-      <c r="N135" s="31"/>
-      <c r="O135" s="2"/>
-      <c r="P135" s="2" t="s">
+      <c r="F137" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="G137" s="35">
+        <v>206</v>
+      </c>
+      <c r="H137" s="35">
+        <v>1</v>
+      </c>
+      <c r="I137" s="35">
+        <v>1</v>
+      </c>
+      <c r="J137" s="39" t="s">
         <v>496</v>
       </c>
-      <c r="Q135" s="41"/>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A136" s="27"/>
-      <c r="B136" s="21"/>
-      <c r="C136" s="27">
-        <v>125</v>
-      </c>
-      <c r="D136" s="21"/>
-      <c r="E136" s="21" t="s">
-        <v>493</v>
-      </c>
-      <c r="F136" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="G136" s="27"/>
-      <c r="H136" s="27"/>
-      <c r="I136" s="27">
-        <v>2</v>
-      </c>
-      <c r="J136" s="31"/>
-      <c r="K136" s="31"/>
-      <c r="L136" s="31"/>
-      <c r="M136" s="31"/>
-      <c r="N136" s="31"/>
-      <c r="O136" s="2"/>
-      <c r="P136" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q136" s="41"/>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A137" s="27"/>
-      <c r="B137" s="21"/>
-      <c r="C137" s="27">
-        <v>126</v>
-      </c>
-      <c r="D137" s="21"/>
-      <c r="E137" s="21" t="s">
-        <v>493</v>
-      </c>
-      <c r="F137" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="G137" s="27"/>
-      <c r="H137" s="27"/>
-      <c r="I137" s="27">
-        <v>3</v>
-      </c>
-      <c r="J137" s="31"/>
-      <c r="K137" s="31"/>
-      <c r="L137" s="31"/>
-      <c r="M137" s="31"/>
-      <c r="N137" s="31"/>
-      <c r="O137" s="2"/>
-      <c r="P137" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q137" s="41"/>
+      <c r="K137" s="39" t="s">
+        <v>497</v>
+      </c>
+      <c r="L137" s="39"/>
+      <c r="M137" s="39"/>
+      <c r="N137" s="39"/>
+      <c r="O137" s="1"/>
+      <c r="P137" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q137" s="34"/>
     </row>
     <row r="138" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="35">
+        <v>90</v>
+      </c>
+      <c r="B138" s="3">
+        <v>89</v>
+      </c>
+      <c r="C138" s="35">
+        <v>136</v>
+      </c>
+      <c r="D138" s="3"/>
+      <c r="E138" s="49" t="s">
+        <v>499</v>
+      </c>
+      <c r="F138" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="G138" s="35">
         <v>206</v>
       </c>
-      <c r="B138" s="3">
-        <v>72</v>
-      </c>
-      <c r="C138" s="35"/>
-      <c r="D138" s="3"/>
-      <c r="E138" s="3"/>
-      <c r="F138" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G138" s="35">
-        <v>43</v>
-      </c>
       <c r="H138" s="35">
-        <v>3</v>
-      </c>
-      <c r="I138" s="35"/>
-      <c r="J138" s="39"/>
-      <c r="K138" s="39"/>
+        <v>2</v>
+      </c>
+      <c r="I138" s="35">
+        <v>1</v>
+      </c>
+      <c r="J138" s="39" t="s">
+        <v>500</v>
+      </c>
+      <c r="K138" s="39" t="s">
+        <v>501</v>
+      </c>
       <c r="L138" s="39"/>
       <c r="M138" s="39"/>
       <c r="N138" s="39"/>
       <c r="O138" s="1"/>
       <c r="P138" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="Q138" s="34"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="35">
-        <v>85</v>
-      </c>
-      <c r="B139" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="B139" s="3">
+        <v>90</v>
+      </c>
       <c r="C139" s="35">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="49" t="s">
-        <v>498</v>
-      </c>
-      <c r="F139" s="50" t="s">
-        <v>164</v>
+        <v>631</v>
+      </c>
+      <c r="F139" s="52" t="s">
+        <v>503</v>
       </c>
       <c r="G139" s="35">
         <v>206</v>
       </c>
       <c r="H139" s="35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I139" s="35">
         <v>1</v>
       </c>
       <c r="J139" s="39" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="K139" s="39" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="L139" s="39"/>
       <c r="M139" s="39"/>
       <c r="N139" s="39"/>
       <c r="O139" s="1"/>
       <c r="P139" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q139" s="41"/>
+        <v>506</v>
+      </c>
+      <c r="Q139" s="34"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A140" s="35"/>
-      <c r="B140" s="3"/>
+      <c r="A140" s="35">
+        <v>92</v>
+      </c>
+      <c r="B140" s="3">
+        <v>91</v>
+      </c>
       <c r="C140" s="35">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="49" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="F140" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="G140" s="35"/>
-      <c r="H140" s="35"/>
+        <v>170</v>
+      </c>
+      <c r="G140" s="35">
+        <v>206</v>
+      </c>
+      <c r="H140" s="35">
+        <v>1</v>
+      </c>
       <c r="I140" s="35">
-        <v>2</v>
-      </c>
-      <c r="J140" s="39"/>
-      <c r="K140" s="39"/>
+        <v>1</v>
+      </c>
+      <c r="J140" s="39" t="s">
+        <v>508</v>
+      </c>
+      <c r="K140" s="39" t="s">
+        <v>509</v>
+      </c>
       <c r="L140" s="39"/>
       <c r="M140" s="39"/>
       <c r="N140" s="39"/>
       <c r="O140" s="1"/>
       <c r="P140" s="1" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="Q140" s="41"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A141" s="35"/>
-      <c r="B141" s="3"/>
-      <c r="C141" s="35">
-        <v>129</v>
-      </c>
-      <c r="D141" s="3"/>
-      <c r="E141" s="49" t="s">
-        <v>498</v>
-      </c>
-      <c r="F141" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="G141" s="35"/>
-      <c r="H141" s="35"/>
-      <c r="I141" s="35">
+    <row r="141" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A141" s="27">
+        <v>93</v>
+      </c>
+      <c r="B141" s="21">
+        <v>72.206000000000003</v>
+      </c>
+      <c r="C141" s="27">
+        <v>139</v>
+      </c>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G141" s="27">
+        <v>43</v>
+      </c>
+      <c r="H141" s="27">
+        <v>2</v>
+      </c>
+      <c r="I141" s="27">
+        <v>1</v>
+      </c>
+      <c r="J141" s="31"/>
+      <c r="K141" s="31"/>
+      <c r="L141" s="31"/>
+      <c r="M141" s="31"/>
+      <c r="N141" s="31"/>
+      <c r="O141" s="2"/>
+      <c r="P141" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q141" s="34"/>
+    </row>
+    <row r="142" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A142" s="27"/>
+      <c r="B142" s="21"/>
+      <c r="C142" s="27">
+        <v>140</v>
+      </c>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="G142" s="27"/>
+      <c r="H142" s="27"/>
+      <c r="I142" s="27">
+        <v>2</v>
+      </c>
+      <c r="J142" s="31"/>
+      <c r="K142" s="31"/>
+      <c r="L142" s="31"/>
+      <c r="M142" s="31"/>
+      <c r="N142" s="31"/>
+      <c r="O142" s="2"/>
+      <c r="P142" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q142" s="34"/>
+    </row>
+    <row r="143" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A143" s="27">
+        <v>94</v>
+      </c>
+      <c r="B143" s="21"/>
+      <c r="C143" s="27">
+        <v>141</v>
+      </c>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="F143" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="G143" s="27">
+        <v>93</v>
+      </c>
+      <c r="H143" s="27">
+        <v>1</v>
+      </c>
+      <c r="I143" s="27">
+        <v>1</v>
+      </c>
+      <c r="J143" s="31" t="s">
+        <v>513</v>
+      </c>
+      <c r="K143" s="31" t="s">
+        <v>514</v>
+      </c>
+      <c r="L143" s="31"/>
+      <c r="M143" s="31"/>
+      <c r="N143" s="31"/>
+      <c r="O143" s="2"/>
+      <c r="P143" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q143" s="34"/>
+    </row>
+    <row r="144" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A144" s="27">
+        <v>95</v>
+      </c>
+      <c r="B144" s="21">
+        <v>94</v>
+      </c>
+      <c r="C144" s="27">
+        <v>142</v>
+      </c>
+      <c r="D144" s="21"/>
+      <c r="E144" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="F144" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="G144" s="27">
+        <v>93</v>
+      </c>
+      <c r="H144" s="27">
         <v>3</v>
       </c>
-      <c r="J141" s="39"/>
-      <c r="K141" s="39"/>
-      <c r="L141" s="39"/>
-      <c r="M141" s="39"/>
-      <c r="N141" s="39"/>
-      <c r="O141" s="1"/>
-      <c r="P141" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q141" s="41"/>
-    </row>
-    <row r="142" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A142" s="35"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="35">
-        <v>130</v>
-      </c>
-      <c r="D142" s="3"/>
-      <c r="E142" s="49" t="s">
-        <v>498</v>
-      </c>
-      <c r="F142" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="G142" s="35">
-        <v>206</v>
-      </c>
-      <c r="H142" s="35"/>
-      <c r="I142" s="35">
-        <v>1</v>
-      </c>
-      <c r="J142" s="39" t="s">
-        <v>502</v>
-      </c>
-      <c r="K142" s="39"/>
-      <c r="L142" s="39"/>
-      <c r="M142" s="39"/>
-      <c r="N142" s="39"/>
-      <c r="O142" s="1"/>
-      <c r="P142" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="Q142" s="34"/>
-    </row>
-    <row r="143" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A143" s="35">
-        <v>86</v>
-      </c>
-      <c r="B143" s="3">
-        <v>85</v>
-      </c>
-      <c r="C143" s="35">
-        <v>131</v>
-      </c>
-      <c r="D143" s="3"/>
-      <c r="E143" s="49" t="s">
-        <v>504</v>
-      </c>
-      <c r="F143" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="G143" s="35">
-        <v>206</v>
-      </c>
-      <c r="H143" s="35">
-        <v>2</v>
-      </c>
-      <c r="I143" s="35">
-        <v>1</v>
-      </c>
-      <c r="J143" s="39" t="s">
-        <v>505</v>
-      </c>
-      <c r="K143" s="39" t="s">
-        <v>506</v>
-      </c>
-      <c r="L143" s="39"/>
-      <c r="M143" s="39"/>
-      <c r="N143" s="39"/>
-      <c r="O143" s="1"/>
-      <c r="P143" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q143" s="34"/>
-    </row>
-    <row r="144" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A144" s="35"/>
-      <c r="B144" s="3"/>
-      <c r="C144" s="35">
-        <v>132</v>
-      </c>
-      <c r="D144" s="3"/>
-      <c r="E144" s="49" t="s">
-        <v>504</v>
-      </c>
-      <c r="F144" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="G144" s="35"/>
-      <c r="H144" s="35"/>
-      <c r="I144" s="35">
-        <v>2</v>
-      </c>
-      <c r="J144" s="39"/>
-      <c r="K144" s="39"/>
-      <c r="L144" s="39"/>
-      <c r="M144" s="39"/>
-      <c r="N144" s="39"/>
-      <c r="O144" s="1"/>
-      <c r="P144" s="1" t="s">
-        <v>507</v>
+      <c r="I144" s="27">
+        <v>1</v>
+      </c>
+      <c r="J144" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="K144" s="31" t="s">
+        <v>518</v>
+      </c>
+      <c r="L144" s="31"/>
+      <c r="M144" s="31"/>
+      <c r="N144" s="31"/>
+      <c r="O144" s="2"/>
+      <c r="P144" s="2" t="s">
+        <v>519</v>
       </c>
       <c r="Q144" s="34"/>
     </row>
     <row r="145" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A145" s="35">
-        <v>87</v>
-      </c>
-      <c r="B145" s="3">
-        <v>86</v>
-      </c>
-      <c r="C145" s="35">
-        <v>133</v>
-      </c>
-      <c r="D145" s="3"/>
-      <c r="E145" s="49" t="s">
-        <v>508</v>
-      </c>
-      <c r="F145" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="G145" s="35">
-        <v>206</v>
-      </c>
-      <c r="H145" s="35">
-        <v>2</v>
-      </c>
-      <c r="I145" s="35">
-        <v>1</v>
-      </c>
-      <c r="J145" s="39" t="s">
-        <v>509</v>
-      </c>
-      <c r="K145" s="39" t="s">
-        <v>510</v>
-      </c>
-      <c r="L145" s="39"/>
-      <c r="M145" s="39"/>
-      <c r="N145" s="39"/>
-      <c r="O145" s="1"/>
-      <c r="P145" s="1" t="s">
-        <v>511</v>
+      <c r="A145" s="27"/>
+      <c r="B145" s="21"/>
+      <c r="C145" s="27">
+        <v>159</v>
+      </c>
+      <c r="D145" s="21"/>
+      <c r="E145" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="F145" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="G145" s="27">
+        <v>95</v>
+      </c>
+      <c r="H145" s="27"/>
+      <c r="I145" s="27">
+        <v>3</v>
+      </c>
+      <c r="J145" s="31"/>
+      <c r="K145" s="31"/>
+      <c r="L145" s="31"/>
+      <c r="M145" s="31"/>
+      <c r="N145" s="31"/>
+      <c r="O145" s="2"/>
+      <c r="P145" s="2" t="s">
+        <v>519</v>
       </c>
       <c r="Q145" s="34"/>
     </row>
     <row r="146" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A146" s="35">
-        <v>88</v>
-      </c>
-      <c r="B146" s="3">
-        <v>87</v>
-      </c>
-      <c r="C146" s="35">
-        <v>134</v>
-      </c>
-      <c r="D146" s="3"/>
-      <c r="E146" s="49" t="s">
-        <v>512</v>
-      </c>
-      <c r="F146" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="G146" s="35">
-        <v>206</v>
-      </c>
-      <c r="H146" s="35">
-        <v>2</v>
-      </c>
-      <c r="I146" s="35">
-        <v>1</v>
-      </c>
-      <c r="J146" s="39" t="s">
-        <v>513</v>
-      </c>
-      <c r="K146" s="39" t="s">
-        <v>514</v>
-      </c>
-      <c r="L146" s="39"/>
-      <c r="M146" s="39"/>
-      <c r="N146" s="39"/>
-      <c r="O146" s="1"/>
-      <c r="P146" s="1" t="s">
-        <v>515</v>
+      <c r="A146" s="27">
+        <v>96</v>
+      </c>
+      <c r="B146" s="21">
+        <v>95</v>
+      </c>
+      <c r="C146" s="27">
+        <v>143</v>
+      </c>
+      <c r="D146" s="21"/>
+      <c r="E146" s="80" t="s">
+        <v>629</v>
+      </c>
+      <c r="F146" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="G146" s="27">
+        <v>93</v>
+      </c>
+      <c r="H146" s="27">
+        <v>1</v>
+      </c>
+      <c r="I146" s="27">
+        <v>1</v>
+      </c>
+      <c r="J146" s="31" t="s">
+        <v>520</v>
+      </c>
+      <c r="K146" s="31" t="s">
+        <v>521</v>
+      </c>
+      <c r="L146" s="31"/>
+      <c r="M146" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="N146" s="31"/>
+      <c r="O146" s="2"/>
+      <c r="P146" s="2" t="s">
+        <v>523</v>
       </c>
       <c r="Q146" s="34"/>
     </row>
     <row r="147" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A147" s="35">
-        <v>89</v>
-      </c>
-      <c r="B147" s="3">
-        <v>88</v>
-      </c>
-      <c r="C147" s="35">
-        <v>135</v>
-      </c>
-      <c r="D147" s="3"/>
-      <c r="E147" s="49" t="s">
-        <v>516</v>
-      </c>
-      <c r="F147" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="G147" s="35">
-        <v>206</v>
-      </c>
-      <c r="H147" s="35">
-        <v>2</v>
-      </c>
-      <c r="I147" s="35">
-        <v>1</v>
-      </c>
-      <c r="J147" s="39" t="s">
-        <v>517</v>
-      </c>
-      <c r="K147" s="39" t="s">
-        <v>518</v>
-      </c>
-      <c r="L147" s="39"/>
-      <c r="M147" s="39"/>
-      <c r="N147" s="39"/>
-      <c r="O147" s="1"/>
-      <c r="P147" s="1" t="s">
-        <v>519</v>
+      <c r="A147" s="27">
+        <v>97</v>
+      </c>
+      <c r="B147" s="21">
+        <v>96</v>
+      </c>
+      <c r="C147" s="27">
+        <v>144</v>
+      </c>
+      <c r="D147" s="21"/>
+      <c r="E147" s="80" t="s">
+        <v>630</v>
+      </c>
+      <c r="F147" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="G147" s="27">
+        <v>93</v>
+      </c>
+      <c r="H147" s="27">
+        <v>3</v>
+      </c>
+      <c r="I147" s="27">
+        <v>1</v>
+      </c>
+      <c r="J147" s="31" t="s">
+        <v>524</v>
+      </c>
+      <c r="K147" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="L147" s="31"/>
+      <c r="M147" s="31" t="s">
+        <v>526</v>
+      </c>
+      <c r="N147" s="31"/>
+      <c r="O147" s="2"/>
+      <c r="P147" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="Q147" s="34"/>
     </row>
     <row r="148" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A148" s="35">
-        <v>90</v>
-      </c>
-      <c r="B148" s="3">
-        <v>89</v>
-      </c>
-      <c r="C148" s="35">
-        <v>136</v>
-      </c>
-      <c r="D148" s="3"/>
-      <c r="E148" s="49" t="s">
-        <v>520</v>
-      </c>
-      <c r="F148" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="G148" s="35">
-        <v>206</v>
-      </c>
-      <c r="H148" s="35">
-        <v>2</v>
-      </c>
-      <c r="I148" s="35">
-        <v>1</v>
-      </c>
-      <c r="J148" s="39" t="s">
-        <v>521</v>
-      </c>
-      <c r="K148" s="39" t="s">
-        <v>522</v>
-      </c>
-      <c r="L148" s="39"/>
-      <c r="M148" s="39"/>
-      <c r="N148" s="39"/>
-      <c r="O148" s="1"/>
-      <c r="P148" s="1" t="s">
-        <v>523</v>
+      <c r="A148" s="27"/>
+      <c r="B148" s="21"/>
+      <c r="C148" s="27">
+        <v>162</v>
+      </c>
+      <c r="D148" s="21"/>
+      <c r="E148" s="80" t="s">
+        <v>630</v>
+      </c>
+      <c r="F148" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="G148" s="27">
+        <v>97</v>
+      </c>
+      <c r="H148" s="27"/>
+      <c r="I148" s="27">
+        <v>3</v>
+      </c>
+      <c r="J148" s="31"/>
+      <c r="K148" s="31"/>
+      <c r="L148" s="31"/>
+      <c r="M148" s="31"/>
+      <c r="N148" s="31"/>
+      <c r="O148" s="2"/>
+      <c r="P148" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="Q148" s="34"/>
     </row>
     <row r="149" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="35">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="B149" s="3">
-        <v>90</v>
-      </c>
-      <c r="C149" s="35">
-        <v>137</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C149" s="3"/>
       <c r="D149" s="3"/>
-      <c r="E149" s="49" t="s">
-        <v>524</v>
-      </c>
-      <c r="F149" s="52" t="s">
-        <v>525</v>
+      <c r="E149" s="3"/>
+      <c r="F149" s="49" t="s">
+        <v>528</v>
       </c>
       <c r="G149" s="35">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="H149" s="35">
         <v>2</v>
       </c>
-      <c r="I149" s="35">
-        <v>1</v>
-      </c>
-      <c r="J149" s="39" t="s">
-        <v>526</v>
-      </c>
-      <c r="K149" s="39" t="s">
-        <v>527</v>
-      </c>
+      <c r="I149" s="35"/>
+      <c r="J149" s="39"/>
+      <c r="K149" s="39"/>
       <c r="L149" s="39"/>
       <c r="M149" s="39"/>
       <c r="N149" s="39"/>
       <c r="O149" s="1"/>
       <c r="P149" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Q149" s="34"/>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="35">
-        <v>92</v>
-      </c>
-      <c r="B150" s="3">
-        <v>91</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B150" s="3"/>
       <c r="C150" s="35">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="49" t="s">
-        <v>529</v>
-      </c>
-      <c r="F150" s="50" t="s">
-        <v>170</v>
+        <v>530</v>
+      </c>
+      <c r="F150" s="49" t="s">
+        <v>528</v>
       </c>
       <c r="G150" s="35">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H150" s="35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I150" s="35">
         <v>1</v>
       </c>
       <c r="J150" s="39" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K150" s="39" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L150" s="39"/>
       <c r="M150" s="39"/>
       <c r="N150" s="39"/>
       <c r="O150" s="1"/>
       <c r="P150" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q150" s="41"/>
-    </row>
-    <row r="151" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A151" s="27">
-        <v>93</v>
-      </c>
-      <c r="B151" s="21">
-        <v>72.206000000000003</v>
-      </c>
-      <c r="C151" s="27">
-        <v>139</v>
-      </c>
-      <c r="D151" s="21"/>
-      <c r="E151" s="21"/>
-      <c r="F151" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="G151" s="27">
-        <v>43</v>
-      </c>
-      <c r="H151" s="27">
+        <v>529</v>
+      </c>
+      <c r="Q150" s="34"/>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A151" s="35">
+        <v>99</v>
+      </c>
+      <c r="B151" s="3">
+        <v>98</v>
+      </c>
+      <c r="C151" s="35">
+        <v>146</v>
+      </c>
+      <c r="D151" s="3"/>
+      <c r="E151" s="49" t="s">
+        <v>533</v>
+      </c>
+      <c r="F151" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="G151" s="35">
+        <v>207</v>
+      </c>
+      <c r="H151" s="35">
         <v>2</v>
       </c>
-      <c r="I151" s="27">
-        <v>1</v>
-      </c>
-      <c r="J151" s="31"/>
-      <c r="K151" s="31"/>
-      <c r="L151" s="31"/>
-      <c r="M151" s="31"/>
-      <c r="N151" s="31"/>
-      <c r="O151" s="2"/>
-      <c r="P151" s="2" t="s">
+      <c r="I151" s="35">
+        <v>1</v>
+      </c>
+      <c r="J151" s="39" t="s">
+        <v>534</v>
+      </c>
+      <c r="K151" s="39" t="s">
+        <v>535</v>
+      </c>
+      <c r="L151" s="39"/>
+      <c r="M151" s="39"/>
+      <c r="N151" s="39"/>
+      <c r="O151" s="1"/>
+      <c r="P151" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A152" s="35"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="35">
+        <v>147</v>
+      </c>
+      <c r="D152" s="3"/>
+      <c r="E152" s="49" t="s">
         <v>533</v>
       </c>
-      <c r="Q151" s="34"/>
-    </row>
-    <row r="152" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A152" s="27"/>
-      <c r="B152" s="21"/>
-      <c r="C152" s="27">
-        <v>140</v>
-      </c>
-      <c r="D152" s="21"/>
-      <c r="E152" s="21"/>
-      <c r="F152" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="G152" s="27"/>
-      <c r="H152" s="27"/>
-      <c r="I152" s="27">
+      <c r="F152" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="G152" s="35"/>
+      <c r="H152" s="35"/>
+      <c r="I152" s="35">
         <v>2</v>
       </c>
-      <c r="J152" s="31"/>
-      <c r="K152" s="31"/>
-      <c r="L152" s="31"/>
-      <c r="M152" s="31"/>
-      <c r="N152" s="31"/>
-      <c r="O152" s="2"/>
-      <c r="P152" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="Q152" s="34"/>
+      <c r="J152" s="39"/>
+      <c r="K152" s="39"/>
+      <c r="L152" s="39"/>
+      <c r="M152" s="39"/>
+      <c r="N152" s="39"/>
+      <c r="O152" s="1"/>
+      <c r="P152" s="1" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="153" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="27">
-        <v>94</v>
-      </c>
-      <c r="B153" s="21"/>
-      <c r="C153" s="27">
-        <v>141</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B153" s="21">
+        <v>72.102999999999994</v>
+      </c>
+      <c r="C153" s="27"/>
       <c r="D153" s="21"/>
-      <c r="E153" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="F153" s="29" t="s">
-        <v>172</v>
+      <c r="E153" s="21"/>
+      <c r="F153" s="21" t="s">
+        <v>177</v>
       </c>
       <c r="G153" s="27">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="H153" s="27">
         <v>2</v>
       </c>
-      <c r="I153" s="27">
-        <v>1</v>
-      </c>
-      <c r="J153" s="31" t="s">
-        <v>535</v>
-      </c>
-      <c r="K153" s="31" t="s">
-        <v>536</v>
-      </c>
+      <c r="I153" s="27"/>
+      <c r="J153" s="31"/>
+      <c r="K153" s="31"/>
       <c r="L153" s="31"/>
       <c r="M153" s="31"/>
       <c r="N153" s="31"/>
@@ -11902,26 +12051,24 @@
     </row>
     <row r="154" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="27">
-        <v>95</v>
-      </c>
-      <c r="B154" s="21">
-        <v>94</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B154" s="21"/>
       <c r="C154" s="27">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D154" s="21"/>
       <c r="E154" s="21" t="s">
         <v>538</v>
       </c>
       <c r="F154" s="29" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G154" s="27">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H154" s="27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I154" s="27">
         <v>1</v>
@@ -11945,221 +12092,246 @@
       <c r="A155" s="27"/>
       <c r="B155" s="21"/>
       <c r="C155" s="27">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D155" s="21"/>
       <c r="E155" s="21" t="s">
         <v>538</v>
       </c>
       <c r="F155" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="G155" s="27">
-        <v>95</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="G155" s="27"/>
       <c r="H155" s="27"/>
       <c r="I155" s="27">
         <v>2</v>
       </c>
+      <c r="J155" s="31"/>
+      <c r="K155" s="31"/>
       <c r="L155" s="31"/>
       <c r="M155" s="31"/>
       <c r="N155" s="31"/>
       <c r="O155" s="2"/>
-      <c r="P155" s="2"/>
+      <c r="P155" s="2" t="s">
+        <v>541</v>
+      </c>
       <c r="Q155" s="34"/>
     </row>
     <row r="156" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A156" s="27"/>
-      <c r="B156" s="21"/>
+      <c r="A156" s="27">
+        <v>102</v>
+      </c>
+      <c r="B156" s="21">
+        <v>101</v>
+      </c>
       <c r="C156" s="27">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D156" s="21"/>
-      <c r="E156" s="21" t="s">
-        <v>538</v>
+      <c r="E156" s="43" t="s">
+        <v>542</v>
       </c>
       <c r="F156" s="29" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G156" s="27">
-        <v>95</v>
-      </c>
-      <c r="H156" s="27"/>
+        <v>100</v>
+      </c>
+      <c r="H156" s="27">
+        <v>1</v>
+      </c>
       <c r="I156" s="27">
-        <v>3</v>
-      </c>
-      <c r="J156" s="31"/>
-      <c r="K156" s="31"/>
-      <c r="L156" s="31"/>
+        <v>1</v>
+      </c>
+      <c r="J156" s="31" t="s">
+        <v>543</v>
+      </c>
+      <c r="K156" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="L156" s="31" t="s">
+        <v>546</v>
+      </c>
       <c r="M156" s="31"/>
       <c r="N156" s="31"/>
       <c r="O156" s="2"/>
-      <c r="P156" s="2"/>
+      <c r="P156" s="2" t="s">
+        <v>545</v>
+      </c>
       <c r="Q156" s="34"/>
     </row>
     <row r="157" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A157" s="27">
-        <v>96</v>
-      </c>
-      <c r="B157" s="21">
-        <v>95</v>
-      </c>
-      <c r="C157" s="27">
-        <v>143</v>
-      </c>
-      <c r="D157" s="21"/>
-      <c r="E157" s="21" t="s">
-        <v>542</v>
-      </c>
-      <c r="F157" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="G157" s="27">
-        <v>93</v>
-      </c>
-      <c r="H157" s="27">
-        <v>2</v>
-      </c>
-      <c r="I157" s="27">
-        <v>1</v>
-      </c>
-      <c r="J157" s="31" t="s">
-        <v>543</v>
-      </c>
-      <c r="K157" s="31" t="s">
-        <v>544</v>
-      </c>
-      <c r="L157" s="31"/>
-      <c r="M157" s="31" t="s">
-        <v>545</v>
-      </c>
-      <c r="N157" s="31"/>
-      <c r="O157" s="2"/>
-      <c r="P157" s="2" t="s">
-        <v>546</v>
+      <c r="A157" s="35">
+        <v>103</v>
+      </c>
+      <c r="B157" s="3">
+        <v>68.72</v>
+      </c>
+      <c r="C157" s="35"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="G157" s="35">
+        <v>43</v>
+      </c>
+      <c r="H157" s="35">
+        <v>1</v>
+      </c>
+      <c r="I157" s="35"/>
+      <c r="J157" s="39"/>
+      <c r="K157" s="39"/>
+      <c r="L157" s="39"/>
+      <c r="M157" s="39"/>
+      <c r="N157" s="39"/>
+      <c r="O157" s="1"/>
+      <c r="P157" s="1" t="s">
+        <v>548</v>
       </c>
       <c r="Q157" s="34"/>
     </row>
-    <row r="158" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A158" s="27">
-        <v>97</v>
-      </c>
-      <c r="B158" s="21">
-        <v>96</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B158" s="21"/>
       <c r="C158" s="27">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="D158" s="21"/>
-      <c r="E158" s="21" t="s">
-        <v>547</v>
+      <c r="E158" s="80" t="s">
+        <v>619</v>
       </c>
       <c r="F158" s="29" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="G158" s="27">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H158" s="27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I158" s="27">
         <v>1</v>
       </c>
       <c r="J158" s="31" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K158" s="31" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L158" s="31"/>
-      <c r="M158" s="31" t="s">
-        <v>550</v>
-      </c>
+      <c r="M158" s="31"/>
       <c r="N158" s="31"/>
       <c r="O158" s="2"/>
       <c r="P158" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="Q158" s="34"/>
     </row>
     <row r="159" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A159" s="27"/>
-      <c r="B159" s="21"/>
-      <c r="C159" s="27">
-        <v>162</v>
-      </c>
-      <c r="D159" s="21"/>
-      <c r="E159" s="21" t="s">
-        <v>547</v>
-      </c>
-      <c r="F159" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="G159" s="27">
-        <v>97</v>
-      </c>
-      <c r="H159" s="27"/>
-      <c r="I159" s="27">
-        <v>3</v>
-      </c>
-      <c r="J159" s="31"/>
-      <c r="K159" s="31"/>
-      <c r="L159" s="31"/>
-      <c r="M159" s="31"/>
-      <c r="N159" s="31"/>
-      <c r="O159" s="2"/>
-      <c r="P159" s="2"/>
+      <c r="A159" s="35">
+        <v>104</v>
+      </c>
+      <c r="B159" s="3">
+        <v>71</v>
+      </c>
+      <c r="C159" s="35">
+        <v>152</v>
+      </c>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="F159" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="G159" s="35">
+        <v>103</v>
+      </c>
+      <c r="H159" s="35">
+        <v>1</v>
+      </c>
+      <c r="I159" s="35">
+        <v>1</v>
+      </c>
+      <c r="J159" s="39" t="s">
+        <v>553</v>
+      </c>
+      <c r="K159" s="39" t="s">
+        <v>554</v>
+      </c>
+      <c r="L159" s="39"/>
+      <c r="M159" s="39"/>
+      <c r="N159" s="39"/>
+      <c r="O159" s="1"/>
+      <c r="P159" s="1" t="s">
+        <v>555</v>
+      </c>
       <c r="Q159" s="34"/>
     </row>
     <row r="160" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="35">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="B160" s="3">
-        <v>93</v>
-      </c>
-      <c r="C160" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="C160" s="35">
+        <v>153</v>
+      </c>
       <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-      <c r="F160" s="49" t="s">
-        <v>552</v>
+      <c r="E160" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F160" s="50" t="s">
+        <v>182</v>
       </c>
       <c r="G160" s="35">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="H160" s="35">
-        <v>2</v>
-      </c>
-      <c r="I160" s="35"/>
-      <c r="J160" s="39"/>
-      <c r="K160" s="39"/>
+        <v>1</v>
+      </c>
+      <c r="I160" s="35">
+        <v>1</v>
+      </c>
+      <c r="J160" s="39" t="s">
+        <v>557</v>
+      </c>
+      <c r="K160" s="39" t="s">
+        <v>558</v>
+      </c>
       <c r="L160" s="39"/>
-      <c r="M160" s="39"/>
+      <c r="M160" s="39" t="s">
+        <v>559</v>
+      </c>
       <c r="N160" s="39"/>
       <c r="O160" s="1"/>
       <c r="P160" s="1" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="Q160" s="34"/>
     </row>
-    <row r="161" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A161" s="35">
-        <v>98</v>
-      </c>
-      <c r="B161" s="3"/>
+        <v>106</v>
+      </c>
+      <c r="B161" s="3">
+        <v>104</v>
+      </c>
       <c r="C161" s="35">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D161" s="3"/>
-      <c r="E161" s="49" t="s">
-        <v>554</v>
-      </c>
-      <c r="F161" s="49" t="s">
-        <v>552</v>
+      <c r="E161" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="F161" s="50" t="s">
+        <v>183</v>
       </c>
       <c r="G161" s="35">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="H161" s="35">
         <v>1</v>
@@ -12168,704 +12340,264 @@
         <v>1</v>
       </c>
       <c r="J161" s="39" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="K161" s="39" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="L161" s="39"/>
-      <c r="M161" s="39"/>
+      <c r="M161" s="39" t="s">
+        <v>564</v>
+      </c>
       <c r="N161" s="39"/>
       <c r="O161" s="1"/>
-      <c r="P161" s="1"/>
-      <c r="Q161" s="34"/>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A162" s="35">
-        <v>99</v>
-      </c>
-      <c r="B162" s="3">
-        <v>98</v>
-      </c>
-      <c r="C162" s="35">
-        <v>146</v>
-      </c>
-      <c r="D162" s="3"/>
-      <c r="E162" s="49" t="s">
-        <v>557</v>
-      </c>
-      <c r="F162" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G162" s="35">
-        <v>207</v>
-      </c>
-      <c r="H162" s="35">
-        <v>2</v>
-      </c>
-      <c r="I162" s="35">
-        <v>1</v>
-      </c>
-      <c r="J162" s="39" t="s">
-        <v>558</v>
-      </c>
-      <c r="K162" s="39" t="s">
-        <v>559</v>
-      </c>
-      <c r="L162" s="39"/>
-      <c r="M162" s="39"/>
-      <c r="N162" s="39"/>
-      <c r="O162" s="1"/>
-      <c r="P162" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A163" s="35"/>
-      <c r="B163" s="3"/>
-      <c r="C163" s="35">
-        <v>147</v>
-      </c>
-      <c r="D163" s="3"/>
-      <c r="E163" s="49" t="s">
-        <v>557</v>
-      </c>
-      <c r="F163" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G163" s="35"/>
-      <c r="H163" s="35"/>
-      <c r="I163" s="35">
-        <v>2</v>
-      </c>
-      <c r="J163" s="39"/>
-      <c r="K163" s="39"/>
-      <c r="L163" s="39"/>
-      <c r="M163" s="39"/>
-      <c r="N163" s="39"/>
-      <c r="O163" s="1"/>
-      <c r="P163" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A164" s="27">
-        <v>100</v>
-      </c>
-      <c r="B164" s="21">
-        <v>72.102999999999994</v>
-      </c>
-      <c r="C164" s="27"/>
-      <c r="D164" s="21"/>
-      <c r="E164" s="21"/>
-      <c r="F164" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="G164" s="27">
+      <c r="P161" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A162" s="27">
+        <v>107</v>
+      </c>
+      <c r="B162" s="21">
+        <v>103</v>
+      </c>
+      <c r="C162" s="27">
+        <v>155</v>
+      </c>
+      <c r="D162" s="21"/>
+      <c r="E162" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="F162" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G162" s="27">
         <v>43</v>
       </c>
-      <c r="H164" s="27">
-        <v>2</v>
-      </c>
-      <c r="I164" s="27"/>
-      <c r="J164" s="31"/>
-      <c r="K164" s="31"/>
-      <c r="L164" s="31"/>
-      <c r="M164" s="31"/>
-      <c r="N164" s="31"/>
-      <c r="O164" s="2"/>
-      <c r="P164" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="Q164" s="34"/>
-    </row>
-    <row r="165" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A165" s="27">
-        <v>101</v>
-      </c>
-      <c r="B165" s="21"/>
-      <c r="C165" s="27">
-        <v>148</v>
-      </c>
-      <c r="D165" s="21"/>
-      <c r="E165" s="21" t="s">
-        <v>562</v>
-      </c>
-      <c r="F165" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="G165" s="27">
-        <v>100</v>
-      </c>
-      <c r="H165" s="27">
-        <v>2</v>
-      </c>
-      <c r="I165" s="27">
-        <v>1</v>
-      </c>
-      <c r="J165" s="31" t="s">
-        <v>563</v>
-      </c>
-      <c r="K165" s="31" t="s">
-        <v>564</v>
-      </c>
-      <c r="L165" s="31"/>
-      <c r="M165" s="31"/>
-      <c r="N165" s="31"/>
-      <c r="O165" s="2"/>
-      <c r="P165" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="Q165" s="34"/>
-    </row>
-    <row r="166" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A166" s="27"/>
-      <c r="B166" s="21"/>
-      <c r="C166" s="27">
-        <v>149</v>
-      </c>
-      <c r="D166" s="21"/>
-      <c r="E166" s="21" t="s">
-        <v>562</v>
-      </c>
-      <c r="F166" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="G166" s="27"/>
-      <c r="H166" s="27"/>
-      <c r="I166" s="27">
-        <v>2</v>
-      </c>
-      <c r="J166" s="31"/>
-      <c r="K166" s="31"/>
-      <c r="L166" s="31"/>
-      <c r="M166" s="31"/>
-      <c r="N166" s="31"/>
-      <c r="O166" s="2"/>
-      <c r="P166" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="Q166" s="34"/>
-    </row>
-    <row r="167" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A167" s="27">
-        <v>102</v>
-      </c>
-      <c r="B167" s="21">
-        <v>101</v>
-      </c>
-      <c r="C167" s="27">
-        <v>150</v>
-      </c>
-      <c r="D167" s="21"/>
-      <c r="E167" s="43" t="s">
+      <c r="H162" s="27">
+        <v>3</v>
+      </c>
+      <c r="I162" s="27">
+        <v>1</v>
+      </c>
+      <c r="J162" s="31" t="s">
+        <v>567</v>
+      </c>
+      <c r="K162" s="31"/>
+      <c r="L162" s="31"/>
+      <c r="M162" s="31"/>
+      <c r="N162" s="31"/>
+      <c r="O162" s="2"/>
+      <c r="P162" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A163" s="27"/>
+      <c r="B163" s="21"/>
+      <c r="C163" s="27">
+        <v>161</v>
+      </c>
+      <c r="D163" s="21"/>
+      <c r="E163" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="F167" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="G167" s="27">
-        <v>100</v>
-      </c>
-      <c r="H167" s="27">
-        <v>2</v>
-      </c>
-      <c r="I167" s="27">
-        <v>1</v>
-      </c>
-      <c r="J167" s="31" t="s">
-        <v>567</v>
-      </c>
-      <c r="K167" s="31" t="s">
+      <c r="F163" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G163" s="27">
+        <v>107</v>
+      </c>
+      <c r="H163" s="27"/>
+      <c r="I163" s="27">
+        <v>3</v>
+      </c>
+      <c r="J163" s="31"/>
+      <c r="K163" s="31"/>
+      <c r="L163" s="31"/>
+      <c r="M163" s="31"/>
+      <c r="N163" s="31"/>
+      <c r="O163" s="2"/>
+      <c r="P163" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="L167" s="31"/>
-      <c r="M167" s="31"/>
-      <c r="N167" s="31"/>
-      <c r="O167" s="2"/>
-      <c r="P167" s="2" t="s">
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A164" s="35">
+        <v>209</v>
+      </c>
+      <c r="B164" s="3">
+        <v>107</v>
+      </c>
+      <c r="C164" s="39"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G164" s="35">
+        <v>43</v>
+      </c>
+      <c r="H164" s="75">
+        <v>1</v>
+      </c>
+      <c r="I164" s="35"/>
+      <c r="J164" s="39"/>
+      <c r="K164" s="39"/>
+      <c r="L164" s="39"/>
+      <c r="M164" s="39"/>
+      <c r="N164" s="39"/>
+      <c r="O164" s="1"/>
+      <c r="P164" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="Q167" s="34"/>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A168" s="27"/>
-      <c r="B168" s="21"/>
-      <c r="C168" s="27">
-        <v>151</v>
-      </c>
-      <c r="D168" s="21"/>
-      <c r="E168" s="43" t="s">
-        <v>566</v>
-      </c>
-      <c r="F168" s="21"/>
-      <c r="G168" s="27"/>
-      <c r="H168" s="27"/>
-      <c r="I168" s="27">
-        <v>1</v>
-      </c>
-      <c r="J168" s="31"/>
-      <c r="K168" s="31" t="s">
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A165" s="35">
+        <v>108</v>
+      </c>
+      <c r="B165" s="3"/>
+      <c r="C165" s="35">
+        <v>156</v>
+      </c>
+      <c r="D165" s="3"/>
+      <c r="E165" s="49" t="s">
         <v>570</v>
       </c>
-      <c r="L168" s="31"/>
-      <c r="M168" s="31" t="s">
+      <c r="F165" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G165" s="35">
+        <v>209</v>
+      </c>
+      <c r="H165" s="35">
+        <v>1</v>
+      </c>
+      <c r="I165" s="35">
+        <v>1</v>
+      </c>
+      <c r="J165" s="39" t="s">
         <v>571</v>
       </c>
-      <c r="N168" s="31"/>
-      <c r="O168" s="2"/>
-      <c r="P168" s="2" t="s">
+      <c r="K165" s="39"/>
+      <c r="L165" s="39"/>
+      <c r="M165" s="39"/>
+      <c r="N165" s="39"/>
+      <c r="O165" s="1"/>
+      <c r="P165" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A166" s="35">
+        <v>109</v>
+      </c>
+      <c r="B166" s="3">
+        <v>108</v>
+      </c>
+      <c r="C166" s="35">
+        <v>157</v>
+      </c>
+      <c r="D166" s="3"/>
+      <c r="E166" s="49" t="s">
+        <v>623</v>
+      </c>
+      <c r="F166" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="G166" s="35">
+        <v>209</v>
+      </c>
+      <c r="H166" s="35">
+        <v>1</v>
+      </c>
+      <c r="I166" s="35">
+        <v>1</v>
+      </c>
+      <c r="J166" s="39" t="s">
         <v>572</v>
       </c>
-      <c r="Q168" s="41"/>
-    </row>
-    <row r="169" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A169" s="35">
-        <v>103</v>
-      </c>
-      <c r="B169" s="3">
-        <v>68.72</v>
-      </c>
-      <c r="C169" s="35"/>
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-      <c r="F169" s="3" t="s">
+      <c r="K166" s="39"/>
+      <c r="L166" s="39"/>
+      <c r="M166" s="39"/>
+      <c r="N166" s="39"/>
+      <c r="O166" s="1"/>
+      <c r="P166" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="G169" s="35">
-        <v>43</v>
-      </c>
-      <c r="H169" s="35">
-        <v>1</v>
-      </c>
-      <c r="I169" s="35"/>
-      <c r="J169" s="39"/>
-      <c r="K169" s="39"/>
-      <c r="L169" s="39"/>
-      <c r="M169" s="39"/>
-      <c r="N169" s="39"/>
-      <c r="O169" s="1"/>
-      <c r="P169" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q169" s="34"/>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A170" s="27">
-        <v>71</v>
-      </c>
-      <c r="B170" s="21"/>
-      <c r="C170" s="27">
-        <v>109</v>
-      </c>
-      <c r="D170" s="21"/>
-      <c r="E170" s="21" t="s">
-        <v>575</v>
-      </c>
-      <c r="F170" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="G170" s="27">
-        <v>103</v>
-      </c>
-      <c r="H170" s="27">
-        <v>1</v>
-      </c>
-      <c r="I170" s="27">
-        <v>1</v>
-      </c>
-      <c r="J170" s="31" t="s">
-        <v>576</v>
-      </c>
-      <c r="K170" s="31" t="s">
-        <v>577</v>
-      </c>
-      <c r="L170" s="31"/>
-      <c r="M170" s="31"/>
-      <c r="N170" s="31"/>
-      <c r="O170" s="2"/>
-      <c r="P170" s="2" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A171" s="35">
-        <v>104</v>
-      </c>
-      <c r="B171" s="3">
-        <v>71</v>
-      </c>
-      <c r="C171" s="35">
-        <v>152</v>
-      </c>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="F171" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="G171" s="35">
-        <v>103</v>
-      </c>
-      <c r="H171" s="35">
-        <v>1</v>
-      </c>
-      <c r="I171" s="35">
-        <v>1</v>
-      </c>
-      <c r="J171" s="39" t="s">
-        <v>580</v>
-      </c>
-      <c r="K171" s="39" t="s">
-        <v>581</v>
-      </c>
-      <c r="L171" s="39"/>
-      <c r="M171" s="39"/>
-      <c r="N171" s="39"/>
-      <c r="O171" s="1"/>
-      <c r="P171" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="Q171" s="34"/>
-    </row>
-    <row r="172" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A172" s="35">
-        <v>105</v>
-      </c>
-      <c r="B172" s="3">
-        <v>104</v>
-      </c>
-      <c r="C172" s="35">
-        <v>153</v>
-      </c>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="F172" s="50" t="s">
-        <v>182</v>
-      </c>
-      <c r="G172" s="35">
-        <v>103</v>
-      </c>
-      <c r="H172" s="35">
-        <v>1</v>
-      </c>
-      <c r="I172" s="35">
-        <v>1</v>
-      </c>
-      <c r="J172" s="39" t="s">
-        <v>584</v>
-      </c>
-      <c r="K172" s="39" t="s">
-        <v>585</v>
-      </c>
-      <c r="L172" s="39"/>
-      <c r="M172" s="39" t="s">
-        <v>586</v>
-      </c>
-      <c r="N172" s="39"/>
-      <c r="O172" s="1"/>
-      <c r="P172" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q172" s="34"/>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A173" s="35">
-        <v>106</v>
-      </c>
-      <c r="B173" s="3">
-        <v>104</v>
-      </c>
-      <c r="C173" s="35">
-        <v>154</v>
-      </c>
-      <c r="D173" s="3"/>
-      <c r="E173" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="F173" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="G173" s="35">
-        <v>103</v>
-      </c>
-      <c r="H173" s="35">
-        <v>1</v>
-      </c>
-      <c r="I173" s="35">
-        <v>1</v>
-      </c>
-      <c r="J173" s="39" t="s">
-        <v>589</v>
-      </c>
-      <c r="K173" s="39" t="s">
-        <v>590</v>
-      </c>
-      <c r="L173" s="39"/>
-      <c r="M173" s="39" t="s">
-        <v>591</v>
-      </c>
-      <c r="N173" s="39"/>
-      <c r="O173" s="1"/>
-      <c r="P173" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A174" s="27">
-        <v>107</v>
-      </c>
-      <c r="B174" s="21">
-        <v>103</v>
-      </c>
-      <c r="C174" s="27">
-        <v>155</v>
-      </c>
-      <c r="D174" s="21"/>
-      <c r="E174" s="21" t="s">
-        <v>593</v>
-      </c>
-      <c r="F174" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G174" s="27">
-        <v>43</v>
-      </c>
-      <c r="H174" s="27">
-        <v>3</v>
-      </c>
-      <c r="I174" s="27">
-        <v>1</v>
-      </c>
-      <c r="J174" s="31" t="s">
-        <v>594</v>
-      </c>
-      <c r="K174" s="31"/>
-      <c r="L174" s="31"/>
-      <c r="M174" s="31"/>
-      <c r="N174" s="31"/>
-      <c r="O174" s="2"/>
-      <c r="P174" s="2" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A175" s="27"/>
-      <c r="B175" s="21"/>
-      <c r="C175" s="27">
-        <v>160</v>
-      </c>
-      <c r="D175" s="21"/>
-      <c r="E175" s="21" t="s">
-        <v>593</v>
-      </c>
-      <c r="F175" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G175" s="27">
-        <v>107</v>
-      </c>
-      <c r="H175" s="27"/>
-      <c r="I175" s="27">
-        <v>2</v>
-      </c>
-      <c r="J175" s="31"/>
-      <c r="K175" s="31"/>
-      <c r="L175" s="31"/>
-      <c r="M175" s="31"/>
-      <c r="N175" s="31"/>
-      <c r="O175" s="2"/>
-      <c r="P175" s="2"/>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A176" s="27"/>
-      <c r="B176" s="21"/>
-      <c r="C176" s="27">
-        <v>161</v>
-      </c>
-      <c r="D176" s="21"/>
-      <c r="E176" s="21" t="s">
-        <v>593</v>
-      </c>
-      <c r="F176" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G176" s="27">
-        <v>107</v>
-      </c>
-      <c r="H176" s="27"/>
-      <c r="I176" s="27">
-        <v>3</v>
-      </c>
-      <c r="J176" s="31"/>
-      <c r="K176" s="31"/>
-      <c r="L176" s="31"/>
-      <c r="M176" s="31"/>
-      <c r="N176" s="31"/>
-      <c r="O176" s="2"/>
-      <c r="P176" s="2"/>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A177" s="35">
-        <v>209</v>
-      </c>
-      <c r="B177" s="3">
-        <v>107</v>
-      </c>
-      <c r="C177" s="39"/>
-      <c r="D177" s="3"/>
-      <c r="E177" s="3"/>
-      <c r="F177" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G177" s="35">
-        <v>43</v>
-      </c>
-      <c r="H177" s="75">
-        <v>1</v>
-      </c>
-      <c r="I177" s="35"/>
-      <c r="J177" s="39"/>
-      <c r="K177" s="39"/>
-      <c r="L177" s="39"/>
-      <c r="M177" s="39"/>
-      <c r="N177" s="39"/>
-      <c r="O177" s="1"/>
-      <c r="P177" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A178" s="35">
-        <v>108</v>
-      </c>
-      <c r="B178" s="3"/>
-      <c r="C178" s="35">
-        <v>156</v>
-      </c>
-      <c r="D178" s="3"/>
-      <c r="E178" s="49" t="s">
-        <v>597</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G178" s="35">
-        <v>209</v>
-      </c>
-      <c r="H178" s="35">
-        <v>1</v>
-      </c>
-      <c r="I178" s="35">
-        <v>1</v>
-      </c>
-      <c r="J178" s="39" t="s">
-        <v>598</v>
-      </c>
-      <c r="K178" s="39"/>
-      <c r="L178" s="39"/>
-      <c r="M178" s="39"/>
-      <c r="N178" s="39"/>
-      <c r="O178" s="1"/>
-      <c r="P178" s="1"/>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A179" s="35">
-        <v>109</v>
-      </c>
-      <c r="B179" s="3">
-        <v>108</v>
-      </c>
-      <c r="C179" s="35">
-        <v>157</v>
-      </c>
-      <c r="D179" s="3"/>
-      <c r="E179" s="49" t="s">
-        <v>599</v>
-      </c>
-      <c r="F179" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="G179" s="35">
-        <v>209</v>
-      </c>
-      <c r="H179" s="35">
-        <v>1</v>
-      </c>
-      <c r="I179" s="35">
-        <v>1</v>
-      </c>
-      <c r="J179" s="39" t="s">
-        <v>600</v>
-      </c>
-      <c r="K179" s="39"/>
-      <c r="L179" s="39"/>
-      <c r="M179" s="39"/>
-      <c r="N179" s="39"/>
-      <c r="O179" s="1"/>
-      <c r="P179" s="1" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A180" s="69"/>
-      <c r="C180" s="69"/>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A181" s="69"/>
-      <c r="C181" s="69"/>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A167" s="69"/>
+      <c r="C167" s="69"/>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A168" s="69"/>
+      <c r="C168" s="69"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J62">
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J156:J1048576 K45 J63:J154 J1:J61">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+  <conditionalFormatting sqref="K45 J1:J61 J63:J1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52">
-    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K156:K1048576 K46:K51 L45 K53:K72 K74:K154 K1:K44">
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
+  <conditionalFormatting sqref="K46:K51 L45 K1:K44 K53:K72 K74:K1048576">
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L46 L48:L1048576 L1:L44">
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  <conditionalFormatting sqref="L157:L1048576 L102:L130 L46 L1:L44 L48:L99 L132:L155">
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M53:M72 M74:M1048576 M1:M51">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+  <conditionalFormatting sqref="M102:M1048576 M1:M51 M53:M72 M74:M99">
+    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="duplicateValues" dxfId="5" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N74:N1048576 N1:N72">
-    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
+  <conditionalFormatting sqref="N1:N72 N74:N1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K73">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M73">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N73">
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L100">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M100">
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L156">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L131">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.70069444444444395" right="0.70069444444444395" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -12917,7 +12649,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>602</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -12927,7 +12659,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -12942,18 +12674,18 @@
       <c r="B6" s="21"/>
       <c r="C6" s="2"/>
       <c r="E6" s="8" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="64" x14ac:dyDescent="0.2">
@@ -12962,10 +12694,10 @@
       <c r="C7" s="2"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>607</v>
+        <v>579</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
@@ -12979,10 +12711,10 @@
       <c r="C8" s="2"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
@@ -12995,7 +12727,7 @@
       <c r="B9" s="21"/>
       <c r="C9" s="2"/>
       <c r="E9" s="7" t="s">
-        <v>611</v>
+        <v>583</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="1"/>
@@ -13004,7 +12736,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -13013,7 +12745,7 @@
       <c r="C10" s="2"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
@@ -13023,7 +12755,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -13032,17 +12764,17 @@
       <c r="C11" s="2"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>615</v>
+        <v>587</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -13050,11 +12782,11 @@
       <c r="B12" s="21"/>
       <c r="C12" s="2"/>
       <c r="E12" s="8" t="s">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="2" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
@@ -13068,10 +12800,10 @@
       <c r="C13" s="2"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
@@ -13085,10 +12817,10 @@
       <c r="C14" s="2"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>620</v>
+        <v>592</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
@@ -13102,14 +12834,14 @@
       <c r="C15" s="2"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8" t="s">
-        <v>621</v>
+        <v>593</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="J15" s="2"/>
     </row>
@@ -13118,7 +12850,7 @@
       <c r="B16" s="21"/>
       <c r="C16" s="2"/>
       <c r="E16" s="7" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="1"/>
@@ -13131,7 +12863,7 @@
       <c r="B17" s="21"/>
       <c r="C17" s="2"/>
       <c r="E17" s="8" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="2"/>
@@ -13154,13 +12886,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>83</v>
